--- a/Hoàng/SALE/BÁO GIÁ KSK 2025 - THAM KHẢO.xlsx
+++ b/Hoàng/SALE/BÁO GIÁ KSK 2025 - THAM KHẢO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\SALE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA85B94-E323-4654-A8D4-1B875E793AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA3AA22E-0CAD-442C-BFE7-9BBEFC4123A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2214,197 +2214,197 @@
     <xf numFmtId="3" fontId="11" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="21" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2788,43 +2788,43 @@
       <c r="A1" s="22"/>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
-      <c r="D1" s="164" t="s">
+      <c r="D1" s="125" t="s">
         <v>312</v>
       </c>
-      <c r="E1" s="164"/>
-      <c r="F1" s="164"/>
+      <c r="E1" s="125"/>
+      <c r="F1" s="125"/>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="24"/>
       <c r="B2" s="24"/>
       <c r="C2" s="24"/>
-      <c r="D2" s="165"/>
-      <c r="E2" s="165"/>
-      <c r="F2" s="165"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="126"/>
+      <c r="F2" s="126"/>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A3" s="24"/>
       <c r="B3" s="24"/>
       <c r="C3" s="24"/>
-      <c r="D3" s="165"/>
-      <c r="E3" s="165"/>
-      <c r="F3" s="165"/>
+      <c r="D3" s="126"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="126"/>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="24"/>
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
-      <c r="D4" s="165"/>
-      <c r="E4" s="165"/>
-      <c r="F4" s="165"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="126"/>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5" s="24"/>
       <c r="B5" s="24"/>
       <c r="C5" s="24"/>
-      <c r="D5" s="165"/>
-      <c r="E5" s="165"/>
-      <c r="F5" s="165"/>
+      <c r="D5" s="126"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="23"/>
@@ -2835,14 +2835,14 @@
       <c r="F6" s="23"/>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="166" t="s">
+      <c r="A7" s="127" t="s">
         <v>418</v>
       </c>
-      <c r="B7" s="166"/>
-      <c r="C7" s="166"/>
-      <c r="D7" s="166"/>
-      <c r="E7" s="166"/>
-      <c r="F7" s="166"/>
+      <c r="B7" s="127"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="127"/>
+      <c r="F7" s="127"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
@@ -2864,27 +2864,27 @@
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="28"/>
-      <c r="B9" s="167" t="s">
+      <c r="B9" s="128" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="167"/>
-      <c r="D9" s="167"/>
-      <c r="E9" s="167"/>
-      <c r="F9" s="167"/>
+      <c r="C9" s="128"/>
+      <c r="D9" s="128"/>
+      <c r="E9" s="128"/>
+      <c r="F9" s="128"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="168" t="s">
+      <c r="A10" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="169"/>
-      <c r="C10" s="169"/>
-      <c r="D10" s="169"/>
-      <c r="E10" s="169"/>
-      <c r="F10" s="170"/>
+      <c r="B10" s="130"/>
+      <c r="C10" s="130"/>
+      <c r="D10" s="130"/>
+      <c r="E10" s="130"/>
+      <c r="F10" s="131"/>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
@@ -2892,12 +2892,12 @@
       <c r="K10" s="8"/>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="171"/>
-      <c r="B11" s="172"/>
-      <c r="C11" s="172"/>
-      <c r="D11" s="172"/>
-      <c r="E11" s="172"/>
-      <c r="F11" s="173"/>
+      <c r="A11" s="132"/>
+      <c r="B11" s="133"/>
+      <c r="C11" s="133"/>
+      <c r="D11" s="133"/>
+      <c r="E11" s="133"/>
+      <c r="F11" s="134"/>
       <c r="G11" s="21"/>
       <c r="H11" s="21"/>
       <c r="I11" s="21"/>
@@ -2916,10 +2916,10 @@
       <c r="A13" s="33" t="s">
         <v>259</v>
       </c>
-      <c r="B13" s="174" t="s">
+      <c r="B13" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="174"/>
+      <c r="C13" s="135"/>
       <c r="D13" s="33" t="s">
         <v>3</v>
       </c>
@@ -2932,78 +2932,78 @@
       <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="175">
+      <c r="A14" s="136">
         <f>IF(LEN(C14)=0,"",COUNTA($C$14:C14))</f>
         <v>1</v>
       </c>
-      <c r="B14" s="143" t="s">
+      <c r="B14" s="139" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="178" t="s">
+      <c r="C14" s="142" t="s">
         <v>326</v>
       </c>
       <c r="D14" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="134">
+      <c r="E14" s="145">
         <v>200000</v>
       </c>
-      <c r="F14" s="181"/>
+      <c r="F14" s="148"/>
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="176"/>
-      <c r="B15" s="144"/>
-      <c r="C15" s="179"/>
+      <c r="A15" s="137"/>
+      <c r="B15" s="140"/>
+      <c r="C15" s="143"/>
       <c r="D15" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="E15" s="135"/>
-      <c r="F15" s="182"/>
+      <c r="E15" s="146"/>
+      <c r="F15" s="149"/>
       <c r="G15" s="11"/>
     </row>
     <row r="16" spans="1:11" ht="33" x14ac:dyDescent="0.25">
-      <c r="A16" s="176"/>
-      <c r="B16" s="144"/>
-      <c r="C16" s="179"/>
+      <c r="A16" s="137"/>
+      <c r="B16" s="140"/>
+      <c r="C16" s="143"/>
       <c r="D16" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="135"/>
-      <c r="F16" s="182"/>
+      <c r="E16" s="146"/>
+      <c r="F16" s="149"/>
       <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="176"/>
-      <c r="B17" s="144"/>
-      <c r="C17" s="179"/>
+      <c r="A17" s="137"/>
+      <c r="B17" s="140"/>
+      <c r="C17" s="143"/>
       <c r="D17" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="E17" s="135"/>
-      <c r="F17" s="182"/>
+      <c r="E17" s="146"/>
+      <c r="F17" s="149"/>
       <c r="G17" s="12"/>
     </row>
     <row r="18" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="176"/>
-      <c r="B18" s="144"/>
-      <c r="C18" s="179"/>
+      <c r="A18" s="137"/>
+      <c r="B18" s="140"/>
+      <c r="C18" s="143"/>
       <c r="D18" s="35" t="s">
         <v>411</v>
       </c>
-      <c r="E18" s="135"/>
-      <c r="F18" s="182"/>
+      <c r="E18" s="146"/>
+      <c r="F18" s="149"/>
       <c r="G18" s="12"/>
     </row>
     <row r="19" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="177"/>
-      <c r="B19" s="145"/>
-      <c r="C19" s="180"/>
+      <c r="A19" s="138"/>
+      <c r="B19" s="141"/>
+      <c r="C19" s="144"/>
       <c r="D19" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="136"/>
-      <c r="F19" s="183"/>
+      <c r="E19" s="147"/>
+      <c r="F19" s="150"/>
       <c r="G19" s="12"/>
     </row>
     <row r="20" spans="1:7" ht="33" x14ac:dyDescent="0.25">
@@ -3091,7 +3091,7 @@
         <f>IF(LEN(C24)=0,"",COUNTA($C$14:C24))</f>
         <v>6</v>
       </c>
-      <c r="B24" s="146" t="s">
+      <c r="B24" s="151" t="s">
         <v>40</v>
       </c>
       <c r="C24" s="41" t="s">
@@ -3100,10 +3100,10 @@
       <c r="D24" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="E24" s="184">
+      <c r="E24" s="152">
         <v>60000</v>
       </c>
-      <c r="F24" s="156" t="s">
+      <c r="F24" s="154" t="s">
         <v>381</v>
       </c>
       <c r="G24" s="12"/>
@@ -3113,15 +3113,15 @@
         <f>IF(LEN(C25)=0,"",COUNTA($C$14:C25))</f>
         <v>7</v>
       </c>
-      <c r="B25" s="146"/>
+      <c r="B25" s="151"/>
       <c r="C25" s="41" t="s">
         <v>43</v>
       </c>
       <c r="D25" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="185"/>
-      <c r="F25" s="157"/>
+      <c r="E25" s="153"/>
+      <c r="F25" s="155"/>
       <c r="G25" s="12"/>
     </row>
     <row r="26" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
@@ -3163,12 +3163,12 @@
       <c r="G27" s="12"/>
     </row>
     <row r="28" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="161" t="s">
+      <c r="A28" s="122" t="s">
         <v>26</v>
       </c>
-      <c r="B28" s="163"/>
-      <c r="C28" s="163"/>
-      <c r="D28" s="162"/>
+      <c r="B28" s="123"/>
+      <c r="C28" s="123"/>
+      <c r="D28" s="124"/>
       <c r="E28" s="121">
         <f>SUM(E14:E27)</f>
         <v>564000</v>
@@ -3209,14 +3209,14 @@
       <c r="A32" s="61" t="s">
         <v>259</v>
       </c>
-      <c r="B32" s="161" t="s">
+      <c r="B32" s="122" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="162"/>
+      <c r="C32" s="124"/>
       <c r="D32" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="E32" s="115" t="s">
+      <c r="E32" s="121" t="s">
         <v>4</v>
       </c>
       <c r="F32" s="34" t="s">
@@ -3320,7 +3320,7 @@
         <f>IF(LEN(C38)=0,"",COUNTA($C$34:C38))</f>
         <v>5</v>
       </c>
-      <c r="B38" s="143" t="s">
+      <c r="B38" s="139" t="s">
         <v>44</v>
       </c>
       <c r="C38" s="41" t="s">
@@ -3342,7 +3342,7 @@
         <f>IF(LEN(C39)=0,"",COUNTA($C$34:C39))</f>
         <v>6</v>
       </c>
-      <c r="B39" s="145"/>
+      <c r="B39" s="141"/>
       <c r="C39" s="41" t="s">
         <v>274</v>
       </c>
@@ -3362,7 +3362,7 @@
         <f>IF(LEN(C40)=0,"",COUNTA($C$34:C40))</f>
         <v>7</v>
       </c>
-      <c r="B40" s="153" t="s">
+      <c r="B40" s="156" t="s">
         <v>60</v>
       </c>
       <c r="C40" s="41" t="s">
@@ -3374,7 +3374,7 @@
       <c r="E40" s="69">
         <v>41000</v>
       </c>
-      <c r="F40" s="128" t="s">
+      <c r="F40" s="157" t="s">
         <v>377</v>
       </c>
       <c r="G40" s="12"/>
@@ -3384,7 +3384,7 @@
         <f>IF(LEN(C41)=0,"",COUNTA($C$34:C41))</f>
         <v>8</v>
       </c>
-      <c r="B41" s="153"/>
+      <c r="B41" s="156"/>
       <c r="C41" s="41" t="s">
         <v>63</v>
       </c>
@@ -3394,7 +3394,7 @@
       <c r="E41" s="69">
         <v>59000</v>
       </c>
-      <c r="F41" s="129"/>
+      <c r="F41" s="158"/>
       <c r="G41" s="12"/>
     </row>
     <row r="42" spans="1:7" ht="33" x14ac:dyDescent="0.25">
@@ -3402,7 +3402,7 @@
         <f>IF(LEN(C42)=0,"",COUNTA($C$34:C42))</f>
         <v>9</v>
       </c>
-      <c r="B42" s="153"/>
+      <c r="B42" s="156"/>
       <c r="C42" s="41" t="s">
         <v>65</v>
       </c>
@@ -3412,7 +3412,7 @@
       <c r="E42" s="69">
         <v>59000</v>
       </c>
-      <c r="F42" s="129"/>
+      <c r="F42" s="158"/>
       <c r="G42" s="12"/>
     </row>
     <row r="43" spans="1:7" ht="33" x14ac:dyDescent="0.25">
@@ -3420,7 +3420,7 @@
         <f>IF(LEN(C43)=0,"",COUNTA($C$34:C43))</f>
         <v>10</v>
       </c>
-      <c r="B43" s="153"/>
+      <c r="B43" s="156"/>
       <c r="C43" s="41" t="s">
         <v>67</v>
       </c>
@@ -3430,7 +3430,7 @@
       <c r="E43" s="69">
         <v>47000</v>
       </c>
-      <c r="F43" s="129"/>
+      <c r="F43" s="158"/>
       <c r="G43" s="12"/>
     </row>
     <row r="44" spans="1:7" ht="33" x14ac:dyDescent="0.25">
@@ -3438,7 +3438,7 @@
         <f>IF(LEN(C44)=0,"",COUNTA($C$34:C44))</f>
         <v>11</v>
       </c>
-      <c r="B44" s="153"/>
+      <c r="B44" s="156"/>
       <c r="C44" s="41" t="s">
         <v>69</v>
       </c>
@@ -3448,7 +3448,7 @@
       <c r="E44" s="69">
         <v>41000</v>
       </c>
-      <c r="F44" s="130"/>
+      <c r="F44" s="159"/>
       <c r="G44" s="12"/>
     </row>
     <row r="45" spans="1:7" ht="33" x14ac:dyDescent="0.25">
@@ -3476,7 +3476,7 @@
         <f>IF(LEN(C46)=0,"",COUNTA($C$34:C46))</f>
         <v>13</v>
       </c>
-      <c r="B46" s="143" t="s">
+      <c r="B46" s="139" t="s">
         <v>277</v>
       </c>
       <c r="C46" s="35" t="s">
@@ -3488,7 +3488,7 @@
       <c r="E46" s="72">
         <v>62000</v>
       </c>
-      <c r="F46" s="128" t="s">
+      <c r="F46" s="157" t="s">
         <v>378</v>
       </c>
       <c r="G46" s="12"/>
@@ -3498,7 +3498,7 @@
         <f>IF(LEN(C47)=0,"",COUNTA($C$34:C47))</f>
         <v>14</v>
       </c>
-      <c r="B47" s="144"/>
+      <c r="B47" s="140"/>
       <c r="C47" s="35" t="s">
         <v>196</v>
       </c>
@@ -3508,7 +3508,7 @@
       <c r="E47" s="72">
         <v>165000</v>
       </c>
-      <c r="F47" s="129"/>
+      <c r="F47" s="158"/>
       <c r="G47" s="12"/>
     </row>
     <row r="48" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -3516,7 +3516,7 @@
         <f>IF(LEN(C48)=0,"",COUNTA($C$34:C48))</f>
         <v>15</v>
       </c>
-      <c r="B48" s="145"/>
+      <c r="B48" s="141"/>
       <c r="C48" s="35" t="s">
         <v>201</v>
       </c>
@@ -3526,7 +3526,7 @@
       <c r="E48" s="72">
         <v>116000</v>
       </c>
-      <c r="F48" s="130"/>
+      <c r="F48" s="159"/>
       <c r="G48" s="12"/>
     </row>
     <row r="49" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -3534,7 +3534,7 @@
         <f>IF(LEN(C49)=0,"",COUNTA($C$34:C49))</f>
         <v>16</v>
       </c>
-      <c r="B49" s="143" t="s">
+      <c r="B49" s="139" t="s">
         <v>272</v>
       </c>
       <c r="C49" s="35" t="s">
@@ -3554,7 +3554,7 @@
         <f>IF(LEN(C50)=0,"",COUNTA($C$34:C50))</f>
         <v>17</v>
       </c>
-      <c r="B50" s="144"/>
+      <c r="B50" s="140"/>
       <c r="C50" s="35" t="s">
         <v>269</v>
       </c>
@@ -3564,7 +3564,7 @@
       <c r="E50" s="72">
         <v>130000</v>
       </c>
-      <c r="F50" s="128" t="s">
+      <c r="F50" s="157" t="s">
         <v>378</v>
       </c>
       <c r="G50" s="12"/>
@@ -3574,7 +3574,7 @@
         <f>IF(LEN(C51)=0,"",COUNTA($C$34:C51))</f>
         <v>18</v>
       </c>
-      <c r="B51" s="144"/>
+      <c r="B51" s="140"/>
       <c r="C51" s="35" t="s">
         <v>270</v>
       </c>
@@ -3584,7 +3584,7 @@
       <c r="E51" s="72">
         <v>120000</v>
       </c>
-      <c r="F51" s="129"/>
+      <c r="F51" s="158"/>
       <c r="G51" s="12"/>
     </row>
     <row r="52" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -3592,7 +3592,7 @@
         <f>IF(LEN(C52)=0,"",COUNTA($C$34:C52))</f>
         <v>19</v>
       </c>
-      <c r="B52" s="145"/>
+      <c r="B52" s="141"/>
       <c r="C52" s="35" t="s">
         <v>271</v>
       </c>
@@ -3602,7 +3602,7 @@
       <c r="E52" s="72">
         <v>282000</v>
       </c>
-      <c r="F52" s="130"/>
+      <c r="F52" s="159"/>
       <c r="G52" s="12"/>
     </row>
     <row r="53" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -3630,7 +3630,7 @@
         <f>IF(LEN(C54)=0,"",COUNTA($C$34:C54))</f>
         <v>21</v>
       </c>
-      <c r="B54" s="137" t="s">
+      <c r="B54" s="165" t="s">
         <v>130</v>
       </c>
       <c r="C54" s="35" t="s">
@@ -3642,7 +3642,7 @@
       <c r="E54" s="72">
         <v>71000</v>
       </c>
-      <c r="F54" s="156" t="s">
+      <c r="F54" s="154" t="s">
         <v>380</v>
       </c>
       <c r="G54" s="12"/>
@@ -3652,7 +3652,7 @@
         <f>IF(LEN(C55)=0,"",COUNTA($C$34:C55))</f>
         <v>22</v>
       </c>
-      <c r="B55" s="138"/>
+      <c r="B55" s="166"/>
       <c r="C55" s="35" t="s">
         <v>133</v>
       </c>
@@ -3662,7 +3662,7 @@
       <c r="E55" s="68">
         <v>138000</v>
       </c>
-      <c r="F55" s="157"/>
+      <c r="F55" s="155"/>
       <c r="G55" s="12"/>
     </row>
     <row r="56" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -3690,7 +3690,7 @@
         <f>IF(LEN(C57)=0,"",COUNTA($C$34:C57))</f>
         <v>24</v>
       </c>
-      <c r="B57" s="158" t="s">
+      <c r="B57" s="167" t="s">
         <v>205</v>
       </c>
       <c r="C57" s="35" t="s">
@@ -3702,7 +3702,7 @@
       <c r="E57" s="72">
         <v>30000</v>
       </c>
-      <c r="F57" s="159" t="s">
+      <c r="F57" s="168" t="s">
         <v>382</v>
       </c>
       <c r="G57" s="13"/>
@@ -3712,7 +3712,7 @@
         <f>IF(LEN(C58)=0,"",COUNTA($C$34:C58))</f>
         <v>25</v>
       </c>
-      <c r="B58" s="158"/>
+      <c r="B58" s="167"/>
       <c r="C58" s="35" t="s">
         <v>278</v>
       </c>
@@ -3722,16 +3722,16 @@
       <c r="E58" s="72">
         <v>20000</v>
       </c>
-      <c r="F58" s="160"/>
+      <c r="F58" s="169"/>
       <c r="G58" s="13"/>
     </row>
     <row r="59" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A59" s="131" t="s">
+      <c r="A59" s="170" t="s">
         <v>208</v>
       </c>
-      <c r="B59" s="132"/>
-      <c r="C59" s="132"/>
-      <c r="D59" s="133"/>
+      <c r="B59" s="171"/>
+      <c r="C59" s="171"/>
+      <c r="D59" s="172"/>
       <c r="E59" s="66"/>
       <c r="F59" s="67"/>
       <c r="G59" s="12"/>
@@ -3741,7 +3741,7 @@
         <f>IF(LEN(C60)=0,"",COUNTA($C$34:C60))</f>
         <v>26</v>
       </c>
-      <c r="B60" s="147" t="s">
+      <c r="B60" s="160" t="s">
         <v>260</v>
       </c>
       <c r="C60" s="73" t="s">
@@ -3761,7 +3761,7 @@
         <f>IF(LEN(C61)=0,"",COUNTA($C$34:C61))</f>
         <v>27</v>
       </c>
-      <c r="B61" s="148"/>
+      <c r="B61" s="161"/>
       <c r="C61" s="73" t="s">
         <v>83</v>
       </c>
@@ -3779,7 +3779,7 @@
         <f>IF(LEN(C62)=0,"",COUNTA($C$34:C62))</f>
         <v>28</v>
       </c>
-      <c r="B62" s="148"/>
+      <c r="B62" s="161"/>
       <c r="C62" s="73" t="s">
         <v>85</v>
       </c>
@@ -3797,7 +3797,7 @@
         <f>IF(LEN(C63)=0,"",COUNTA($C$34:C63))</f>
         <v>29</v>
       </c>
-      <c r="B63" s="148"/>
+      <c r="B63" s="161"/>
       <c r="C63" s="73" t="s">
         <v>79</v>
       </c>
@@ -3815,7 +3815,7 @@
         <f>IF(LEN(C64)=0,"",COUNTA($C$34:C64))</f>
         <v>30</v>
       </c>
-      <c r="B64" s="148"/>
+      <c r="B64" s="161"/>
       <c r="C64" s="73" t="s">
         <v>93</v>
       </c>
@@ -3833,7 +3833,7 @@
         <f>IF(LEN(C65)=0,"",COUNTA($C$34:C65))</f>
         <v>31</v>
       </c>
-      <c r="B65" s="148"/>
+      <c r="B65" s="161"/>
       <c r="C65" s="73" t="s">
         <v>80</v>
       </c>
@@ -3851,7 +3851,7 @@
         <f>IF(LEN(C66)=0,"",COUNTA($C$34:C66))</f>
         <v>32</v>
       </c>
-      <c r="B66" s="148"/>
+      <c r="B66" s="161"/>
       <c r="C66" s="73" t="s">
         <v>82</v>
       </c>
@@ -3871,7 +3871,7 @@
         <f>IF(LEN(C67)=0,"",COUNTA($C$34:C67))</f>
         <v>33</v>
       </c>
-      <c r="B67" s="148"/>
+      <c r="B67" s="161"/>
       <c r="C67" s="75" t="s">
         <v>234</v>
       </c>
@@ -3889,7 +3889,7 @@
         <f>IF(LEN(C68)=0,"",COUNTA($C$34:C68))</f>
         <v>34</v>
       </c>
-      <c r="B68" s="148"/>
+      <c r="B68" s="161"/>
       <c r="C68" s="73" t="s">
         <v>73</v>
       </c>
@@ -3909,7 +3909,7 @@
         <f>IF(LEN(C69)=0,"",COUNTA($C$34:C69))</f>
         <v>35</v>
       </c>
-      <c r="B69" s="148"/>
+      <c r="B69" s="161"/>
       <c r="C69" s="73" t="s">
         <v>75</v>
       </c>
@@ -3927,7 +3927,7 @@
         <f>IF(LEN(C70)=0,"",COUNTA($C$34:C70))</f>
         <v>36</v>
       </c>
-      <c r="B70" s="148"/>
+      <c r="B70" s="161"/>
       <c r="C70" s="73" t="s">
         <v>77</v>
       </c>
@@ -3945,7 +3945,7 @@
         <f>IF(LEN(C71)=0,"",COUNTA($C$34:C71))</f>
         <v>37</v>
       </c>
-      <c r="B71" s="148"/>
+      <c r="B71" s="161"/>
       <c r="C71" s="73" t="s">
         <v>87</v>
       </c>
@@ -3963,7 +3963,7 @@
         <f>IF(LEN(C72)=0,"",COUNTA($C$34:C72))</f>
         <v>38</v>
       </c>
-      <c r="B72" s="149"/>
+      <c r="B72" s="162"/>
       <c r="C72" s="73" t="s">
         <v>95</v>
       </c>
@@ -3981,19 +3981,19 @@
         <f>IF(LEN(C73)=0,"",COUNTA($C$34:C73))</f>
         <v>39</v>
       </c>
-      <c r="B73" s="147" t="s">
+      <c r="B73" s="160" t="s">
         <v>90</v>
       </c>
       <c r="C73" s="73" t="s">
         <v>89</v>
       </c>
-      <c r="D73" s="150" t="s">
+      <c r="D73" s="173" t="s">
         <v>396</v>
       </c>
       <c r="E73" s="39">
         <v>137000</v>
       </c>
-      <c r="F73" s="128" t="s">
+      <c r="F73" s="157" t="s">
         <v>379</v>
       </c>
       <c r="G73" s="13"/>
@@ -4003,15 +4003,15 @@
         <f>IF(LEN(C74)=0,"",COUNTA($C$34:C74))</f>
         <v>40</v>
       </c>
-      <c r="B74" s="148"/>
+      <c r="B74" s="161"/>
       <c r="C74" s="73" t="s">
         <v>91</v>
       </c>
-      <c r="D74" s="151"/>
+      <c r="D74" s="174"/>
       <c r="E74" s="39">
         <v>137000</v>
       </c>
-      <c r="F74" s="129"/>
+      <c r="F74" s="158"/>
       <c r="G74" s="13"/>
     </row>
     <row r="75" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
@@ -4019,15 +4019,15 @@
         <f>IF(LEN(C75)=0,"",COUNTA($C$34:C75))</f>
         <v>41</v>
       </c>
-      <c r="B75" s="149"/>
+      <c r="B75" s="162"/>
       <c r="C75" s="73" t="s">
         <v>92</v>
       </c>
-      <c r="D75" s="152"/>
+      <c r="D75" s="175"/>
       <c r="E75" s="39">
         <v>208000</v>
       </c>
-      <c r="F75" s="130"/>
+      <c r="F75" s="159"/>
       <c r="G75" s="13"/>
     </row>
     <row r="76" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
@@ -4035,13 +4035,13 @@
         <f>IF(LEN(C76)=0,"",COUNTA($C$34:C76))</f>
         <v>42</v>
       </c>
-      <c r="B76" s="147" t="s">
+      <c r="B76" s="160" t="s">
         <v>397</v>
       </c>
       <c r="C76" s="73" t="s">
         <v>398</v>
       </c>
-      <c r="D76" s="154" t="s">
+      <c r="D76" s="163" t="s">
         <v>400</v>
       </c>
       <c r="E76" s="39">
@@ -4055,11 +4055,11 @@
         <f>IF(LEN(C77)=0,"",COUNTA($C$34:C77))</f>
         <v>43</v>
       </c>
-      <c r="B77" s="148"/>
+      <c r="B77" s="161"/>
       <c r="C77" s="73" t="s">
         <v>399</v>
       </c>
-      <c r="D77" s="155"/>
+      <c r="D77" s="164"/>
       <c r="E77" s="39">
         <v>323000</v>
       </c>
@@ -4071,7 +4071,7 @@
         <f>IF(LEN(C78)=0,"",COUNTA($C$34:C78))</f>
         <v>44</v>
       </c>
-      <c r="B78" s="148"/>
+      <c r="B78" s="161"/>
       <c r="C78" s="73" t="s">
         <v>402</v>
       </c>
@@ -4089,7 +4089,7 @@
         <f>IF(LEN(C79)=0,"",COUNTA($C$34:C79))</f>
         <v>45</v>
       </c>
-      <c r="B79" s="149"/>
+      <c r="B79" s="162"/>
       <c r="C79" s="73" t="s">
         <v>403</v>
       </c>
@@ -4103,12 +4103,12 @@
       <c r="G79" s="13"/>
     </row>
     <row r="80" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A80" s="131" t="s">
+      <c r="A80" s="170" t="s">
         <v>207</v>
       </c>
-      <c r="B80" s="132"/>
-      <c r="C80" s="132"/>
-      <c r="D80" s="133"/>
+      <c r="B80" s="171"/>
+      <c r="C80" s="171"/>
+      <c r="D80" s="172"/>
       <c r="E80" s="66"/>
       <c r="F80" s="67"/>
       <c r="G80" s="13"/>
@@ -4118,7 +4118,7 @@
         <f>IF(LEN(C81)=0,"",COUNTA($C$34:C81))</f>
         <v>46</v>
       </c>
-      <c r="B81" s="153" t="s">
+      <c r="B81" s="156" t="s">
         <v>97</v>
       </c>
       <c r="C81" s="35" t="s">
@@ -4138,7 +4138,7 @@
         <f>IF(LEN(C82)=0,"",COUNTA($C$34:C82))</f>
         <v>47</v>
       </c>
-      <c r="B82" s="153"/>
+      <c r="B82" s="156"/>
       <c r="C82" s="35" t="s">
         <v>100</v>
       </c>
@@ -4156,7 +4156,7 @@
         <f>IF(LEN(C83)=0,"",COUNTA($C$34:C83))</f>
         <v>48</v>
       </c>
-      <c r="B83" s="153"/>
+      <c r="B83" s="156"/>
       <c r="C83" s="35" t="s">
         <v>102</v>
       </c>
@@ -4176,7 +4176,7 @@
         <f>IF(LEN(C84)=0,"",COUNTA($C$34:C84))</f>
         <v>49</v>
       </c>
-      <c r="B84" s="153"/>
+      <c r="B84" s="156"/>
       <c r="C84" s="35" t="s">
         <v>105</v>
       </c>
@@ -4196,7 +4196,7 @@
         <f>IF(LEN(C85)=0,"",COUNTA($C$34:C85))</f>
         <v>50</v>
       </c>
-      <c r="B85" s="153"/>
+      <c r="B85" s="156"/>
       <c r="C85" s="35" t="s">
         <v>405</v>
       </c>
@@ -4214,7 +4214,7 @@
         <f>IF(LEN(C86)=0,"",COUNTA($C$34:C86))</f>
         <v>51</v>
       </c>
-      <c r="B86" s="153"/>
+      <c r="B86" s="156"/>
       <c r="C86" s="35" t="s">
         <v>107</v>
       </c>
@@ -4234,7 +4234,7 @@
         <f>IF(LEN(C87)=0,"",COUNTA($C$34:C87))</f>
         <v>52</v>
       </c>
-      <c r="B87" s="153"/>
+      <c r="B87" s="156"/>
       <c r="C87" s="35" t="s">
         <v>110</v>
       </c>
@@ -4254,7 +4254,7 @@
         <f>IF(LEN(C88)=0,"",COUNTA($C$34:C88))</f>
         <v>53</v>
       </c>
-      <c r="B88" s="153"/>
+      <c r="B88" s="156"/>
       <c r="C88" s="35" t="s">
         <v>113</v>
       </c>
@@ -4274,7 +4274,7 @@
         <f>IF(LEN(C89)=0,"",COUNTA($C$34:C89))</f>
         <v>54</v>
       </c>
-      <c r="B89" s="153" t="s">
+      <c r="B89" s="156" t="s">
         <v>116</v>
       </c>
       <c r="C89" s="35" t="s">
@@ -4294,7 +4294,7 @@
         <f>IF(LEN(C90)=0,"",COUNTA($C$34:C90))</f>
         <v>55</v>
       </c>
-      <c r="B90" s="153"/>
+      <c r="B90" s="156"/>
       <c r="C90" s="35" t="s">
         <v>119</v>
       </c>
@@ -4312,7 +4312,7 @@
         <f>IF(LEN(C91)=0,"",COUNTA($C$34:C91))</f>
         <v>56</v>
       </c>
-      <c r="B91" s="137" t="s">
+      <c r="B91" s="165" t="s">
         <v>121</v>
       </c>
       <c r="C91" s="35" t="s">
@@ -4332,7 +4332,7 @@
         <f>IF(LEN(C92)=0,"",COUNTA($C$34:C92))</f>
         <v>57</v>
       </c>
-      <c r="B92" s="139"/>
+      <c r="B92" s="176"/>
       <c r="C92" s="35" t="s">
         <v>388</v>
       </c>
@@ -4350,7 +4350,7 @@
         <f>IF(LEN(C93)=0,"",COUNTA($C$34:C93))</f>
         <v>58</v>
       </c>
-      <c r="B93" s="138"/>
+      <c r="B93" s="166"/>
       <c r="C93" s="35" t="s">
         <v>125</v>
       </c>
@@ -4364,12 +4364,12 @@
       <c r="G93" s="12"/>
     </row>
     <row r="94" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A94" s="131" t="s">
+      <c r="A94" s="170" t="s">
         <v>261</v>
       </c>
-      <c r="B94" s="132"/>
-      <c r="C94" s="132"/>
-      <c r="D94" s="133"/>
+      <c r="B94" s="171"/>
+      <c r="C94" s="171"/>
+      <c r="D94" s="172"/>
       <c r="E94" s="77"/>
       <c r="F94" s="67"/>
       <c r="G94" s="12"/>
@@ -4379,7 +4379,7 @@
         <f>IF(LEN(C95)=0,"",COUNTA($C$34:C95))</f>
         <v>59</v>
       </c>
-      <c r="B95" s="143" t="s">
+      <c r="B95" s="139" t="s">
         <v>240</v>
       </c>
       <c r="C95" s="35" t="s">
@@ -4399,7 +4399,7 @@
         <f>IF(LEN(C96)=0,"",COUNTA($C$34:C96))</f>
         <v>60</v>
       </c>
-      <c r="B96" s="145"/>
+      <c r="B96" s="141"/>
       <c r="C96" s="35" t="s">
         <v>239</v>
       </c>
@@ -4417,7 +4417,7 @@
         <f>IF(LEN(C97)=0,"",COUNTA($C$34:C97))</f>
         <v>61</v>
       </c>
-      <c r="B97" s="137" t="s">
+      <c r="B97" s="165" t="s">
         <v>243</v>
       </c>
       <c r="C97" s="35" t="s">
@@ -4435,7 +4435,7 @@
         <f>IF(LEN(C98)=0,"",COUNTA($C$34:C98))</f>
         <v>62</v>
       </c>
-      <c r="B98" s="138"/>
+      <c r="B98" s="166"/>
       <c r="C98" s="35" t="s">
         <v>242</v>
       </c>
@@ -4471,7 +4471,7 @@
         <f>IF(LEN(C100)=0,"",COUNTA($C$34:C100))</f>
         <v>64</v>
       </c>
-      <c r="B100" s="137" t="s">
+      <c r="B100" s="165" t="s">
         <v>258</v>
       </c>
       <c r="C100" s="35" t="s">
@@ -4489,7 +4489,7 @@
         <f>IF(LEN(C101)=0,"",COUNTA($C$34:C101))</f>
         <v>65</v>
       </c>
-      <c r="B101" s="139"/>
+      <c r="B101" s="176"/>
       <c r="C101" s="35" t="s">
         <v>245</v>
       </c>
@@ -4505,7 +4505,7 @@
         <f>IF(LEN(C102)=0,"",COUNTA($C$34:C102))</f>
         <v>66</v>
       </c>
-      <c r="B102" s="139"/>
+      <c r="B102" s="176"/>
       <c r="C102" s="35" t="s">
         <v>246</v>
       </c>
@@ -4521,7 +4521,7 @@
         <f>IF(LEN(C103)=0,"",COUNTA($C$34:C103))</f>
         <v>67</v>
       </c>
-      <c r="B103" s="139"/>
+      <c r="B103" s="176"/>
       <c r="C103" s="35" t="s">
         <v>247</v>
       </c>
@@ -4537,7 +4537,7 @@
         <f>IF(LEN(C104)=0,"",COUNTA($C$34:C104))</f>
         <v>68</v>
       </c>
-      <c r="B104" s="139"/>
+      <c r="B104" s="176"/>
       <c r="C104" s="35" t="s">
         <v>248</v>
       </c>
@@ -4553,7 +4553,7 @@
         <f>IF(LEN(C105)=0,"",COUNTA($C$34:C105))</f>
         <v>69</v>
       </c>
-      <c r="B105" s="139"/>
+      <c r="B105" s="176"/>
       <c r="C105" s="35" t="s">
         <v>249</v>
       </c>
@@ -4569,7 +4569,7 @@
         <f>IF(LEN(C106)=0,"",COUNTA($C$34:C106))</f>
         <v>70</v>
       </c>
-      <c r="B106" s="139"/>
+      <c r="B106" s="176"/>
       <c r="C106" s="35" t="s">
         <v>250</v>
       </c>
@@ -4585,7 +4585,7 @@
         <f>IF(LEN(C107)=0,"",COUNTA($C$34:C107))</f>
         <v>71</v>
       </c>
-      <c r="B107" s="139"/>
+      <c r="B107" s="176"/>
       <c r="C107" s="35" t="s">
         <v>251</v>
       </c>
@@ -4601,7 +4601,7 @@
         <f>IF(LEN(C108)=0,"",COUNTA($C$34:C108))</f>
         <v>72</v>
       </c>
-      <c r="B108" s="139"/>
+      <c r="B108" s="176"/>
       <c r="C108" s="35" t="s">
         <v>252</v>
       </c>
@@ -4617,7 +4617,7 @@
         <f>IF(LEN(C109)=0,"",COUNTA($C$34:C109))</f>
         <v>73</v>
       </c>
-      <c r="B109" s="139"/>
+      <c r="B109" s="176"/>
       <c r="C109" s="35" t="s">
         <v>253</v>
       </c>
@@ -4633,7 +4633,7 @@
         <f>IF(LEN(C110)=0,"",COUNTA($C$34:C110))</f>
         <v>74</v>
       </c>
-      <c r="B110" s="139"/>
+      <c r="B110" s="176"/>
       <c r="C110" s="35" t="s">
         <v>254</v>
       </c>
@@ -4649,7 +4649,7 @@
         <f>IF(LEN(C111)=0,"",COUNTA($C$34:C111))</f>
         <v>75</v>
       </c>
-      <c r="B111" s="139"/>
+      <c r="B111" s="176"/>
       <c r="C111" s="35" t="s">
         <v>255</v>
       </c>
@@ -4665,7 +4665,7 @@
         <f>IF(LEN(C112)=0,"",COUNTA($C$34:C112))</f>
         <v>76</v>
       </c>
-      <c r="B112" s="139"/>
+      <c r="B112" s="176"/>
       <c r="C112" s="35" t="s">
         <v>256</v>
       </c>
@@ -4681,7 +4681,7 @@
         <f>IF(LEN(C113)=0,"",COUNTA($C$34:C113))</f>
         <v>77</v>
       </c>
-      <c r="B113" s="138"/>
+      <c r="B113" s="166"/>
       <c r="C113" s="35" t="s">
         <v>257</v>
       </c>
@@ -4693,12 +4693,12 @@
       <c r="G113" s="12"/>
     </row>
     <row r="114" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="131" t="s">
+      <c r="A114" s="170" t="s">
         <v>226</v>
       </c>
-      <c r="B114" s="132"/>
-      <c r="C114" s="132"/>
-      <c r="D114" s="133"/>
+      <c r="B114" s="171"/>
+      <c r="C114" s="171"/>
+      <c r="D114" s="172"/>
       <c r="E114" s="66"/>
       <c r="F114" s="67"/>
       <c r="G114" s="12"/>
@@ -4744,12 +4744,12 @@
       <c r="G116" s="12"/>
     </row>
     <row r="117" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A117" s="127" t="s">
+      <c r="A117" s="177" t="s">
         <v>262</v>
       </c>
-      <c r="B117" s="127"/>
-      <c r="C117" s="127"/>
-      <c r="D117" s="127"/>
+      <c r="B117" s="177"/>
+      <c r="C117" s="177"/>
+      <c r="D117" s="177"/>
       <c r="E117" s="77"/>
       <c r="F117" s="67"/>
       <c r="G117" s="12"/>
@@ -4759,7 +4759,7 @@
         <f>IF(LEN(C118)=0,"",COUNTA($C$34:C118))</f>
         <v>80</v>
       </c>
-      <c r="B118" s="140" t="s">
+      <c r="B118" s="178" t="s">
         <v>204</v>
       </c>
       <c r="C118" s="36" t="s">
@@ -4779,7 +4779,7 @@
         <f>IF(LEN(C119)=0,"",COUNTA($C$34:C119))</f>
         <v>81</v>
       </c>
-      <c r="B119" s="141"/>
+      <c r="B119" s="179"/>
       <c r="C119" s="36" t="s">
         <v>34</v>
       </c>
@@ -4797,7 +4797,7 @@
         <f>IF(LEN(C120)=0,"",COUNTA($C$34:C120))</f>
         <v>82</v>
       </c>
-      <c r="B120" s="141"/>
+      <c r="B120" s="179"/>
       <c r="C120" s="36" t="s">
         <v>324</v>
       </c>
@@ -4815,7 +4815,7 @@
         <f>IF(LEN(C121)=0,"",COUNTA($C$34:C121))</f>
         <v>83</v>
       </c>
-      <c r="B121" s="141"/>
+      <c r="B121" s="179"/>
       <c r="C121" s="35" t="s">
         <v>407</v>
       </c>
@@ -4831,7 +4831,7 @@
         <f>IF(LEN(C122)=0,"",COUNTA($C$34:C122))</f>
         <v>84</v>
       </c>
-      <c r="B122" s="141"/>
+      <c r="B122" s="179"/>
       <c r="C122" s="35" t="s">
         <v>408</v>
       </c>
@@ -4847,7 +4847,7 @@
         <f>IF(LEN(C123)=0,"",COUNTA($C$34:C123))</f>
         <v>85</v>
       </c>
-      <c r="B123" s="141"/>
+      <c r="B123" s="179"/>
       <c r="C123" s="35" t="s">
         <v>409</v>
       </c>
@@ -4863,7 +4863,7 @@
         <f>IF(LEN(C124)=0,"",COUNTA($C$34:C124))</f>
         <v>86</v>
       </c>
-      <c r="B124" s="141"/>
+      <c r="B124" s="179"/>
       <c r="C124" s="36" t="s">
         <v>410</v>
       </c>
@@ -4881,7 +4881,7 @@
         <f>IF(LEN(C125)=0,"",COUNTA($C$34:C125))</f>
         <v>87</v>
       </c>
-      <c r="B125" s="141"/>
+      <c r="B125" s="179"/>
       <c r="C125" s="36" t="s">
         <v>138</v>
       </c>
@@ -4899,7 +4899,7 @@
         <f>IF(LEN(C126)=0,"",COUNTA($C$34:C126))</f>
         <v>88</v>
       </c>
-      <c r="B126" s="142"/>
+      <c r="B126" s="180"/>
       <c r="C126" s="36" t="s">
         <v>139</v>
       </c>
@@ -4917,7 +4917,7 @@
         <f>IF(LEN(C127)=0,"",COUNTA($C$34:C127))</f>
         <v>89</v>
       </c>
-      <c r="B127" s="143" t="s">
+      <c r="B127" s="139" t="s">
         <v>282</v>
       </c>
       <c r="C127" s="35" t="s">
@@ -4937,7 +4937,7 @@
         <f>IF(LEN(C128)=0,"",COUNTA($C$34:C128))</f>
         <v>90</v>
       </c>
-      <c r="B128" s="144"/>
+      <c r="B128" s="140"/>
       <c r="C128" s="35" t="s">
         <v>143</v>
       </c>
@@ -4955,7 +4955,7 @@
         <f>IF(LEN(C129)=0,"",COUNTA($C$34:C129))</f>
         <v>91</v>
       </c>
-      <c r="B129" s="144"/>
+      <c r="B129" s="140"/>
       <c r="C129" s="35" t="s">
         <v>392</v>
       </c>
@@ -4973,7 +4973,7 @@
         <f>IF(LEN(C130)=0,"",COUNTA($C$34:C130))</f>
         <v>92</v>
       </c>
-      <c r="B130" s="144"/>
+      <c r="B130" s="140"/>
       <c r="C130" s="35" t="s">
         <v>394</v>
       </c>
@@ -4991,7 +4991,7 @@
         <f>IF(LEN(C131)=0,"",COUNTA($C$34:C131))</f>
         <v>93</v>
       </c>
-      <c r="B131" s="144"/>
+      <c r="B131" s="140"/>
       <c r="C131" s="35" t="s">
         <v>369</v>
       </c>
@@ -5009,7 +5009,7 @@
         <f>IF(LEN(C132)=0,"",COUNTA($C$34:C132))</f>
         <v>94</v>
       </c>
-      <c r="B132" s="145"/>
+      <c r="B132" s="141"/>
       <c r="C132" s="35" t="s">
         <v>145</v>
       </c>
@@ -5025,7 +5025,7 @@
         <f>IF(LEN(C133)=0,"",COUNTA($C$34:C133))</f>
         <v>95</v>
       </c>
-      <c r="B133" s="144" t="s">
+      <c r="B133" s="140" t="s">
         <v>283</v>
       </c>
       <c r="C133" s="35" t="s">
@@ -5043,7 +5043,7 @@
         <f>IF(LEN(C134)=0,"",COUNTA($C$34:C134))</f>
         <v>96</v>
       </c>
-      <c r="B134" s="144"/>
+      <c r="B134" s="140"/>
       <c r="C134" s="35" t="s">
         <v>330</v>
       </c>
@@ -5061,7 +5061,7 @@
         <f>IF(LEN(C135)=0,"",COUNTA($C$34:C135))</f>
         <v>97</v>
       </c>
-      <c r="B135" s="144"/>
+      <c r="B135" s="140"/>
       <c r="C135" s="35" t="s">
         <v>151</v>
       </c>
@@ -5079,7 +5079,7 @@
         <f>IF(LEN(C136)=0,"",COUNTA($C$34:C136))</f>
         <v>98</v>
       </c>
-      <c r="B136" s="144"/>
+      <c r="B136" s="140"/>
       <c r="C136" s="35" t="s">
         <v>153</v>
       </c>
@@ -5097,7 +5097,7 @@
         <f>IF(LEN(C137)=0,"",COUNTA($C$34:C137))</f>
         <v>99</v>
       </c>
-      <c r="B137" s="144"/>
+      <c r="B137" s="140"/>
       <c r="C137" s="35" t="s">
         <v>155</v>
       </c>
@@ -5115,7 +5115,7 @@
         <f>IF(LEN(C138)=0,"",COUNTA($C$34:C138))</f>
         <v>100</v>
       </c>
-      <c r="B138" s="144"/>
+      <c r="B138" s="140"/>
       <c r="C138" s="35" t="s">
         <v>157</v>
       </c>
@@ -5133,7 +5133,7 @@
         <f>IF(LEN(C139)=0,"",COUNTA($C$34:C139))</f>
         <v>101</v>
       </c>
-      <c r="B139" s="144"/>
+      <c r="B139" s="140"/>
       <c r="C139" s="35" t="s">
         <v>158</v>
       </c>
@@ -5149,7 +5149,7 @@
         <f>IF(LEN(C140)=0,"",COUNTA($C$34:C140))</f>
         <v>102</v>
       </c>
-      <c r="B140" s="146" t="s">
+      <c r="B140" s="151" t="s">
         <v>304</v>
       </c>
       <c r="C140" s="35" t="s">
@@ -5171,7 +5171,7 @@
         <f>IF(LEN(C141)=0,"",COUNTA($C$34:C141))</f>
         <v>103</v>
       </c>
-      <c r="B141" s="146"/>
+      <c r="B141" s="151"/>
       <c r="C141" s="35" t="s">
         <v>342</v>
       </c>
@@ -5189,7 +5189,7 @@
         <f>IF(LEN(C142)=0,"",COUNTA($C$34:C142))</f>
         <v>104</v>
       </c>
-      <c r="B142" s="146"/>
+      <c r="B142" s="151"/>
       <c r="C142" s="35" t="s">
         <v>343</v>
       </c>
@@ -5209,7 +5209,7 @@
         <f>IF(LEN(C143)=0,"",COUNTA($C$34:C143))</f>
         <v>105</v>
       </c>
-      <c r="B143" s="146"/>
+      <c r="B143" s="151"/>
       <c r="C143" s="35" t="s">
         <v>344</v>
       </c>
@@ -5227,7 +5227,7 @@
         <f>IF(LEN(C144)=0,"",COUNTA($C$34:C144))</f>
         <v>106</v>
       </c>
-      <c r="B144" s="146"/>
+      <c r="B144" s="151"/>
       <c r="C144" s="35" t="s">
         <v>345</v>
       </c>
@@ -5245,7 +5245,7 @@
         <f>IF(LEN(C145)=0,"",COUNTA($C$34:C145))</f>
         <v>107</v>
       </c>
-      <c r="B145" s="146"/>
+      <c r="B145" s="151"/>
       <c r="C145" s="107" t="s">
         <v>372</v>
       </c>
@@ -5263,7 +5263,7 @@
         <f>IF(LEN(C146)=0,"",COUNTA($C$34:C146))</f>
         <v>108</v>
       </c>
-      <c r="B146" s="146"/>
+      <c r="B146" s="151"/>
       <c r="C146" s="35" t="s">
         <v>346</v>
       </c>
@@ -5281,7 +5281,7 @@
         <f>IF(LEN(C147)=0,"",COUNTA($C$34:C147))</f>
         <v>109</v>
       </c>
-      <c r="B147" s="146"/>
+      <c r="B147" s="151"/>
       <c r="C147" s="35" t="s">
         <v>347</v>
       </c>
@@ -5299,7 +5299,7 @@
         <f>IF(LEN(C148)=0,"",COUNTA($C$34:C148))</f>
         <v>110</v>
       </c>
-      <c r="B148" s="146"/>
+      <c r="B148" s="151"/>
       <c r="C148" s="35" t="s">
         <v>348</v>
       </c>
@@ -5317,7 +5317,7 @@
         <f>IF(LEN(C149)=0,"",COUNTA($C$34:C149))</f>
         <v>111</v>
       </c>
-      <c r="B149" s="146"/>
+      <c r="B149" s="151"/>
       <c r="C149" s="107" t="s">
         <v>371</v>
       </c>
@@ -5335,7 +5335,7 @@
         <f>IF(LEN(C150)=0,"",COUNTA($C$34:C150))</f>
         <v>112</v>
       </c>
-      <c r="B150" s="146"/>
+      <c r="B150" s="151"/>
       <c r="C150" s="35" t="s">
         <v>349</v>
       </c>
@@ -5355,7 +5355,7 @@
         <f>IF(LEN(C151)=0,"",COUNTA($C$34:C151))</f>
         <v>113</v>
       </c>
-      <c r="B151" s="146"/>
+      <c r="B151" s="151"/>
       <c r="C151" s="35" t="s">
         <v>350</v>
       </c>
@@ -5373,7 +5373,7 @@
         <f>IF(LEN(C152)=0,"",COUNTA($C$34:C152))</f>
         <v>114</v>
       </c>
-      <c r="B152" s="146"/>
+      <c r="B152" s="151"/>
       <c r="C152" s="35" t="s">
         <v>351</v>
       </c>
@@ -5391,7 +5391,7 @@
         <f>IF(LEN(C153)=0,"",COUNTA($C$34:C153))</f>
         <v>115</v>
       </c>
-      <c r="B153" s="146"/>
+      <c r="B153" s="151"/>
       <c r="C153" s="35" t="s">
         <v>352</v>
       </c>
@@ -5409,7 +5409,7 @@
         <f>IF(LEN(C154)=0,"",COUNTA($C$34:C154))</f>
         <v>116</v>
       </c>
-      <c r="B154" s="146"/>
+      <c r="B154" s="151"/>
       <c r="C154" s="35" t="s">
         <v>353</v>
       </c>
@@ -5427,7 +5427,7 @@
         <f>IF(LEN(C155)=0,"",COUNTA($C$34:C155))</f>
         <v>117</v>
       </c>
-      <c r="B155" s="146"/>
+      <c r="B155" s="151"/>
       <c r="C155" s="35" t="s">
         <v>354</v>
       </c>
@@ -5445,7 +5445,7 @@
         <f>IF(LEN(C156)=0,"",COUNTA($C$34:C156))</f>
         <v>118</v>
       </c>
-      <c r="B156" s="146"/>
+      <c r="B156" s="151"/>
       <c r="C156" s="35" t="s">
         <v>355</v>
       </c>
@@ -5463,7 +5463,7 @@
         <f>IF(LEN(C157)=0,"",COUNTA($C$34:C157))</f>
         <v>119</v>
       </c>
-      <c r="B157" s="146"/>
+      <c r="B157" s="151"/>
       <c r="C157" s="35" t="s">
         <v>356</v>
       </c>
@@ -5481,7 +5481,7 @@
         <f>IF(LEN(C158)=0,"",COUNTA($C$34:C158))</f>
         <v>120</v>
       </c>
-      <c r="B158" s="146"/>
+      <c r="B158" s="151"/>
       <c r="C158" s="35" t="s">
         <v>357</v>
       </c>
@@ -5499,7 +5499,7 @@
         <f>IF(LEN(C159)=0,"",COUNTA($C$34:C159))</f>
         <v>121</v>
       </c>
-      <c r="B159" s="146"/>
+      <c r="B159" s="151"/>
       <c r="C159" s="35" t="s">
         <v>358</v>
       </c>
@@ -5517,7 +5517,7 @@
         <f>IF(LEN(C160)=0,"",COUNTA($C$34:C160))</f>
         <v>122</v>
       </c>
-      <c r="B160" s="146"/>
+      <c r="B160" s="151"/>
       <c r="C160" s="35" t="s">
         <v>359</v>
       </c>
@@ -5535,7 +5535,7 @@
         <f>IF(LEN(C161)=0,"",COUNTA($C$34:C161))</f>
         <v>123</v>
       </c>
-      <c r="B161" s="146"/>
+      <c r="B161" s="151"/>
       <c r="C161" s="35" t="s">
         <v>360</v>
       </c>
@@ -5553,7 +5553,7 @@
         <f>IF(LEN(C162)=0,"",COUNTA($C$34:C162))</f>
         <v>124</v>
       </c>
-      <c r="B162" s="146"/>
+      <c r="B162" s="151"/>
       <c r="C162" s="35" t="s">
         <v>361</v>
       </c>
@@ -5571,7 +5571,7 @@
         <f>IF(LEN(C163)=0,"",COUNTA($C$34:C163))</f>
         <v>125</v>
       </c>
-      <c r="B163" s="146"/>
+      <c r="B163" s="151"/>
       <c r="C163" s="35" t="s">
         <v>362</v>
       </c>
@@ -5589,7 +5589,7 @@
         <f>IF(LEN(C164)=0,"",COUNTA($C$34:C164))</f>
         <v>126</v>
       </c>
-      <c r="B164" s="146"/>
+      <c r="B164" s="151"/>
       <c r="C164" s="35" t="s">
         <v>363</v>
       </c>
@@ -5605,7 +5605,7 @@
         <f>IF(LEN(C165)=0,"",COUNTA($C$34:C165))</f>
         <v>127</v>
       </c>
-      <c r="B165" s="146"/>
+      <c r="B165" s="151"/>
       <c r="C165" s="35" t="s">
         <v>364</v>
       </c>
@@ -5621,7 +5621,7 @@
         <f>IF(LEN(C166)=0,"",COUNTA($C$34:C166))</f>
         <v>128</v>
       </c>
-      <c r="B166" s="146"/>
+      <c r="B166" s="151"/>
       <c r="C166" s="35" t="s">
         <v>365</v>
       </c>
@@ -5639,7 +5639,7 @@
         <f>IF(LEN(C167)=0,"",COUNTA($C$34:C167))</f>
         <v>129</v>
       </c>
-      <c r="B167" s="146"/>
+      <c r="B167" s="151"/>
       <c r="C167" s="35" t="s">
         <v>366</v>
       </c>
@@ -5657,7 +5657,7 @@
         <f>IF(LEN(C168)=0,"",COUNTA($C$34:C168))</f>
         <v>130</v>
       </c>
-      <c r="B168" s="146"/>
+      <c r="B168" s="151"/>
       <c r="C168" s="35" t="s">
         <v>367</v>
       </c>
@@ -5675,7 +5675,7 @@
         <f>IF(LEN(C169)=0,"",COUNTA($C$34:C169))</f>
         <v>131</v>
       </c>
-      <c r="B169" s="146"/>
+      <c r="B169" s="151"/>
       <c r="C169" s="35" t="s">
         <v>368</v>
       </c>
@@ -5689,12 +5689,12 @@
       <c r="G169" s="12"/>
     </row>
     <row r="170" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A170" s="127" t="s">
+      <c r="A170" s="177" t="s">
         <v>206</v>
       </c>
-      <c r="B170" s="127"/>
-      <c r="C170" s="127"/>
-      <c r="D170" s="127"/>
+      <c r="B170" s="177"/>
+      <c r="C170" s="177"/>
+      <c r="D170" s="177"/>
       <c r="E170" s="77"/>
       <c r="F170" s="67"/>
       <c r="G170" s="12"/>
@@ -5759,7 +5759,7 @@
         <f>IF(LEN(C174)=0,"",COUNTA($C$34:C174))</f>
         <v>135</v>
       </c>
-      <c r="B174" s="143" t="s">
+      <c r="B174" s="139" t="s">
         <v>203</v>
       </c>
       <c r="C174" s="35" t="s">
@@ -5778,7 +5778,7 @@
         <f>IF(LEN(C175)=0,"",COUNTA($C$34:C175))</f>
         <v>136</v>
       </c>
-      <c r="B175" s="145"/>
+      <c r="B175" s="141"/>
       <c r="C175" s="35" t="s">
         <v>224</v>
       </c>
@@ -5791,12 +5791,12 @@
       <c r="F175" s="40"/>
     </row>
     <row r="176" spans="1:8" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A176" s="131" t="s">
+      <c r="A176" s="170" t="s">
         <v>163</v>
       </c>
-      <c r="B176" s="132"/>
-      <c r="C176" s="132"/>
-      <c r="D176" s="133"/>
+      <c r="B176" s="171"/>
+      <c r="C176" s="171"/>
+      <c r="D176" s="172"/>
       <c r="E176" s="120"/>
       <c r="F176" s="62"/>
     </row>
@@ -5815,7 +5815,7 @@
       <c r="E177" s="83">
         <v>71000</v>
       </c>
-      <c r="F177" s="125" t="s">
+      <c r="F177" s="182" t="s">
         <v>383</v>
       </c>
     </row>
@@ -5834,15 +5834,15 @@
       <c r="E178" s="83">
         <v>86000</v>
       </c>
-      <c r="F178" s="126"/>
+      <c r="F178" s="183"/>
     </row>
     <row r="179" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A179" s="127" t="s">
+      <c r="A179" s="177" t="s">
         <v>168</v>
       </c>
-      <c r="B179" s="127"/>
-      <c r="C179" s="127"/>
-      <c r="D179" s="127"/>
+      <c r="B179" s="177"/>
+      <c r="C179" s="177"/>
+      <c r="D179" s="177"/>
       <c r="E179" s="77"/>
       <c r="F179" s="67"/>
       <c r="G179" s="12"/>
@@ -5862,7 +5862,7 @@
       <c r="E180" s="106">
         <v>1968000</v>
       </c>
-      <c r="F180" s="128" t="s">
+      <c r="F180" s="157" t="s">
         <v>325</v>
       </c>
       <c r="G180" s="12"/>
@@ -5882,7 +5882,7 @@
       <c r="E181" s="106">
         <v>2952000</v>
       </c>
-      <c r="F181" s="129"/>
+      <c r="F181" s="158"/>
       <c r="G181" s="12"/>
     </row>
     <row r="182" spans="1:7" ht="66" x14ac:dyDescent="0.25">
@@ -5900,7 +5900,7 @@
       <c r="E182" s="106">
         <v>4100000</v>
       </c>
-      <c r="F182" s="130"/>
+      <c r="F182" s="159"/>
       <c r="G182" s="12"/>
     </row>
     <row r="183" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
@@ -5996,12 +5996,12 @@
       <c r="G187" s="12"/>
     </row>
     <row r="188" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A188" s="127" t="s">
+      <c r="A188" s="177" t="s">
         <v>263</v>
       </c>
-      <c r="B188" s="127"/>
-      <c r="C188" s="127"/>
-      <c r="D188" s="127"/>
+      <c r="B188" s="177"/>
+      <c r="C188" s="177"/>
+      <c r="D188" s="177"/>
       <c r="E188" s="77"/>
       <c r="F188" s="67"/>
       <c r="G188" s="12"/>
@@ -6025,12 +6025,12 @@
       <c r="G189" s="12"/>
     </row>
     <row r="190" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A190" s="127" t="s">
+      <c r="A190" s="177" t="s">
         <v>233</v>
       </c>
-      <c r="B190" s="127"/>
-      <c r="C190" s="127"/>
-      <c r="D190" s="127"/>
+      <c r="B190" s="177"/>
+      <c r="C190" s="177"/>
+      <c r="D190" s="177"/>
       <c r="E190" s="77"/>
       <c r="F190" s="67"/>
       <c r="G190" s="12"/>
@@ -6216,12 +6216,12 @@
       <c r="G200" s="12"/>
     </row>
     <row r="201" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A201" s="131" t="s">
+      <c r="A201" s="170" t="s">
         <v>322</v>
       </c>
-      <c r="B201" s="132"/>
-      <c r="C201" s="132"/>
-      <c r="D201" s="133"/>
+      <c r="B201" s="171"/>
+      <c r="C201" s="171"/>
+      <c r="D201" s="172"/>
       <c r="E201" s="66"/>
       <c r="F201" s="67"/>
       <c r="G201" s="12"/>
@@ -6315,12 +6315,12 @@
       <c r="G206" s="12"/>
     </row>
     <row r="207" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A207" s="131" t="s">
+      <c r="A207" s="170" t="s">
         <v>221</v>
       </c>
-      <c r="B207" s="132"/>
-      <c r="C207" s="132"/>
-      <c r="D207" s="133"/>
+      <c r="B207" s="171"/>
+      <c r="C207" s="171"/>
+      <c r="D207" s="172"/>
       <c r="E207" s="66"/>
       <c r="F207" s="67"/>
       <c r="G207" s="12"/>
@@ -6380,12 +6380,12 @@
       <c r="G210" s="12"/>
     </row>
     <row r="211" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A211" s="131" t="s">
+      <c r="A211" s="170" t="s">
         <v>210</v>
       </c>
-      <c r="B211" s="132"/>
-      <c r="C211" s="132"/>
-      <c r="D211" s="133"/>
+      <c r="B211" s="171"/>
+      <c r="C211" s="171"/>
+      <c r="D211" s="172"/>
       <c r="E211" s="66"/>
       <c r="F211" s="67"/>
       <c r="G211" s="12"/>
@@ -6400,7 +6400,7 @@
         <v>211</v>
       </c>
       <c r="D212" s="35"/>
-      <c r="E212" s="134">
+      <c r="E212" s="145">
         <v>183000</v>
       </c>
       <c r="F212" s="40"/>
@@ -6416,7 +6416,7 @@
         <v>212</v>
       </c>
       <c r="D213" s="35"/>
-      <c r="E213" s="135"/>
+      <c r="E213" s="146"/>
       <c r="F213" s="40"/>
       <c r="G213" s="12"/>
     </row>
@@ -6430,7 +6430,7 @@
         <v>213</v>
       </c>
       <c r="D214" s="35"/>
-      <c r="E214" s="135"/>
+      <c r="E214" s="146"/>
       <c r="F214" s="40"/>
       <c r="G214" s="12"/>
     </row>
@@ -6444,17 +6444,17 @@
         <v>214</v>
       </c>
       <c r="D215" s="35"/>
-      <c r="E215" s="136"/>
+      <c r="E215" s="147"/>
       <c r="F215" s="40"/>
       <c r="G215" s="12"/>
     </row>
     <row r="216" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A216" s="131" t="s">
+      <c r="A216" s="170" t="s">
         <v>412</v>
       </c>
-      <c r="B216" s="132"/>
-      <c r="C216" s="132"/>
-      <c r="D216" s="133"/>
+      <c r="B216" s="171"/>
+      <c r="C216" s="171"/>
+      <c r="D216" s="172"/>
       <c r="E216" s="66"/>
       <c r="F216" s="67"/>
       <c r="G216" s="12"/>
@@ -6532,64 +6532,64 @@
       <c r="F221" s="93"/>
     </row>
     <row r="222" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A222" s="124" t="s">
+      <c r="A222" s="181" t="s">
         <v>27</v>
       </c>
-      <c r="B222" s="124"/>
-      <c r="C222" s="124"/>
-      <c r="D222" s="124"/>
+      <c r="B222" s="181"/>
+      <c r="C222" s="181"/>
+      <c r="D222" s="181"/>
       <c r="E222" s="26"/>
       <c r="F222" s="94"/>
     </row>
     <row r="223" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A223" s="95"/>
-      <c r="B223" s="122" t="s">
+      <c r="B223" s="184" t="s">
         <v>266</v>
       </c>
-      <c r="C223" s="122"/>
-      <c r="D223" s="122"/>
-      <c r="E223" s="122"/>
-      <c r="F223" s="122"/>
+      <c r="C223" s="184"/>
+      <c r="D223" s="184"/>
+      <c r="E223" s="184"/>
+      <c r="F223" s="184"/>
     </row>
     <row r="224" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A224" s="95"/>
-      <c r="B224" s="122" t="s">
+      <c r="B224" s="184" t="s">
         <v>417</v>
       </c>
-      <c r="C224" s="122"/>
-      <c r="D224" s="122"/>
-      <c r="E224" s="122"/>
-      <c r="F224" s="122"/>
+      <c r="C224" s="184"/>
+      <c r="D224" s="184"/>
+      <c r="E224" s="184"/>
+      <c r="F224" s="184"/>
     </row>
     <row r="225" spans="1:6" s="2" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="96"/>
-      <c r="B225" s="122" t="s">
+      <c r="B225" s="184" t="s">
         <v>28</v>
       </c>
-      <c r="C225" s="122"/>
-      <c r="D225" s="122"/>
-      <c r="E225" s="122"/>
-      <c r="F225" s="122"/>
+      <c r="C225" s="184"/>
+      <c r="D225" s="184"/>
+      <c r="E225" s="184"/>
+      <c r="F225" s="184"/>
     </row>
     <row r="226" spans="1:6" s="17" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="97"/>
-      <c r="B226" s="123" t="s">
+      <c r="B226" s="185" t="s">
         <v>29</v>
       </c>
-      <c r="C226" s="123"/>
-      <c r="D226" s="123"/>
-      <c r="E226" s="123"/>
-      <c r="F226" s="123"/>
+      <c r="C226" s="185"/>
+      <c r="D226" s="185"/>
+      <c r="E226" s="185"/>
+      <c r="F226" s="185"/>
     </row>
     <row r="227" spans="1:6" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="94"/>
-      <c r="B227" s="122" t="s">
+      <c r="B227" s="184" t="s">
         <v>30</v>
       </c>
-      <c r="C227" s="122"/>
-      <c r="D227" s="122"/>
-      <c r="E227" s="122"/>
-      <c r="F227" s="122"/>
+      <c r="C227" s="184"/>
+      <c r="D227" s="184"/>
+      <c r="E227" s="184"/>
+      <c r="F227" s="184"/>
     </row>
     <row r="228" spans="1:6" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A228" s="94"/>
@@ -6653,6 +6653,58 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="B223:F223"/>
+    <mergeCell ref="B224:F224"/>
+    <mergeCell ref="B225:F225"/>
+    <mergeCell ref="B226:F226"/>
+    <mergeCell ref="B227:F227"/>
+    <mergeCell ref="A222:D222"/>
+    <mergeCell ref="F177:F178"/>
+    <mergeCell ref="A179:D179"/>
+    <mergeCell ref="F180:F182"/>
+    <mergeCell ref="A188:D188"/>
+    <mergeCell ref="A190:D190"/>
+    <mergeCell ref="A201:D201"/>
+    <mergeCell ref="A207:D207"/>
+    <mergeCell ref="A211:D211"/>
+    <mergeCell ref="E212:E215"/>
+    <mergeCell ref="A216:D216"/>
+    <mergeCell ref="A176:D176"/>
+    <mergeCell ref="B97:B98"/>
+    <mergeCell ref="B100:B113"/>
+    <mergeCell ref="A114:D114"/>
+    <mergeCell ref="A117:D117"/>
+    <mergeCell ref="B118:B126"/>
+    <mergeCell ref="B127:B132"/>
+    <mergeCell ref="B133:B139"/>
+    <mergeCell ref="B140:B169"/>
+    <mergeCell ref="A170:D170"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="B60:B72"/>
+    <mergeCell ref="B73:B75"/>
+    <mergeCell ref="D73:D75"/>
+    <mergeCell ref="A80:D80"/>
+    <mergeCell ref="B81:B88"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="B91:B93"/>
+    <mergeCell ref="A94:D94"/>
+    <mergeCell ref="F73:F75"/>
+    <mergeCell ref="B76:B79"/>
+    <mergeCell ref="D76:D77"/>
+    <mergeCell ref="B49:B52"/>
+    <mergeCell ref="F50:F52"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="F57:F58"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="B40:B44"/>
+    <mergeCell ref="F40:F44"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="F46:F48"/>
     <mergeCell ref="A28:D28"/>
     <mergeCell ref="D1:F5"/>
     <mergeCell ref="A7:F7"/>
@@ -6667,58 +6719,6 @@
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="E24:E25"/>
     <mergeCell ref="F24:F25"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="B40:B44"/>
-    <mergeCell ref="F40:F44"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="F46:F48"/>
-    <mergeCell ref="F73:F75"/>
-    <mergeCell ref="B76:B79"/>
-    <mergeCell ref="D76:D77"/>
-    <mergeCell ref="B49:B52"/>
-    <mergeCell ref="F50:F52"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="F54:F55"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="F57:F58"/>
-    <mergeCell ref="B95:B96"/>
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="B60:B72"/>
-    <mergeCell ref="B73:B75"/>
-    <mergeCell ref="D73:D75"/>
-    <mergeCell ref="A80:D80"/>
-    <mergeCell ref="B81:B88"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="B91:B93"/>
-    <mergeCell ref="A94:D94"/>
-    <mergeCell ref="A176:D176"/>
-    <mergeCell ref="B97:B98"/>
-    <mergeCell ref="B100:B113"/>
-    <mergeCell ref="A114:D114"/>
-    <mergeCell ref="A117:D117"/>
-    <mergeCell ref="B118:B126"/>
-    <mergeCell ref="B127:B132"/>
-    <mergeCell ref="B133:B139"/>
-    <mergeCell ref="B140:B169"/>
-    <mergeCell ref="A170:D170"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="A222:D222"/>
-    <mergeCell ref="F177:F178"/>
-    <mergeCell ref="A179:D179"/>
-    <mergeCell ref="F180:F182"/>
-    <mergeCell ref="A188:D188"/>
-    <mergeCell ref="A190:D190"/>
-    <mergeCell ref="A201:D201"/>
-    <mergeCell ref="A207:D207"/>
-    <mergeCell ref="A211:D211"/>
-    <mergeCell ref="E212:E215"/>
-    <mergeCell ref="A216:D216"/>
-    <mergeCell ref="B223:F223"/>
-    <mergeCell ref="B224:F224"/>
-    <mergeCell ref="B225:F225"/>
-    <mergeCell ref="B226:F226"/>
-    <mergeCell ref="B227:F227"/>
   </mergeCells>
   <pageMargins left="0.35433070866141736" right="0.15748031496062992" top="0.23622047244094491" bottom="0.19685039370078741" header="0.15748031496062992" footer="0.15748031496062992"/>
   <pageSetup paperSize="9" scale="70" fitToHeight="0" orientation="landscape" r:id="rId1"/>

--- a/Hoàng/SALE/BÁO GIÁ KSK 2025 - THAM KHẢO.xlsx
+++ b/Hoàng/SALE/BÁO GIÁ KSK 2025 - THAM KHẢO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\SALE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA3AA22E-0CAD-442C-BFE7-9BBEFC4123A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C51A12-77E4-4449-80A6-112EDA9740D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2214,15 +2214,132 @@
     <xf numFmtId="3" fontId="11" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -2265,15 +2382,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2283,15 +2391,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2301,110 +2400,11 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2788,43 +2788,43 @@
       <c r="A1" s="22"/>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
-      <c r="D1" s="125" t="s">
+      <c r="D1" s="164" t="s">
         <v>312</v>
       </c>
-      <c r="E1" s="125"/>
-      <c r="F1" s="125"/>
+      <c r="E1" s="164"/>
+      <c r="F1" s="164"/>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="24"/>
       <c r="B2" s="24"/>
       <c r="C2" s="24"/>
-      <c r="D2" s="126"/>
-      <c r="E2" s="126"/>
-      <c r="F2" s="126"/>
+      <c r="D2" s="165"/>
+      <c r="E2" s="165"/>
+      <c r="F2" s="165"/>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A3" s="24"/>
       <c r="B3" s="24"/>
       <c r="C3" s="24"/>
-      <c r="D3" s="126"/>
-      <c r="E3" s="126"/>
-      <c r="F3" s="126"/>
+      <c r="D3" s="165"/>
+      <c r="E3" s="165"/>
+      <c r="F3" s="165"/>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="24"/>
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
-      <c r="D4" s="126"/>
-      <c r="E4" s="126"/>
-      <c r="F4" s="126"/>
+      <c r="D4" s="165"/>
+      <c r="E4" s="165"/>
+      <c r="F4" s="165"/>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5" s="24"/>
       <c r="B5" s="24"/>
       <c r="C5" s="24"/>
-      <c r="D5" s="126"/>
-      <c r="E5" s="126"/>
-      <c r="F5" s="126"/>
+      <c r="D5" s="165"/>
+      <c r="E5" s="165"/>
+      <c r="F5" s="165"/>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="23"/>
@@ -2835,14 +2835,14 @@
       <c r="F6" s="23"/>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="127" t="s">
+      <c r="A7" s="166" t="s">
         <v>418</v>
       </c>
-      <c r="B7" s="127"/>
-      <c r="C7" s="127"/>
-      <c r="D7" s="127"/>
-      <c r="E7" s="127"/>
-      <c r="F7" s="127"/>
+      <c r="B7" s="166"/>
+      <c r="C7" s="166"/>
+      <c r="D7" s="166"/>
+      <c r="E7" s="166"/>
+      <c r="F7" s="166"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
@@ -2864,27 +2864,27 @@
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="28"/>
-      <c r="B9" s="128" t="s">
+      <c r="B9" s="167" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="128"/>
-      <c r="D9" s="128"/>
-      <c r="E9" s="128"/>
-      <c r="F9" s="128"/>
+      <c r="C9" s="167"/>
+      <c r="D9" s="167"/>
+      <c r="E9" s="167"/>
+      <c r="F9" s="167"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="129" t="s">
+      <c r="A10" s="168" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="130"/>
-      <c r="C10" s="130"/>
-      <c r="D10" s="130"/>
-      <c r="E10" s="130"/>
-      <c r="F10" s="131"/>
+      <c r="B10" s="169"/>
+      <c r="C10" s="169"/>
+      <c r="D10" s="169"/>
+      <c r="E10" s="169"/>
+      <c r="F10" s="170"/>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
@@ -2892,12 +2892,12 @@
       <c r="K10" s="8"/>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="132"/>
-      <c r="B11" s="133"/>
-      <c r="C11" s="133"/>
-      <c r="D11" s="133"/>
-      <c r="E11" s="133"/>
-      <c r="F11" s="134"/>
+      <c r="A11" s="171"/>
+      <c r="B11" s="172"/>
+      <c r="C11" s="172"/>
+      <c r="D11" s="172"/>
+      <c r="E11" s="172"/>
+      <c r="F11" s="173"/>
       <c r="G11" s="21"/>
       <c r="H11" s="21"/>
       <c r="I11" s="21"/>
@@ -2916,10 +2916,10 @@
       <c r="A13" s="33" t="s">
         <v>259</v>
       </c>
-      <c r="B13" s="135" t="s">
+      <c r="B13" s="174" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="135"/>
+      <c r="C13" s="174"/>
       <c r="D13" s="33" t="s">
         <v>3</v>
       </c>
@@ -2932,78 +2932,78 @@
       <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="136">
+      <c r="A14" s="175">
         <f>IF(LEN(C14)=0,"",COUNTA($C$14:C14))</f>
         <v>1</v>
       </c>
-      <c r="B14" s="139" t="s">
+      <c r="B14" s="143" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="142" t="s">
+      <c r="C14" s="178" t="s">
         <v>326</v>
       </c>
       <c r="D14" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="145">
+      <c r="E14" s="134">
         <v>200000</v>
       </c>
-      <c r="F14" s="148"/>
+      <c r="F14" s="181"/>
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="137"/>
-      <c r="B15" s="140"/>
-      <c r="C15" s="143"/>
+      <c r="A15" s="176"/>
+      <c r="B15" s="144"/>
+      <c r="C15" s="179"/>
       <c r="D15" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="E15" s="146"/>
-      <c r="F15" s="149"/>
+      <c r="E15" s="135"/>
+      <c r="F15" s="182"/>
       <c r="G15" s="11"/>
     </row>
     <row r="16" spans="1:11" ht="33" x14ac:dyDescent="0.25">
-      <c r="A16" s="137"/>
-      <c r="B16" s="140"/>
-      <c r="C16" s="143"/>
+      <c r="A16" s="176"/>
+      <c r="B16" s="144"/>
+      <c r="C16" s="179"/>
       <c r="D16" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="146"/>
-      <c r="F16" s="149"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="182"/>
       <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="137"/>
-      <c r="B17" s="140"/>
-      <c r="C17" s="143"/>
+      <c r="A17" s="176"/>
+      <c r="B17" s="144"/>
+      <c r="C17" s="179"/>
       <c r="D17" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="E17" s="146"/>
-      <c r="F17" s="149"/>
+      <c r="E17" s="135"/>
+      <c r="F17" s="182"/>
       <c r="G17" s="12"/>
     </row>
     <row r="18" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="137"/>
-      <c r="B18" s="140"/>
-      <c r="C18" s="143"/>
+      <c r="A18" s="176"/>
+      <c r="B18" s="144"/>
+      <c r="C18" s="179"/>
       <c r="D18" s="35" t="s">
         <v>411</v>
       </c>
-      <c r="E18" s="146"/>
-      <c r="F18" s="149"/>
+      <c r="E18" s="135"/>
+      <c r="F18" s="182"/>
       <c r="G18" s="12"/>
     </row>
     <row r="19" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="138"/>
-      <c r="B19" s="141"/>
-      <c r="C19" s="144"/>
+      <c r="A19" s="177"/>
+      <c r="B19" s="145"/>
+      <c r="C19" s="180"/>
       <c r="D19" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="147"/>
-      <c r="F19" s="150"/>
+      <c r="E19" s="136"/>
+      <c r="F19" s="183"/>
       <c r="G19" s="12"/>
     </row>
     <row r="20" spans="1:7" ht="33" x14ac:dyDescent="0.25">
@@ -3091,7 +3091,7 @@
         <f>IF(LEN(C24)=0,"",COUNTA($C$14:C24))</f>
         <v>6</v>
       </c>
-      <c r="B24" s="151" t="s">
+      <c r="B24" s="146" t="s">
         <v>40</v>
       </c>
       <c r="C24" s="41" t="s">
@@ -3100,10 +3100,10 @@
       <c r="D24" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="E24" s="152">
+      <c r="E24" s="184">
         <v>60000</v>
       </c>
-      <c r="F24" s="154" t="s">
+      <c r="F24" s="156" t="s">
         <v>381</v>
       </c>
       <c r="G24" s="12"/>
@@ -3113,15 +3113,15 @@
         <f>IF(LEN(C25)=0,"",COUNTA($C$14:C25))</f>
         <v>7</v>
       </c>
-      <c r="B25" s="151"/>
+      <c r="B25" s="146"/>
       <c r="C25" s="41" t="s">
         <v>43</v>
       </c>
       <c r="D25" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="153"/>
-      <c r="F25" s="155"/>
+      <c r="E25" s="185"/>
+      <c r="F25" s="157"/>
       <c r="G25" s="12"/>
     </row>
     <row r="26" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
@@ -3163,12 +3163,12 @@
       <c r="G27" s="12"/>
     </row>
     <row r="28" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="122" t="s">
+      <c r="A28" s="161" t="s">
         <v>26</v>
       </c>
-      <c r="B28" s="123"/>
-      <c r="C28" s="123"/>
-      <c r="D28" s="124"/>
+      <c r="B28" s="163"/>
+      <c r="C28" s="163"/>
+      <c r="D28" s="162"/>
       <c r="E28" s="121">
         <f>SUM(E14:E27)</f>
         <v>564000</v>
@@ -3209,10 +3209,10 @@
       <c r="A32" s="61" t="s">
         <v>259</v>
       </c>
-      <c r="B32" s="122" t="s">
+      <c r="B32" s="161" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="124"/>
+      <c r="C32" s="162"/>
       <c r="D32" s="61" t="s">
         <v>3</v>
       </c>
@@ -3320,7 +3320,7 @@
         <f>IF(LEN(C38)=0,"",COUNTA($C$34:C38))</f>
         <v>5</v>
       </c>
-      <c r="B38" s="139" t="s">
+      <c r="B38" s="143" t="s">
         <v>44</v>
       </c>
       <c r="C38" s="41" t="s">
@@ -3342,7 +3342,7 @@
         <f>IF(LEN(C39)=0,"",COUNTA($C$34:C39))</f>
         <v>6</v>
       </c>
-      <c r="B39" s="141"/>
+      <c r="B39" s="145"/>
       <c r="C39" s="41" t="s">
         <v>274</v>
       </c>
@@ -3362,7 +3362,7 @@
         <f>IF(LEN(C40)=0,"",COUNTA($C$34:C40))</f>
         <v>7</v>
       </c>
-      <c r="B40" s="156" t="s">
+      <c r="B40" s="153" t="s">
         <v>60</v>
       </c>
       <c r="C40" s="41" t="s">
@@ -3374,7 +3374,7 @@
       <c r="E40" s="69">
         <v>41000</v>
       </c>
-      <c r="F40" s="157" t="s">
+      <c r="F40" s="128" t="s">
         <v>377</v>
       </c>
       <c r="G40" s="12"/>
@@ -3384,7 +3384,7 @@
         <f>IF(LEN(C41)=0,"",COUNTA($C$34:C41))</f>
         <v>8</v>
       </c>
-      <c r="B41" s="156"/>
+      <c r="B41" s="153"/>
       <c r="C41" s="41" t="s">
         <v>63</v>
       </c>
@@ -3394,7 +3394,7 @@
       <c r="E41" s="69">
         <v>59000</v>
       </c>
-      <c r="F41" s="158"/>
+      <c r="F41" s="129"/>
       <c r="G41" s="12"/>
     </row>
     <row r="42" spans="1:7" ht="33" x14ac:dyDescent="0.25">
@@ -3402,7 +3402,7 @@
         <f>IF(LEN(C42)=0,"",COUNTA($C$34:C42))</f>
         <v>9</v>
       </c>
-      <c r="B42" s="156"/>
+      <c r="B42" s="153"/>
       <c r="C42" s="41" t="s">
         <v>65</v>
       </c>
@@ -3412,7 +3412,7 @@
       <c r="E42" s="69">
         <v>59000</v>
       </c>
-      <c r="F42" s="158"/>
+      <c r="F42" s="129"/>
       <c r="G42" s="12"/>
     </row>
     <row r="43" spans="1:7" ht="33" x14ac:dyDescent="0.25">
@@ -3420,7 +3420,7 @@
         <f>IF(LEN(C43)=0,"",COUNTA($C$34:C43))</f>
         <v>10</v>
       </c>
-      <c r="B43" s="156"/>
+      <c r="B43" s="153"/>
       <c r="C43" s="41" t="s">
         <v>67</v>
       </c>
@@ -3430,7 +3430,7 @@
       <c r="E43" s="69">
         <v>47000</v>
       </c>
-      <c r="F43" s="158"/>
+      <c r="F43" s="129"/>
       <c r="G43" s="12"/>
     </row>
     <row r="44" spans="1:7" ht="33" x14ac:dyDescent="0.25">
@@ -3438,7 +3438,7 @@
         <f>IF(LEN(C44)=0,"",COUNTA($C$34:C44))</f>
         <v>11</v>
       </c>
-      <c r="B44" s="156"/>
+      <c r="B44" s="153"/>
       <c r="C44" s="41" t="s">
         <v>69</v>
       </c>
@@ -3448,7 +3448,7 @@
       <c r="E44" s="69">
         <v>41000</v>
       </c>
-      <c r="F44" s="159"/>
+      <c r="F44" s="130"/>
       <c r="G44" s="12"/>
     </row>
     <row r="45" spans="1:7" ht="33" x14ac:dyDescent="0.25">
@@ -3476,7 +3476,7 @@
         <f>IF(LEN(C46)=0,"",COUNTA($C$34:C46))</f>
         <v>13</v>
       </c>
-      <c r="B46" s="139" t="s">
+      <c r="B46" s="143" t="s">
         <v>277</v>
       </c>
       <c r="C46" s="35" t="s">
@@ -3488,7 +3488,7 @@
       <c r="E46" s="72">
         <v>62000</v>
       </c>
-      <c r="F46" s="157" t="s">
+      <c r="F46" s="128" t="s">
         <v>378</v>
       </c>
       <c r="G46" s="12"/>
@@ -3498,7 +3498,7 @@
         <f>IF(LEN(C47)=0,"",COUNTA($C$34:C47))</f>
         <v>14</v>
       </c>
-      <c r="B47" s="140"/>
+      <c r="B47" s="144"/>
       <c r="C47" s="35" t="s">
         <v>196</v>
       </c>
@@ -3508,7 +3508,7 @@
       <c r="E47" s="72">
         <v>165000</v>
       </c>
-      <c r="F47" s="158"/>
+      <c r="F47" s="129"/>
       <c r="G47" s="12"/>
     </row>
     <row r="48" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -3516,7 +3516,7 @@
         <f>IF(LEN(C48)=0,"",COUNTA($C$34:C48))</f>
         <v>15</v>
       </c>
-      <c r="B48" s="141"/>
+      <c r="B48" s="145"/>
       <c r="C48" s="35" t="s">
         <v>201</v>
       </c>
@@ -3526,7 +3526,7 @@
       <c r="E48" s="72">
         <v>116000</v>
       </c>
-      <c r="F48" s="159"/>
+      <c r="F48" s="130"/>
       <c r="G48" s="12"/>
     </row>
     <row r="49" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -3534,7 +3534,7 @@
         <f>IF(LEN(C49)=0,"",COUNTA($C$34:C49))</f>
         <v>16</v>
       </c>
-      <c r="B49" s="139" t="s">
+      <c r="B49" s="143" t="s">
         <v>272</v>
       </c>
       <c r="C49" s="35" t="s">
@@ -3554,7 +3554,7 @@
         <f>IF(LEN(C50)=0,"",COUNTA($C$34:C50))</f>
         <v>17</v>
       </c>
-      <c r="B50" s="140"/>
+      <c r="B50" s="144"/>
       <c r="C50" s="35" t="s">
         <v>269</v>
       </c>
@@ -3564,7 +3564,7 @@
       <c r="E50" s="72">
         <v>130000</v>
       </c>
-      <c r="F50" s="157" t="s">
+      <c r="F50" s="128" t="s">
         <v>378</v>
       </c>
       <c r="G50" s="12"/>
@@ -3574,7 +3574,7 @@
         <f>IF(LEN(C51)=0,"",COUNTA($C$34:C51))</f>
         <v>18</v>
       </c>
-      <c r="B51" s="140"/>
+      <c r="B51" s="144"/>
       <c r="C51" s="35" t="s">
         <v>270</v>
       </c>
@@ -3584,7 +3584,7 @@
       <c r="E51" s="72">
         <v>120000</v>
       </c>
-      <c r="F51" s="158"/>
+      <c r="F51" s="129"/>
       <c r="G51" s="12"/>
     </row>
     <row r="52" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -3592,7 +3592,7 @@
         <f>IF(LEN(C52)=0,"",COUNTA($C$34:C52))</f>
         <v>19</v>
       </c>
-      <c r="B52" s="141"/>
+      <c r="B52" s="145"/>
       <c r="C52" s="35" t="s">
         <v>271</v>
       </c>
@@ -3602,7 +3602,7 @@
       <c r="E52" s="72">
         <v>282000</v>
       </c>
-      <c r="F52" s="159"/>
+      <c r="F52" s="130"/>
       <c r="G52" s="12"/>
     </row>
     <row r="53" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -3630,7 +3630,7 @@
         <f>IF(LEN(C54)=0,"",COUNTA($C$34:C54))</f>
         <v>21</v>
       </c>
-      <c r="B54" s="165" t="s">
+      <c r="B54" s="137" t="s">
         <v>130</v>
       </c>
       <c r="C54" s="35" t="s">
@@ -3642,7 +3642,7 @@
       <c r="E54" s="72">
         <v>71000</v>
       </c>
-      <c r="F54" s="154" t="s">
+      <c r="F54" s="156" t="s">
         <v>380</v>
       </c>
       <c r="G54" s="12"/>
@@ -3652,7 +3652,7 @@
         <f>IF(LEN(C55)=0,"",COUNTA($C$34:C55))</f>
         <v>22</v>
       </c>
-      <c r="B55" s="166"/>
+      <c r="B55" s="138"/>
       <c r="C55" s="35" t="s">
         <v>133</v>
       </c>
@@ -3662,7 +3662,7 @@
       <c r="E55" s="68">
         <v>138000</v>
       </c>
-      <c r="F55" s="155"/>
+      <c r="F55" s="157"/>
       <c r="G55" s="12"/>
     </row>
     <row r="56" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -3690,7 +3690,7 @@
         <f>IF(LEN(C57)=0,"",COUNTA($C$34:C57))</f>
         <v>24</v>
       </c>
-      <c r="B57" s="167" t="s">
+      <c r="B57" s="158" t="s">
         <v>205</v>
       </c>
       <c r="C57" s="35" t="s">
@@ -3702,7 +3702,7 @@
       <c r="E57" s="72">
         <v>30000</v>
       </c>
-      <c r="F57" s="168" t="s">
+      <c r="F57" s="159" t="s">
         <v>382</v>
       </c>
       <c r="G57" s="13"/>
@@ -3712,7 +3712,7 @@
         <f>IF(LEN(C58)=0,"",COUNTA($C$34:C58))</f>
         <v>25</v>
       </c>
-      <c r="B58" s="167"/>
+      <c r="B58" s="158"/>
       <c r="C58" s="35" t="s">
         <v>278</v>
       </c>
@@ -3722,16 +3722,16 @@
       <c r="E58" s="72">
         <v>20000</v>
       </c>
-      <c r="F58" s="169"/>
+      <c r="F58" s="160"/>
       <c r="G58" s="13"/>
     </row>
     <row r="59" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A59" s="170" t="s">
+      <c r="A59" s="131" t="s">
         <v>208</v>
       </c>
-      <c r="B59" s="171"/>
-      <c r="C59" s="171"/>
-      <c r="D59" s="172"/>
+      <c r="B59" s="132"/>
+      <c r="C59" s="132"/>
+      <c r="D59" s="133"/>
       <c r="E59" s="66"/>
       <c r="F59" s="67"/>
       <c r="G59" s="12"/>
@@ -3741,7 +3741,7 @@
         <f>IF(LEN(C60)=0,"",COUNTA($C$34:C60))</f>
         <v>26</v>
       </c>
-      <c r="B60" s="160" t="s">
+      <c r="B60" s="147" t="s">
         <v>260</v>
       </c>
       <c r="C60" s="73" t="s">
@@ -3761,7 +3761,7 @@
         <f>IF(LEN(C61)=0,"",COUNTA($C$34:C61))</f>
         <v>27</v>
       </c>
-      <c r="B61" s="161"/>
+      <c r="B61" s="148"/>
       <c r="C61" s="73" t="s">
         <v>83</v>
       </c>
@@ -3779,7 +3779,7 @@
         <f>IF(LEN(C62)=0,"",COUNTA($C$34:C62))</f>
         <v>28</v>
       </c>
-      <c r="B62" s="161"/>
+      <c r="B62" s="148"/>
       <c r="C62" s="73" t="s">
         <v>85</v>
       </c>
@@ -3797,7 +3797,7 @@
         <f>IF(LEN(C63)=0,"",COUNTA($C$34:C63))</f>
         <v>29</v>
       </c>
-      <c r="B63" s="161"/>
+      <c r="B63" s="148"/>
       <c r="C63" s="73" t="s">
         <v>79</v>
       </c>
@@ -3815,7 +3815,7 @@
         <f>IF(LEN(C64)=0,"",COUNTA($C$34:C64))</f>
         <v>30</v>
       </c>
-      <c r="B64" s="161"/>
+      <c r="B64" s="148"/>
       <c r="C64" s="73" t="s">
         <v>93</v>
       </c>
@@ -3833,7 +3833,7 @@
         <f>IF(LEN(C65)=0,"",COUNTA($C$34:C65))</f>
         <v>31</v>
       </c>
-      <c r="B65" s="161"/>
+      <c r="B65" s="148"/>
       <c r="C65" s="73" t="s">
         <v>80</v>
       </c>
@@ -3851,7 +3851,7 @@
         <f>IF(LEN(C66)=0,"",COUNTA($C$34:C66))</f>
         <v>32</v>
       </c>
-      <c r="B66" s="161"/>
+      <c r="B66" s="148"/>
       <c r="C66" s="73" t="s">
         <v>82</v>
       </c>
@@ -3871,7 +3871,7 @@
         <f>IF(LEN(C67)=0,"",COUNTA($C$34:C67))</f>
         <v>33</v>
       </c>
-      <c r="B67" s="161"/>
+      <c r="B67" s="148"/>
       <c r="C67" s="75" t="s">
         <v>234</v>
       </c>
@@ -3889,7 +3889,7 @@
         <f>IF(LEN(C68)=0,"",COUNTA($C$34:C68))</f>
         <v>34</v>
       </c>
-      <c r="B68" s="161"/>
+      <c r="B68" s="148"/>
       <c r="C68" s="73" t="s">
         <v>73</v>
       </c>
@@ -3909,7 +3909,7 @@
         <f>IF(LEN(C69)=0,"",COUNTA($C$34:C69))</f>
         <v>35</v>
       </c>
-      <c r="B69" s="161"/>
+      <c r="B69" s="148"/>
       <c r="C69" s="73" t="s">
         <v>75</v>
       </c>
@@ -3927,7 +3927,7 @@
         <f>IF(LEN(C70)=0,"",COUNTA($C$34:C70))</f>
         <v>36</v>
       </c>
-      <c r="B70" s="161"/>
+      <c r="B70" s="148"/>
       <c r="C70" s="73" t="s">
         <v>77</v>
       </c>
@@ -3945,7 +3945,7 @@
         <f>IF(LEN(C71)=0,"",COUNTA($C$34:C71))</f>
         <v>37</v>
       </c>
-      <c r="B71" s="161"/>
+      <c r="B71" s="148"/>
       <c r="C71" s="73" t="s">
         <v>87</v>
       </c>
@@ -3963,7 +3963,7 @@
         <f>IF(LEN(C72)=0,"",COUNTA($C$34:C72))</f>
         <v>38</v>
       </c>
-      <c r="B72" s="162"/>
+      <c r="B72" s="149"/>
       <c r="C72" s="73" t="s">
         <v>95</v>
       </c>
@@ -3981,19 +3981,19 @@
         <f>IF(LEN(C73)=0,"",COUNTA($C$34:C73))</f>
         <v>39</v>
       </c>
-      <c r="B73" s="160" t="s">
+      <c r="B73" s="147" t="s">
         <v>90</v>
       </c>
       <c r="C73" s="73" t="s">
         <v>89</v>
       </c>
-      <c r="D73" s="173" t="s">
+      <c r="D73" s="150" t="s">
         <v>396</v>
       </c>
       <c r="E73" s="39">
         <v>137000</v>
       </c>
-      <c r="F73" s="157" t="s">
+      <c r="F73" s="128" t="s">
         <v>379</v>
       </c>
       <c r="G73" s="13"/>
@@ -4003,15 +4003,15 @@
         <f>IF(LEN(C74)=0,"",COUNTA($C$34:C74))</f>
         <v>40</v>
       </c>
-      <c r="B74" s="161"/>
+      <c r="B74" s="148"/>
       <c r="C74" s="73" t="s">
         <v>91</v>
       </c>
-      <c r="D74" s="174"/>
+      <c r="D74" s="151"/>
       <c r="E74" s="39">
         <v>137000</v>
       </c>
-      <c r="F74" s="158"/>
+      <c r="F74" s="129"/>
       <c r="G74" s="13"/>
     </row>
     <row r="75" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
@@ -4019,15 +4019,15 @@
         <f>IF(LEN(C75)=0,"",COUNTA($C$34:C75))</f>
         <v>41</v>
       </c>
-      <c r="B75" s="162"/>
+      <c r="B75" s="149"/>
       <c r="C75" s="73" t="s">
         <v>92</v>
       </c>
-      <c r="D75" s="175"/>
+      <c r="D75" s="152"/>
       <c r="E75" s="39">
         <v>208000</v>
       </c>
-      <c r="F75" s="159"/>
+      <c r="F75" s="130"/>
       <c r="G75" s="13"/>
     </row>
     <row r="76" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
@@ -4035,13 +4035,13 @@
         <f>IF(LEN(C76)=0,"",COUNTA($C$34:C76))</f>
         <v>42</v>
       </c>
-      <c r="B76" s="160" t="s">
+      <c r="B76" s="147" t="s">
         <v>397</v>
       </c>
       <c r="C76" s="73" t="s">
         <v>398</v>
       </c>
-      <c r="D76" s="163" t="s">
+      <c r="D76" s="154" t="s">
         <v>400</v>
       </c>
       <c r="E76" s="39">
@@ -4055,11 +4055,11 @@
         <f>IF(LEN(C77)=0,"",COUNTA($C$34:C77))</f>
         <v>43</v>
       </c>
-      <c r="B77" s="161"/>
+      <c r="B77" s="148"/>
       <c r="C77" s="73" t="s">
         <v>399</v>
       </c>
-      <c r="D77" s="164"/>
+      <c r="D77" s="155"/>
       <c r="E77" s="39">
         <v>323000</v>
       </c>
@@ -4071,7 +4071,7 @@
         <f>IF(LEN(C78)=0,"",COUNTA($C$34:C78))</f>
         <v>44</v>
       </c>
-      <c r="B78" s="161"/>
+      <c r="B78" s="148"/>
       <c r="C78" s="73" t="s">
         <v>402</v>
       </c>
@@ -4084,12 +4084,12 @@
       <c r="F78" s="104"/>
       <c r="G78" s="13"/>
     </row>
-    <row r="79" spans="1:7" s="14" customFormat="1" ht="82.5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" s="14" customFormat="1" ht="66" x14ac:dyDescent="0.25">
       <c r="A79" s="37">
         <f>IF(LEN(C79)=0,"",COUNTA($C$34:C79))</f>
         <v>45</v>
       </c>
-      <c r="B79" s="162"/>
+      <c r="B79" s="149"/>
       <c r="C79" s="73" t="s">
         <v>403</v>
       </c>
@@ -4103,12 +4103,12 @@
       <c r="G79" s="13"/>
     </row>
     <row r="80" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A80" s="170" t="s">
+      <c r="A80" s="131" t="s">
         <v>207</v>
       </c>
-      <c r="B80" s="171"/>
-      <c r="C80" s="171"/>
-      <c r="D80" s="172"/>
+      <c r="B80" s="132"/>
+      <c r="C80" s="132"/>
+      <c r="D80" s="133"/>
       <c r="E80" s="66"/>
       <c r="F80" s="67"/>
       <c r="G80" s="13"/>
@@ -4118,7 +4118,7 @@
         <f>IF(LEN(C81)=0,"",COUNTA($C$34:C81))</f>
         <v>46</v>
       </c>
-      <c r="B81" s="156" t="s">
+      <c r="B81" s="153" t="s">
         <v>97</v>
       </c>
       <c r="C81" s="35" t="s">
@@ -4138,7 +4138,7 @@
         <f>IF(LEN(C82)=0,"",COUNTA($C$34:C82))</f>
         <v>47</v>
       </c>
-      <c r="B82" s="156"/>
+      <c r="B82" s="153"/>
       <c r="C82" s="35" t="s">
         <v>100</v>
       </c>
@@ -4156,7 +4156,7 @@
         <f>IF(LEN(C83)=0,"",COUNTA($C$34:C83))</f>
         <v>48</v>
       </c>
-      <c r="B83" s="156"/>
+      <c r="B83" s="153"/>
       <c r="C83" s="35" t="s">
         <v>102</v>
       </c>
@@ -4176,7 +4176,7 @@
         <f>IF(LEN(C84)=0,"",COUNTA($C$34:C84))</f>
         <v>49</v>
       </c>
-      <c r="B84" s="156"/>
+      <c r="B84" s="153"/>
       <c r="C84" s="35" t="s">
         <v>105</v>
       </c>
@@ -4196,7 +4196,7 @@
         <f>IF(LEN(C85)=0,"",COUNTA($C$34:C85))</f>
         <v>50</v>
       </c>
-      <c r="B85" s="156"/>
+      <c r="B85" s="153"/>
       <c r="C85" s="35" t="s">
         <v>405</v>
       </c>
@@ -4214,7 +4214,7 @@
         <f>IF(LEN(C86)=0,"",COUNTA($C$34:C86))</f>
         <v>51</v>
       </c>
-      <c r="B86" s="156"/>
+      <c r="B86" s="153"/>
       <c r="C86" s="35" t="s">
         <v>107</v>
       </c>
@@ -4234,7 +4234,7 @@
         <f>IF(LEN(C87)=0,"",COUNTA($C$34:C87))</f>
         <v>52</v>
       </c>
-      <c r="B87" s="156"/>
+      <c r="B87" s="153"/>
       <c r="C87" s="35" t="s">
         <v>110</v>
       </c>
@@ -4254,7 +4254,7 @@
         <f>IF(LEN(C88)=0,"",COUNTA($C$34:C88))</f>
         <v>53</v>
       </c>
-      <c r="B88" s="156"/>
+      <c r="B88" s="153"/>
       <c r="C88" s="35" t="s">
         <v>113</v>
       </c>
@@ -4274,7 +4274,7 @@
         <f>IF(LEN(C89)=0,"",COUNTA($C$34:C89))</f>
         <v>54</v>
       </c>
-      <c r="B89" s="156" t="s">
+      <c r="B89" s="153" t="s">
         <v>116</v>
       </c>
       <c r="C89" s="35" t="s">
@@ -4294,7 +4294,7 @@
         <f>IF(LEN(C90)=0,"",COUNTA($C$34:C90))</f>
         <v>55</v>
       </c>
-      <c r="B90" s="156"/>
+      <c r="B90" s="153"/>
       <c r="C90" s="35" t="s">
         <v>119</v>
       </c>
@@ -4312,7 +4312,7 @@
         <f>IF(LEN(C91)=0,"",COUNTA($C$34:C91))</f>
         <v>56</v>
       </c>
-      <c r="B91" s="165" t="s">
+      <c r="B91" s="137" t="s">
         <v>121</v>
       </c>
       <c r="C91" s="35" t="s">
@@ -4332,7 +4332,7 @@
         <f>IF(LEN(C92)=0,"",COUNTA($C$34:C92))</f>
         <v>57</v>
       </c>
-      <c r="B92" s="176"/>
+      <c r="B92" s="139"/>
       <c r="C92" s="35" t="s">
         <v>388</v>
       </c>
@@ -4350,7 +4350,7 @@
         <f>IF(LEN(C93)=0,"",COUNTA($C$34:C93))</f>
         <v>58</v>
       </c>
-      <c r="B93" s="166"/>
+      <c r="B93" s="138"/>
       <c r="C93" s="35" t="s">
         <v>125</v>
       </c>
@@ -4364,12 +4364,12 @@
       <c r="G93" s="12"/>
     </row>
     <row r="94" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A94" s="170" t="s">
+      <c r="A94" s="131" t="s">
         <v>261</v>
       </c>
-      <c r="B94" s="171"/>
-      <c r="C94" s="171"/>
-      <c r="D94" s="172"/>
+      <c r="B94" s="132"/>
+      <c r="C94" s="132"/>
+      <c r="D94" s="133"/>
       <c r="E94" s="77"/>
       <c r="F94" s="67"/>
       <c r="G94" s="12"/>
@@ -4379,7 +4379,7 @@
         <f>IF(LEN(C95)=0,"",COUNTA($C$34:C95))</f>
         <v>59</v>
       </c>
-      <c r="B95" s="139" t="s">
+      <c r="B95" s="143" t="s">
         <v>240</v>
       </c>
       <c r="C95" s="35" t="s">
@@ -4399,7 +4399,7 @@
         <f>IF(LEN(C96)=0,"",COUNTA($C$34:C96))</f>
         <v>60</v>
       </c>
-      <c r="B96" s="141"/>
+      <c r="B96" s="145"/>
       <c r="C96" s="35" t="s">
         <v>239</v>
       </c>
@@ -4417,7 +4417,7 @@
         <f>IF(LEN(C97)=0,"",COUNTA($C$34:C97))</f>
         <v>61</v>
       </c>
-      <c r="B97" s="165" t="s">
+      <c r="B97" s="137" t="s">
         <v>243</v>
       </c>
       <c r="C97" s="35" t="s">
@@ -4435,7 +4435,7 @@
         <f>IF(LEN(C98)=0,"",COUNTA($C$34:C98))</f>
         <v>62</v>
       </c>
-      <c r="B98" s="166"/>
+      <c r="B98" s="138"/>
       <c r="C98" s="35" t="s">
         <v>242</v>
       </c>
@@ -4471,7 +4471,7 @@
         <f>IF(LEN(C100)=0,"",COUNTA($C$34:C100))</f>
         <v>64</v>
       </c>
-      <c r="B100" s="165" t="s">
+      <c r="B100" s="137" t="s">
         <v>258</v>
       </c>
       <c r="C100" s="35" t="s">
@@ -4489,7 +4489,7 @@
         <f>IF(LEN(C101)=0,"",COUNTA($C$34:C101))</f>
         <v>65</v>
       </c>
-      <c r="B101" s="176"/>
+      <c r="B101" s="139"/>
       <c r="C101" s="35" t="s">
         <v>245</v>
       </c>
@@ -4505,7 +4505,7 @@
         <f>IF(LEN(C102)=0,"",COUNTA($C$34:C102))</f>
         <v>66</v>
       </c>
-      <c r="B102" s="176"/>
+      <c r="B102" s="139"/>
       <c r="C102" s="35" t="s">
         <v>246</v>
       </c>
@@ -4521,7 +4521,7 @@
         <f>IF(LEN(C103)=0,"",COUNTA($C$34:C103))</f>
         <v>67</v>
       </c>
-      <c r="B103" s="176"/>
+      <c r="B103" s="139"/>
       <c r="C103" s="35" t="s">
         <v>247</v>
       </c>
@@ -4537,7 +4537,7 @@
         <f>IF(LEN(C104)=0,"",COUNTA($C$34:C104))</f>
         <v>68</v>
       </c>
-      <c r="B104" s="176"/>
+      <c r="B104" s="139"/>
       <c r="C104" s="35" t="s">
         <v>248</v>
       </c>
@@ -4553,7 +4553,7 @@
         <f>IF(LEN(C105)=0,"",COUNTA($C$34:C105))</f>
         <v>69</v>
       </c>
-      <c r="B105" s="176"/>
+      <c r="B105" s="139"/>
       <c r="C105" s="35" t="s">
         <v>249</v>
       </c>
@@ -4569,7 +4569,7 @@
         <f>IF(LEN(C106)=0,"",COUNTA($C$34:C106))</f>
         <v>70</v>
       </c>
-      <c r="B106" s="176"/>
+      <c r="B106" s="139"/>
       <c r="C106" s="35" t="s">
         <v>250</v>
       </c>
@@ -4585,7 +4585,7 @@
         <f>IF(LEN(C107)=0,"",COUNTA($C$34:C107))</f>
         <v>71</v>
       </c>
-      <c r="B107" s="176"/>
+      <c r="B107" s="139"/>
       <c r="C107" s="35" t="s">
         <v>251</v>
       </c>
@@ -4601,7 +4601,7 @@
         <f>IF(LEN(C108)=0,"",COUNTA($C$34:C108))</f>
         <v>72</v>
       </c>
-      <c r="B108" s="176"/>
+      <c r="B108" s="139"/>
       <c r="C108" s="35" t="s">
         <v>252</v>
       </c>
@@ -4617,7 +4617,7 @@
         <f>IF(LEN(C109)=0,"",COUNTA($C$34:C109))</f>
         <v>73</v>
       </c>
-      <c r="B109" s="176"/>
+      <c r="B109" s="139"/>
       <c r="C109" s="35" t="s">
         <v>253</v>
       </c>
@@ -4633,7 +4633,7 @@
         <f>IF(LEN(C110)=0,"",COUNTA($C$34:C110))</f>
         <v>74</v>
       </c>
-      <c r="B110" s="176"/>
+      <c r="B110" s="139"/>
       <c r="C110" s="35" t="s">
         <v>254</v>
       </c>
@@ -4649,7 +4649,7 @@
         <f>IF(LEN(C111)=0,"",COUNTA($C$34:C111))</f>
         <v>75</v>
       </c>
-      <c r="B111" s="176"/>
+      <c r="B111" s="139"/>
       <c r="C111" s="35" t="s">
         <v>255</v>
       </c>
@@ -4665,7 +4665,7 @@
         <f>IF(LEN(C112)=0,"",COUNTA($C$34:C112))</f>
         <v>76</v>
       </c>
-      <c r="B112" s="176"/>
+      <c r="B112" s="139"/>
       <c r="C112" s="35" t="s">
         <v>256</v>
       </c>
@@ -4681,7 +4681,7 @@
         <f>IF(LEN(C113)=0,"",COUNTA($C$34:C113))</f>
         <v>77</v>
       </c>
-      <c r="B113" s="166"/>
+      <c r="B113" s="138"/>
       <c r="C113" s="35" t="s">
         <v>257</v>
       </c>
@@ -4693,12 +4693,12 @@
       <c r="G113" s="12"/>
     </row>
     <row r="114" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="170" t="s">
+      <c r="A114" s="131" t="s">
         <v>226</v>
       </c>
-      <c r="B114" s="171"/>
-      <c r="C114" s="171"/>
-      <c r="D114" s="172"/>
+      <c r="B114" s="132"/>
+      <c r="C114" s="132"/>
+      <c r="D114" s="133"/>
       <c r="E114" s="66"/>
       <c r="F114" s="67"/>
       <c r="G114" s="12"/>
@@ -4744,12 +4744,12 @@
       <c r="G116" s="12"/>
     </row>
     <row r="117" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A117" s="177" t="s">
+      <c r="A117" s="127" t="s">
         <v>262</v>
       </c>
-      <c r="B117" s="177"/>
-      <c r="C117" s="177"/>
-      <c r="D117" s="177"/>
+      <c r="B117" s="127"/>
+      <c r="C117" s="127"/>
+      <c r="D117" s="127"/>
       <c r="E117" s="77"/>
       <c r="F117" s="67"/>
       <c r="G117" s="12"/>
@@ -4759,7 +4759,7 @@
         <f>IF(LEN(C118)=0,"",COUNTA($C$34:C118))</f>
         <v>80</v>
       </c>
-      <c r="B118" s="178" t="s">
+      <c r="B118" s="140" t="s">
         <v>204</v>
       </c>
       <c r="C118" s="36" t="s">
@@ -4779,7 +4779,7 @@
         <f>IF(LEN(C119)=0,"",COUNTA($C$34:C119))</f>
         <v>81</v>
       </c>
-      <c r="B119" s="179"/>
+      <c r="B119" s="141"/>
       <c r="C119" s="36" t="s">
         <v>34</v>
       </c>
@@ -4797,7 +4797,7 @@
         <f>IF(LEN(C120)=0,"",COUNTA($C$34:C120))</f>
         <v>82</v>
       </c>
-      <c r="B120" s="179"/>
+      <c r="B120" s="141"/>
       <c r="C120" s="36" t="s">
         <v>324</v>
       </c>
@@ -4815,7 +4815,7 @@
         <f>IF(LEN(C121)=0,"",COUNTA($C$34:C121))</f>
         <v>83</v>
       </c>
-      <c r="B121" s="179"/>
+      <c r="B121" s="141"/>
       <c r="C121" s="35" t="s">
         <v>407</v>
       </c>
@@ -4831,7 +4831,7 @@
         <f>IF(LEN(C122)=0,"",COUNTA($C$34:C122))</f>
         <v>84</v>
       </c>
-      <c r="B122" s="179"/>
+      <c r="B122" s="141"/>
       <c r="C122" s="35" t="s">
         <v>408</v>
       </c>
@@ -4847,7 +4847,7 @@
         <f>IF(LEN(C123)=0,"",COUNTA($C$34:C123))</f>
         <v>85</v>
       </c>
-      <c r="B123" s="179"/>
+      <c r="B123" s="141"/>
       <c r="C123" s="35" t="s">
         <v>409</v>
       </c>
@@ -4863,7 +4863,7 @@
         <f>IF(LEN(C124)=0,"",COUNTA($C$34:C124))</f>
         <v>86</v>
       </c>
-      <c r="B124" s="179"/>
+      <c r="B124" s="141"/>
       <c r="C124" s="36" t="s">
         <v>410</v>
       </c>
@@ -4881,7 +4881,7 @@
         <f>IF(LEN(C125)=0,"",COUNTA($C$34:C125))</f>
         <v>87</v>
       </c>
-      <c r="B125" s="179"/>
+      <c r="B125" s="141"/>
       <c r="C125" s="36" t="s">
         <v>138</v>
       </c>
@@ -4899,7 +4899,7 @@
         <f>IF(LEN(C126)=0,"",COUNTA($C$34:C126))</f>
         <v>88</v>
       </c>
-      <c r="B126" s="180"/>
+      <c r="B126" s="142"/>
       <c r="C126" s="36" t="s">
         <v>139</v>
       </c>
@@ -4917,7 +4917,7 @@
         <f>IF(LEN(C127)=0,"",COUNTA($C$34:C127))</f>
         <v>89</v>
       </c>
-      <c r="B127" s="139" t="s">
+      <c r="B127" s="143" t="s">
         <v>282</v>
       </c>
       <c r="C127" s="35" t="s">
@@ -4937,7 +4937,7 @@
         <f>IF(LEN(C128)=0,"",COUNTA($C$34:C128))</f>
         <v>90</v>
       </c>
-      <c r="B128" s="140"/>
+      <c r="B128" s="144"/>
       <c r="C128" s="35" t="s">
         <v>143</v>
       </c>
@@ -4955,7 +4955,7 @@
         <f>IF(LEN(C129)=0,"",COUNTA($C$34:C129))</f>
         <v>91</v>
       </c>
-      <c r="B129" s="140"/>
+      <c r="B129" s="144"/>
       <c r="C129" s="35" t="s">
         <v>392</v>
       </c>
@@ -4973,7 +4973,7 @@
         <f>IF(LEN(C130)=0,"",COUNTA($C$34:C130))</f>
         <v>92</v>
       </c>
-      <c r="B130" s="140"/>
+      <c r="B130" s="144"/>
       <c r="C130" s="35" t="s">
         <v>394</v>
       </c>
@@ -4991,7 +4991,7 @@
         <f>IF(LEN(C131)=0,"",COUNTA($C$34:C131))</f>
         <v>93</v>
       </c>
-      <c r="B131" s="140"/>
+      <c r="B131" s="144"/>
       <c r="C131" s="35" t="s">
         <v>369</v>
       </c>
@@ -5009,7 +5009,7 @@
         <f>IF(LEN(C132)=0,"",COUNTA($C$34:C132))</f>
         <v>94</v>
       </c>
-      <c r="B132" s="141"/>
+      <c r="B132" s="145"/>
       <c r="C132" s="35" t="s">
         <v>145</v>
       </c>
@@ -5025,7 +5025,7 @@
         <f>IF(LEN(C133)=0,"",COUNTA($C$34:C133))</f>
         <v>95</v>
       </c>
-      <c r="B133" s="140" t="s">
+      <c r="B133" s="144" t="s">
         <v>283</v>
       </c>
       <c r="C133" s="35" t="s">
@@ -5043,7 +5043,7 @@
         <f>IF(LEN(C134)=0,"",COUNTA($C$34:C134))</f>
         <v>96</v>
       </c>
-      <c r="B134" s="140"/>
+      <c r="B134" s="144"/>
       <c r="C134" s="35" t="s">
         <v>330</v>
       </c>
@@ -5061,7 +5061,7 @@
         <f>IF(LEN(C135)=0,"",COUNTA($C$34:C135))</f>
         <v>97</v>
       </c>
-      <c r="B135" s="140"/>
+      <c r="B135" s="144"/>
       <c r="C135" s="35" t="s">
         <v>151</v>
       </c>
@@ -5079,7 +5079,7 @@
         <f>IF(LEN(C136)=0,"",COUNTA($C$34:C136))</f>
         <v>98</v>
       </c>
-      <c r="B136" s="140"/>
+      <c r="B136" s="144"/>
       <c r="C136" s="35" t="s">
         <v>153</v>
       </c>
@@ -5097,7 +5097,7 @@
         <f>IF(LEN(C137)=0,"",COUNTA($C$34:C137))</f>
         <v>99</v>
       </c>
-      <c r="B137" s="140"/>
+      <c r="B137" s="144"/>
       <c r="C137" s="35" t="s">
         <v>155</v>
       </c>
@@ -5115,7 +5115,7 @@
         <f>IF(LEN(C138)=0,"",COUNTA($C$34:C138))</f>
         <v>100</v>
       </c>
-      <c r="B138" s="140"/>
+      <c r="B138" s="144"/>
       <c r="C138" s="35" t="s">
         <v>157</v>
       </c>
@@ -5133,7 +5133,7 @@
         <f>IF(LEN(C139)=0,"",COUNTA($C$34:C139))</f>
         <v>101</v>
       </c>
-      <c r="B139" s="140"/>
+      <c r="B139" s="144"/>
       <c r="C139" s="35" t="s">
         <v>158</v>
       </c>
@@ -5149,7 +5149,7 @@
         <f>IF(LEN(C140)=0,"",COUNTA($C$34:C140))</f>
         <v>102</v>
       </c>
-      <c r="B140" s="151" t="s">
+      <c r="B140" s="146" t="s">
         <v>304</v>
       </c>
       <c r="C140" s="35" t="s">
@@ -5171,7 +5171,7 @@
         <f>IF(LEN(C141)=0,"",COUNTA($C$34:C141))</f>
         <v>103</v>
       </c>
-      <c r="B141" s="151"/>
+      <c r="B141" s="146"/>
       <c r="C141" s="35" t="s">
         <v>342</v>
       </c>
@@ -5189,7 +5189,7 @@
         <f>IF(LEN(C142)=0,"",COUNTA($C$34:C142))</f>
         <v>104</v>
       </c>
-      <c r="B142" s="151"/>
+      <c r="B142" s="146"/>
       <c r="C142" s="35" t="s">
         <v>343</v>
       </c>
@@ -5209,7 +5209,7 @@
         <f>IF(LEN(C143)=0,"",COUNTA($C$34:C143))</f>
         <v>105</v>
       </c>
-      <c r="B143" s="151"/>
+      <c r="B143" s="146"/>
       <c r="C143" s="35" t="s">
         <v>344</v>
       </c>
@@ -5227,7 +5227,7 @@
         <f>IF(LEN(C144)=0,"",COUNTA($C$34:C144))</f>
         <v>106</v>
       </c>
-      <c r="B144" s="151"/>
+      <c r="B144" s="146"/>
       <c r="C144" s="35" t="s">
         <v>345</v>
       </c>
@@ -5245,7 +5245,7 @@
         <f>IF(LEN(C145)=0,"",COUNTA($C$34:C145))</f>
         <v>107</v>
       </c>
-      <c r="B145" s="151"/>
+      <c r="B145" s="146"/>
       <c r="C145" s="107" t="s">
         <v>372</v>
       </c>
@@ -5263,7 +5263,7 @@
         <f>IF(LEN(C146)=0,"",COUNTA($C$34:C146))</f>
         <v>108</v>
       </c>
-      <c r="B146" s="151"/>
+      <c r="B146" s="146"/>
       <c r="C146" s="35" t="s">
         <v>346</v>
       </c>
@@ -5281,7 +5281,7 @@
         <f>IF(LEN(C147)=0,"",COUNTA($C$34:C147))</f>
         <v>109</v>
       </c>
-      <c r="B147" s="151"/>
+      <c r="B147" s="146"/>
       <c r="C147" s="35" t="s">
         <v>347</v>
       </c>
@@ -5299,7 +5299,7 @@
         <f>IF(LEN(C148)=0,"",COUNTA($C$34:C148))</f>
         <v>110</v>
       </c>
-      <c r="B148" s="151"/>
+      <c r="B148" s="146"/>
       <c r="C148" s="35" t="s">
         <v>348</v>
       </c>
@@ -5317,7 +5317,7 @@
         <f>IF(LEN(C149)=0,"",COUNTA($C$34:C149))</f>
         <v>111</v>
       </c>
-      <c r="B149" s="151"/>
+      <c r="B149" s="146"/>
       <c r="C149" s="107" t="s">
         <v>371</v>
       </c>
@@ -5335,7 +5335,7 @@
         <f>IF(LEN(C150)=0,"",COUNTA($C$34:C150))</f>
         <v>112</v>
       </c>
-      <c r="B150" s="151"/>
+      <c r="B150" s="146"/>
       <c r="C150" s="35" t="s">
         <v>349</v>
       </c>
@@ -5355,7 +5355,7 @@
         <f>IF(LEN(C151)=0,"",COUNTA($C$34:C151))</f>
         <v>113</v>
       </c>
-      <c r="B151" s="151"/>
+      <c r="B151" s="146"/>
       <c r="C151" s="35" t="s">
         <v>350</v>
       </c>
@@ -5373,7 +5373,7 @@
         <f>IF(LEN(C152)=0,"",COUNTA($C$34:C152))</f>
         <v>114</v>
       </c>
-      <c r="B152" s="151"/>
+      <c r="B152" s="146"/>
       <c r="C152" s="35" t="s">
         <v>351</v>
       </c>
@@ -5391,7 +5391,7 @@
         <f>IF(LEN(C153)=0,"",COUNTA($C$34:C153))</f>
         <v>115</v>
       </c>
-      <c r="B153" s="151"/>
+      <c r="B153" s="146"/>
       <c r="C153" s="35" t="s">
         <v>352</v>
       </c>
@@ -5409,7 +5409,7 @@
         <f>IF(LEN(C154)=0,"",COUNTA($C$34:C154))</f>
         <v>116</v>
       </c>
-      <c r="B154" s="151"/>
+      <c r="B154" s="146"/>
       <c r="C154" s="35" t="s">
         <v>353</v>
       </c>
@@ -5427,7 +5427,7 @@
         <f>IF(LEN(C155)=0,"",COUNTA($C$34:C155))</f>
         <v>117</v>
       </c>
-      <c r="B155" s="151"/>
+      <c r="B155" s="146"/>
       <c r="C155" s="35" t="s">
         <v>354</v>
       </c>
@@ -5445,7 +5445,7 @@
         <f>IF(LEN(C156)=0,"",COUNTA($C$34:C156))</f>
         <v>118</v>
       </c>
-      <c r="B156" s="151"/>
+      <c r="B156" s="146"/>
       <c r="C156" s="35" t="s">
         <v>355</v>
       </c>
@@ -5463,7 +5463,7 @@
         <f>IF(LEN(C157)=0,"",COUNTA($C$34:C157))</f>
         <v>119</v>
       </c>
-      <c r="B157" s="151"/>
+      <c r="B157" s="146"/>
       <c r="C157" s="35" t="s">
         <v>356</v>
       </c>
@@ -5481,7 +5481,7 @@
         <f>IF(LEN(C158)=0,"",COUNTA($C$34:C158))</f>
         <v>120</v>
       </c>
-      <c r="B158" s="151"/>
+      <c r="B158" s="146"/>
       <c r="C158" s="35" t="s">
         <v>357</v>
       </c>
@@ -5499,7 +5499,7 @@
         <f>IF(LEN(C159)=0,"",COUNTA($C$34:C159))</f>
         <v>121</v>
       </c>
-      <c r="B159" s="151"/>
+      <c r="B159" s="146"/>
       <c r="C159" s="35" t="s">
         <v>358</v>
       </c>
@@ -5517,7 +5517,7 @@
         <f>IF(LEN(C160)=0,"",COUNTA($C$34:C160))</f>
         <v>122</v>
       </c>
-      <c r="B160" s="151"/>
+      <c r="B160" s="146"/>
       <c r="C160" s="35" t="s">
         <v>359</v>
       </c>
@@ -5535,7 +5535,7 @@
         <f>IF(LEN(C161)=0,"",COUNTA($C$34:C161))</f>
         <v>123</v>
       </c>
-      <c r="B161" s="151"/>
+      <c r="B161" s="146"/>
       <c r="C161" s="35" t="s">
         <v>360</v>
       </c>
@@ -5553,7 +5553,7 @@
         <f>IF(LEN(C162)=0,"",COUNTA($C$34:C162))</f>
         <v>124</v>
       </c>
-      <c r="B162" s="151"/>
+      <c r="B162" s="146"/>
       <c r="C162" s="35" t="s">
         <v>361</v>
       </c>
@@ -5571,7 +5571,7 @@
         <f>IF(LEN(C163)=0,"",COUNTA($C$34:C163))</f>
         <v>125</v>
       </c>
-      <c r="B163" s="151"/>
+      <c r="B163" s="146"/>
       <c r="C163" s="35" t="s">
         <v>362</v>
       </c>
@@ -5589,7 +5589,7 @@
         <f>IF(LEN(C164)=0,"",COUNTA($C$34:C164))</f>
         <v>126</v>
       </c>
-      <c r="B164" s="151"/>
+      <c r="B164" s="146"/>
       <c r="C164" s="35" t="s">
         <v>363</v>
       </c>
@@ -5605,7 +5605,7 @@
         <f>IF(LEN(C165)=0,"",COUNTA($C$34:C165))</f>
         <v>127</v>
       </c>
-      <c r="B165" s="151"/>
+      <c r="B165" s="146"/>
       <c r="C165" s="35" t="s">
         <v>364</v>
       </c>
@@ -5621,7 +5621,7 @@
         <f>IF(LEN(C166)=0,"",COUNTA($C$34:C166))</f>
         <v>128</v>
       </c>
-      <c r="B166" s="151"/>
+      <c r="B166" s="146"/>
       <c r="C166" s="35" t="s">
         <v>365</v>
       </c>
@@ -5639,7 +5639,7 @@
         <f>IF(LEN(C167)=0,"",COUNTA($C$34:C167))</f>
         <v>129</v>
       </c>
-      <c r="B167" s="151"/>
+      <c r="B167" s="146"/>
       <c r="C167" s="35" t="s">
         <v>366</v>
       </c>
@@ -5657,7 +5657,7 @@
         <f>IF(LEN(C168)=0,"",COUNTA($C$34:C168))</f>
         <v>130</v>
       </c>
-      <c r="B168" s="151"/>
+      <c r="B168" s="146"/>
       <c r="C168" s="35" t="s">
         <v>367</v>
       </c>
@@ -5675,7 +5675,7 @@
         <f>IF(LEN(C169)=0,"",COUNTA($C$34:C169))</f>
         <v>131</v>
       </c>
-      <c r="B169" s="151"/>
+      <c r="B169" s="146"/>
       <c r="C169" s="35" t="s">
         <v>368</v>
       </c>
@@ -5689,12 +5689,12 @@
       <c r="G169" s="12"/>
     </row>
     <row r="170" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A170" s="177" t="s">
+      <c r="A170" s="127" t="s">
         <v>206</v>
       </c>
-      <c r="B170" s="177"/>
-      <c r="C170" s="177"/>
-      <c r="D170" s="177"/>
+      <c r="B170" s="127"/>
+      <c r="C170" s="127"/>
+      <c r="D170" s="127"/>
       <c r="E170" s="77"/>
       <c r="F170" s="67"/>
       <c r="G170" s="12"/>
@@ -5759,7 +5759,7 @@
         <f>IF(LEN(C174)=0,"",COUNTA($C$34:C174))</f>
         <v>135</v>
       </c>
-      <c r="B174" s="139" t="s">
+      <c r="B174" s="143" t="s">
         <v>203</v>
       </c>
       <c r="C174" s="35" t="s">
@@ -5778,7 +5778,7 @@
         <f>IF(LEN(C175)=0,"",COUNTA($C$34:C175))</f>
         <v>136</v>
       </c>
-      <c r="B175" s="141"/>
+      <c r="B175" s="145"/>
       <c r="C175" s="35" t="s">
         <v>224</v>
       </c>
@@ -5791,12 +5791,12 @@
       <c r="F175" s="40"/>
     </row>
     <row r="176" spans="1:8" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A176" s="170" t="s">
+      <c r="A176" s="131" t="s">
         <v>163</v>
       </c>
-      <c r="B176" s="171"/>
-      <c r="C176" s="171"/>
-      <c r="D176" s="172"/>
+      <c r="B176" s="132"/>
+      <c r="C176" s="132"/>
+      <c r="D176" s="133"/>
       <c r="E176" s="120"/>
       <c r="F176" s="62"/>
     </row>
@@ -5815,7 +5815,7 @@
       <c r="E177" s="83">
         <v>71000</v>
       </c>
-      <c r="F177" s="182" t="s">
+      <c r="F177" s="125" t="s">
         <v>383</v>
       </c>
     </row>
@@ -5834,15 +5834,15 @@
       <c r="E178" s="83">
         <v>86000</v>
       </c>
-      <c r="F178" s="183"/>
+      <c r="F178" s="126"/>
     </row>
     <row r="179" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A179" s="177" t="s">
+      <c r="A179" s="127" t="s">
         <v>168</v>
       </c>
-      <c r="B179" s="177"/>
-      <c r="C179" s="177"/>
-      <c r="D179" s="177"/>
+      <c r="B179" s="127"/>
+      <c r="C179" s="127"/>
+      <c r="D179" s="127"/>
       <c r="E179" s="77"/>
       <c r="F179" s="67"/>
       <c r="G179" s="12"/>
@@ -5862,7 +5862,7 @@
       <c r="E180" s="106">
         <v>1968000</v>
       </c>
-      <c r="F180" s="157" t="s">
+      <c r="F180" s="128" t="s">
         <v>325</v>
       </c>
       <c r="G180" s="12"/>
@@ -5882,7 +5882,7 @@
       <c r="E181" s="106">
         <v>2952000</v>
       </c>
-      <c r="F181" s="158"/>
+      <c r="F181" s="129"/>
       <c r="G181" s="12"/>
     </row>
     <row r="182" spans="1:7" ht="66" x14ac:dyDescent="0.25">
@@ -5900,7 +5900,7 @@
       <c r="E182" s="106">
         <v>4100000</v>
       </c>
-      <c r="F182" s="159"/>
+      <c r="F182" s="130"/>
       <c r="G182" s="12"/>
     </row>
     <row r="183" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
@@ -5996,12 +5996,12 @@
       <c r="G187" s="12"/>
     </row>
     <row r="188" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A188" s="177" t="s">
+      <c r="A188" s="127" t="s">
         <v>263</v>
       </c>
-      <c r="B188" s="177"/>
-      <c r="C188" s="177"/>
-      <c r="D188" s="177"/>
+      <c r="B188" s="127"/>
+      <c r="C188" s="127"/>
+      <c r="D188" s="127"/>
       <c r="E188" s="77"/>
       <c r="F188" s="67"/>
       <c r="G188" s="12"/>
@@ -6025,12 +6025,12 @@
       <c r="G189" s="12"/>
     </row>
     <row r="190" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A190" s="177" t="s">
+      <c r="A190" s="127" t="s">
         <v>233</v>
       </c>
-      <c r="B190" s="177"/>
-      <c r="C190" s="177"/>
-      <c r="D190" s="177"/>
+      <c r="B190" s="127"/>
+      <c r="C190" s="127"/>
+      <c r="D190" s="127"/>
       <c r="E190" s="77"/>
       <c r="F190" s="67"/>
       <c r="G190" s="12"/>
@@ -6216,12 +6216,12 @@
       <c r="G200" s="12"/>
     </row>
     <row r="201" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A201" s="170" t="s">
+      <c r="A201" s="131" t="s">
         <v>322</v>
       </c>
-      <c r="B201" s="171"/>
-      <c r="C201" s="171"/>
-      <c r="D201" s="172"/>
+      <c r="B201" s="132"/>
+      <c r="C201" s="132"/>
+      <c r="D201" s="133"/>
       <c r="E201" s="66"/>
       <c r="F201" s="67"/>
       <c r="G201" s="12"/>
@@ -6315,12 +6315,12 @@
       <c r="G206" s="12"/>
     </row>
     <row r="207" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A207" s="170" t="s">
+      <c r="A207" s="131" t="s">
         <v>221</v>
       </c>
-      <c r="B207" s="171"/>
-      <c r="C207" s="171"/>
-      <c r="D207" s="172"/>
+      <c r="B207" s="132"/>
+      <c r="C207" s="132"/>
+      <c r="D207" s="133"/>
       <c r="E207" s="66"/>
       <c r="F207" s="67"/>
       <c r="G207" s="12"/>
@@ -6380,12 +6380,12 @@
       <c r="G210" s="12"/>
     </row>
     <row r="211" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A211" s="170" t="s">
+      <c r="A211" s="131" t="s">
         <v>210</v>
       </c>
-      <c r="B211" s="171"/>
-      <c r="C211" s="171"/>
-      <c r="D211" s="172"/>
+      <c r="B211" s="132"/>
+      <c r="C211" s="132"/>
+      <c r="D211" s="133"/>
       <c r="E211" s="66"/>
       <c r="F211" s="67"/>
       <c r="G211" s="12"/>
@@ -6400,7 +6400,7 @@
         <v>211</v>
       </c>
       <c r="D212" s="35"/>
-      <c r="E212" s="145">
+      <c r="E212" s="134">
         <v>183000</v>
       </c>
       <c r="F212" s="40"/>
@@ -6416,7 +6416,7 @@
         <v>212</v>
       </c>
       <c r="D213" s="35"/>
-      <c r="E213" s="146"/>
+      <c r="E213" s="135"/>
       <c r="F213" s="40"/>
       <c r="G213" s="12"/>
     </row>
@@ -6430,7 +6430,7 @@
         <v>213</v>
       </c>
       <c r="D214" s="35"/>
-      <c r="E214" s="146"/>
+      <c r="E214" s="135"/>
       <c r="F214" s="40"/>
       <c r="G214" s="12"/>
     </row>
@@ -6444,17 +6444,17 @@
         <v>214</v>
       </c>
       <c r="D215" s="35"/>
-      <c r="E215" s="147"/>
+      <c r="E215" s="136"/>
       <c r="F215" s="40"/>
       <c r="G215" s="12"/>
     </row>
     <row r="216" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A216" s="170" t="s">
+      <c r="A216" s="131" t="s">
         <v>412</v>
       </c>
-      <c r="B216" s="171"/>
-      <c r="C216" s="171"/>
-      <c r="D216" s="172"/>
+      <c r="B216" s="132"/>
+      <c r="C216" s="132"/>
+      <c r="D216" s="133"/>
       <c r="E216" s="66"/>
       <c r="F216" s="67"/>
       <c r="G216" s="12"/>
@@ -6532,64 +6532,64 @@
       <c r="F221" s="93"/>
     </row>
     <row r="222" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A222" s="181" t="s">
+      <c r="A222" s="124" t="s">
         <v>27</v>
       </c>
-      <c r="B222" s="181"/>
-      <c r="C222" s="181"/>
-      <c r="D222" s="181"/>
+      <c r="B222" s="124"/>
+      <c r="C222" s="124"/>
+      <c r="D222" s="124"/>
       <c r="E222" s="26"/>
       <c r="F222" s="94"/>
     </row>
     <row r="223" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A223" s="95"/>
-      <c r="B223" s="184" t="s">
+      <c r="B223" s="122" t="s">
         <v>266</v>
       </c>
-      <c r="C223" s="184"/>
-      <c r="D223" s="184"/>
-      <c r="E223" s="184"/>
-      <c r="F223" s="184"/>
+      <c r="C223" s="122"/>
+      <c r="D223" s="122"/>
+      <c r="E223" s="122"/>
+      <c r="F223" s="122"/>
     </row>
     <row r="224" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A224" s="95"/>
-      <c r="B224" s="184" t="s">
+      <c r="B224" s="122" t="s">
         <v>417</v>
       </c>
-      <c r="C224" s="184"/>
-      <c r="D224" s="184"/>
-      <c r="E224" s="184"/>
-      <c r="F224" s="184"/>
+      <c r="C224" s="122"/>
+      <c r="D224" s="122"/>
+      <c r="E224" s="122"/>
+      <c r="F224" s="122"/>
     </row>
     <row r="225" spans="1:6" s="2" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="96"/>
-      <c r="B225" s="184" t="s">
+      <c r="B225" s="122" t="s">
         <v>28</v>
       </c>
-      <c r="C225" s="184"/>
-      <c r="D225" s="184"/>
-      <c r="E225" s="184"/>
-      <c r="F225" s="184"/>
+      <c r="C225" s="122"/>
+      <c r="D225" s="122"/>
+      <c r="E225" s="122"/>
+      <c r="F225" s="122"/>
     </row>
     <row r="226" spans="1:6" s="17" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="97"/>
-      <c r="B226" s="185" t="s">
+      <c r="B226" s="123" t="s">
         <v>29</v>
       </c>
-      <c r="C226" s="185"/>
-      <c r="D226" s="185"/>
-      <c r="E226" s="185"/>
-      <c r="F226" s="185"/>
+      <c r="C226" s="123"/>
+      <c r="D226" s="123"/>
+      <c r="E226" s="123"/>
+      <c r="F226" s="123"/>
     </row>
     <row r="227" spans="1:6" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="94"/>
-      <c r="B227" s="184" t="s">
+      <c r="B227" s="122" t="s">
         <v>30</v>
       </c>
-      <c r="C227" s="184"/>
-      <c r="D227" s="184"/>
-      <c r="E227" s="184"/>
-      <c r="F227" s="184"/>
+      <c r="C227" s="122"/>
+      <c r="D227" s="122"/>
+      <c r="E227" s="122"/>
+      <c r="F227" s="122"/>
     </row>
     <row r="228" spans="1:6" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A228" s="94"/>
@@ -6653,58 +6653,6 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="B223:F223"/>
-    <mergeCell ref="B224:F224"/>
-    <mergeCell ref="B225:F225"/>
-    <mergeCell ref="B226:F226"/>
-    <mergeCell ref="B227:F227"/>
-    <mergeCell ref="A222:D222"/>
-    <mergeCell ref="F177:F178"/>
-    <mergeCell ref="A179:D179"/>
-    <mergeCell ref="F180:F182"/>
-    <mergeCell ref="A188:D188"/>
-    <mergeCell ref="A190:D190"/>
-    <mergeCell ref="A201:D201"/>
-    <mergeCell ref="A207:D207"/>
-    <mergeCell ref="A211:D211"/>
-    <mergeCell ref="E212:E215"/>
-    <mergeCell ref="A216:D216"/>
-    <mergeCell ref="A176:D176"/>
-    <mergeCell ref="B97:B98"/>
-    <mergeCell ref="B100:B113"/>
-    <mergeCell ref="A114:D114"/>
-    <mergeCell ref="A117:D117"/>
-    <mergeCell ref="B118:B126"/>
-    <mergeCell ref="B127:B132"/>
-    <mergeCell ref="B133:B139"/>
-    <mergeCell ref="B140:B169"/>
-    <mergeCell ref="A170:D170"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="B95:B96"/>
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="B60:B72"/>
-    <mergeCell ref="B73:B75"/>
-    <mergeCell ref="D73:D75"/>
-    <mergeCell ref="A80:D80"/>
-    <mergeCell ref="B81:B88"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="B91:B93"/>
-    <mergeCell ref="A94:D94"/>
-    <mergeCell ref="F73:F75"/>
-    <mergeCell ref="B76:B79"/>
-    <mergeCell ref="D76:D77"/>
-    <mergeCell ref="B49:B52"/>
-    <mergeCell ref="F50:F52"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="F54:F55"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="F57:F58"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="B40:B44"/>
-    <mergeCell ref="F40:F44"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="F46:F48"/>
     <mergeCell ref="A28:D28"/>
     <mergeCell ref="D1:F5"/>
     <mergeCell ref="A7:F7"/>
@@ -6719,6 +6667,58 @@
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="E24:E25"/>
     <mergeCell ref="F24:F25"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="B40:B44"/>
+    <mergeCell ref="F40:F44"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="F46:F48"/>
+    <mergeCell ref="F73:F75"/>
+    <mergeCell ref="B76:B79"/>
+    <mergeCell ref="D76:D77"/>
+    <mergeCell ref="B49:B52"/>
+    <mergeCell ref="F50:F52"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="F57:F58"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="B60:B72"/>
+    <mergeCell ref="B73:B75"/>
+    <mergeCell ref="D73:D75"/>
+    <mergeCell ref="A80:D80"/>
+    <mergeCell ref="B81:B88"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="B91:B93"/>
+    <mergeCell ref="A94:D94"/>
+    <mergeCell ref="A176:D176"/>
+    <mergeCell ref="B97:B98"/>
+    <mergeCell ref="B100:B113"/>
+    <mergeCell ref="A114:D114"/>
+    <mergeCell ref="A117:D117"/>
+    <mergeCell ref="B118:B126"/>
+    <mergeCell ref="B127:B132"/>
+    <mergeCell ref="B133:B139"/>
+    <mergeCell ref="B140:B169"/>
+    <mergeCell ref="A170:D170"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="A222:D222"/>
+    <mergeCell ref="F177:F178"/>
+    <mergeCell ref="A179:D179"/>
+    <mergeCell ref="F180:F182"/>
+    <mergeCell ref="A188:D188"/>
+    <mergeCell ref="A190:D190"/>
+    <mergeCell ref="A201:D201"/>
+    <mergeCell ref="A207:D207"/>
+    <mergeCell ref="A211:D211"/>
+    <mergeCell ref="E212:E215"/>
+    <mergeCell ref="A216:D216"/>
+    <mergeCell ref="B223:F223"/>
+    <mergeCell ref="B224:F224"/>
+    <mergeCell ref="B225:F225"/>
+    <mergeCell ref="B226:F226"/>
+    <mergeCell ref="B227:F227"/>
   </mergeCells>
   <pageMargins left="0.35433070866141736" right="0.15748031496062992" top="0.23622047244094491" bottom="0.19685039370078741" header="0.15748031496062992" footer="0.15748031496062992"/>
   <pageSetup paperSize="9" scale="70" fitToHeight="0" orientation="landscape" r:id="rId1"/>

--- a/Hoàng/SALE/BÁO GIÁ KSK 2025 - THAM KHẢO.xlsx
+++ b/Hoàng/SALE/BÁO GIÁ KSK 2025 - THAM KHẢO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\SALE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C51A12-77E4-4449-80A6-112EDA9740D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C8589E-D9D8-4D5E-B8C4-6A12FFFCF1E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,8 @@
     <sheet name="BÁO GIÁ KSK" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'BÁO GIÁ KSK'!$A$1:$F$233</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'BÁO GIÁ KSK'!$32:$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'BÁO GIÁ KSK'!$A$1:$F$253</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'BÁO GIÁ KSK'!$52:$52</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="422">
   <si>
     <t>Ghi chú</t>
   </si>
@@ -1325,6 +1325,12 @@
   </si>
   <si>
     <t>. Ms Sương (TP.KD) : 0935 345 693</t>
+  </si>
+  <si>
+    <t>Tư vấn khám phụ khoa, khám vú</t>
+  </si>
+  <si>
+    <t>Ưu đãi trong gói khám</t>
   </si>
 </sst>
 </file>
@@ -1885,7 +1891,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="186">
+  <cellXfs count="189">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2193,9 +2199,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="19" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2214,204 +2217,227 @@
     <xf numFmtId="3" fontId="11" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="21" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2770,14 +2796,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46C4EFAC-5358-4031-B8BC-663929F6ADDF}">
-  <dimension ref="A1:K233"/>
+  <dimension ref="A1:K253"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.42578125" style="18" customWidth="1"/>
     <col min="3" max="3" width="53.28515625" style="9" customWidth="1"/>
     <col min="4" max="4" width="48.5703125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="19" customWidth="1"/>
+    <col min="5" max="5" width="17" style="19" customWidth="1"/>
     <col min="6" max="6" width="28.28515625" style="20" customWidth="1"/>
     <col min="7" max="7" width="19.7109375" style="9" customWidth="1"/>
     <col min="8" max="8" width="9.85546875" style="9" bestFit="1" customWidth="1"/>
@@ -2788,43 +2814,43 @@
       <c r="A1" s="22"/>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
-      <c r="D1" s="164" t="s">
+      <c r="D1" s="126" t="s">
         <v>312</v>
       </c>
-      <c r="E1" s="164"/>
-      <c r="F1" s="164"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="126"/>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="24"/>
       <c r="B2" s="24"/>
       <c r="C2" s="24"/>
-      <c r="D2" s="165"/>
-      <c r="E2" s="165"/>
-      <c r="F2" s="165"/>
+      <c r="D2" s="127"/>
+      <c r="E2" s="127"/>
+      <c r="F2" s="127"/>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A3" s="24"/>
       <c r="B3" s="24"/>
       <c r="C3" s="24"/>
-      <c r="D3" s="165"/>
-      <c r="E3" s="165"/>
-      <c r="F3" s="165"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="24"/>
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
-      <c r="D4" s="165"/>
-      <c r="E4" s="165"/>
-      <c r="F4" s="165"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="127"/>
+      <c r="F4" s="127"/>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5" s="24"/>
       <c r="B5" s="24"/>
       <c r="C5" s="24"/>
-      <c r="D5" s="165"/>
-      <c r="E5" s="165"/>
-      <c r="F5" s="165"/>
+      <c r="D5" s="127"/>
+      <c r="E5" s="127"/>
+      <c r="F5" s="127"/>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="23"/>
@@ -2835,14 +2861,14 @@
       <c r="F6" s="23"/>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="166" t="s">
+      <c r="A7" s="128" t="s">
         <v>418</v>
       </c>
-      <c r="B7" s="166"/>
-      <c r="C7" s="166"/>
-      <c r="D7" s="166"/>
-      <c r="E7" s="166"/>
-      <c r="F7" s="166"/>
+      <c r="B7" s="128"/>
+      <c r="C7" s="128"/>
+      <c r="D7" s="128"/>
+      <c r="E7" s="128"/>
+      <c r="F7" s="128"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
@@ -2864,27 +2890,27 @@
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="28"/>
-      <c r="B9" s="167" t="s">
+      <c r="B9" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="167"/>
-      <c r="D9" s="167"/>
-      <c r="E9" s="167"/>
-      <c r="F9" s="167"/>
+      <c r="C9" s="129"/>
+      <c r="D9" s="129"/>
+      <c r="E9" s="129"/>
+      <c r="F9" s="129"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="168" t="s">
+      <c r="A10" s="130" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="169"/>
-      <c r="C10" s="169"/>
-      <c r="D10" s="169"/>
-      <c r="E10" s="169"/>
-      <c r="F10" s="170"/>
+      <c r="B10" s="131"/>
+      <c r="C10" s="131"/>
+      <c r="D10" s="131"/>
+      <c r="E10" s="131"/>
+      <c r="F10" s="132"/>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
@@ -2892,12 +2918,12 @@
       <c r="K10" s="8"/>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="171"/>
-      <c r="B11" s="172"/>
-      <c r="C11" s="172"/>
-      <c r="D11" s="172"/>
-      <c r="E11" s="172"/>
-      <c r="F11" s="173"/>
+      <c r="A11" s="133"/>
+      <c r="B11" s="134"/>
+      <c r="C11" s="134"/>
+      <c r="D11" s="134"/>
+      <c r="E11" s="134"/>
+      <c r="F11" s="135"/>
       <c r="G11" s="21"/>
       <c r="H11" s="21"/>
       <c r="I11" s="21"/>
@@ -2916,14 +2942,14 @@
       <c r="A13" s="33" t="s">
         <v>259</v>
       </c>
-      <c r="B13" s="174" t="s">
+      <c r="B13" s="136" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="174"/>
+      <c r="C13" s="136"/>
       <c r="D13" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E13" s="115" t="s">
+      <c r="E13" s="120" t="s">
         <v>4</v>
       </c>
       <c r="F13" s="34" t="s">
@@ -2932,78 +2958,78 @@
       <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="175">
+      <c r="A14" s="137">
         <f>IF(LEN(C14)=0,"",COUNTA($C$14:C14))</f>
         <v>1</v>
       </c>
-      <c r="B14" s="143" t="s">
+      <c r="B14" s="140" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="178" t="s">
+      <c r="C14" s="143" t="s">
         <v>326</v>
       </c>
       <c r="D14" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="134">
+      <c r="E14" s="146">
         <v>200000</v>
       </c>
-      <c r="F14" s="181"/>
+      <c r="F14" s="149"/>
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:11" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="176"/>
-      <c r="B15" s="144"/>
-      <c r="C15" s="179"/>
+      <c r="A15" s="138"/>
+      <c r="B15" s="141"/>
+      <c r="C15" s="144"/>
       <c r="D15" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="E15" s="135"/>
-      <c r="F15" s="182"/>
+      <c r="E15" s="147"/>
+      <c r="F15" s="150"/>
       <c r="G15" s="11"/>
     </row>
     <row r="16" spans="1:11" ht="33" x14ac:dyDescent="0.25">
-      <c r="A16" s="176"/>
-      <c r="B16" s="144"/>
-      <c r="C16" s="179"/>
+      <c r="A16" s="138"/>
+      <c r="B16" s="141"/>
+      <c r="C16" s="144"/>
       <c r="D16" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="135"/>
-      <c r="F16" s="182"/>
+      <c r="E16" s="147"/>
+      <c r="F16" s="150"/>
       <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="176"/>
-      <c r="B17" s="144"/>
-      <c r="C17" s="179"/>
+      <c r="A17" s="138"/>
+      <c r="B17" s="141"/>
+      <c r="C17" s="144"/>
       <c r="D17" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="E17" s="135"/>
-      <c r="F17" s="182"/>
+      <c r="E17" s="147"/>
+      <c r="F17" s="150"/>
       <c r="G17" s="12"/>
     </row>
     <row r="18" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="176"/>
-      <c r="B18" s="144"/>
-      <c r="C18" s="179"/>
+      <c r="A18" s="138"/>
+      <c r="B18" s="141"/>
+      <c r="C18" s="144"/>
       <c r="D18" s="35" t="s">
         <v>411</v>
       </c>
-      <c r="E18" s="135"/>
-      <c r="F18" s="182"/>
+      <c r="E18" s="147"/>
+      <c r="F18" s="150"/>
       <c r="G18" s="12"/>
     </row>
     <row r="19" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="177"/>
-      <c r="B19" s="145"/>
-      <c r="C19" s="180"/>
+      <c r="A19" s="139"/>
+      <c r="B19" s="142"/>
+      <c r="C19" s="145"/>
       <c r="D19" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="136"/>
-      <c r="F19" s="183"/>
+      <c r="E19" s="148"/>
+      <c r="F19" s="151"/>
       <c r="G19" s="12"/>
     </row>
     <row r="20" spans="1:7" ht="33" x14ac:dyDescent="0.25">
@@ -3011,117 +3037,107 @@
         <f>IF(LEN(C20)=0,"",COUNTA($C$14:C20))</f>
         <v>2</v>
       </c>
-      <c r="B20" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="107" t="s">
-        <v>333</v>
-      </c>
-      <c r="E20" s="39">
-        <v>102000</v>
-      </c>
-      <c r="F20" s="40"/>
+      <c r="B20" s="71"/>
+      <c r="C20" s="187" t="s">
+        <v>420</v>
+      </c>
+      <c r="D20" s="188"/>
+      <c r="E20" s="121" t="s">
+        <v>421</v>
+      </c>
+      <c r="F20" s="122"/>
       <c r="G20" s="12"/>
     </row>
-    <row r="21" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A21" s="37">
         <f>IF(LEN(C21)=0,"",COUNTA($C$14:C21))</f>
         <v>3</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C21" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="36" t="s">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="D21" s="107" t="s">
+        <v>333</v>
       </c>
       <c r="E21" s="39">
-        <v>59000</v>
+        <v>102000</v>
       </c>
       <c r="F21" s="40"/>
       <c r="G21" s="12"/>
     </row>
-    <row r="22" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A22" s="37">
         <f>IF(LEN(C22)=0,"",COUNTA($C$14:C22))</f>
         <v>4</v>
       </c>
-      <c r="B22" s="38" t="s">
-        <v>15</v>
-      </c>
+      <c r="B22" s="79"/>
       <c r="C22" s="36" t="s">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="39">
-        <v>75000</v>
+        <v>136</v>
+      </c>
+      <c r="E22" s="105">
+        <v>140000</v>
       </c>
       <c r="F22" s="40"/>
       <c r="G22" s="12"/>
     </row>
-    <row r="23" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A23" s="37">
         <f>IF(LEN(C23)=0,"",COUNTA($C$14:C23))</f>
         <v>5</v>
       </c>
-      <c r="B23" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="39">
-        <v>27000</v>
+      <c r="B23" s="78"/>
+      <c r="C23" s="35" t="s">
+        <v>159</v>
+      </c>
+      <c r="D23" s="35" t="s">
+        <v>160</v>
+      </c>
+      <c r="E23" s="72">
+        <v>88000</v>
       </c>
       <c r="F23" s="40"/>
       <c r="G23" s="12"/>
     </row>
-    <row r="24" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A24" s="37">
         <f>IF(LEN(C24)=0,"",COUNTA($C$14:C24))</f>
         <v>6</v>
       </c>
-      <c r="B24" s="146" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24" s="41" t="s">
-        <v>42</v>
-      </c>
-      <c r="E24" s="184">
-        <v>60000</v>
-      </c>
-      <c r="F24" s="156" t="s">
-        <v>381</v>
-      </c>
+      <c r="B24" s="78"/>
+      <c r="C24" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="D24" s="107" t="s">
+        <v>328</v>
+      </c>
+      <c r="E24" s="105">
+        <v>230000</v>
+      </c>
+      <c r="F24" s="40"/>
       <c r="G24" s="12"/>
     </row>
-    <row r="25" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <f>IF(LEN(C25)=0,"",COUNTA($C$14:C25))</f>
         <v>7</v>
       </c>
-      <c r="B25" s="146"/>
-      <c r="C25" s="41" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="41" t="s">
-        <v>42</v>
-      </c>
-      <c r="E25" s="185"/>
-      <c r="F25" s="157"/>
+      <c r="B25" s="78"/>
+      <c r="C25" s="36" t="s">
+        <v>323</v>
+      </c>
+      <c r="D25" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="105">
+        <v>230000</v>
+      </c>
+      <c r="F25" s="40"/>
       <c r="G25" s="12"/>
     </row>
     <row r="26" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
@@ -3129,2418 +3145,2430 @@
         <f>IF(LEN(C26)=0,"",COUNTA($C$14:C26))</f>
         <v>8</v>
       </c>
-      <c r="B26" s="38" t="s">
-        <v>44</v>
-      </c>
+      <c r="B26" s="78"/>
       <c r="C26" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="E26" s="43">
-        <v>41000</v>
+        <v>34</v>
+      </c>
+      <c r="D26" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="105">
+        <v>220000</v>
       </c>
       <c r="F26" s="40"/>
       <c r="G26" s="12"/>
     </row>
-    <row r="27" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A27" s="37">
         <f>IF(LEN(C27)=0,"",COUNTA($C$14:C27))</f>
         <v>9</v>
       </c>
-      <c r="B27" s="78"/>
-      <c r="C27" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="D27" s="45" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="46" t="s">
-        <v>25</v>
+      <c r="B27" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="39">
+        <v>75000</v>
       </c>
       <c r="F27" s="40"/>
       <c r="G27" s="12"/>
     </row>
-    <row r="28" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="161" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="163"/>
-      <c r="C28" s="163"/>
-      <c r="D28" s="162"/>
-      <c r="E28" s="121">
-        <f>SUM(E14:E27)</f>
-        <v>564000</v>
-      </c>
-      <c r="F28" s="47"/>
+    <row r="28" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="37">
+        <f>IF(LEN(C28)=0,"",COUNTA($C$14:C28))</f>
+        <v>10</v>
+      </c>
+      <c r="B28" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="39">
+        <v>27000</v>
+      </c>
+      <c r="F28" s="40"/>
       <c r="G28" s="12"/>
     </row>
-    <row r="29" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="48"/>
-      <c r="B29" s="49"/>
-      <c r="C29" s="50"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="52"/>
+    <row r="29" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="37">
+        <f>IF(LEN(C29)=0,"",COUNTA($C$14:C29))</f>
+        <v>11</v>
+      </c>
+      <c r="B29" s="157" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" s="70" t="s">
+        <v>62</v>
+      </c>
+      <c r="E29" s="69">
+        <v>41000</v>
+      </c>
+      <c r="F29" s="158" t="s">
+        <v>377</v>
+      </c>
       <c r="G29" s="12"/>
     </row>
-    <row r="30" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="53" t="s">
-        <v>47</v>
-      </c>
-      <c r="B30" s="54"/>
-      <c r="C30" s="54"/>
-      <c r="D30" s="54"/>
-      <c r="E30" s="116"/>
-      <c r="F30" s="55"/>
-      <c r="G30" s="13"/>
-    </row>
-    <row r="31" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A31" s="56"/>
-      <c r="B31" s="57"/>
-      <c r="C31" s="58"/>
-      <c r="D31" s="58"/>
-      <c r="E31" s="59"/>
-      <c r="F31" s="60"/>
+    <row r="30" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A30" s="37">
+        <f>IF(LEN(C30)=0,"",COUNTA($C$14:C30))</f>
+        <v>12</v>
+      </c>
+      <c r="B30" s="157"/>
+      <c r="C30" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" s="70" t="s">
+        <v>64</v>
+      </c>
+      <c r="E30" s="69">
+        <v>59000</v>
+      </c>
+      <c r="F30" s="159"/>
+      <c r="G30" s="12"/>
+    </row>
+    <row r="31" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A31" s="37">
+        <f>IF(LEN(C31)=0,"",COUNTA($C$14:C31))</f>
+        <v>13</v>
+      </c>
+      <c r="B31" s="157"/>
+      <c r="C31" s="41" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" s="70" t="s">
+        <v>66</v>
+      </c>
+      <c r="E31" s="69">
+        <v>59000</v>
+      </c>
+      <c r="F31" s="159"/>
       <c r="G31" s="12"/>
     </row>
     <row r="32" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A32" s="61" t="s">
-        <v>259</v>
-      </c>
-      <c r="B32" s="161" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="162"/>
-      <c r="D32" s="61" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="121" t="s">
-        <v>4</v>
-      </c>
-      <c r="F32" s="34" t="s">
-        <v>0</v>
-      </c>
+      <c r="A32" s="37">
+        <f>IF(LEN(C32)=0,"",COUNTA($C$14:C32))</f>
+        <v>14</v>
+      </c>
+      <c r="B32" s="157"/>
+      <c r="C32" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="70" t="s">
+        <v>68</v>
+      </c>
+      <c r="E32" s="69">
+        <v>47000</v>
+      </c>
+      <c r="F32" s="159"/>
       <c r="G32" s="12"/>
     </row>
-    <row r="33" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="62" t="s">
-        <v>209</v>
-      </c>
-      <c r="B33" s="63"/>
-      <c r="C33" s="64"/>
-      <c r="D33" s="65"/>
-      <c r="E33" s="66"/>
-      <c r="F33" s="67"/>
+    <row r="33" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A33" s="37">
+        <f>IF(LEN(C33)=0,"",COUNTA($C$14:C33))</f>
+        <v>15</v>
+      </c>
+      <c r="B33" s="157"/>
+      <c r="C33" s="41" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" s="70" t="s">
+        <v>70</v>
+      </c>
+      <c r="E33" s="69">
+        <v>41000</v>
+      </c>
+      <c r="F33" s="160"/>
       <c r="G33" s="12"/>
     </row>
-    <row r="34" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A34" s="37">
-        <f>IF(LEN(C34)=0,"",COUNTA($C$34:C34))</f>
-        <v>1</v>
+        <f>IF(LEN(C34)=0,"",COUNTA($C$14:C34))</f>
+        <v>16</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C34" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="D34" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="E34" s="68">
-        <v>169000</v>
+        <v>45</v>
+      </c>
+      <c r="D34" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" s="43">
+        <v>41000</v>
       </c>
       <c r="F34" s="40"/>
       <c r="G34" s="12"/>
     </row>
     <row r="35" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
-        <f>IF(LEN(C35)=0,"",COUNTA($C$34:C35))</f>
-        <v>2</v>
-      </c>
-      <c r="B35" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="C35" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D35" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="E35" s="68">
-        <v>41000</v>
-      </c>
-      <c r="F35" s="40"/>
+        <f>IF(LEN(C35)=0,"",COUNTA($C$14:C35))</f>
+        <v>17</v>
+      </c>
+      <c r="B35" s="152" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="D35" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E35" s="153">
+        <v>60000</v>
+      </c>
+      <c r="F35" s="155" t="s">
+        <v>381</v>
+      </c>
       <c r="G35" s="12"/>
     </row>
-    <row r="36" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A36" s="37">
-        <f>IF(LEN(C36)=0,"",COUNTA($C$34:C36))</f>
-        <v>3</v>
-      </c>
-      <c r="B36" s="38" t="s">
-        <v>54</v>
-      </c>
+        <f>IF(LEN(C36)=0,"",COUNTA($C$14:C36))</f>
+        <v>18</v>
+      </c>
+      <c r="B36" s="152"/>
       <c r="C36" s="41" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D36" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="E36" s="69">
-        <v>41000</v>
-      </c>
-      <c r="F36" s="40"/>
+        <v>42</v>
+      </c>
+      <c r="E36" s="154"/>
+      <c r="F36" s="156"/>
       <c r="G36" s="12"/>
     </row>
-    <row r="37" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
-        <f>IF(LEN(C37)=0,"",COUNTA($C$34:C37))</f>
-        <v>4</v>
-      </c>
-      <c r="B37" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="C37" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="D37" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="E37" s="69">
-        <v>47000</v>
+        <f>IF(LEN(C37)=0,"",COUNTA($C37:C$54))</f>
+        <v>12</v>
+      </c>
+      <c r="B37" s="38"/>
+      <c r="C37" s="35" t="s">
+        <v>98</v>
+      </c>
+      <c r="D37" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="E37" s="72">
+        <v>123000</v>
       </c>
       <c r="F37" s="40"/>
       <c r="G37" s="12"/>
     </row>
-    <row r="38" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A38" s="37">
-        <f>IF(LEN(C38)=0,"",COUNTA($C$34:C38))</f>
-        <v>5</v>
-      </c>
-      <c r="B38" s="143" t="s">
-        <v>44</v>
-      </c>
-      <c r="C38" s="41" t="s">
-        <v>267</v>
-      </c>
-      <c r="D38" s="41" t="s">
-        <v>268</v>
-      </c>
-      <c r="E38" s="69">
-        <v>41000</v>
-      </c>
-      <c r="F38" s="108" t="s">
-        <v>376</v>
-      </c>
+        <f>IF(LEN(C38)=0,"",COUNTA($C38:C$54))</f>
+        <v>11</v>
+      </c>
+      <c r="B38" s="38"/>
+      <c r="C38" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="D38" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="E38" s="72">
+        <v>174000</v>
+      </c>
+      <c r="F38" s="40"/>
       <c r="G38" s="12"/>
     </row>
     <row r="39" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A39" s="37">
-        <f>IF(LEN(C39)=0,"",COUNTA($C$34:C39))</f>
-        <v>6</v>
-      </c>
-      <c r="B39" s="145"/>
-      <c r="C39" s="41" t="s">
-        <v>274</v>
-      </c>
-      <c r="D39" s="41" t="s">
-        <v>275</v>
-      </c>
-      <c r="E39" s="69">
+        <f>IF(LEN(C39)=0,"",COUNTA($C39:C$54))</f>
+        <v>10</v>
+      </c>
+      <c r="B39" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D39" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="E39" s="68">
         <v>41000</v>
       </c>
-      <c r="F39" s="108" t="s">
-        <v>375</v>
-      </c>
+      <c r="F39" s="40"/>
       <c r="G39" s="12"/>
     </row>
-    <row r="40" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A40" s="37">
-        <f>IF(LEN(C40)=0,"",COUNTA($C$34:C40))</f>
-        <v>7</v>
-      </c>
-      <c r="B40" s="153" t="s">
-        <v>60</v>
-      </c>
-      <c r="C40" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="D40" s="70" t="s">
-        <v>62</v>
-      </c>
-      <c r="E40" s="69">
-        <v>41000</v>
-      </c>
-      <c r="F40" s="128" t="s">
-        <v>377</v>
-      </c>
+        <f>IF(LEN(C40)=0,"",COUNTA($C$14:C40))</f>
+        <v>22</v>
+      </c>
+      <c r="B40" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40" s="39">
+        <v>59000</v>
+      </c>
+      <c r="F40" s="40"/>
       <c r="G40" s="12"/>
     </row>
     <row r="41" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A41" s="37">
-        <f>IF(LEN(C41)=0,"",COUNTA($C$34:C41))</f>
+        <f>IF(LEN(C41)=0,"",COUNTA($C41:C$54))</f>
         <v>8</v>
       </c>
-      <c r="B41" s="153"/>
-      <c r="C41" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="D41" s="70" t="s">
-        <v>64</v>
-      </c>
-      <c r="E41" s="69">
-        <v>59000</v>
-      </c>
-      <c r="F41" s="129"/>
+      <c r="B41" s="78"/>
+      <c r="C41" s="35" t="s">
+        <v>183</v>
+      </c>
+      <c r="D41" s="35" t="s">
+        <v>184</v>
+      </c>
+      <c r="E41" s="68">
+        <v>329000</v>
+      </c>
+      <c r="F41" s="40"/>
       <c r="G41" s="12"/>
     </row>
     <row r="42" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A42" s="37">
-        <f>IF(LEN(C42)=0,"",COUNTA($C$34:C42))</f>
-        <v>9</v>
-      </c>
-      <c r="B42" s="153"/>
-      <c r="C42" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="D42" s="70" t="s">
-        <v>66</v>
-      </c>
-      <c r="E42" s="69">
-        <v>59000</v>
-      </c>
-      <c r="F42" s="129"/>
+        <f>IF(LEN(C42)=0,"",COUNTA($C42:C$54))</f>
+        <v>7</v>
+      </c>
+      <c r="B42" s="78"/>
+      <c r="C42" s="36" t="s">
+        <v>181</v>
+      </c>
+      <c r="D42" s="36" t="s">
+        <v>182</v>
+      </c>
+      <c r="E42" s="68">
+        <v>72000</v>
+      </c>
+      <c r="F42" s="40"/>
       <c r="G42" s="12"/>
     </row>
-    <row r="43" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A43" s="37">
-        <f>IF(LEN(C43)=0,"",COUNTA($C$34:C43))</f>
-        <v>10</v>
-      </c>
-      <c r="B43" s="153"/>
-      <c r="C43" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D43" s="70" t="s">
-        <v>68</v>
-      </c>
-      <c r="E43" s="69">
-        <v>47000</v>
-      </c>
-      <c r="F43" s="129"/>
+        <f>IF(LEN(C43)=0,"",COUNTA($C43:C$54))</f>
+        <v>6</v>
+      </c>
+      <c r="B43" s="78"/>
+      <c r="C43" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="D43" s="74" t="s">
+        <v>280</v>
+      </c>
+      <c r="E43" s="39">
+        <v>290000</v>
+      </c>
+      <c r="F43" s="40" t="s">
+        <v>74</v>
+      </c>
       <c r="G43" s="12"/>
     </row>
-    <row r="44" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A44" s="37">
-        <f>IF(LEN(C44)=0,"",COUNTA($C$34:C44))</f>
-        <v>11</v>
-      </c>
-      <c r="B44" s="153"/>
-      <c r="C44" s="41" t="s">
-        <v>69</v>
-      </c>
-      <c r="D44" s="70" t="s">
-        <v>70</v>
-      </c>
-      <c r="E44" s="69">
-        <v>41000</v>
-      </c>
-      <c r="F44" s="130"/>
-      <c r="G44" s="12"/>
-    </row>
-    <row r="45" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+        <f>IF(LEN(C44)=0,"",COUNTA($C44:C$54))</f>
+        <v>5</v>
+      </c>
+      <c r="B44" s="78"/>
+      <c r="C44" s="73" t="s">
+        <v>71</v>
+      </c>
+      <c r="D44" s="74" t="s">
+        <v>72</v>
+      </c>
+      <c r="E44" s="39">
+        <v>174000</v>
+      </c>
+      <c r="F44" s="40"/>
+      <c r="G44" s="13"/>
+    </row>
+    <row r="45" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A45" s="37">
-        <f>IF(LEN(C45)=0,"",COUNTA($C$34:C45))</f>
-        <v>12</v>
-      </c>
-      <c r="B45" s="71" t="s">
-        <v>127</v>
-      </c>
-      <c r="C45" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="D45" s="35" t="s">
-        <v>129</v>
-      </c>
-      <c r="E45" s="72">
-        <v>102000</v>
+        <f>IF(LEN(C45)=0,"",COUNTA($C45:C$54))</f>
+        <v>4</v>
+      </c>
+      <c r="B45" s="78"/>
+      <c r="C45" s="73" t="s">
+        <v>79</v>
+      </c>
+      <c r="D45" s="74" t="s">
+        <v>279</v>
+      </c>
+      <c r="E45" s="116">
+        <v>121000</v>
       </c>
       <c r="F45" s="40"/>
-      <c r="G45" s="12"/>
-    </row>
-    <row r="46" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G45" s="13"/>
+    </row>
+    <row r="46" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A46" s="37">
-        <f>IF(LEN(C46)=0,"",COUNTA($C$34:C46))</f>
-        <v>13</v>
-      </c>
-      <c r="B46" s="143" t="s">
-        <v>277</v>
-      </c>
-      <c r="C46" s="35" t="s">
-        <v>194</v>
-      </c>
-      <c r="D46" s="35" t="s">
-        <v>195</v>
-      </c>
-      <c r="E46" s="72">
-        <v>62000</v>
-      </c>
-      <c r="F46" s="128" t="s">
-        <v>378</v>
-      </c>
-      <c r="G46" s="12"/>
+        <f>IF(LEN(C46)=0,"",COUNTA($C46:C$54))</f>
+        <v>3</v>
+      </c>
+      <c r="B46" s="78"/>
+      <c r="C46" s="73" t="s">
+        <v>75</v>
+      </c>
+      <c r="D46" s="74" t="s">
+        <v>76</v>
+      </c>
+      <c r="E46" s="39">
+        <v>231000</v>
+      </c>
+      <c r="F46" s="40"/>
+      <c r="G46" s="13"/>
     </row>
     <row r="47" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A47" s="37">
-        <f>IF(LEN(C47)=0,"",COUNTA($C$34:C47))</f>
+        <f>IF(LEN(C47)=0,"",COUNTA($C$14:C47))</f>
+        <v>29</v>
+      </c>
+      <c r="B47" s="78"/>
+      <c r="C47" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="D47" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" s="46" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" s="40"/>
+      <c r="G47" s="12"/>
+    </row>
+    <row r="48" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="123" t="s">
+        <v>26</v>
+      </c>
+      <c r="B48" s="124"/>
+      <c r="C48" s="124"/>
+      <c r="D48" s="125"/>
+      <c r="E48" s="120">
+        <f>SUM(E14:E47)</f>
+        <v>3274000</v>
+      </c>
+      <c r="F48" s="47"/>
+      <c r="G48" s="12"/>
+    </row>
+    <row r="49" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A49" s="48"/>
+      <c r="B49" s="49"/>
+      <c r="C49" s="50"/>
+      <c r="D49" s="50"/>
+      <c r="E49" s="51"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="12"/>
+    </row>
+    <row r="50" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A50" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="B50" s="54"/>
+      <c r="C50" s="54"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="115"/>
+      <c r="F50" s="55"/>
+      <c r="G50" s="13"/>
+    </row>
+    <row r="51" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A51" s="56"/>
+      <c r="B51" s="57"/>
+      <c r="C51" s="58"/>
+      <c r="D51" s="58"/>
+      <c r="E51" s="59"/>
+      <c r="F51" s="60"/>
+      <c r="G51" s="12"/>
+    </row>
+    <row r="52" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A52" s="61" t="s">
+        <v>259</v>
+      </c>
+      <c r="B52" s="123" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="125"/>
+      <c r="D52" s="61" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="120" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="G52" s="12"/>
+    </row>
+    <row r="53" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A53" s="62" t="s">
+        <v>209</v>
+      </c>
+      <c r="B53" s="63"/>
+      <c r="C53" s="64"/>
+      <c r="D53" s="65"/>
+      <c r="E53" s="66"/>
+      <c r="F53" s="67"/>
+      <c r="G53" s="12"/>
+    </row>
+    <row r="54" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A54" s="37">
+        <f>IF(LEN(C54)=0,"",COUNTA($C$54:C54))</f>
+        <v>1</v>
+      </c>
+      <c r="B54" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="C54" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="D54" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="E54" s="68">
+        <v>169000</v>
+      </c>
+      <c r="F54" s="40"/>
+      <c r="G54" s="12"/>
+    </row>
+    <row r="55" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A55" s="37">
+        <f>IF(LEN(C55)=0,"",COUNTA($C$54:C55))</f>
+        <v>2</v>
+      </c>
+      <c r="B55" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="C55" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D55" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="E55" s="68">
+        <v>41000</v>
+      </c>
+      <c r="F55" s="40"/>
+      <c r="G55" s="12"/>
+    </row>
+    <row r="56" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+      <c r="A56" s="37">
+        <f>IF(LEN(C56)=0,"",COUNTA($C$54:C56))</f>
+        <v>3</v>
+      </c>
+      <c r="B56" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C56" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="D56" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="E56" s="69">
+        <v>41000</v>
+      </c>
+      <c r="F56" s="40"/>
+      <c r="G56" s="12"/>
+    </row>
+    <row r="57" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A57" s="37">
+        <f>IF(LEN(C57)=0,"",COUNTA($C$54:C57))</f>
+        <v>4</v>
+      </c>
+      <c r="B57" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C57" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="D57" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="E57" s="69">
+        <v>47000</v>
+      </c>
+      <c r="F57" s="40"/>
+      <c r="G57" s="12"/>
+    </row>
+    <row r="58" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A58" s="37">
+        <f>IF(LEN(C58)=0,"",COUNTA($C$54:C58))</f>
+        <v>5</v>
+      </c>
+      <c r="B58" s="140" t="s">
+        <v>44</v>
+      </c>
+      <c r="C58" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="D58" s="41" t="s">
+        <v>268</v>
+      </c>
+      <c r="E58" s="69">
+        <v>41000</v>
+      </c>
+      <c r="F58" s="108" t="s">
+        <v>376</v>
+      </c>
+      <c r="G58" s="12"/>
+    </row>
+    <row r="59" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A59" s="37">
+        <f>IF(LEN(C59)=0,"",COUNTA($C$54:C59))</f>
+        <v>6</v>
+      </c>
+      <c r="B59" s="142"/>
+      <c r="C59" s="41" t="s">
+        <v>274</v>
+      </c>
+      <c r="D59" s="41" t="s">
+        <v>275</v>
+      </c>
+      <c r="E59" s="69">
+        <v>41000</v>
+      </c>
+      <c r="F59" s="108" t="s">
+        <v>375</v>
+      </c>
+      <c r="G59" s="12"/>
+    </row>
+    <row r="60" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="37">
+        <f>IF(LEN(C60)=0,"",COUNTA($C$54:C60))</f>
+        <v>7</v>
+      </c>
+      <c r="B60" s="157" t="s">
+        <v>60</v>
+      </c>
+      <c r="C60" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="D60" s="70" t="s">
+        <v>62</v>
+      </c>
+      <c r="E60" s="69">
+        <v>41000</v>
+      </c>
+      <c r="F60" s="158" t="s">
+        <v>377</v>
+      </c>
+      <c r="G60" s="12"/>
+    </row>
+    <row r="61" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A61" s="37">
+        <f>IF(LEN(C61)=0,"",COUNTA($C$54:C61))</f>
+        <v>8</v>
+      </c>
+      <c r="B61" s="157"/>
+      <c r="C61" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="D61" s="70" t="s">
+        <v>64</v>
+      </c>
+      <c r="E61" s="69">
+        <v>59000</v>
+      </c>
+      <c r="F61" s="159"/>
+      <c r="G61" s="12"/>
+    </row>
+    <row r="62" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A62" s="37">
+        <f>IF(LEN(C62)=0,"",COUNTA($C$54:C62))</f>
+        <v>9</v>
+      </c>
+      <c r="B62" s="157"/>
+      <c r="C62" s="41" t="s">
+        <v>65</v>
+      </c>
+      <c r="D62" s="70" t="s">
+        <v>66</v>
+      </c>
+      <c r="E62" s="69">
+        <v>59000</v>
+      </c>
+      <c r="F62" s="159"/>
+      <c r="G62" s="12"/>
+    </row>
+    <row r="63" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A63" s="37">
+        <f>IF(LEN(C63)=0,"",COUNTA($C$54:C63))</f>
+        <v>10</v>
+      </c>
+      <c r="B63" s="157"/>
+      <c r="C63" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D63" s="70" t="s">
+        <v>68</v>
+      </c>
+      <c r="E63" s="69">
+        <v>47000</v>
+      </c>
+      <c r="F63" s="159"/>
+      <c r="G63" s="12"/>
+    </row>
+    <row r="64" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A64" s="37">
+        <f>IF(LEN(C64)=0,"",COUNTA($C$54:C64))</f>
+        <v>11</v>
+      </c>
+      <c r="B64" s="157"/>
+      <c r="C64" s="41" t="s">
+        <v>69</v>
+      </c>
+      <c r="D64" s="70" t="s">
+        <v>70</v>
+      </c>
+      <c r="E64" s="69">
+        <v>41000</v>
+      </c>
+      <c r="F64" s="160"/>
+      <c r="G64" s="12"/>
+    </row>
+    <row r="65" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A65" s="37">
+        <f>IF(LEN(C65)=0,"",COUNTA($C$54:C65))</f>
+        <v>12</v>
+      </c>
+      <c r="B65" s="71" t="s">
+        <v>127</v>
+      </c>
+      <c r="C65" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="D65" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="E65" s="72">
+        <v>102000</v>
+      </c>
+      <c r="F65" s="40"/>
+      <c r="G65" s="12"/>
+    </row>
+    <row r="66" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="37">
+        <f>IF(LEN(C66)=0,"",COUNTA($C$54:C66))</f>
+        <v>13</v>
+      </c>
+      <c r="B66" s="140" t="s">
+        <v>277</v>
+      </c>
+      <c r="C66" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="D66" s="35" t="s">
+        <v>195</v>
+      </c>
+      <c r="E66" s="72">
+        <v>62000</v>
+      </c>
+      <c r="F66" s="158" t="s">
+        <v>378</v>
+      </c>
+      <c r="G66" s="12"/>
+    </row>
+    <row r="67" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A67" s="37">
+        <f>IF(LEN(C67)=0,"",COUNTA($C$54:C67))</f>
         <v>14</v>
       </c>
-      <c r="B47" s="144"/>
-      <c r="C47" s="35" t="s">
+      <c r="B67" s="141"/>
+      <c r="C67" s="35" t="s">
         <v>196</v>
       </c>
-      <c r="D47" s="35" t="s">
+      <c r="D67" s="35" t="s">
         <v>197</v>
       </c>
-      <c r="E47" s="72">
+      <c r="E67" s="72">
         <v>165000</v>
       </c>
-      <c r="F47" s="129"/>
-      <c r="G47" s="12"/>
-    </row>
-    <row r="48" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="37">
-        <f>IF(LEN(C48)=0,"",COUNTA($C$34:C48))</f>
+      <c r="F67" s="159"/>
+      <c r="G67" s="12"/>
+    </row>
+    <row r="68" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A68" s="37">
+        <f>IF(LEN(C68)=0,"",COUNTA($C$54:C68))</f>
         <v>15</v>
       </c>
-      <c r="B48" s="145"/>
-      <c r="C48" s="35" t="s">
+      <c r="B68" s="142"/>
+      <c r="C68" s="35" t="s">
         <v>201</v>
       </c>
-      <c r="D48" s="35" t="s">
+      <c r="D68" s="35" t="s">
         <v>202</v>
       </c>
-      <c r="E48" s="72">
+      <c r="E68" s="72">
         <v>116000</v>
       </c>
-      <c r="F48" s="130"/>
-      <c r="G48" s="12"/>
-    </row>
-    <row r="49" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="37">
-        <f>IF(LEN(C49)=0,"",COUNTA($C$34:C49))</f>
+      <c r="F68" s="160"/>
+      <c r="G68" s="12"/>
+    </row>
+    <row r="69" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A69" s="37">
+        <f>IF(LEN(C69)=0,"",COUNTA($C$54:C69))</f>
         <v>16</v>
       </c>
-      <c r="B49" s="143" t="s">
+      <c r="B69" s="140" t="s">
         <v>272</v>
       </c>
-      <c r="C49" s="35" t="s">
+      <c r="C69" s="35" t="s">
         <v>198</v>
       </c>
-      <c r="D49" s="35" t="s">
+      <c r="D69" s="35" t="s">
         <v>199</v>
       </c>
-      <c r="E49" s="72">
+      <c r="E69" s="72">
         <v>83000</v>
       </c>
-      <c r="F49" s="40"/>
-      <c r="G49" s="12"/>
-    </row>
-    <row r="50" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A50" s="37">
-        <f>IF(LEN(C50)=0,"",COUNTA($C$34:C50))</f>
+      <c r="F69" s="40"/>
+      <c r="G69" s="12"/>
+    </row>
+    <row r="70" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A70" s="37">
+        <f>IF(LEN(C70)=0,"",COUNTA($C$54:C70))</f>
         <v>17</v>
       </c>
-      <c r="B50" s="144"/>
-      <c r="C50" s="35" t="s">
+      <c r="B70" s="141"/>
+      <c r="C70" s="35" t="s">
         <v>269</v>
       </c>
-      <c r="D50" s="35" t="s">
+      <c r="D70" s="35" t="s">
         <v>199</v>
       </c>
-      <c r="E50" s="72">
+      <c r="E70" s="72">
         <v>130000</v>
       </c>
-      <c r="F50" s="128" t="s">
+      <c r="F70" s="158" t="s">
         <v>378</v>
       </c>
-      <c r="G50" s="12"/>
-    </row>
-    <row r="51" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="37">
-        <f>IF(LEN(C51)=0,"",COUNTA($C$34:C51))</f>
+      <c r="G70" s="12"/>
+    </row>
+    <row r="71" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A71" s="37">
+        <f>IF(LEN(C71)=0,"",COUNTA($C$54:C71))</f>
         <v>18</v>
       </c>
-      <c r="B51" s="144"/>
-      <c r="C51" s="35" t="s">
+      <c r="B71" s="141"/>
+      <c r="C71" s="35" t="s">
         <v>270</v>
       </c>
-      <c r="D51" s="35" t="s">
+      <c r="D71" s="35" t="s">
         <v>199</v>
       </c>
-      <c r="E51" s="72">
+      <c r="E71" s="72">
         <v>120000</v>
       </c>
-      <c r="F51" s="129"/>
-      <c r="G51" s="12"/>
-    </row>
-    <row r="52" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="37">
-        <f>IF(LEN(C52)=0,"",COUNTA($C$34:C52))</f>
+      <c r="F71" s="159"/>
+      <c r="G71" s="12"/>
+    </row>
+    <row r="72" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A72" s="37">
+        <f>IF(LEN(C72)=0,"",COUNTA($C$54:C72))</f>
         <v>19</v>
       </c>
-      <c r="B52" s="145"/>
-      <c r="C52" s="35" t="s">
+      <c r="B72" s="142"/>
+      <c r="C72" s="35" t="s">
         <v>271</v>
       </c>
-      <c r="D52" s="35" t="s">
+      <c r="D72" s="35" t="s">
         <v>200</v>
       </c>
-      <c r="E52" s="72">
+      <c r="E72" s="72">
         <v>282000</v>
       </c>
-      <c r="F52" s="130"/>
-      <c r="G52" s="12"/>
-    </row>
-    <row r="53" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="37">
-        <f>IF(LEN(C53)=0,"",COUNTA($C$34:C53))</f>
+      <c r="F72" s="160"/>
+      <c r="G72" s="12"/>
+    </row>
+    <row r="73" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A73" s="37">
+        <f>IF(LEN(C73)=0,"",COUNTA($C$54:C73))</f>
         <v>20</v>
       </c>
-      <c r="B53" s="71" t="s">
+      <c r="B73" s="71" t="s">
         <v>373</v>
       </c>
-      <c r="C53" s="35" t="s">
+      <c r="C73" s="35" t="s">
         <v>336</v>
       </c>
-      <c r="D53" s="35" t="s">
+      <c r="D73" s="35" t="s">
         <v>193</v>
       </c>
-      <c r="E53" s="72">
+      <c r="E73" s="72">
         <v>128000</v>
       </c>
-      <c r="F53" s="40"/>
-      <c r="G53" s="12"/>
-    </row>
-    <row r="54" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="37">
-        <f>IF(LEN(C54)=0,"",COUNTA($C$34:C54))</f>
+      <c r="F73" s="40"/>
+      <c r="G73" s="12"/>
+    </row>
+    <row r="74" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="37">
+        <f>IF(LEN(C74)=0,"",COUNTA($C$54:C74))</f>
         <v>21</v>
       </c>
-      <c r="B54" s="137" t="s">
+      <c r="B74" s="166" t="s">
         <v>130</v>
       </c>
-      <c r="C54" s="35" t="s">
+      <c r="C74" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="D54" s="35" t="s">
+      <c r="D74" s="35" t="s">
         <v>132</v>
       </c>
-      <c r="E54" s="72">
+      <c r="E74" s="72">
         <v>71000</v>
       </c>
-      <c r="F54" s="156" t="s">
+      <c r="F74" s="155" t="s">
         <v>380</v>
       </c>
-      <c r="G54" s="12"/>
-    </row>
-    <row r="55" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="37">
-        <f>IF(LEN(C55)=0,"",COUNTA($C$34:C55))</f>
+      <c r="G74" s="12"/>
+    </row>
+    <row r="75" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A75" s="37">
+        <f>IF(LEN(C75)=0,"",COUNTA($C$54:C75))</f>
         <v>22</v>
       </c>
-      <c r="B55" s="138"/>
-      <c r="C55" s="35" t="s">
+      <c r="B75" s="167"/>
+      <c r="C75" s="35" t="s">
         <v>133</v>
       </c>
-      <c r="D55" s="35" t="s">
+      <c r="D75" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="E55" s="68">
+      <c r="E75" s="68">
         <v>138000</v>
       </c>
-      <c r="F55" s="157"/>
-      <c r="G55" s="12"/>
-    </row>
-    <row r="56" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A56" s="37">
-        <f>IF(LEN(C56)=0,"",COUNTA($C$34:C56))</f>
+      <c r="F75" s="156"/>
+      <c r="G75" s="12"/>
+    </row>
+    <row r="76" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A76" s="37">
+        <f>IF(LEN(C76)=0,"",COUNTA($C$54:C76))</f>
         <v>23</v>
       </c>
-      <c r="B56" s="109" t="s">
+      <c r="B76" s="109" t="s">
         <v>389</v>
       </c>
-      <c r="C56" s="35" t="s">
+      <c r="C76" s="35" t="s">
         <v>390</v>
       </c>
-      <c r="D56" s="35" t="s">
+      <c r="D76" s="35" t="s">
         <v>391</v>
       </c>
-      <c r="E56" s="68">
+      <c r="E76" s="68">
         <v>282000</v>
       </c>
-      <c r="F56" s="110"/>
-      <c r="G56" s="12"/>
-    </row>
-    <row r="57" spans="1:7" s="14" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="37">
-        <f>IF(LEN(C57)=0,"",COUNTA($C$34:C57))</f>
+      <c r="F76" s="110"/>
+      <c r="G76" s="12"/>
+    </row>
+    <row r="77" spans="1:7" s="14" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="37">
+        <f>IF(LEN(C77)=0,"",COUNTA($C$54:C77))</f>
         <v>24</v>
       </c>
-      <c r="B57" s="158" t="s">
+      <c r="B77" s="168" t="s">
         <v>205</v>
       </c>
-      <c r="C57" s="35" t="s">
+      <c r="C77" s="35" t="s">
         <v>161</v>
       </c>
-      <c r="D57" s="35" t="s">
+      <c r="D77" s="35" t="s">
         <v>162</v>
       </c>
-      <c r="E57" s="72">
+      <c r="E77" s="72">
         <v>30000</v>
       </c>
-      <c r="F57" s="159" t="s">
+      <c r="F77" s="169" t="s">
         <v>382</v>
       </c>
-      <c r="G57" s="13"/>
-    </row>
-    <row r="58" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A58" s="37">
-        <f>IF(LEN(C58)=0,"",COUNTA($C$34:C58))</f>
+      <c r="G77" s="13"/>
+    </row>
+    <row r="78" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A78" s="37">
+        <f>IF(LEN(C78)=0,"",COUNTA($C$54:C78))</f>
         <v>25</v>
       </c>
-      <c r="B58" s="158"/>
-      <c r="C58" s="35" t="s">
+      <c r="B78" s="168"/>
+      <c r="C78" s="35" t="s">
         <v>278</v>
       </c>
-      <c r="D58" s="35" t="s">
+      <c r="D78" s="35" t="s">
         <v>162</v>
       </c>
-      <c r="E58" s="72">
+      <c r="E78" s="72">
         <v>20000</v>
       </c>
-      <c r="F58" s="160"/>
-      <c r="G58" s="13"/>
-    </row>
-    <row r="59" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A59" s="131" t="s">
+      <c r="F78" s="170"/>
+      <c r="G78" s="13"/>
+    </row>
+    <row r="79" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A79" s="171" t="s">
         <v>208</v>
       </c>
-      <c r="B59" s="132"/>
-      <c r="C59" s="132"/>
-      <c r="D59" s="133"/>
-      <c r="E59" s="66"/>
-      <c r="F59" s="67"/>
-      <c r="G59" s="12"/>
-    </row>
-    <row r="60" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A60" s="37">
-        <f>IF(LEN(C60)=0,"",COUNTA($C$34:C60))</f>
+      <c r="B79" s="172"/>
+      <c r="C79" s="172"/>
+      <c r="D79" s="173"/>
+      <c r="E79" s="66"/>
+      <c r="F79" s="67"/>
+      <c r="G79" s="12"/>
+    </row>
+    <row r="80" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A80" s="37">
+        <f>IF(LEN(C80)=0,"",COUNTA($C$54:C80))</f>
         <v>26</v>
       </c>
-      <c r="B60" s="147" t="s">
+      <c r="B80" s="161" t="s">
         <v>260</v>
       </c>
-      <c r="C60" s="73" t="s">
+      <c r="C80" s="73" t="s">
         <v>71</v>
       </c>
-      <c r="D60" s="74" t="s">
+      <c r="D80" s="74" t="s">
         <v>72</v>
       </c>
-      <c r="E60" s="39">
+      <c r="E80" s="39">
         <v>174000</v>
       </c>
-      <c r="F60" s="40"/>
-      <c r="G60" s="13"/>
-    </row>
-    <row r="61" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A61" s="37">
-        <f>IF(LEN(C61)=0,"",COUNTA($C$34:C61))</f>
+      <c r="F80" s="40"/>
+      <c r="G80" s="13"/>
+    </row>
+    <row r="81" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A81" s="37">
+        <f>IF(LEN(C81)=0,"",COUNTA($C$54:C81))</f>
         <v>27</v>
       </c>
-      <c r="B61" s="148"/>
-      <c r="C61" s="73" t="s">
+      <c r="B81" s="162"/>
+      <c r="C81" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="D61" s="74" t="s">
+      <c r="D81" s="74" t="s">
         <v>84</v>
       </c>
-      <c r="E61" s="106">
+      <c r="E81" s="106">
         <v>231000</v>
       </c>
-      <c r="F61" s="40"/>
-      <c r="G61" s="13"/>
-    </row>
-    <row r="62" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A62" s="37">
-        <f>IF(LEN(C62)=0,"",COUNTA($C$34:C62))</f>
+      <c r="F81" s="40"/>
+      <c r="G81" s="13"/>
+    </row>
+    <row r="82" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A82" s="37">
+        <f>IF(LEN(C82)=0,"",COUNTA($C$54:C82))</f>
         <v>28</v>
       </c>
-      <c r="B62" s="148"/>
-      <c r="C62" s="73" t="s">
+      <c r="B82" s="162"/>
+      <c r="C82" s="73" t="s">
         <v>85</v>
       </c>
-      <c r="D62" s="74" t="s">
+      <c r="D82" s="74" t="s">
         <v>86</v>
       </c>
-      <c r="E62" s="39">
+      <c r="E82" s="39">
         <v>732000</v>
       </c>
-      <c r="F62" s="40"/>
-      <c r="G62" s="13"/>
-    </row>
-    <row r="63" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A63" s="37">
-        <f>IF(LEN(C63)=0,"",COUNTA($C$34:C63))</f>
+      <c r="F82" s="40"/>
+      <c r="G82" s="13"/>
+    </row>
+    <row r="83" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A83" s="37">
+        <f>IF(LEN(C83)=0,"",COUNTA($C$54:C83))</f>
         <v>29</v>
       </c>
-      <c r="B63" s="148"/>
-      <c r="C63" s="73" t="s">
+      <c r="B83" s="162"/>
+      <c r="C83" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="D63" s="74" t="s">
+      <c r="D83" s="74" t="s">
         <v>279</v>
       </c>
-      <c r="E63" s="117">
+      <c r="E83" s="116">
         <v>121000</v>
       </c>
-      <c r="F63" s="40"/>
-      <c r="G63" s="13"/>
-    </row>
-    <row r="64" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A64" s="37">
-        <f>IF(LEN(C64)=0,"",COUNTA($C$34:C64))</f>
+      <c r="F83" s="40"/>
+      <c r="G83" s="13"/>
+    </row>
+    <row r="84" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A84" s="37">
+        <f>IF(LEN(C84)=0,"",COUNTA($C$54:C84))</f>
         <v>30</v>
       </c>
-      <c r="B64" s="148"/>
-      <c r="C64" s="73" t="s">
+      <c r="B84" s="162"/>
+      <c r="C84" s="73" t="s">
         <v>93</v>
       </c>
-      <c r="D64" s="74" t="s">
+      <c r="D84" s="74" t="s">
         <v>94</v>
       </c>
-      <c r="E64" s="39">
+      <c r="E84" s="39">
         <v>192000</v>
       </c>
-      <c r="F64" s="40"/>
-      <c r="G64" s="13"/>
-    </row>
-    <row r="65" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A65" s="37">
-        <f>IF(LEN(C65)=0,"",COUNTA($C$34:C65))</f>
+      <c r="F84" s="40"/>
+      <c r="G84" s="13"/>
+    </row>
+    <row r="85" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A85" s="37">
+        <f>IF(LEN(C85)=0,"",COUNTA($C$54:C85))</f>
         <v>31</v>
       </c>
-      <c r="B65" s="148"/>
-      <c r="C65" s="73" t="s">
+      <c r="B85" s="162"/>
+      <c r="C85" s="73" t="s">
         <v>80</v>
       </c>
-      <c r="D65" s="74" t="s">
+      <c r="D85" s="74" t="s">
         <v>81</v>
       </c>
-      <c r="E65" s="39">
+      <c r="E85" s="39">
         <v>173000</v>
       </c>
-      <c r="F65" s="40"/>
-      <c r="G65" s="13"/>
-    </row>
-    <row r="66" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A66" s="37">
-        <f>IF(LEN(C66)=0,"",COUNTA($C$34:C66))</f>
+      <c r="F85" s="40"/>
+      <c r="G85" s="13"/>
+    </row>
+    <row r="86" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A86" s="37">
+        <f>IF(LEN(C86)=0,"",COUNTA($C$54:C86))</f>
         <v>32</v>
       </c>
-      <c r="B66" s="148"/>
-      <c r="C66" s="73" t="s">
+      <c r="B86" s="162"/>
+      <c r="C86" s="73" t="s">
         <v>82</v>
       </c>
-      <c r="D66" s="74" t="s">
+      <c r="D86" s="74" t="s">
         <v>281</v>
       </c>
-      <c r="E66" s="106">
+      <c r="E86" s="106">
         <v>231000</v>
       </c>
-      <c r="F66" s="108" t="s">
+      <c r="F86" s="108" t="s">
         <v>395</v>
       </c>
-      <c r="G66" s="13"/>
-    </row>
-    <row r="67" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A67" s="37">
-        <f>IF(LEN(C67)=0,"",COUNTA($C$34:C67))</f>
+      <c r="G86" s="13"/>
+    </row>
+    <row r="87" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A87" s="37">
+        <f>IF(LEN(C87)=0,"",COUNTA($C$54:C87))</f>
         <v>33</v>
       </c>
-      <c r="B67" s="148"/>
-      <c r="C67" s="75" t="s">
+      <c r="B87" s="162"/>
+      <c r="C87" s="75" t="s">
         <v>234</v>
       </c>
-      <c r="D67" s="76" t="s">
+      <c r="D87" s="76" t="s">
         <v>235</v>
       </c>
-      <c r="E67" s="118">
+      <c r="E87" s="117">
         <v>500000</v>
       </c>
-      <c r="F67" s="40"/>
-      <c r="G67" s="13"/>
-    </row>
-    <row r="68" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A68" s="37">
-        <f>IF(LEN(C68)=0,"",COUNTA($C$34:C68))</f>
+      <c r="F87" s="40"/>
+      <c r="G87" s="13"/>
+    </row>
+    <row r="88" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A88" s="37">
+        <f>IF(LEN(C88)=0,"",COUNTA($C$54:C88))</f>
         <v>34</v>
       </c>
-      <c r="B68" s="148"/>
-      <c r="C68" s="73" t="s">
+      <c r="B88" s="162"/>
+      <c r="C88" s="73" t="s">
         <v>73</v>
       </c>
-      <c r="D68" s="74" t="s">
+      <c r="D88" s="74" t="s">
         <v>280</v>
       </c>
-      <c r="E68" s="39">
+      <c r="E88" s="39">
         <v>290000</v>
       </c>
-      <c r="F68" s="40" t="s">
+      <c r="F88" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="G68" s="12"/>
-    </row>
-    <row r="69" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A69" s="37">
-        <f>IF(LEN(C69)=0,"",COUNTA($C$34:C69))</f>
+      <c r="G88" s="12"/>
+    </row>
+    <row r="89" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A89" s="37">
+        <f>IF(LEN(C89)=0,"",COUNTA($C$54:C89))</f>
         <v>35</v>
       </c>
-      <c r="B69" s="148"/>
-      <c r="C69" s="73" t="s">
+      <c r="B89" s="162"/>
+      <c r="C89" s="73" t="s">
         <v>75</v>
       </c>
-      <c r="D69" s="74" t="s">
+      <c r="D89" s="74" t="s">
         <v>76</v>
       </c>
-      <c r="E69" s="39">
+      <c r="E89" s="39">
         <v>231000</v>
       </c>
-      <c r="F69" s="40"/>
-      <c r="G69" s="13"/>
-    </row>
-    <row r="70" spans="1:7" s="14" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A70" s="37">
-        <f>IF(LEN(C70)=0,"",COUNTA($C$34:C70))</f>
+      <c r="F89" s="40"/>
+      <c r="G89" s="13"/>
+    </row>
+    <row r="90" spans="1:7" s="14" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A90" s="37">
+        <f>IF(LEN(C90)=0,"",COUNTA($C$54:C90))</f>
         <v>36</v>
       </c>
-      <c r="B70" s="148"/>
-      <c r="C70" s="73" t="s">
+      <c r="B90" s="162"/>
+      <c r="C90" s="73" t="s">
         <v>77</v>
       </c>
-      <c r="D70" s="74" t="s">
+      <c r="D90" s="74" t="s">
         <v>78</v>
       </c>
-      <c r="E70" s="39">
+      <c r="E90" s="39">
         <v>616000</v>
       </c>
-      <c r="F70" s="40"/>
-      <c r="G70" s="13"/>
-    </row>
-    <row r="71" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A71" s="37">
-        <f>IF(LEN(C71)=0,"",COUNTA($C$34:C71))</f>
+      <c r="F90" s="40"/>
+      <c r="G90" s="13"/>
+    </row>
+    <row r="91" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A91" s="37">
+        <f>IF(LEN(C91)=0,"",COUNTA($C$54:C91))</f>
         <v>37</v>
       </c>
-      <c r="B71" s="148"/>
-      <c r="C71" s="73" t="s">
+      <c r="B91" s="162"/>
+      <c r="C91" s="73" t="s">
         <v>87</v>
       </c>
-      <c r="D71" s="74" t="s">
+      <c r="D91" s="74" t="s">
         <v>88</v>
       </c>
-      <c r="E71" s="106">
+      <c r="E91" s="106">
         <v>231000</v>
       </c>
-      <c r="F71" s="40"/>
-      <c r="G71" s="13"/>
-    </row>
-    <row r="72" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A72" s="37">
-        <f>IF(LEN(C72)=0,"",COUNTA($C$34:C72))</f>
+      <c r="F91" s="40"/>
+      <c r="G91" s="13"/>
+    </row>
+    <row r="92" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A92" s="37">
+        <f>IF(LEN(C92)=0,"",COUNTA($C$54:C92))</f>
         <v>38</v>
       </c>
-      <c r="B72" s="149"/>
-      <c r="C72" s="73" t="s">
+      <c r="B92" s="163"/>
+      <c r="C92" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="D72" s="74" t="s">
+      <c r="D92" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="E72" s="39">
+      <c r="E92" s="39">
         <v>412000</v>
       </c>
-      <c r="F72" s="40"/>
-      <c r="G72" s="13"/>
-    </row>
-    <row r="73" spans="1:7" s="14" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="37">
-        <f>IF(LEN(C73)=0,"",COUNTA($C$34:C73))</f>
+      <c r="F92" s="40"/>
+      <c r="G92" s="13"/>
+    </row>
+    <row r="93" spans="1:7" s="14" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="37">
+        <f>IF(LEN(C93)=0,"",COUNTA($C$54:C93))</f>
         <v>39</v>
       </c>
-      <c r="B73" s="147" t="s">
+      <c r="B93" s="161" t="s">
         <v>90</v>
       </c>
-      <c r="C73" s="73" t="s">
+      <c r="C93" s="73" t="s">
         <v>89</v>
       </c>
-      <c r="D73" s="150" t="s">
+      <c r="D93" s="174" t="s">
         <v>396</v>
       </c>
-      <c r="E73" s="39">
+      <c r="E93" s="39">
         <v>137000</v>
       </c>
-      <c r="F73" s="128" t="s">
+      <c r="F93" s="158" t="s">
         <v>379</v>
       </c>
-      <c r="G73" s="13"/>
-    </row>
-    <row r="74" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A74" s="37">
-        <f>IF(LEN(C74)=0,"",COUNTA($C$34:C74))</f>
+      <c r="G93" s="13"/>
+    </row>
+    <row r="94" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A94" s="37">
+        <f>IF(LEN(C94)=0,"",COUNTA($C$54:C94))</f>
         <v>40</v>
       </c>
-      <c r="B74" s="148"/>
-      <c r="C74" s="73" t="s">
+      <c r="B94" s="162"/>
+      <c r="C94" s="73" t="s">
         <v>91</v>
       </c>
-      <c r="D74" s="151"/>
-      <c r="E74" s="39">
+      <c r="D94" s="175"/>
+      <c r="E94" s="39">
         <v>137000</v>
       </c>
-      <c r="F74" s="129"/>
-      <c r="G74" s="13"/>
-    </row>
-    <row r="75" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A75" s="37">
-        <f>IF(LEN(C75)=0,"",COUNTA($C$34:C75))</f>
+      <c r="F94" s="159"/>
+      <c r="G94" s="13"/>
+    </row>
+    <row r="95" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A95" s="37">
+        <f>IF(LEN(C95)=0,"",COUNTA($C$54:C95))</f>
         <v>41</v>
       </c>
-      <c r="B75" s="149"/>
-      <c r="C75" s="73" t="s">
+      <c r="B95" s="163"/>
+      <c r="C95" s="73" t="s">
         <v>92</v>
       </c>
-      <c r="D75" s="152"/>
-      <c r="E75" s="39">
+      <c r="D95" s="176"/>
+      <c r="E95" s="39">
         <v>208000</v>
       </c>
-      <c r="F75" s="130"/>
-      <c r="G75" s="13"/>
-    </row>
-    <row r="76" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="37">
-        <f>IF(LEN(C76)=0,"",COUNTA($C$34:C76))</f>
+      <c r="F95" s="160"/>
+      <c r="G95" s="13"/>
+    </row>
+    <row r="96" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A96" s="37">
+        <f>IF(LEN(C96)=0,"",COUNTA($C$54:C96))</f>
         <v>42</v>
       </c>
-      <c r="B76" s="147" t="s">
+      <c r="B96" s="161" t="s">
         <v>397</v>
       </c>
-      <c r="C76" s="73" t="s">
+      <c r="C96" s="73" t="s">
         <v>398</v>
       </c>
-      <c r="D76" s="154" t="s">
+      <c r="D96" s="164" t="s">
         <v>400</v>
       </c>
-      <c r="E76" s="39">
+      <c r="E96" s="39">
         <v>215000</v>
       </c>
-      <c r="F76" s="104"/>
-      <c r="G76" s="13"/>
-    </row>
-    <row r="77" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A77" s="37">
-        <f>IF(LEN(C77)=0,"",COUNTA($C$34:C77))</f>
+      <c r="F96" s="104"/>
+      <c r="G96" s="13"/>
+    </row>
+    <row r="97" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A97" s="37">
+        <f>IF(LEN(C97)=0,"",COUNTA($C$54:C97))</f>
         <v>43</v>
       </c>
-      <c r="B77" s="148"/>
-      <c r="C77" s="73" t="s">
+      <c r="B97" s="162"/>
+      <c r="C97" s="73" t="s">
         <v>399</v>
       </c>
-      <c r="D77" s="155"/>
-      <c r="E77" s="39">
+      <c r="D97" s="165"/>
+      <c r="E97" s="39">
         <v>323000</v>
       </c>
-      <c r="F77" s="104"/>
-      <c r="G77" s="13"/>
-    </row>
-    <row r="78" spans="1:7" s="14" customFormat="1" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="37">
-        <f>IF(LEN(C78)=0,"",COUNTA($C$34:C78))</f>
+      <c r="F97" s="104"/>
+      <c r="G97" s="13"/>
+    </row>
+    <row r="98" spans="1:7" s="14" customFormat="1" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="37">
+        <f>IF(LEN(C98)=0,"",COUNTA($C$54:C98))</f>
         <v>44</v>
       </c>
-      <c r="B78" s="148"/>
-      <c r="C78" s="73" t="s">
+      <c r="B98" s="162"/>
+      <c r="C98" s="73" t="s">
         <v>402</v>
       </c>
-      <c r="D78" s="111" t="s">
+      <c r="D98" s="111" t="s">
         <v>401</v>
       </c>
-      <c r="E78" s="39">
+      <c r="E98" s="39">
         <v>269000</v>
       </c>
-      <c r="F78" s="104"/>
-      <c r="G78" s="13"/>
-    </row>
-    <row r="79" spans="1:7" s="14" customFormat="1" ht="66" x14ac:dyDescent="0.25">
-      <c r="A79" s="37">
-        <f>IF(LEN(C79)=0,"",COUNTA($C$34:C79))</f>
+      <c r="F98" s="104"/>
+      <c r="G98" s="13"/>
+    </row>
+    <row r="99" spans="1:7" s="14" customFormat="1" ht="66" x14ac:dyDescent="0.25">
+      <c r="A99" s="37">
+        <f>IF(LEN(C99)=0,"",COUNTA($C$54:C99))</f>
         <v>45</v>
       </c>
-      <c r="B79" s="149"/>
-      <c r="C79" s="73" t="s">
+      <c r="B99" s="163"/>
+      <c r="C99" s="73" t="s">
         <v>403</v>
       </c>
-      <c r="D79" s="111" t="s">
+      <c r="D99" s="111" t="s">
         <v>404</v>
       </c>
-      <c r="E79" s="39">
+      <c r="E99" s="39">
         <v>588000</v>
       </c>
-      <c r="F79" s="104"/>
-      <c r="G79" s="13"/>
-    </row>
-    <row r="80" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A80" s="131" t="s">
+      <c r="F99" s="104"/>
+      <c r="G99" s="13"/>
+    </row>
+    <row r="100" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A100" s="171" t="s">
         <v>207</v>
       </c>
-      <c r="B80" s="132"/>
-      <c r="C80" s="132"/>
-      <c r="D80" s="133"/>
-      <c r="E80" s="66"/>
-      <c r="F80" s="67"/>
-      <c r="G80" s="13"/>
-    </row>
-    <row r="81" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A81" s="37">
-        <f>IF(LEN(C81)=0,"",COUNTA($C$34:C81))</f>
+      <c r="B100" s="172"/>
+      <c r="C100" s="172"/>
+      <c r="D100" s="173"/>
+      <c r="E100" s="66"/>
+      <c r="F100" s="67"/>
+      <c r="G100" s="13"/>
+    </row>
+    <row r="101" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A101" s="37">
+        <f>IF(LEN(C101)=0,"",COUNTA($C$54:C101))</f>
         <v>46</v>
       </c>
-      <c r="B81" s="153" t="s">
+      <c r="B101" s="157" t="s">
         <v>97</v>
       </c>
-      <c r="C81" s="35" t="s">
+      <c r="C101" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="D81" s="35" t="s">
+      <c r="D101" s="35" t="s">
         <v>99</v>
       </c>
-      <c r="E81" s="72">
+      <c r="E101" s="72">
         <v>123000</v>
-      </c>
-      <c r="F81" s="40"/>
-      <c r="G81" s="12"/>
-    </row>
-    <row r="82" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A82" s="37">
-        <f>IF(LEN(C82)=0,"",COUNTA($C$34:C82))</f>
-        <v>47</v>
-      </c>
-      <c r="B82" s="153"/>
-      <c r="C82" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="D82" s="35" t="s">
-        <v>101</v>
-      </c>
-      <c r="E82" s="72">
-        <v>66000</v>
-      </c>
-      <c r="F82" s="40"/>
-      <c r="G82" s="12"/>
-    </row>
-    <row r="83" spans="1:7" ht="115.5" x14ac:dyDescent="0.25">
-      <c r="A83" s="37">
-        <f>IF(LEN(C83)=0,"",COUNTA($C$34:C83))</f>
-        <v>48</v>
-      </c>
-      <c r="B83" s="153"/>
-      <c r="C83" s="35" t="s">
-        <v>102</v>
-      </c>
-      <c r="D83" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="E83" s="72">
-        <v>139000</v>
-      </c>
-      <c r="F83" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="G83" s="12"/>
-    </row>
-    <row r="84" spans="1:7" ht="115.5" x14ac:dyDescent="0.25">
-      <c r="A84" s="37">
-        <f>IF(LEN(C84)=0,"",COUNTA($C$34:C84))</f>
-        <v>49</v>
-      </c>
-      <c r="B84" s="153"/>
-      <c r="C84" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="D84" s="35" t="s">
-        <v>106</v>
-      </c>
-      <c r="E84" s="72">
-        <v>66000</v>
-      </c>
-      <c r="F84" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="G84" s="12"/>
-    </row>
-    <row r="85" spans="1:7" ht="148.5" x14ac:dyDescent="0.25">
-      <c r="A85" s="37">
-        <f>IF(LEN(C85)=0,"",COUNTA($C$34:C85))</f>
-        <v>50</v>
-      </c>
-      <c r="B85" s="153"/>
-      <c r="C85" s="35" t="s">
-        <v>405</v>
-      </c>
-      <c r="D85" s="35" t="s">
-        <v>406</v>
-      </c>
-      <c r="E85" s="72">
-        <v>212000</v>
-      </c>
-      <c r="F85" s="40"/>
-      <c r="G85" s="12"/>
-    </row>
-    <row r="86" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A86" s="37">
-        <f>IF(LEN(C86)=0,"",COUNTA($C$34:C86))</f>
-        <v>51</v>
-      </c>
-      <c r="B86" s="153"/>
-      <c r="C86" s="35" t="s">
-        <v>107</v>
-      </c>
-      <c r="D86" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="E86" s="72">
-        <v>868000</v>
-      </c>
-      <c r="F86" s="108" t="s">
-        <v>109</v>
-      </c>
-      <c r="G86" s="12"/>
-    </row>
-    <row r="87" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A87" s="37">
-        <f>IF(LEN(C87)=0,"",COUNTA($C$34:C87))</f>
-        <v>52</v>
-      </c>
-      <c r="B87" s="153"/>
-      <c r="C87" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="D87" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="E87" s="72">
-        <v>139000</v>
-      </c>
-      <c r="F87" s="108" t="s">
-        <v>112</v>
-      </c>
-      <c r="G87" s="12"/>
-    </row>
-    <row r="88" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A88" s="37">
-        <f>IF(LEN(C88)=0,"",COUNTA($C$34:C88))</f>
-        <v>53</v>
-      </c>
-      <c r="B88" s="153"/>
-      <c r="C88" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="D88" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="E88" s="72">
-        <v>72000</v>
-      </c>
-      <c r="F88" s="108" t="s">
-        <v>115</v>
-      </c>
-      <c r="G88" s="12"/>
-    </row>
-    <row r="89" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A89" s="37">
-        <f>IF(LEN(C89)=0,"",COUNTA($C$34:C89))</f>
-        <v>54</v>
-      </c>
-      <c r="B89" s="153" t="s">
-        <v>116</v>
-      </c>
-      <c r="C89" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="D89" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="E89" s="72">
-        <v>174000</v>
-      </c>
-      <c r="F89" s="40"/>
-      <c r="G89" s="12"/>
-    </row>
-    <row r="90" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A90" s="37">
-        <f>IF(LEN(C90)=0,"",COUNTA($C$34:C90))</f>
-        <v>55</v>
-      </c>
-      <c r="B90" s="153"/>
-      <c r="C90" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="D90" s="35" t="s">
-        <v>120</v>
-      </c>
-      <c r="E90" s="72">
-        <v>88000</v>
-      </c>
-      <c r="F90" s="40"/>
-      <c r="G90" s="12"/>
-    </row>
-    <row r="91" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A91" s="37">
-        <f>IF(LEN(C91)=0,"",COUNTA($C$34:C91))</f>
-        <v>56</v>
-      </c>
-      <c r="B91" s="137" t="s">
-        <v>121</v>
-      </c>
-      <c r="C91" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="D91" s="35" t="s">
-        <v>123</v>
-      </c>
-      <c r="E91" s="68">
-        <v>168000</v>
-      </c>
-      <c r="F91" s="40"/>
-      <c r="G91" s="12"/>
-    </row>
-    <row r="92" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A92" s="37">
-        <f>IF(LEN(C92)=0,"",COUNTA($C$34:C92))</f>
-        <v>57</v>
-      </c>
-      <c r="B92" s="139"/>
-      <c r="C92" s="35" t="s">
-        <v>388</v>
-      </c>
-      <c r="D92" s="35" t="s">
-        <v>124</v>
-      </c>
-      <c r="E92" s="68">
-        <v>168000</v>
-      </c>
-      <c r="F92" s="40"/>
-      <c r="G92" s="12"/>
-    </row>
-    <row r="93" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A93" s="37">
-        <f>IF(LEN(C93)=0,"",COUNTA($C$34:C93))</f>
-        <v>58</v>
-      </c>
-      <c r="B93" s="138"/>
-      <c r="C93" s="35" t="s">
-        <v>125</v>
-      </c>
-      <c r="D93" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="E93" s="68">
-        <v>253000</v>
-      </c>
-      <c r="F93" s="40"/>
-      <c r="G93" s="12"/>
-    </row>
-    <row r="94" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A94" s="131" t="s">
-        <v>261</v>
-      </c>
-      <c r="B94" s="132"/>
-      <c r="C94" s="132"/>
-      <c r="D94" s="133"/>
-      <c r="E94" s="77"/>
-      <c r="F94" s="67"/>
-      <c r="G94" s="12"/>
-    </row>
-    <row r="95" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A95" s="37">
-        <f>IF(LEN(C95)=0,"",COUNTA($C$34:C95))</f>
-        <v>59</v>
-      </c>
-      <c r="B95" s="143" t="s">
-        <v>240</v>
-      </c>
-      <c r="C95" s="35" t="s">
-        <v>236</v>
-      </c>
-      <c r="D95" s="35" t="s">
-        <v>237</v>
-      </c>
-      <c r="E95" s="68">
-        <v>250000</v>
-      </c>
-      <c r="F95" s="40"/>
-      <c r="G95" s="12"/>
-    </row>
-    <row r="96" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A96" s="37">
-        <f>IF(LEN(C96)=0,"",COUNTA($C$34:C96))</f>
-        <v>60</v>
-      </c>
-      <c r="B96" s="145"/>
-      <c r="C96" s="35" t="s">
-        <v>239</v>
-      </c>
-      <c r="D96" s="35" t="s">
-        <v>238</v>
-      </c>
-      <c r="E96" s="68">
-        <v>399000</v>
-      </c>
-      <c r="F96" s="40"/>
-      <c r="G96" s="12"/>
-    </row>
-    <row r="97" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A97" s="37">
-        <f>IF(LEN(C97)=0,"",COUNTA($C$34:C97))</f>
-        <v>61</v>
-      </c>
-      <c r="B97" s="137" t="s">
-        <v>243</v>
-      </c>
-      <c r="C97" s="35" t="s">
-        <v>241</v>
-      </c>
-      <c r="D97" s="35"/>
-      <c r="E97" s="68">
-        <v>2500000</v>
-      </c>
-      <c r="F97" s="40"/>
-      <c r="G97" s="12"/>
-    </row>
-    <row r="98" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A98" s="37">
-        <f>IF(LEN(C98)=0,"",COUNTA($C$34:C98))</f>
-        <v>62</v>
-      </c>
-      <c r="B98" s="138"/>
-      <c r="C98" s="35" t="s">
-        <v>242</v>
-      </c>
-      <c r="D98" s="35"/>
-      <c r="E98" s="68">
-        <v>2200000</v>
-      </c>
-      <c r="F98" s="40"/>
-      <c r="G98" s="12"/>
-    </row>
-    <row r="99" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A99" s="37">
-        <f>IF(LEN(C99)=0,"",COUNTA($C$34:C99))</f>
-        <v>63</v>
-      </c>
-      <c r="B99" s="103" t="s">
-        <v>311</v>
-      </c>
-      <c r="C99" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="D99" s="35"/>
-      <c r="E99" s="68">
-        <v>250000</v>
-      </c>
-      <c r="F99" s="40" t="s">
-        <v>335</v>
-      </c>
-      <c r="G99" s="12"/>
-    </row>
-    <row r="100" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A100" s="37">
-        <f>IF(LEN(C100)=0,"",COUNTA($C$34:C100))</f>
-        <v>64</v>
-      </c>
-      <c r="B100" s="137" t="s">
-        <v>258</v>
-      </c>
-      <c r="C100" s="35" t="s">
-        <v>244</v>
-      </c>
-      <c r="D100" s="35"/>
-      <c r="E100" s="68">
-        <v>275000</v>
-      </c>
-      <c r="F100" s="40"/>
-      <c r="G100" s="12"/>
-    </row>
-    <row r="101" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A101" s="37">
-        <f>IF(LEN(C101)=0,"",COUNTA($C$34:C101))</f>
-        <v>65</v>
-      </c>
-      <c r="B101" s="139"/>
-      <c r="C101" s="35" t="s">
-        <v>245</v>
-      </c>
-      <c r="D101" s="35"/>
-      <c r="E101" s="68">
-        <v>187000</v>
       </c>
       <c r="F101" s="40"/>
       <c r="G101" s="12"/>
     </row>
-    <row r="102" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A102" s="37">
-        <f>IF(LEN(C102)=0,"",COUNTA($C$34:C102))</f>
-        <v>66</v>
-      </c>
-      <c r="B102" s="139"/>
+        <f>IF(LEN(C102)=0,"",COUNTA($C$54:C102))</f>
+        <v>47</v>
+      </c>
+      <c r="B102" s="157"/>
       <c r="C102" s="35" t="s">
-        <v>246</v>
-      </c>
-      <c r="D102" s="35"/>
-      <c r="E102" s="68">
-        <v>187000</v>
+        <v>100</v>
+      </c>
+      <c r="D102" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="E102" s="72">
+        <v>66000</v>
       </c>
       <c r="F102" s="40"/>
       <c r="G102" s="12"/>
     </row>
-    <row r="103" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" ht="115.5" x14ac:dyDescent="0.25">
       <c r="A103" s="37">
-        <f>IF(LEN(C103)=0,"",COUNTA($C$34:C103))</f>
-        <v>67</v>
-      </c>
-      <c r="B103" s="139"/>
+        <f>IF(LEN(C103)=0,"",COUNTA($C$54:C103))</f>
+        <v>48</v>
+      </c>
+      <c r="B103" s="157"/>
       <c r="C103" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="D103" s="35"/>
-      <c r="E103" s="68">
-        <v>189000</v>
-      </c>
-      <c r="F103" s="40"/>
+        <v>102</v>
+      </c>
+      <c r="D103" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="E103" s="72">
+        <v>139000</v>
+      </c>
+      <c r="F103" s="40" t="s">
+        <v>104</v>
+      </c>
       <c r="G103" s="12"/>
     </row>
-    <row r="104" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" ht="115.5" x14ac:dyDescent="0.25">
       <c r="A104" s="37">
-        <f>IF(LEN(C104)=0,"",COUNTA($C$34:C104))</f>
-        <v>68</v>
-      </c>
-      <c r="B104" s="139"/>
+        <f>IF(LEN(C104)=0,"",COUNTA($C$54:C104))</f>
+        <v>49</v>
+      </c>
+      <c r="B104" s="157"/>
       <c r="C104" s="35" t="s">
-        <v>248</v>
-      </c>
-      <c r="D104" s="35"/>
-      <c r="E104" s="68">
-        <v>150000</v>
-      </c>
-      <c r="F104" s="40"/>
+        <v>105</v>
+      </c>
+      <c r="D104" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="E104" s="72">
+        <v>66000</v>
+      </c>
+      <c r="F104" s="40" t="s">
+        <v>104</v>
+      </c>
       <c r="G104" s="12"/>
     </row>
-    <row r="105" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" ht="148.5" x14ac:dyDescent="0.25">
       <c r="A105" s="37">
-        <f>IF(LEN(C105)=0,"",COUNTA($C$34:C105))</f>
-        <v>69</v>
-      </c>
-      <c r="B105" s="139"/>
+        <f>IF(LEN(C105)=0,"",COUNTA($C$54:C105))</f>
+        <v>50</v>
+      </c>
+      <c r="B105" s="157"/>
       <c r="C105" s="35" t="s">
-        <v>249</v>
-      </c>
-      <c r="D105" s="35"/>
-      <c r="E105" s="68">
-        <v>189000</v>
+        <v>405</v>
+      </c>
+      <c r="D105" s="35" t="s">
+        <v>406</v>
+      </c>
+      <c r="E105" s="72">
+        <v>212000</v>
       </c>
       <c r="F105" s="40"/>
       <c r="G105" s="12"/>
     </row>
-    <row r="106" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A106" s="37">
-        <f>IF(LEN(C106)=0,"",COUNTA($C$34:C106))</f>
-        <v>70</v>
-      </c>
-      <c r="B106" s="139"/>
+        <f>IF(LEN(C106)=0,"",COUNTA($C$54:C106))</f>
+        <v>51</v>
+      </c>
+      <c r="B106" s="157"/>
       <c r="C106" s="35" t="s">
-        <v>250</v>
-      </c>
-      <c r="D106" s="35"/>
-      <c r="E106" s="68">
-        <v>189000</v>
-      </c>
-      <c r="F106" s="40"/>
+        <v>107</v>
+      </c>
+      <c r="D106" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="E106" s="72">
+        <v>868000</v>
+      </c>
+      <c r="F106" s="108" t="s">
+        <v>109</v>
+      </c>
       <c r="G106" s="12"/>
     </row>
-    <row r="107" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A107" s="37">
-        <f>IF(LEN(C107)=0,"",COUNTA($C$34:C107))</f>
-        <v>71</v>
-      </c>
-      <c r="B107" s="139"/>
+        <f>IF(LEN(C107)=0,"",COUNTA($C$54:C107))</f>
+        <v>52</v>
+      </c>
+      <c r="B107" s="157"/>
       <c r="C107" s="35" t="s">
-        <v>251</v>
-      </c>
-      <c r="D107" s="35"/>
-      <c r="E107" s="68">
-        <v>187000</v>
-      </c>
-      <c r="F107" s="40"/>
+        <v>110</v>
+      </c>
+      <c r="D107" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="E107" s="72">
+        <v>139000</v>
+      </c>
+      <c r="F107" s="108" t="s">
+        <v>112</v>
+      </c>
       <c r="G107" s="12"/>
     </row>
-    <row r="108" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A108" s="37">
-        <f>IF(LEN(C108)=0,"",COUNTA($C$34:C108))</f>
-        <v>72</v>
-      </c>
-      <c r="B108" s="139"/>
+        <f>IF(LEN(C108)=0,"",COUNTA($C$54:C108))</f>
+        <v>53</v>
+      </c>
+      <c r="B108" s="157"/>
       <c r="C108" s="35" t="s">
-        <v>252</v>
-      </c>
-      <c r="D108" s="35"/>
-      <c r="E108" s="68">
-        <v>201000</v>
-      </c>
-      <c r="F108" s="40"/>
+        <v>113</v>
+      </c>
+      <c r="D108" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="E108" s="72">
+        <v>72000</v>
+      </c>
+      <c r="F108" s="108" t="s">
+        <v>115</v>
+      </c>
       <c r="G108" s="12"/>
     </row>
-    <row r="109" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A109" s="37">
-        <f>IF(LEN(C109)=0,"",COUNTA($C$34:C109))</f>
-        <v>73</v>
-      </c>
-      <c r="B109" s="139"/>
+        <f>IF(LEN(C109)=0,"",COUNTA($C$54:C109))</f>
+        <v>54</v>
+      </c>
+      <c r="B109" s="157" t="s">
+        <v>116</v>
+      </c>
       <c r="C109" s="35" t="s">
-        <v>253</v>
-      </c>
-      <c r="D109" s="35"/>
-      <c r="E109" s="68">
-        <v>187000</v>
+        <v>117</v>
+      </c>
+      <c r="D109" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="E109" s="72">
+        <v>174000</v>
       </c>
       <c r="F109" s="40"/>
       <c r="G109" s="12"/>
     </row>
-    <row r="110" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A110" s="37">
-        <f>IF(LEN(C110)=0,"",COUNTA($C$34:C110))</f>
-        <v>74</v>
-      </c>
-      <c r="B110" s="139"/>
+        <f>IF(LEN(C110)=0,"",COUNTA($C$54:C110))</f>
+        <v>55</v>
+      </c>
+      <c r="B110" s="157"/>
       <c r="C110" s="35" t="s">
-        <v>254</v>
-      </c>
-      <c r="D110" s="35"/>
-      <c r="E110" s="68">
-        <v>187000</v>
+        <v>119</v>
+      </c>
+      <c r="D110" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="E110" s="72">
+        <v>88000</v>
       </c>
       <c r="F110" s="40"/>
       <c r="G110" s="12"/>
     </row>
-    <row r="111" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A111" s="37">
-        <f>IF(LEN(C111)=0,"",COUNTA($C$34:C111))</f>
-        <v>75</v>
-      </c>
-      <c r="B111" s="139"/>
+        <f>IF(LEN(C111)=0,"",COUNTA($C$54:C111))</f>
+        <v>56</v>
+      </c>
+      <c r="B111" s="166" t="s">
+        <v>121</v>
+      </c>
       <c r="C111" s="35" t="s">
-        <v>255</v>
-      </c>
-      <c r="D111" s="35"/>
+        <v>122</v>
+      </c>
+      <c r="D111" s="35" t="s">
+        <v>123</v>
+      </c>
       <c r="E111" s="68">
-        <v>132000</v>
+        <v>168000</v>
       </c>
       <c r="F111" s="40"/>
       <c r="G111" s="12"/>
     </row>
-    <row r="112" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A112" s="37">
-        <f>IF(LEN(C112)=0,"",COUNTA($C$34:C112))</f>
-        <v>76</v>
-      </c>
-      <c r="B112" s="139"/>
+        <f>IF(LEN(C112)=0,"",COUNTA($C$54:C112))</f>
+        <v>57</v>
+      </c>
+      <c r="B112" s="177"/>
       <c r="C112" s="35" t="s">
-        <v>256</v>
-      </c>
-      <c r="D112" s="35"/>
+        <v>388</v>
+      </c>
+      <c r="D112" s="35" t="s">
+        <v>124</v>
+      </c>
       <c r="E112" s="68">
-        <v>187000</v>
+        <v>168000</v>
       </c>
       <c r="F112" s="40"/>
       <c r="G112" s="12"/>
     </row>
     <row r="113" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A113" s="37">
-        <f>IF(LEN(C113)=0,"",COUNTA($C$34:C113))</f>
-        <v>77</v>
-      </c>
-      <c r="B113" s="138"/>
+        <f>IF(LEN(C113)=0,"",COUNTA($C$54:C113))</f>
+        <v>58</v>
+      </c>
+      <c r="B113" s="167"/>
       <c r="C113" s="35" t="s">
-        <v>257</v>
-      </c>
-      <c r="D113" s="35"/>
+        <v>125</v>
+      </c>
+      <c r="D113" s="35" t="s">
+        <v>126</v>
+      </c>
       <c r="E113" s="68">
-        <v>1073000</v>
+        <v>253000</v>
       </c>
       <c r="F113" s="40"/>
       <c r="G113" s="12"/>
     </row>
     <row r="114" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="131" t="s">
-        <v>226</v>
-      </c>
-      <c r="B114" s="132"/>
-      <c r="C114" s="132"/>
-      <c r="D114" s="133"/>
-      <c r="E114" s="66"/>
+      <c r="A114" s="171" t="s">
+        <v>261</v>
+      </c>
+      <c r="B114" s="172"/>
+      <c r="C114" s="172"/>
+      <c r="D114" s="173"/>
+      <c r="E114" s="77"/>
       <c r="F114" s="67"/>
       <c r="G114" s="12"/>
     </row>
-    <row r="115" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A115" s="37">
-        <f>IF(LEN(C115)=0,"",COUNTA($C$34:C115))</f>
-        <v>78</v>
-      </c>
-      <c r="B115" s="71" t="s">
-        <v>231</v>
+        <f>IF(LEN(C115)=0,"",COUNTA($C$54:C115))</f>
+        <v>59</v>
+      </c>
+      <c r="B115" s="140" t="s">
+        <v>240</v>
       </c>
       <c r="C115" s="35" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D115" s="35" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="E115" s="68">
-        <v>50000</v>
+        <v>250000</v>
       </c>
       <c r="F115" s="40"/>
       <c r="G115" s="12"/>
     </row>
     <row r="116" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A116" s="37">
-        <f>IF(LEN(C116)=0,"",COUNTA($C$34:C116))</f>
-        <v>79</v>
-      </c>
-      <c r="B116" s="71" t="s">
-        <v>230</v>
-      </c>
+        <f>IF(LEN(C116)=0,"",COUNTA($C$54:C116))</f>
+        <v>60</v>
+      </c>
+      <c r="B116" s="142"/>
       <c r="C116" s="35" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="D116" s="35" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="E116" s="68">
-        <v>108000</v>
+        <v>399000</v>
       </c>
       <c r="F116" s="40"/>
       <c r="G116" s="12"/>
     </row>
     <row r="117" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A117" s="127" t="s">
-        <v>262</v>
-      </c>
-      <c r="B117" s="127"/>
-      <c r="C117" s="127"/>
-      <c r="D117" s="127"/>
-      <c r="E117" s="77"/>
-      <c r="F117" s="67"/>
+      <c r="A117" s="37">
+        <f>IF(LEN(C117)=0,"",COUNTA($C$54:C117))</f>
+        <v>61</v>
+      </c>
+      <c r="B117" s="166" t="s">
+        <v>243</v>
+      </c>
+      <c r="C117" s="35" t="s">
+        <v>241</v>
+      </c>
+      <c r="D117" s="35"/>
+      <c r="E117" s="68">
+        <v>2500000</v>
+      </c>
+      <c r="F117" s="40"/>
       <c r="G117" s="12"/>
     </row>
-    <row r="118" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A118" s="37">
-        <f>IF(LEN(C118)=0,"",COUNTA($C$34:C118))</f>
-        <v>80</v>
-      </c>
-      <c r="B118" s="140" t="s">
-        <v>204</v>
-      </c>
-      <c r="C118" s="36" t="s">
-        <v>323</v>
-      </c>
-      <c r="D118" s="36" t="s">
-        <v>11</v>
-      </c>
-      <c r="E118" s="105">
-        <v>230000</v>
+        <f>IF(LEN(C118)=0,"",COUNTA($C$54:C118))</f>
+        <v>62</v>
+      </c>
+      <c r="B118" s="167"/>
+      <c r="C118" s="35" t="s">
+        <v>242</v>
+      </c>
+      <c r="D118" s="35"/>
+      <c r="E118" s="68">
+        <v>2200000</v>
       </c>
       <c r="F118" s="40"/>
       <c r="G118" s="12"/>
     </row>
-    <row r="119" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A119" s="37">
-        <f>IF(LEN(C119)=0,"",COUNTA($C$34:C119))</f>
-        <v>81</v>
-      </c>
-      <c r="B119" s="141"/>
-      <c r="C119" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="D119" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E119" s="105">
-        <v>220000</v>
-      </c>
-      <c r="F119" s="40"/>
+        <f>IF(LEN(C119)=0,"",COUNTA($C$54:C119))</f>
+        <v>63</v>
+      </c>
+      <c r="B119" s="103" t="s">
+        <v>311</v>
+      </c>
+      <c r="C119" s="35" t="s">
+        <v>374</v>
+      </c>
+      <c r="D119" s="35"/>
+      <c r="E119" s="68">
+        <v>250000</v>
+      </c>
+      <c r="F119" s="40" t="s">
+        <v>335</v>
+      </c>
       <c r="G119" s="12"/>
     </row>
-    <row r="120" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A120" s="37">
-        <f>IF(LEN(C120)=0,"",COUNTA($C$34:C120))</f>
-        <v>82</v>
-      </c>
-      <c r="B120" s="141"/>
-      <c r="C120" s="36" t="s">
-        <v>324</v>
-      </c>
-      <c r="D120" s="107" t="s">
-        <v>328</v>
-      </c>
-      <c r="E120" s="105">
-        <v>230000</v>
+        <f>IF(LEN(C120)=0,"",COUNTA($C$54:C120))</f>
+        <v>64</v>
+      </c>
+      <c r="B120" s="166" t="s">
+        <v>258</v>
+      </c>
+      <c r="C120" s="35" t="s">
+        <v>244</v>
+      </c>
+      <c r="D120" s="35"/>
+      <c r="E120" s="68">
+        <v>275000</v>
       </c>
       <c r="F120" s="40"/>
       <c r="G120" s="12"/>
     </row>
-    <row r="121" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A121" s="37">
-        <f>IF(LEN(C121)=0,"",COUNTA($C$34:C121))</f>
-        <v>83</v>
-      </c>
-      <c r="B121" s="141"/>
+        <f>IF(LEN(C121)=0,"",COUNTA($C$54:C121))</f>
+        <v>65</v>
+      </c>
+      <c r="B121" s="177"/>
       <c r="C121" s="35" t="s">
-        <v>407</v>
+        <v>245</v>
       </c>
       <c r="D121" s="35"/>
-      <c r="E121" s="72">
-        <v>250000</v>
+      <c r="E121" s="68">
+        <v>187000</v>
       </c>
       <c r="F121" s="40"/>
       <c r="G121" s="12"/>
     </row>
     <row r="122" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A122" s="37">
-        <f>IF(LEN(C122)=0,"",COUNTA($C$34:C122))</f>
-        <v>84</v>
-      </c>
-      <c r="B122" s="141"/>
+        <f>IF(LEN(C122)=0,"",COUNTA($C$54:C122))</f>
+        <v>66</v>
+      </c>
+      <c r="B122" s="177"/>
       <c r="C122" s="35" t="s">
-        <v>408</v>
+        <v>246</v>
       </c>
       <c r="D122" s="35"/>
-      <c r="E122" s="72">
-        <v>375000</v>
+      <c r="E122" s="68">
+        <v>187000</v>
       </c>
       <c r="F122" s="40"/>
       <c r="G122" s="12"/>
     </row>
-    <row r="123" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A123" s="37">
-        <f>IF(LEN(C123)=0,"",COUNTA($C$34:C123))</f>
-        <v>85</v>
-      </c>
-      <c r="B123" s="141"/>
+        <f>IF(LEN(C123)=0,"",COUNTA($C$54:C123))</f>
+        <v>67</v>
+      </c>
+      <c r="B123" s="177"/>
       <c r="C123" s="35" t="s">
-        <v>409</v>
+        <v>247</v>
       </c>
       <c r="D123" s="35"/>
-      <c r="E123" s="72">
-        <v>500000</v>
+      <c r="E123" s="68">
+        <v>189000</v>
       </c>
       <c r="F123" s="40"/>
       <c r="G123" s="12"/>
     </row>
-    <row r="124" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A124" s="37">
-        <f>IF(LEN(C124)=0,"",COUNTA($C$34:C124))</f>
-        <v>86</v>
-      </c>
-      <c r="B124" s="141"/>
-      <c r="C124" s="36" t="s">
-        <v>410</v>
-      </c>
-      <c r="D124" s="36" t="s">
-        <v>137</v>
-      </c>
+        <f>IF(LEN(C124)=0,"",COUNTA($C$54:C124))</f>
+        <v>68</v>
+      </c>
+      <c r="B124" s="177"/>
+      <c r="C124" s="35" t="s">
+        <v>248</v>
+      </c>
+      <c r="D124" s="35"/>
       <c r="E124" s="68">
-        <v>700000</v>
+        <v>150000</v>
       </c>
       <c r="F124" s="40"/>
       <c r="G124" s="12"/>
     </row>
-    <row r="125" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A125" s="37">
-        <f>IF(LEN(C125)=0,"",COUNTA($C$34:C125))</f>
-        <v>87</v>
-      </c>
-      <c r="B125" s="141"/>
-      <c r="C125" s="36" t="s">
-        <v>138</v>
-      </c>
-      <c r="D125" s="107" t="s">
-        <v>329</v>
-      </c>
+        <f>IF(LEN(C125)=0,"",COUNTA($C$54:C125))</f>
+        <v>69</v>
+      </c>
+      <c r="B125" s="177"/>
+      <c r="C125" s="35" t="s">
+        <v>249</v>
+      </c>
+      <c r="D125" s="35"/>
       <c r="E125" s="68">
-        <v>770000</v>
+        <v>189000</v>
       </c>
       <c r="F125" s="40"/>
       <c r="G125" s="12"/>
     </row>
-    <row r="126" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A126" s="37">
-        <f>IF(LEN(C126)=0,"",COUNTA($C$34:C126))</f>
-        <v>88</v>
-      </c>
-      <c r="B126" s="142"/>
-      <c r="C126" s="36" t="s">
-        <v>139</v>
-      </c>
-      <c r="D126" s="36" t="s">
-        <v>140</v>
-      </c>
+        <f>IF(LEN(C126)=0,"",COUNTA($C$54:C126))</f>
+        <v>70</v>
+      </c>
+      <c r="B126" s="177"/>
+      <c r="C126" s="35" t="s">
+        <v>250</v>
+      </c>
+      <c r="D126" s="35"/>
       <c r="E126" s="68">
-        <v>249000</v>
+        <v>189000</v>
       </c>
       <c r="F126" s="40"/>
       <c r="G126" s="12"/>
     </row>
-    <row r="127" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A127" s="37">
-        <f>IF(LEN(C127)=0,"",COUNTA($C$34:C127))</f>
-        <v>89</v>
-      </c>
-      <c r="B127" s="143" t="s">
-        <v>282</v>
-      </c>
+        <f>IF(LEN(C127)=0,"",COUNTA($C$54:C127))</f>
+        <v>71</v>
+      </c>
+      <c r="B127" s="177"/>
       <c r="C127" s="35" t="s">
-        <v>141</v>
-      </c>
-      <c r="D127" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="E127" s="72">
-        <v>157000</v>
+        <v>251</v>
+      </c>
+      <c r="D127" s="35"/>
+      <c r="E127" s="68">
+        <v>187000</v>
       </c>
       <c r="F127" s="40"/>
       <c r="G127" s="12"/>
     </row>
-    <row r="128" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A128" s="37">
-        <f>IF(LEN(C128)=0,"",COUNTA($C$34:C128))</f>
-        <v>90</v>
-      </c>
-      <c r="B128" s="144"/>
+        <f>IF(LEN(C128)=0,"",COUNTA($C$54:C128))</f>
+        <v>72</v>
+      </c>
+      <c r="B128" s="177"/>
       <c r="C128" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="D128" s="35" t="s">
-        <v>144</v>
-      </c>
-      <c r="E128" s="72">
-        <v>157000</v>
+        <v>252</v>
+      </c>
+      <c r="D128" s="35"/>
+      <c r="E128" s="68">
+        <v>201000</v>
       </c>
       <c r="F128" s="40"/>
       <c r="G128" s="12"/>
     </row>
     <row r="129" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A129" s="37">
-        <f>IF(LEN(C129)=0,"",COUNTA($C$34:C129))</f>
-        <v>91</v>
-      </c>
-      <c r="B129" s="144"/>
+        <f>IF(LEN(C129)=0,"",COUNTA($C$54:C129))</f>
+        <v>73</v>
+      </c>
+      <c r="B129" s="177"/>
       <c r="C129" s="35" t="s">
-        <v>392</v>
-      </c>
-      <c r="D129" s="35" t="s">
-        <v>393</v>
-      </c>
-      <c r="E129" s="72">
-        <v>143000</v>
+        <v>253</v>
+      </c>
+      <c r="D129" s="35"/>
+      <c r="E129" s="68">
+        <v>187000</v>
       </c>
       <c r="F129" s="40"/>
       <c r="G129" s="12"/>
     </row>
     <row r="130" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A130" s="37">
-        <f>IF(LEN(C130)=0,"",COUNTA($C$34:C130))</f>
-        <v>92</v>
-      </c>
-      <c r="B130" s="144"/>
+        <f>IF(LEN(C130)=0,"",COUNTA($C$54:C130))</f>
+        <v>74</v>
+      </c>
+      <c r="B130" s="177"/>
       <c r="C130" s="35" t="s">
-        <v>394</v>
-      </c>
-      <c r="D130" s="35" t="s">
-        <v>393</v>
-      </c>
-      <c r="E130" s="72">
-        <v>185000</v>
+        <v>254</v>
+      </c>
+      <c r="D130" s="35"/>
+      <c r="E130" s="68">
+        <v>187000</v>
       </c>
       <c r="F130" s="40"/>
       <c r="G130" s="12"/>
     </row>
-    <row r="131" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A131" s="37">
-        <f>IF(LEN(C131)=0,"",COUNTA($C$34:C131))</f>
-        <v>93</v>
-      </c>
-      <c r="B131" s="144"/>
+        <f>IF(LEN(C131)=0,"",COUNTA($C$54:C131))</f>
+        <v>75</v>
+      </c>
+      <c r="B131" s="177"/>
       <c r="C131" s="35" t="s">
-        <v>369</v>
-      </c>
-      <c r="D131" s="35" t="s">
-        <v>370</v>
-      </c>
-      <c r="E131" s="72">
-        <v>1200000</v>
-      </c>
-      <c r="F131" s="108"/>
+        <v>255</v>
+      </c>
+      <c r="D131" s="35"/>
+      <c r="E131" s="68">
+        <v>132000</v>
+      </c>
+      <c r="F131" s="40"/>
       <c r="G131" s="12"/>
     </row>
-    <row r="132" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A132" s="37">
-        <f>IF(LEN(C132)=0,"",COUNTA($C$34:C132))</f>
-        <v>94</v>
-      </c>
-      <c r="B132" s="145"/>
+        <f>IF(LEN(C132)=0,"",COUNTA($C$54:C132))</f>
+        <v>76</v>
+      </c>
+      <c r="B132" s="177"/>
       <c r="C132" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="D132" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="E132" s="72"/>
+        <v>256</v>
+      </c>
+      <c r="D132" s="35"/>
+      <c r="E132" s="68">
+        <v>187000</v>
+      </c>
       <c r="F132" s="40"/>
       <c r="G132" s="12"/>
     </row>
-    <row r="133" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A133" s="37">
-        <f>IF(LEN(C133)=0,"",COUNTA($C$34:C133))</f>
-        <v>95</v>
-      </c>
-      <c r="B133" s="144" t="s">
-        <v>283</v>
-      </c>
+        <f>IF(LEN(C133)=0,"",COUNTA($C$54:C133))</f>
+        <v>77</v>
+      </c>
+      <c r="B133" s="167"/>
       <c r="C133" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="D133" s="35" t="s">
-        <v>150</v>
-      </c>
-      <c r="E133" s="72"/>
+        <v>257</v>
+      </c>
+      <c r="D133" s="35"/>
+      <c r="E133" s="68">
+        <v>1073000</v>
+      </c>
       <c r="F133" s="40"/>
       <c r="G133" s="12"/>
     </row>
-    <row r="134" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A134" s="37">
-        <f>IF(LEN(C134)=0,"",COUNTA($C$34:C134))</f>
-        <v>96</v>
-      </c>
-      <c r="B134" s="144"/>
-      <c r="C134" s="35" t="s">
-        <v>330</v>
-      </c>
-      <c r="D134" s="107" t="s">
-        <v>331</v>
-      </c>
-      <c r="E134" s="72">
-        <v>700000</v>
-      </c>
-      <c r="F134" s="40"/>
+    <row r="134" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A134" s="171" t="s">
+        <v>226</v>
+      </c>
+      <c r="B134" s="172"/>
+      <c r="C134" s="172"/>
+      <c r="D134" s="173"/>
+      <c r="E134" s="66"/>
+      <c r="F134" s="67"/>
       <c r="G134" s="12"/>
     </row>
-    <row r="135" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A135" s="37">
-        <f>IF(LEN(C135)=0,"",COUNTA($C$34:C135))</f>
-        <v>97</v>
-      </c>
-      <c r="B135" s="144"/>
+        <f>IF(LEN(C135)=0,"",COUNTA($C$54:C135))</f>
+        <v>78</v>
+      </c>
+      <c r="B135" s="71" t="s">
+        <v>231</v>
+      </c>
       <c r="C135" s="35" t="s">
-        <v>151</v>
+        <v>232</v>
       </c>
       <c r="D135" s="35" t="s">
-        <v>152</v>
+        <v>227</v>
       </c>
       <c r="E135" s="68">
-        <v>847000</v>
+        <v>50000</v>
       </c>
       <c r="F135" s="40"/>
       <c r="G135" s="12"/>
     </row>
-    <row r="136" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A136" s="37">
-        <f>IF(LEN(C136)=0,"",COUNTA($C$34:C136))</f>
-        <v>98</v>
-      </c>
-      <c r="B136" s="144"/>
+        <f>IF(LEN(C136)=0,"",COUNTA($C$54:C136))</f>
+        <v>79</v>
+      </c>
+      <c r="B136" s="71" t="s">
+        <v>230</v>
+      </c>
       <c r="C136" s="35" t="s">
-        <v>153</v>
+        <v>228</v>
       </c>
       <c r="D136" s="35" t="s">
-        <v>154</v>
+        <v>229</v>
       </c>
       <c r="E136" s="68">
-        <v>2178000</v>
+        <v>108000</v>
       </c>
       <c r="F136" s="40"/>
       <c r="G136" s="12"/>
     </row>
-    <row r="137" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A137" s="37">
-        <f>IF(LEN(C137)=0,"",COUNTA($C$34:C137))</f>
-        <v>99</v>
-      </c>
-      <c r="B137" s="144"/>
-      <c r="C137" s="35" t="s">
-        <v>155</v>
-      </c>
-      <c r="D137" s="35" t="s">
-        <v>156</v>
-      </c>
-      <c r="E137" s="68">
-        <v>847000</v>
-      </c>
-      <c r="F137" s="40"/>
+    <row r="137" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A137" s="178" t="s">
+        <v>262</v>
+      </c>
+      <c r="B137" s="178"/>
+      <c r="C137" s="178"/>
+      <c r="D137" s="178"/>
+      <c r="E137" s="77"/>
+      <c r="F137" s="67"/>
       <c r="G137" s="12"/>
     </row>
-    <row r="138" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A138" s="37">
-        <f>IF(LEN(C138)=0,"",COUNTA($C$34:C138))</f>
-        <v>100</v>
-      </c>
-      <c r="B138" s="144"/>
-      <c r="C138" s="35" t="s">
-        <v>157</v>
-      </c>
-      <c r="D138" s="107" t="s">
-        <v>332</v>
-      </c>
-      <c r="E138" s="68">
-        <v>1700000</v>
+        <f>IF(LEN(C138)=0,"",COUNTA($C$54:C138))</f>
+        <v>80</v>
+      </c>
+      <c r="B138" s="179" t="s">
+        <v>204</v>
+      </c>
+      <c r="C138" s="36" t="s">
+        <v>323</v>
+      </c>
+      <c r="D138" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E138" s="105">
+        <v>230000</v>
       </c>
       <c r="F138" s="40"/>
       <c r="G138" s="12"/>
     </row>
-    <row r="139" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A139" s="37">
-        <f>IF(LEN(C139)=0,"",COUNTA($C$34:C139))</f>
-        <v>101</v>
-      </c>
-      <c r="B139" s="144"/>
-      <c r="C139" s="35" t="s">
-        <v>158</v>
-      </c>
-      <c r="D139" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="E139" s="68"/>
+        <f>IF(LEN(C139)=0,"",COUNTA($C$54:C139))</f>
+        <v>81</v>
+      </c>
+      <c r="B139" s="180"/>
+      <c r="C139" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D139" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E139" s="105">
+        <v>220000</v>
+      </c>
       <c r="F139" s="40"/>
       <c r="G139" s="12"/>
     </row>
-    <row r="140" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A140" s="37">
-        <f>IF(LEN(C140)=0,"",COUNTA($C$34:C140))</f>
-        <v>102</v>
-      </c>
-      <c r="B140" s="146" t="s">
-        <v>304</v>
-      </c>
-      <c r="C140" s="35" t="s">
-        <v>341</v>
-      </c>
-      <c r="D140" s="35" t="s">
-        <v>284</v>
-      </c>
-      <c r="E140" s="106">
-        <v>3420000</v>
-      </c>
-      <c r="F140" s="112" t="s">
-        <v>334</v>
-      </c>
-      <c r="G140" s="113"/>
-    </row>
-    <row r="141" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+        <f>IF(LEN(C140)=0,"",COUNTA($C$54:C140))</f>
+        <v>82</v>
+      </c>
+      <c r="B140" s="180"/>
+      <c r="C140" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="D140" s="107" t="s">
+        <v>328</v>
+      </c>
+      <c r="E140" s="105">
+        <v>230000</v>
+      </c>
+      <c r="F140" s="40"/>
+      <c r="G140" s="12"/>
+    </row>
+    <row r="141" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A141" s="37">
-        <f>IF(LEN(C141)=0,"",COUNTA($C$34:C141))</f>
-        <v>103</v>
-      </c>
-      <c r="B141" s="146"/>
+        <f>IF(LEN(C141)=0,"",COUNTA($C$54:C141))</f>
+        <v>83</v>
+      </c>
+      <c r="B141" s="180"/>
       <c r="C141" s="35" t="s">
-        <v>342</v>
-      </c>
-      <c r="D141" s="35" t="s">
-        <v>285</v>
-      </c>
-      <c r="E141" s="106">
-        <v>3420000</v>
+        <v>407</v>
+      </c>
+      <c r="D141" s="35"/>
+      <c r="E141" s="72">
+        <v>250000</v>
       </c>
       <c r="F141" s="40"/>
       <c r="G141" s="12"/>
     </row>
-    <row r="142" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A142" s="37">
-        <f>IF(LEN(C142)=0,"",COUNTA($C$34:C142))</f>
-        <v>104</v>
-      </c>
-      <c r="B142" s="146"/>
+        <f>IF(LEN(C142)=0,"",COUNTA($C$54:C142))</f>
+        <v>84</v>
+      </c>
+      <c r="B142" s="180"/>
       <c r="C142" s="35" t="s">
-        <v>343</v>
-      </c>
-      <c r="D142" s="35" t="s">
-        <v>309</v>
-      </c>
-      <c r="E142" s="106">
-        <v>3420000</v>
-      </c>
-      <c r="F142" s="112" t="s">
-        <v>334</v>
-      </c>
-      <c r="G142" s="113"/>
-    </row>
-    <row r="143" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+        <v>408</v>
+      </c>
+      <c r="D142" s="35"/>
+      <c r="E142" s="72">
+        <v>375000</v>
+      </c>
+      <c r="F142" s="40"/>
+      <c r="G142" s="12"/>
+    </row>
+    <row r="143" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A143" s="37">
-        <f>IF(LEN(C143)=0,"",COUNTA($C$34:C143))</f>
-        <v>105</v>
-      </c>
-      <c r="B143" s="146"/>
+        <f>IF(LEN(C143)=0,"",COUNTA($C$54:C143))</f>
+        <v>85</v>
+      </c>
+      <c r="B143" s="180"/>
       <c r="C143" s="35" t="s">
-        <v>344</v>
-      </c>
-      <c r="D143" s="35" t="s">
-        <v>310</v>
-      </c>
-      <c r="E143" s="106">
-        <v>3420000</v>
+        <v>409</v>
+      </c>
+      <c r="D143" s="35"/>
+      <c r="E143" s="72">
+        <v>500000</v>
       </c>
       <c r="F143" s="40"/>
       <c r="G143" s="12"/>
     </row>
     <row r="144" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A144" s="37">
-        <f>IF(LEN(C144)=0,"",COUNTA($C$34:C144))</f>
-        <v>106</v>
-      </c>
-      <c r="B144" s="146"/>
-      <c r="C144" s="35" t="s">
-        <v>345</v>
-      </c>
-      <c r="D144" s="35" t="s">
-        <v>286</v>
-      </c>
-      <c r="E144" s="106">
-        <v>3420000</v>
+        <f>IF(LEN(C144)=0,"",COUNTA($C$54:C144))</f>
+        <v>86</v>
+      </c>
+      <c r="B144" s="180"/>
+      <c r="C144" s="36" t="s">
+        <v>410</v>
+      </c>
+      <c r="D144" s="36" t="s">
+        <v>137</v>
+      </c>
+      <c r="E144" s="68">
+        <v>700000</v>
       </c>
       <c r="F144" s="40"/>
       <c r="G144" s="12"/>
     </row>
     <row r="145" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A145" s="37">
-        <f>IF(LEN(C145)=0,"",COUNTA($C$34:C145))</f>
-        <v>107</v>
-      </c>
-      <c r="B145" s="146"/>
-      <c r="C145" s="107" t="s">
-        <v>372</v>
-      </c>
-      <c r="D145" s="35" t="s">
-        <v>287</v>
-      </c>
-      <c r="E145" s="106">
-        <v>5730000</v>
+        <f>IF(LEN(C145)=0,"",COUNTA($C$54:C145))</f>
+        <v>87</v>
+      </c>
+      <c r="B145" s="180"/>
+      <c r="C145" s="36" t="s">
+        <v>138</v>
+      </c>
+      <c r="D145" s="107" t="s">
+        <v>329</v>
+      </c>
+      <c r="E145" s="68">
+        <v>770000</v>
       </c>
       <c r="F145" s="40"/>
       <c r="G145" s="12"/>
     </row>
     <row r="146" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A146" s="37">
-        <f>IF(LEN(C146)=0,"",COUNTA($C$34:C146))</f>
-        <v>108</v>
-      </c>
-      <c r="B146" s="146"/>
-      <c r="C146" s="35" t="s">
-        <v>346</v>
-      </c>
-      <c r="D146" s="35" t="s">
-        <v>288</v>
-      </c>
-      <c r="E146" s="106">
-        <v>3420000</v>
+        <f>IF(LEN(C146)=0,"",COUNTA($C$54:C146))</f>
+        <v>88</v>
+      </c>
+      <c r="B146" s="181"/>
+      <c r="C146" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="D146" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="E146" s="68">
+        <v>249000</v>
       </c>
       <c r="F146" s="40"/>
       <c r="G146" s="12"/>
     </row>
-    <row r="147" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A147" s="37">
-        <f>IF(LEN(C147)=0,"",COUNTA($C$34:C147))</f>
-        <v>109</v>
-      </c>
-      <c r="B147" s="146"/>
+        <f>IF(LEN(C147)=0,"",COUNTA($C$54:C147))</f>
+        <v>89</v>
+      </c>
+      <c r="B147" s="140" t="s">
+        <v>282</v>
+      </c>
       <c r="C147" s="35" t="s">
-        <v>347</v>
+        <v>141</v>
       </c>
       <c r="D147" s="35" t="s">
-        <v>288</v>
-      </c>
-      <c r="E147" s="106">
-        <v>4530000</v>
+        <v>142</v>
+      </c>
+      <c r="E147" s="72">
+        <v>157000</v>
       </c>
       <c r="F147" s="40"/>
       <c r="G147" s="12"/>
     </row>
-    <row r="148" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A148" s="37">
-        <f>IF(LEN(C148)=0,"",COUNTA($C$34:C148))</f>
-        <v>110</v>
-      </c>
-      <c r="B148" s="146"/>
+        <f>IF(LEN(C148)=0,"",COUNTA($C$54:C148))</f>
+        <v>90</v>
+      </c>
+      <c r="B148" s="141"/>
       <c r="C148" s="35" t="s">
-        <v>348</v>
+        <v>143</v>
       </c>
       <c r="D148" s="35" t="s">
-        <v>289</v>
-      </c>
-      <c r="E148" s="106">
-        <v>3420000</v>
+        <v>144</v>
+      </c>
+      <c r="E148" s="72">
+        <v>157000</v>
       </c>
       <c r="F148" s="40"/>
       <c r="G148" s="12"/>
     </row>
-    <row r="149" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A149" s="37">
-        <f>IF(LEN(C149)=0,"",COUNTA($C$34:C149))</f>
-        <v>111</v>
-      </c>
-      <c r="B149" s="146"/>
-      <c r="C149" s="107" t="s">
-        <v>371</v>
+        <f>IF(LEN(C149)=0,"",COUNTA($C$54:C149))</f>
+        <v>91</v>
+      </c>
+      <c r="B149" s="141"/>
+      <c r="C149" s="35" t="s">
+        <v>392</v>
       </c>
       <c r="D149" s="35" t="s">
-        <v>290</v>
-      </c>
-      <c r="E149" s="106">
-        <v>5515200</v>
+        <v>393</v>
+      </c>
+      <c r="E149" s="72">
+        <v>143000</v>
       </c>
       <c r="F149" s="40"/>
       <c r="G149" s="12"/>
     </row>
-    <row r="150" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A150" s="37">
-        <f>IF(LEN(C150)=0,"",COUNTA($C$34:C150))</f>
-        <v>112</v>
-      </c>
-      <c r="B150" s="146"/>
+        <f>IF(LEN(C150)=0,"",COUNTA($C$54:C150))</f>
+        <v>92</v>
+      </c>
+      <c r="B150" s="141"/>
       <c r="C150" s="35" t="s">
-        <v>349</v>
+        <v>394</v>
       </c>
       <c r="D150" s="35" t="s">
-        <v>292</v>
+        <v>393</v>
       </c>
       <c r="E150" s="72">
-        <v>2790000</v>
-      </c>
-      <c r="F150" s="114" t="s">
-        <v>291</v>
-      </c>
+        <v>185000</v>
+      </c>
+      <c r="F150" s="40"/>
       <c r="G150" s="12"/>
     </row>
     <row r="151" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A151" s="37">
-        <f>IF(LEN(C151)=0,"",COUNTA($C$34:C151))</f>
-        <v>113</v>
-      </c>
-      <c r="B151" s="146"/>
+        <f>IF(LEN(C151)=0,"",COUNTA($C$54:C151))</f>
+        <v>93</v>
+      </c>
+      <c r="B151" s="141"/>
       <c r="C151" s="35" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="D151" s="35" t="s">
-        <v>293</v>
-      </c>
-      <c r="E151" s="106">
-        <v>3078000</v>
-      </c>
-      <c r="F151" s="40"/>
+        <v>370</v>
+      </c>
+      <c r="E151" s="72">
+        <v>1200000</v>
+      </c>
+      <c r="F151" s="108"/>
       <c r="G151" s="12"/>
     </row>
-    <row r="152" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A152" s="37">
-        <f>IF(LEN(C152)=0,"",COUNTA($C$34:C152))</f>
-        <v>114</v>
-      </c>
-      <c r="B152" s="146"/>
+        <f>IF(LEN(C152)=0,"",COUNTA($C$54:C152))</f>
+        <v>94</v>
+      </c>
+      <c r="B152" s="142"/>
       <c r="C152" s="35" t="s">
-        <v>351</v>
+        <v>145</v>
       </c>
       <c r="D152" s="35" t="s">
-        <v>293</v>
-      </c>
-      <c r="E152" s="106">
-        <v>4200000</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="E152" s="72"/>
       <c r="F152" s="40"/>
       <c r="G152" s="12"/>
     </row>
-    <row r="153" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A153" s="37">
-        <f>IF(LEN(C153)=0,"",COUNTA($C$34:C153))</f>
-        <v>115</v>
-      </c>
-      <c r="B153" s="146"/>
+        <f>IF(LEN(C153)=0,"",COUNTA($C$54:C153))</f>
+        <v>95</v>
+      </c>
+      <c r="B153" s="141" t="s">
+        <v>283</v>
+      </c>
       <c r="C153" s="35" t="s">
-        <v>352</v>
+        <v>149</v>
       </c>
       <c r="D153" s="35" t="s">
-        <v>294</v>
-      </c>
-      <c r="E153" s="106">
-        <v>3078000</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="E153" s="72"/>
       <c r="F153" s="40"/>
       <c r="G153" s="12"/>
     </row>
-    <row r="154" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A154" s="37">
-        <f>IF(LEN(C154)=0,"",COUNTA($C$34:C154))</f>
-        <v>116</v>
-      </c>
-      <c r="B154" s="146"/>
+        <f>IF(LEN(C154)=0,"",COUNTA($C$54:C154))</f>
+        <v>96</v>
+      </c>
+      <c r="B154" s="141"/>
       <c r="C154" s="35" t="s">
-        <v>353</v>
-      </c>
-      <c r="D154" s="35" t="s">
-        <v>294</v>
-      </c>
-      <c r="E154" s="106">
-        <v>4200000</v>
+        <v>330</v>
+      </c>
+      <c r="D154" s="107" t="s">
+        <v>331</v>
+      </c>
+      <c r="E154" s="72">
+        <v>700000</v>
       </c>
       <c r="F154" s="40"/>
       <c r="G154" s="12"/>
     </row>
-    <row r="155" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A155" s="37">
-        <f>IF(LEN(C155)=0,"",COUNTA($C$34:C155))</f>
-        <v>117</v>
-      </c>
-      <c r="B155" s="146"/>
+        <f>IF(LEN(C155)=0,"",COUNTA($C$54:C155))</f>
+        <v>97</v>
+      </c>
+      <c r="B155" s="141"/>
       <c r="C155" s="35" t="s">
-        <v>354</v>
+        <v>151</v>
       </c>
       <c r="D155" s="35" t="s">
-        <v>295</v>
-      </c>
-      <c r="E155" s="106">
-        <v>3078000</v>
+        <v>152</v>
+      </c>
+      <c r="E155" s="68">
+        <v>847000</v>
       </c>
       <c r="F155" s="40"/>
       <c r="G155" s="12"/>
     </row>
     <row r="156" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A156" s="37">
-        <f>IF(LEN(C156)=0,"",COUNTA($C$34:C156))</f>
-        <v>118</v>
-      </c>
-      <c r="B156" s="146"/>
+        <f>IF(LEN(C156)=0,"",COUNTA($C$54:C156))</f>
+        <v>98</v>
+      </c>
+      <c r="B156" s="141"/>
       <c r="C156" s="35" t="s">
-        <v>355</v>
+        <v>153</v>
       </c>
       <c r="D156" s="35" t="s">
-        <v>296</v>
-      </c>
-      <c r="E156" s="106">
-        <v>3420000</v>
+        <v>154</v>
+      </c>
+      <c r="E156" s="68">
+        <v>2178000</v>
       </c>
       <c r="F156" s="40"/>
       <c r="G156" s="12"/>
     </row>
     <row r="157" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A157" s="37">
-        <f>IF(LEN(C157)=0,"",COUNTA($C$34:C157))</f>
-        <v>119</v>
-      </c>
-      <c r="B157" s="146"/>
+        <f>IF(LEN(C157)=0,"",COUNTA($C$54:C157))</f>
+        <v>99</v>
+      </c>
+      <c r="B157" s="141"/>
       <c r="C157" s="35" t="s">
-        <v>356</v>
+        <v>155</v>
       </c>
       <c r="D157" s="35" t="s">
-        <v>297</v>
-      </c>
-      <c r="E157" s="106">
-        <v>3420000</v>
+        <v>156</v>
+      </c>
+      <c r="E157" s="68">
+        <v>847000</v>
       </c>
       <c r="F157" s="40"/>
       <c r="G157" s="12"/>
     </row>
     <row r="158" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A158" s="37">
-        <f>IF(LEN(C158)=0,"",COUNTA($C$34:C158))</f>
-        <v>120</v>
-      </c>
-      <c r="B158" s="146"/>
+        <f>IF(LEN(C158)=0,"",COUNTA($C$54:C158))</f>
+        <v>100</v>
+      </c>
+      <c r="B158" s="141"/>
       <c r="C158" s="35" t="s">
-        <v>357</v>
-      </c>
-      <c r="D158" s="35" t="s">
-        <v>298</v>
-      </c>
-      <c r="E158" s="106">
-        <v>3420000</v>
+        <v>157</v>
+      </c>
+      <c r="D158" s="107" t="s">
+        <v>332</v>
+      </c>
+      <c r="E158" s="68">
+        <v>1700000</v>
       </c>
       <c r="F158" s="40"/>
       <c r="G158" s="12"/>
     </row>
     <row r="159" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A159" s="37">
-        <f>IF(LEN(C159)=0,"",COUNTA($C$34:C159))</f>
-        <v>121</v>
-      </c>
-      <c r="B159" s="146"/>
+        <f>IF(LEN(C159)=0,"",COUNTA($C$54:C159))</f>
+        <v>101</v>
+      </c>
+      <c r="B159" s="141"/>
       <c r="C159" s="35" t="s">
-        <v>358</v>
+        <v>158</v>
       </c>
       <c r="D159" s="35" t="s">
-        <v>305</v>
-      </c>
-      <c r="E159" s="106">
-        <v>3420000</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="E159" s="68"/>
       <c r="F159" s="40"/>
       <c r="G159" s="12"/>
     </row>
-    <row r="160" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A160" s="37">
-        <f>IF(LEN(C160)=0,"",COUNTA($C$34:C160))</f>
-        <v>122</v>
-      </c>
-      <c r="B160" s="146"/>
+        <f>IF(LEN(C160)=0,"",COUNTA($C$54:C160))</f>
+        <v>102</v>
+      </c>
+      <c r="B160" s="152" t="s">
+        <v>304</v>
+      </c>
       <c r="C160" s="35" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="D160" s="35" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="E160" s="106">
-        <v>7740000</v>
-      </c>
-      <c r="F160" s="40"/>
-      <c r="G160" s="12"/>
-    </row>
-    <row r="161" spans="1:8" ht="33" x14ac:dyDescent="0.25">
+        <v>3420000</v>
+      </c>
+      <c r="F160" s="112" t="s">
+        <v>334</v>
+      </c>
+      <c r="G160" s="113"/>
+    </row>
+    <row r="161" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A161" s="37">
-        <f>IF(LEN(C161)=0,"",COUNTA($C$34:C161))</f>
-        <v>123</v>
-      </c>
-      <c r="B161" s="146"/>
+        <f>IF(LEN(C161)=0,"",COUNTA($C$54:C161))</f>
+        <v>103</v>
+      </c>
+      <c r="B161" s="152"/>
       <c r="C161" s="35" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="D161" s="35" t="s">
-        <v>306</v>
+        <v>285</v>
       </c>
       <c r="E161" s="106">
         <v>3420000</v>
@@ -5548,1112 +5576,1529 @@
       <c r="F161" s="40"/>
       <c r="G161" s="12"/>
     </row>
-    <row r="162" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A162" s="37">
-        <f>IF(LEN(C162)=0,"",COUNTA($C$34:C162))</f>
-        <v>124</v>
-      </c>
-      <c r="B162" s="146"/>
+        <f>IF(LEN(C162)=0,"",COUNTA($C$54:C162))</f>
+        <v>104</v>
+      </c>
+      <c r="B162" s="152"/>
       <c r="C162" s="35" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="D162" s="35" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E162" s="106">
-        <v>4740000</v>
-      </c>
-      <c r="F162" s="40"/>
-      <c r="G162" s="12"/>
-    </row>
-    <row r="163" spans="1:8" ht="33" x14ac:dyDescent="0.25">
+        <v>3420000</v>
+      </c>
+      <c r="F162" s="112" t="s">
+        <v>334</v>
+      </c>
+      <c r="G162" s="113"/>
+    </row>
+    <row r="163" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A163" s="37">
-        <f>IF(LEN(C163)=0,"",COUNTA($C$34:C163))</f>
-        <v>125</v>
-      </c>
-      <c r="B163" s="146"/>
+        <f>IF(LEN(C163)=0,"",COUNTA($C$54:C163))</f>
+        <v>105</v>
+      </c>
+      <c r="B163" s="152"/>
       <c r="C163" s="35" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="D163" s="35" t="s">
-        <v>308</v>
-      </c>
-      <c r="E163" s="72">
-        <v>3720000</v>
+        <v>310</v>
+      </c>
+      <c r="E163" s="106">
+        <v>3420000</v>
       </c>
       <c r="F163" s="40"/>
       <c r="G163" s="12"/>
     </row>
-    <row r="164" spans="1:8" ht="33" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A164" s="37">
-        <f>IF(LEN(C164)=0,"",COUNTA($C$34:C164))</f>
-        <v>126</v>
-      </c>
-      <c r="B164" s="146"/>
+        <f>IF(LEN(C164)=0,"",COUNTA($C$54:C164))</f>
+        <v>106</v>
+      </c>
+      <c r="B164" s="152"/>
       <c r="C164" s="35" t="s">
-        <v>363</v>
-      </c>
-      <c r="D164" s="35"/>
+        <v>345</v>
+      </c>
+      <c r="D164" s="35" t="s">
+        <v>286</v>
+      </c>
       <c r="E164" s="106">
-        <v>6060000</v>
+        <v>3420000</v>
       </c>
       <c r="F164" s="40"/>
       <c r="G164" s="12"/>
     </row>
-    <row r="165" spans="1:8" ht="33" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A165" s="37">
-        <f>IF(LEN(C165)=0,"",COUNTA($C$34:C165))</f>
-        <v>127</v>
-      </c>
-      <c r="B165" s="146"/>
-      <c r="C165" s="35" t="s">
-        <v>364</v>
-      </c>
-      <c r="D165" s="35"/>
+        <f>IF(LEN(C165)=0,"",COUNTA($C$54:C165))</f>
+        <v>107</v>
+      </c>
+      <c r="B165" s="152"/>
+      <c r="C165" s="107" t="s">
+        <v>372</v>
+      </c>
+      <c r="D165" s="35" t="s">
+        <v>287</v>
+      </c>
       <c r="E165" s="106">
-        <v>6060000</v>
+        <v>5730000</v>
       </c>
       <c r="F165" s="40"/>
       <c r="G165" s="12"/>
     </row>
-    <row r="166" spans="1:8" ht="33" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A166" s="37">
-        <f>IF(LEN(C166)=0,"",COUNTA($C$34:C166))</f>
-        <v>128</v>
-      </c>
-      <c r="B166" s="146"/>
+        <f>IF(LEN(C166)=0,"",COUNTA($C$54:C166))</f>
+        <v>108</v>
+      </c>
+      <c r="B166" s="152"/>
       <c r="C166" s="35" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="D166" s="35" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="E166" s="106">
-        <v>5520000</v>
+        <v>3420000</v>
       </c>
       <c r="F166" s="40"/>
       <c r="G166" s="12"/>
     </row>
-    <row r="167" spans="1:8" ht="33" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A167" s="37">
-        <f>IF(LEN(C167)=0,"",COUNTA($C$34:C167))</f>
-        <v>129</v>
-      </c>
-      <c r="B167" s="146"/>
+        <f>IF(LEN(C167)=0,"",COUNTA($C$54:C167))</f>
+        <v>109</v>
+      </c>
+      <c r="B167" s="152"/>
       <c r="C167" s="35" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="D167" s="35" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="E167" s="106">
-        <v>9930000</v>
+        <v>4530000</v>
       </c>
       <c r="F167" s="40"/>
       <c r="G167" s="12"/>
     </row>
-    <row r="168" spans="1:8" ht="33" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A168" s="37">
-        <f>IF(LEN(C168)=0,"",COUNTA($C$34:C168))</f>
-        <v>130</v>
-      </c>
-      <c r="B168" s="146"/>
+        <f>IF(LEN(C168)=0,"",COUNTA($C$54:C168))</f>
+        <v>110</v>
+      </c>
+      <c r="B168" s="152"/>
       <c r="C168" s="35" t="s">
-        <v>367</v>
+        <v>348</v>
       </c>
       <c r="D168" s="35" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="E168" s="106">
-        <v>7740000</v>
+        <v>3420000</v>
       </c>
       <c r="F168" s="40"/>
       <c r="G168" s="12"/>
     </row>
-    <row r="169" spans="1:8" ht="33" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A169" s="37">
-        <f>IF(LEN(C169)=0,"",COUNTA($C$34:C169))</f>
-        <v>131</v>
-      </c>
-      <c r="B169" s="146"/>
-      <c r="C169" s="35" t="s">
-        <v>368</v>
+        <f>IF(LEN(C169)=0,"",COUNTA($C$54:C169))</f>
+        <v>111</v>
+      </c>
+      <c r="B169" s="152"/>
+      <c r="C169" s="107" t="s">
+        <v>371</v>
       </c>
       <c r="D169" s="35" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="E169" s="106">
-        <v>23160000</v>
+        <v>5515200</v>
       </c>
       <c r="F169" s="40"/>
       <c r="G169" s="12"/>
     </row>
-    <row r="170" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A170" s="127" t="s">
-        <v>206</v>
-      </c>
-      <c r="B170" s="127"/>
-      <c r="C170" s="127"/>
-      <c r="D170" s="127"/>
-      <c r="E170" s="77"/>
-      <c r="F170" s="67"/>
+    <row r="170" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A170" s="37">
+        <f>IF(LEN(C170)=0,"",COUNTA($C$54:C170))</f>
+        <v>112</v>
+      </c>
+      <c r="B170" s="152"/>
+      <c r="C170" s="35" t="s">
+        <v>349</v>
+      </c>
+      <c r="D170" s="35" t="s">
+        <v>292</v>
+      </c>
+      <c r="E170" s="72">
+        <v>2790000</v>
+      </c>
+      <c r="F170" s="114" t="s">
+        <v>291</v>
+      </c>
       <c r="G170" s="12"/>
     </row>
-    <row r="171" spans="1:8" ht="33" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A171" s="37">
-        <f>IF(LEN(C171)=0,"",COUNTA($C$34:C171))</f>
-        <v>132</v>
-      </c>
-      <c r="B171" s="78"/>
+        <f>IF(LEN(C171)=0,"",COUNTA($C$54:C171))</f>
+        <v>113</v>
+      </c>
+      <c r="B171" s="152"/>
       <c r="C171" s="35" t="s">
-        <v>159</v>
+        <v>350</v>
       </c>
       <c r="D171" s="35" t="s">
-        <v>160</v>
-      </c>
-      <c r="E171" s="72">
-        <v>88000</v>
+        <v>293</v>
+      </c>
+      <c r="E171" s="106">
+        <v>3078000</v>
       </c>
       <c r="F171" s="40"/>
       <c r="G171" s="12"/>
     </row>
-    <row r="172" spans="1:8" ht="33" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A172" s="37">
-        <f>IF(LEN(C172)=0,"",COUNTA($C$34:C172))</f>
-        <v>133</v>
-      </c>
-      <c r="B172" s="79"/>
-      <c r="C172" s="36" t="s">
-        <v>135</v>
-      </c>
-      <c r="D172" s="36" t="s">
-        <v>136</v>
-      </c>
-      <c r="E172" s="105">
-        <v>140000</v>
+        <f>IF(LEN(C172)=0,"",COUNTA($C$54:C172))</f>
+        <v>114</v>
+      </c>
+      <c r="B172" s="152"/>
+      <c r="C172" s="35" t="s">
+        <v>351</v>
+      </c>
+      <c r="D172" s="35" t="s">
+        <v>293</v>
+      </c>
+      <c r="E172" s="106">
+        <v>4200000</v>
       </c>
       <c r="F172" s="40"/>
       <c r="G172" s="12"/>
     </row>
-    <row r="173" spans="1:8" ht="33" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A173" s="37">
-        <f>IF(LEN(C173)=0,"",COUNTA($C$34:C173))</f>
-        <v>134</v>
-      </c>
-      <c r="B173" s="80"/>
-      <c r="C173" s="81" t="s">
-        <v>147</v>
-      </c>
-      <c r="D173" s="81" t="s">
-        <v>148</v>
-      </c>
-      <c r="E173" s="82">
-        <v>450000</v>
+        <f>IF(LEN(C173)=0,"",COUNTA($C$54:C173))</f>
+        <v>115</v>
+      </c>
+      <c r="B173" s="152"/>
+      <c r="C173" s="35" t="s">
+        <v>352</v>
+      </c>
+      <c r="D173" s="35" t="s">
+        <v>294</v>
+      </c>
+      <c r="E173" s="106">
+        <v>3078000</v>
       </c>
       <c r="F173" s="40"/>
       <c r="G173" s="12"/>
-      <c r="H173" s="12"/>
-    </row>
-    <row r="174" spans="1:8" s="15" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="174" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A174" s="37">
-        <f>IF(LEN(C174)=0,"",COUNTA($C$34:C174))</f>
-        <v>135</v>
-      </c>
-      <c r="B174" s="143" t="s">
-        <v>203</v>
-      </c>
+        <f>IF(LEN(C174)=0,"",COUNTA($C$54:C174))</f>
+        <v>116</v>
+      </c>
+      <c r="B174" s="152"/>
       <c r="C174" s="35" t="s">
-        <v>222</v>
+        <v>353</v>
       </c>
       <c r="D174" s="35" t="s">
-        <v>223</v>
-      </c>
-      <c r="E174" s="72">
-        <v>178000</v>
+        <v>294</v>
+      </c>
+      <c r="E174" s="106">
+        <v>4200000</v>
       </c>
       <c r="F174" s="40"/>
-    </row>
-    <row r="175" spans="1:8" s="15" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="G174" s="12"/>
+    </row>
+    <row r="175" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A175" s="37">
-        <f>IF(LEN(C175)=0,"",COUNTA($C$34:C175))</f>
-        <v>136</v>
-      </c>
-      <c r="B175" s="145"/>
+        <f>IF(LEN(C175)=0,"",COUNTA($C$54:C175))</f>
+        <v>117</v>
+      </c>
+      <c r="B175" s="152"/>
       <c r="C175" s="35" t="s">
-        <v>224</v>
+        <v>354</v>
       </c>
       <c r="D175" s="35" t="s">
-        <v>225</v>
-      </c>
-      <c r="E175" s="72">
-        <v>127000</v>
+        <v>295</v>
+      </c>
+      <c r="E175" s="106">
+        <v>3078000</v>
       </c>
       <c r="F175" s="40"/>
-    </row>
-    <row r="176" spans="1:8" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A176" s="131" t="s">
-        <v>163</v>
-      </c>
-      <c r="B176" s="132"/>
-      <c r="C176" s="132"/>
-      <c r="D176" s="133"/>
-      <c r="E176" s="120"/>
-      <c r="F176" s="62"/>
-    </row>
-    <row r="177" spans="1:7" s="16" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="G175" s="12"/>
+    </row>
+    <row r="176" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A176" s="37">
+        <f>IF(LEN(C176)=0,"",COUNTA($C$54:C176))</f>
+        <v>118</v>
+      </c>
+      <c r="B176" s="152"/>
+      <c r="C176" s="35" t="s">
+        <v>355</v>
+      </c>
+      <c r="D176" s="35" t="s">
+        <v>296</v>
+      </c>
+      <c r="E176" s="106">
+        <v>3420000</v>
+      </c>
+      <c r="F176" s="40"/>
+      <c r="G176" s="12"/>
+    </row>
+    <row r="177" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A177" s="37">
-        <f>IF(LEN(C177)=0,"",COUNTA($C$34:C177))</f>
-        <v>137</v>
-      </c>
-      <c r="B177" s="84"/>
-      <c r="C177" s="85" t="s">
-        <v>164</v>
-      </c>
-      <c r="D177" s="85" t="s">
-        <v>165</v>
-      </c>
-      <c r="E177" s="83">
-        <v>71000</v>
-      </c>
-      <c r="F177" s="125" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" s="16" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
+        <f>IF(LEN(C177)=0,"",COUNTA($C$54:C177))</f>
+        <v>119</v>
+      </c>
+      <c r="B177" s="152"/>
+      <c r="C177" s="35" t="s">
+        <v>356</v>
+      </c>
+      <c r="D177" s="35" t="s">
+        <v>297</v>
+      </c>
+      <c r="E177" s="106">
+        <v>3420000</v>
+      </c>
+      <c r="F177" s="40"/>
+      <c r="G177" s="12"/>
+    </row>
+    <row r="178" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A178" s="37">
-        <f>IF(LEN(C178)=0,"",COUNTA($C$34:C178))</f>
-        <v>138</v>
-      </c>
-      <c r="B178" s="84"/>
-      <c r="C178" s="85" t="s">
-        <v>166</v>
-      </c>
-      <c r="D178" s="85" t="s">
-        <v>167</v>
-      </c>
-      <c r="E178" s="83">
-        <v>86000</v>
-      </c>
-      <c r="F178" s="126"/>
-    </row>
-    <row r="179" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A179" s="127" t="s">
-        <v>168</v>
-      </c>
-      <c r="B179" s="127"/>
-      <c r="C179" s="127"/>
-      <c r="D179" s="127"/>
-      <c r="E179" s="77"/>
-      <c r="F179" s="67"/>
+        <f>IF(LEN(C178)=0,"",COUNTA($C$54:C178))</f>
+        <v>120</v>
+      </c>
+      <c r="B178" s="152"/>
+      <c r="C178" s="35" t="s">
+        <v>357</v>
+      </c>
+      <c r="D178" s="35" t="s">
+        <v>298</v>
+      </c>
+      <c r="E178" s="106">
+        <v>3420000</v>
+      </c>
+      <c r="F178" s="40"/>
+      <c r="G178" s="12"/>
+    </row>
+    <row r="179" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A179" s="37">
+        <f>IF(LEN(C179)=0,"",COUNTA($C$54:C179))</f>
+        <v>121</v>
+      </c>
+      <c r="B179" s="152"/>
+      <c r="C179" s="35" t="s">
+        <v>358</v>
+      </c>
+      <c r="D179" s="35" t="s">
+        <v>305</v>
+      </c>
+      <c r="E179" s="106">
+        <v>3420000</v>
+      </c>
+      <c r="F179" s="40"/>
       <c r="G179" s="12"/>
     </row>
-    <row r="180" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A180" s="37">
-        <f>IF(LEN(C180)=0,"",COUNTA($C$34:C180))</f>
-        <v>139</v>
-      </c>
-      <c r="B180" s="38"/>
+        <f>IF(LEN(C180)=0,"",COUNTA($C$54:C180))</f>
+        <v>122</v>
+      </c>
+      <c r="B180" s="152"/>
       <c r="C180" s="35" t="s">
-        <v>169</v>
+        <v>359</v>
       </c>
       <c r="D180" s="35" t="s">
-        <v>170</v>
+        <v>299</v>
       </c>
       <c r="E180" s="106">
-        <v>1968000</v>
-      </c>
-      <c r="F180" s="128" t="s">
-        <v>325</v>
-      </c>
+        <v>7740000</v>
+      </c>
+      <c r="F180" s="40"/>
       <c r="G180" s="12"/>
     </row>
     <row r="181" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A181" s="37">
-        <f>IF(LEN(C181)=0,"",COUNTA($C$34:C181))</f>
-        <v>140</v>
-      </c>
-      <c r="B181" s="38"/>
+        <f>IF(LEN(C181)=0,"",COUNTA($C$54:C181))</f>
+        <v>123</v>
+      </c>
+      <c r="B181" s="152"/>
       <c r="C181" s="35" t="s">
-        <v>171</v>
+        <v>360</v>
       </c>
       <c r="D181" s="35" t="s">
-        <v>172</v>
+        <v>306</v>
       </c>
       <c r="E181" s="106">
-        <v>2952000</v>
-      </c>
-      <c r="F181" s="129"/>
+        <v>3420000</v>
+      </c>
+      <c r="F181" s="40"/>
       <c r="G181" s="12"/>
     </row>
-    <row r="182" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A182" s="37">
-        <f>IF(LEN(C182)=0,"",COUNTA($C$34:C182))</f>
-        <v>141</v>
-      </c>
-      <c r="B182" s="38"/>
+        <f>IF(LEN(C182)=0,"",COUNTA($C$54:C182))</f>
+        <v>124</v>
+      </c>
+      <c r="B182" s="152"/>
       <c r="C182" s="35" t="s">
-        <v>173</v>
+        <v>361</v>
       </c>
       <c r="D182" s="35" t="s">
-        <v>174</v>
+        <v>307</v>
       </c>
       <c r="E182" s="106">
-        <v>4100000</v>
-      </c>
-      <c r="F182" s="130"/>
+        <v>4740000</v>
+      </c>
+      <c r="F182" s="40"/>
       <c r="G182" s="12"/>
     </row>
-    <row r="183" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A183" s="37">
-        <f>IF(LEN(C183)=0,"",COUNTA($C$34:C183))</f>
-        <v>142</v>
-      </c>
-      <c r="B183" s="38"/>
+        <f>IF(LEN(C183)=0,"",COUNTA($C$54:C183))</f>
+        <v>125</v>
+      </c>
+      <c r="B183" s="152"/>
       <c r="C183" s="35" t="s">
-        <v>339</v>
+        <v>362</v>
       </c>
       <c r="D183" s="35" t="s">
-        <v>340</v>
-      </c>
-      <c r="E183" s="106">
-        <v>550000</v>
-      </c>
-      <c r="F183" s="104"/>
+        <v>308</v>
+      </c>
+      <c r="E183" s="72">
+        <v>3720000</v>
+      </c>
+      <c r="F183" s="40"/>
       <c r="G183" s="12"/>
     </row>
-    <row r="184" spans="1:7" ht="148.5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A184" s="37">
-        <f>IF(LEN(C184)=0,"",COUNTA($C$34:C184))</f>
-        <v>143</v>
-      </c>
-      <c r="B184" s="38"/>
+        <f>IF(LEN(C184)=0,"",COUNTA($C$54:C184))</f>
+        <v>126</v>
+      </c>
+      <c r="B184" s="152"/>
       <c r="C184" s="35" t="s">
-        <v>175</v>
-      </c>
-      <c r="D184" s="35" t="s">
-        <v>176</v>
-      </c>
-      <c r="E184" s="72">
-        <v>495000</v>
-      </c>
-      <c r="F184" s="104" t="s">
-        <v>327</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="D184" s="35"/>
+      <c r="E184" s="106">
+        <v>6060000</v>
+      </c>
+      <c r="F184" s="40"/>
       <c r="G184" s="12"/>
     </row>
-    <row r="185" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A185" s="37">
-        <f>IF(LEN(C185)=0,"",COUNTA($C$34:C185))</f>
-        <v>144</v>
-      </c>
-      <c r="B185" s="38"/>
+        <f>IF(LEN(C185)=0,"",COUNTA($C$54:C185))</f>
+        <v>127</v>
+      </c>
+      <c r="B185" s="152"/>
       <c r="C185" s="35" t="s">
-        <v>177</v>
-      </c>
-      <c r="D185" s="35" t="s">
-        <v>178</v>
-      </c>
-      <c r="E185" s="72">
-        <v>268000</v>
+        <v>364</v>
+      </c>
+      <c r="D185" s="35"/>
+      <c r="E185" s="106">
+        <v>6060000</v>
       </c>
       <c r="F185" s="40"/>
       <c r="G185" s="12"/>
     </row>
-    <row r="186" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A186" s="37">
-        <f>IF(LEN(C186)=0,"",COUNTA($C$34:C186))</f>
-        <v>145</v>
-      </c>
-      <c r="B186" s="38"/>
+        <f>IF(LEN(C186)=0,"",COUNTA($C$54:C186))</f>
+        <v>128</v>
+      </c>
+      <c r="B186" s="152"/>
       <c r="C186" s="35" t="s">
-        <v>179</v>
+        <v>365</v>
       </c>
       <c r="D186" s="35" t="s">
-        <v>180</v>
-      </c>
-      <c r="E186" s="72">
-        <v>151000</v>
+        <v>301</v>
+      </c>
+      <c r="E186" s="106">
+        <v>5520000</v>
       </c>
       <c r="F186" s="40"/>
       <c r="G186" s="12"/>
     </row>
-    <row r="187" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A187" s="37">
-        <f>IF(LEN(C187)=0,"",COUNTA($C$34:C187))</f>
-        <v>146</v>
-      </c>
-      <c r="B187" s="38"/>
+        <f>IF(LEN(C187)=0,"",COUNTA($C$54:C187))</f>
+        <v>129</v>
+      </c>
+      <c r="B187" s="152"/>
       <c r="C187" s="35" t="s">
-        <v>337</v>
+        <v>366</v>
       </c>
       <c r="D187" s="35" t="s">
-        <v>338</v>
-      </c>
-      <c r="E187" s="72">
-        <v>220000</v>
+        <v>302</v>
+      </c>
+      <c r="E187" s="106">
+        <v>9930000</v>
       </c>
       <c r="F187" s="40"/>
       <c r="G187" s="12"/>
     </row>
-    <row r="188" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A188" s="127" t="s">
-        <v>263</v>
-      </c>
-      <c r="B188" s="127"/>
-      <c r="C188" s="127"/>
-      <c r="D188" s="127"/>
-      <c r="E188" s="77"/>
-      <c r="F188" s="67"/>
+    <row r="188" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A188" s="37">
+        <f>IF(LEN(C188)=0,"",COUNTA($C$54:C188))</f>
+        <v>130</v>
+      </c>
+      <c r="B188" s="152"/>
+      <c r="C188" s="35" t="s">
+        <v>367</v>
+      </c>
+      <c r="D188" s="35" t="s">
+        <v>303</v>
+      </c>
+      <c r="E188" s="106">
+        <v>7740000</v>
+      </c>
+      <c r="F188" s="40"/>
       <c r="G188" s="12"/>
     </row>
     <row r="189" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A189" s="37">
-        <f>IF(LEN(C189)=0,"",COUNTA($C$34:C189))</f>
-        <v>147</v>
-      </c>
-      <c r="B189" s="38"/>
+        <f>IF(LEN(C189)=0,"",COUNTA($C$54:C189))</f>
+        <v>131</v>
+      </c>
+      <c r="B189" s="152"/>
       <c r="C189" s="35" t="s">
-        <v>264</v>
+        <v>368</v>
       </c>
       <c r="D189" s="35" t="s">
-        <v>265</v>
-      </c>
-      <c r="E189" s="72">
-        <v>390000</v>
+        <v>300</v>
+      </c>
+      <c r="E189" s="106">
+        <v>23160000</v>
       </c>
       <c r="F189" s="40"/>
       <c r="G189" s="12"/>
     </row>
     <row r="190" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A190" s="127" t="s">
-        <v>233</v>
-      </c>
-      <c r="B190" s="127"/>
-      <c r="C190" s="127"/>
-      <c r="D190" s="127"/>
+      <c r="A190" s="178" t="s">
+        <v>206</v>
+      </c>
+      <c r="B190" s="178"/>
+      <c r="C190" s="178"/>
+      <c r="D190" s="178"/>
       <c r="E190" s="77"/>
       <c r="F190" s="67"/>
       <c r="G190" s="12"/>
     </row>
-    <row r="191" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A191" s="37">
-        <f>IF(LEN(C191)=0,"",COUNTA($C$34:C191))</f>
-        <v>148</v>
+        <f>IF(LEN(C191)=0,"",COUNTA($C$54:C191))</f>
+        <v>132</v>
       </c>
       <c r="B191" s="78"/>
-      <c r="C191" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="D191" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="E191" s="105">
-        <v>165000</v>
+      <c r="C191" s="35" t="s">
+        <v>159</v>
+      </c>
+      <c r="D191" s="35" t="s">
+        <v>160</v>
+      </c>
+      <c r="E191" s="72">
+        <v>88000</v>
       </c>
       <c r="F191" s="40"/>
       <c r="G191" s="12"/>
     </row>
     <row r="192" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A192" s="37">
-        <f>IF(LEN(C192)=0,"",COUNTA($C$34:C192))</f>
-        <v>149</v>
-      </c>
-      <c r="B192" s="78"/>
+        <f>IF(LEN(C192)=0,"",COUNTA($C$54:C192))</f>
+        <v>133</v>
+      </c>
+      <c r="B192" s="79"/>
       <c r="C192" s="36" t="s">
-        <v>181</v>
+        <v>135</v>
       </c>
       <c r="D192" s="36" t="s">
-        <v>182</v>
-      </c>
-      <c r="E192" s="68">
-        <v>72000</v>
+        <v>136</v>
+      </c>
+      <c r="E192" s="105">
+        <v>140000</v>
       </c>
       <c r="F192" s="40"/>
       <c r="G192" s="12"/>
     </row>
-    <row r="193" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A193" s="37">
-        <f>IF(LEN(C193)=0,"",COUNTA($C$34:C193))</f>
-        <v>150</v>
-      </c>
-      <c r="B193" s="78"/>
-      <c r="C193" s="35" t="s">
-        <v>183</v>
-      </c>
-      <c r="D193" s="35" t="s">
-        <v>184</v>
-      </c>
-      <c r="E193" s="68">
-        <v>329000</v>
+        <f>IF(LEN(C193)=0,"",COUNTA($C$54:C193))</f>
+        <v>134</v>
+      </c>
+      <c r="B193" s="80"/>
+      <c r="C193" s="81" t="s">
+        <v>147</v>
+      </c>
+      <c r="D193" s="81" t="s">
+        <v>148</v>
+      </c>
+      <c r="E193" s="82">
+        <v>450000</v>
       </c>
       <c r="F193" s="40"/>
       <c r="G193" s="12"/>
-    </row>
-    <row r="194" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="H193" s="12"/>
+    </row>
+    <row r="194" spans="1:8" s="15" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A194" s="37">
-        <f>IF(LEN(C194)=0,"",COUNTA($C$34:C194))</f>
-        <v>151</v>
-      </c>
-      <c r="B194" s="78"/>
-      <c r="C194" s="36" t="s">
-        <v>185</v>
-      </c>
-      <c r="D194" s="36" t="s">
-        <v>186</v>
-      </c>
-      <c r="E194" s="68">
-        <v>605000</v>
+        <f>IF(LEN(C194)=0,"",COUNTA($C$54:C194))</f>
+        <v>135</v>
+      </c>
+      <c r="B194" s="140" t="s">
+        <v>203</v>
+      </c>
+      <c r="C194" s="35" t="s">
+        <v>222</v>
+      </c>
+      <c r="D194" s="35" t="s">
+        <v>223</v>
+      </c>
+      <c r="E194" s="72">
+        <v>178000</v>
       </c>
       <c r="F194" s="40"/>
-      <c r="G194" s="12"/>
-    </row>
-    <row r="195" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    </row>
+    <row r="195" spans="1:8" s="15" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A195" s="37">
-        <f>IF(LEN(C195)=0,"",COUNTA($C$34:C195))</f>
-        <v>152</v>
-      </c>
-      <c r="B195" s="78"/>
-      <c r="C195" s="85" t="s">
-        <v>187</v>
-      </c>
-      <c r="D195" s="85" t="s">
-        <v>188</v>
-      </c>
-      <c r="E195" s="43">
-        <v>1100000</v>
+        <f>IF(LEN(C195)=0,"",COUNTA($C$54:C195))</f>
+        <v>136</v>
+      </c>
+      <c r="B195" s="142"/>
+      <c r="C195" s="35" t="s">
+        <v>224</v>
+      </c>
+      <c r="D195" s="35" t="s">
+        <v>225</v>
+      </c>
+      <c r="E195" s="72">
+        <v>127000</v>
       </c>
       <c r="F195" s="40"/>
-      <c r="G195" s="12"/>
-    </row>
-    <row r="196" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A196" s="37">
-        <f>IF(LEN(C196)=0,"",COUNTA($C$34:C196))</f>
-        <v>153</v>
-      </c>
-      <c r="B196" s="78"/>
-      <c r="C196" s="85" t="s">
-        <v>276</v>
-      </c>
-      <c r="D196" s="85" t="s">
-        <v>273</v>
-      </c>
-      <c r="E196" s="43">
-        <v>187000</v>
-      </c>
-      <c r="F196" s="40"/>
-      <c r="G196" s="12"/>
-    </row>
-    <row r="197" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="196" spans="1:8" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A196" s="171" t="s">
+        <v>163</v>
+      </c>
+      <c r="B196" s="172"/>
+      <c r="C196" s="172"/>
+      <c r="D196" s="173"/>
+      <c r="E196" s="119"/>
+      <c r="F196" s="62"/>
+    </row>
+    <row r="197" spans="1:8" s="16" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A197" s="37">
-        <f>IF(LEN(C197)=0,"",COUNTA($C$34:C197))</f>
-        <v>154</v>
-      </c>
-      <c r="B197" s="78"/>
-      <c r="C197" s="35" t="s">
-        <v>189</v>
-      </c>
-      <c r="D197" s="35" t="s">
-        <v>190</v>
-      </c>
-      <c r="E197" s="68">
-        <v>220000</v>
-      </c>
-      <c r="F197" s="40"/>
-      <c r="G197" s="12"/>
-    </row>
-    <row r="198" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+        <f>IF(LEN(C197)=0,"",COUNTA($C$54:C197))</f>
+        <v>137</v>
+      </c>
+      <c r="B197" s="84"/>
+      <c r="C197" s="85" t="s">
+        <v>164</v>
+      </c>
+      <c r="D197" s="85" t="s">
+        <v>165</v>
+      </c>
+      <c r="E197" s="83">
+        <v>71000</v>
+      </c>
+      <c r="F197" s="183" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" s="16" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A198" s="37">
-        <f>IF(LEN(C198)=0,"",COUNTA($C$34:C198))</f>
-        <v>155</v>
-      </c>
-      <c r="B198" s="78"/>
-      <c r="C198" s="35" t="s">
-        <v>384</v>
-      </c>
-      <c r="D198" s="35" t="s">
-        <v>386</v>
-      </c>
-      <c r="E198" s="68">
-        <v>817000</v>
-      </c>
-      <c r="F198" s="40"/>
-      <c r="G198" s="12"/>
-    </row>
-    <row r="199" spans="1:7" ht="66" x14ac:dyDescent="0.25">
-      <c r="A199" s="37">
-        <f>IF(LEN(C199)=0,"",COUNTA($C$34:C199))</f>
-        <v>156</v>
-      </c>
-      <c r="B199" s="78"/>
-      <c r="C199" s="35" t="s">
-        <v>385</v>
-      </c>
-      <c r="D199" s="35" t="s">
-        <v>387</v>
-      </c>
-      <c r="E199" s="68">
-        <v>1500000</v>
-      </c>
-      <c r="F199" s="40"/>
+        <f>IF(LEN(C198)=0,"",COUNTA($C$54:C198))</f>
+        <v>138</v>
+      </c>
+      <c r="B198" s="84"/>
+      <c r="C198" s="85" t="s">
+        <v>166</v>
+      </c>
+      <c r="D198" s="85" t="s">
+        <v>167</v>
+      </c>
+      <c r="E198" s="83">
+        <v>86000</v>
+      </c>
+      <c r="F198" s="184"/>
+    </row>
+    <row r="199" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A199" s="178" t="s">
+        <v>168</v>
+      </c>
+      <c r="B199" s="178"/>
+      <c r="C199" s="178"/>
+      <c r="D199" s="178"/>
+      <c r="E199" s="77"/>
+      <c r="F199" s="67"/>
       <c r="G199" s="12"/>
     </row>
-    <row r="200" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="37">
-        <f>IF(LEN(C200)=0,"",COUNTA($C$34:C200))</f>
-        <v>157</v>
-      </c>
-      <c r="B200" s="78"/>
+        <f>IF(LEN(C200)=0,"",COUNTA($C$54:C200))</f>
+        <v>139</v>
+      </c>
+      <c r="B200" s="38"/>
       <c r="C200" s="35" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="D200" s="35" t="s">
-        <v>192</v>
-      </c>
-      <c r="E200" s="72">
-        <v>220000</v>
-      </c>
-      <c r="F200" s="40"/>
+        <v>170</v>
+      </c>
+      <c r="E200" s="106">
+        <v>1968000</v>
+      </c>
+      <c r="F200" s="158" t="s">
+        <v>325</v>
+      </c>
       <c r="G200" s="12"/>
     </row>
-    <row r="201" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A201" s="131" t="s">
-        <v>322</v>
-      </c>
-      <c r="B201" s="132"/>
-      <c r="C201" s="132"/>
-      <c r="D201" s="133"/>
-      <c r="E201" s="66"/>
-      <c r="F201" s="67"/>
+    <row r="201" spans="1:8" ht="33" x14ac:dyDescent="0.25">
+      <c r="A201" s="37">
+        <f>IF(LEN(C201)=0,"",COUNTA($C$54:C201))</f>
+        <v>140</v>
+      </c>
+      <c r="B201" s="38"/>
+      <c r="C201" s="35" t="s">
+        <v>171</v>
+      </c>
+      <c r="D201" s="35" t="s">
+        <v>172</v>
+      </c>
+      <c r="E201" s="106">
+        <v>2952000</v>
+      </c>
+      <c r="F201" s="159"/>
       <c r="G201" s="12"/>
     </row>
-    <row r="202" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" ht="66" x14ac:dyDescent="0.25">
       <c r="A202" s="37">
-        <f>IF(LEN(C202)=0,"",COUNTA($C$34:C202))</f>
-        <v>158</v>
-      </c>
-      <c r="B202" s="78"/>
+        <f>IF(LEN(C202)=0,"",COUNTA($C$54:C202))</f>
+        <v>141</v>
+      </c>
+      <c r="B202" s="38"/>
       <c r="C202" s="35" t="s">
-        <v>313</v>
-      </c>
-      <c r="D202" s="35"/>
+        <v>173</v>
+      </c>
+      <c r="D202" s="35" t="s">
+        <v>174</v>
+      </c>
       <c r="E202" s="106">
-        <v>165000</v>
-      </c>
-      <c r="F202" s="40"/>
+        <v>4100000</v>
+      </c>
+      <c r="F202" s="160"/>
       <c r="G202" s="12"/>
     </row>
-    <row r="203" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A203" s="37">
-        <f>IF(LEN(C203)=0,"",COUNTA($C$34:C203))</f>
-        <v>159</v>
-      </c>
-      <c r="B203" s="78"/>
+        <f>IF(LEN(C203)=0,"",COUNTA($C$54:C203))</f>
+        <v>142</v>
+      </c>
+      <c r="B203" s="38"/>
       <c r="C203" s="35" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="D203" s="35" t="s">
-        <v>315</v>
-      </c>
-      <c r="E203" s="72">
-        <v>220000</v>
-      </c>
-      <c r="F203" s="40"/>
+        <v>340</v>
+      </c>
+      <c r="E203" s="106">
+        <v>550000</v>
+      </c>
+      <c r="F203" s="104"/>
       <c r="G203" s="12"/>
     </row>
-    <row r="204" spans="1:7" ht="132" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" ht="148.5" x14ac:dyDescent="0.25">
       <c r="A204" s="37">
-        <f>IF(LEN(C204)=0,"",COUNTA($C$34:C204))</f>
-        <v>160</v>
-      </c>
-      <c r="B204" s="78"/>
+        <f>IF(LEN(C204)=0,"",COUNTA($C$54:C204))</f>
+        <v>143</v>
+      </c>
+      <c r="B204" s="38"/>
       <c r="C204" s="35" t="s">
-        <v>316</v>
+        <v>175</v>
       </c>
       <c r="D204" s="35" t="s">
-        <v>317</v>
+        <v>176</v>
       </c>
       <c r="E204" s="72">
-        <v>380000</v>
-      </c>
-      <c r="F204" s="40"/>
+        <v>495000</v>
+      </c>
+      <c r="F204" s="104" t="s">
+        <v>327</v>
+      </c>
       <c r="G204" s="12"/>
     </row>
-    <row r="205" spans="1:7" ht="99" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A205" s="37">
-        <f>IF(LEN(C205)=0,"",COUNTA($C$34:C205))</f>
-        <v>161</v>
-      </c>
-      <c r="B205" s="78"/>
+        <f>IF(LEN(C205)=0,"",COUNTA($C$54:C205))</f>
+        <v>144</v>
+      </c>
+      <c r="B205" s="38"/>
       <c r="C205" s="35" t="s">
-        <v>318</v>
+        <v>177</v>
       </c>
       <c r="D205" s="35" t="s">
-        <v>319</v>
+        <v>178</v>
       </c>
       <c r="E205" s="72">
-        <v>4500000</v>
+        <v>268000</v>
       </c>
       <c r="F205" s="40"/>
       <c r="G205" s="12"/>
     </row>
-    <row r="206" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A206" s="37">
-        <f>IF(LEN(C206)=0,"",COUNTA($C$34:C206))</f>
-        <v>162</v>
-      </c>
-      <c r="B206" s="78"/>
+        <f>IF(LEN(C206)=0,"",COUNTA($C$54:C206))</f>
+        <v>145</v>
+      </c>
+      <c r="B206" s="38"/>
       <c r="C206" s="35" t="s">
-        <v>320</v>
+        <v>179</v>
       </c>
       <c r="D206" s="35" t="s">
-        <v>321</v>
+        <v>180</v>
       </c>
       <c r="E206" s="72">
-        <v>3200000</v>
+        <v>151000</v>
       </c>
       <c r="F206" s="40"/>
       <c r="G206" s="12"/>
     </row>
-    <row r="207" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A207" s="131" t="s">
-        <v>221</v>
-      </c>
-      <c r="B207" s="132"/>
-      <c r="C207" s="132"/>
-      <c r="D207" s="133"/>
-      <c r="E207" s="66"/>
-      <c r="F207" s="67"/>
+    <row r="207" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A207" s="37">
+        <f>IF(LEN(C207)=0,"",COUNTA($C$54:C207))</f>
+        <v>146</v>
+      </c>
+      <c r="B207" s="38"/>
+      <c r="C207" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="D207" s="35" t="s">
+        <v>338</v>
+      </c>
+      <c r="E207" s="72">
+        <v>220000</v>
+      </c>
+      <c r="F207" s="40"/>
       <c r="G207" s="12"/>
     </row>
-    <row r="208" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A208" s="37">
-        <f>IF(LEN(C208)=0,"",COUNTA($C$34:C208))</f>
-        <v>163</v>
-      </c>
-      <c r="B208" s="78"/>
-      <c r="C208" s="86" t="s">
-        <v>215</v>
-      </c>
-      <c r="D208" s="86" t="s">
-        <v>216</v>
-      </c>
-      <c r="E208" s="87">
-        <v>233000</v>
-      </c>
-      <c r="F208" s="40"/>
+    <row r="208" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A208" s="178" t="s">
+        <v>263</v>
+      </c>
+      <c r="B208" s="178"/>
+      <c r="C208" s="178"/>
+      <c r="D208" s="178"/>
+      <c r="E208" s="77"/>
+      <c r="F208" s="67"/>
       <c r="G208" s="12"/>
     </row>
-    <row r="209" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A209" s="37">
-        <f>IF(LEN(C209)=0,"",COUNTA($C$34:C209))</f>
-        <v>164</v>
-      </c>
-      <c r="B209" s="78"/>
-      <c r="C209" s="88" t="s">
-        <v>217</v>
-      </c>
-      <c r="D209" s="88" t="s">
-        <v>218</v>
-      </c>
-      <c r="E209" s="89">
-        <v>227000</v>
+        <f>IF(LEN(C209)=0,"",COUNTA($C$54:C209))</f>
+        <v>147</v>
+      </c>
+      <c r="B209" s="38"/>
+      <c r="C209" s="35" t="s">
+        <v>264</v>
+      </c>
+      <c r="D209" s="35" t="s">
+        <v>265</v>
+      </c>
+      <c r="E209" s="72">
+        <v>390000</v>
       </c>
       <c r="F209" s="40"/>
       <c r="G209" s="12"/>
     </row>
     <row r="210" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A210" s="37">
-        <f>IF(LEN(C210)=0,"",COUNTA($C$34:C210))</f>
-        <v>165</v>
-      </c>
-      <c r="B210" s="78"/>
-      <c r="C210" s="88" t="s">
-        <v>219</v>
-      </c>
-      <c r="D210" s="88" t="s">
-        <v>220</v>
-      </c>
-      <c r="E210" s="89">
+      <c r="A210" s="178" t="s">
+        <v>233</v>
+      </c>
+      <c r="B210" s="178"/>
+      <c r="C210" s="178"/>
+      <c r="D210" s="178"/>
+      <c r="E210" s="77"/>
+      <c r="F210" s="67"/>
+      <c r="G210" s="12"/>
+    </row>
+    <row r="211" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A211" s="37">
+        <f>IF(LEN(C211)=0,"",COUNTA($C$54:C211))</f>
+        <v>148</v>
+      </c>
+      <c r="B211" s="78"/>
+      <c r="C211" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="D211" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="E211" s="105">
+        <v>165000</v>
+      </c>
+      <c r="F211" s="40"/>
+      <c r="G211" s="12"/>
+    </row>
+    <row r="212" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A212" s="37">
+        <f>IF(LEN(C212)=0,"",COUNTA($C$54:C212))</f>
+        <v>149</v>
+      </c>
+      <c r="B212" s="78"/>
+      <c r="C212" s="36" t="s">
+        <v>181</v>
+      </c>
+      <c r="D212" s="36" t="s">
+        <v>182</v>
+      </c>
+      <c r="E212" s="68">
         <v>72000</v>
-      </c>
-      <c r="F210" s="40"/>
-      <c r="G210" s="12"/>
-    </row>
-    <row r="211" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A211" s="131" t="s">
-        <v>210</v>
-      </c>
-      <c r="B211" s="132"/>
-      <c r="C211" s="132"/>
-      <c r="D211" s="133"/>
-      <c r="E211" s="66"/>
-      <c r="F211" s="67"/>
-      <c r="G211" s="12"/>
-    </row>
-    <row r="212" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A212" s="37">
-        <f>IF(LEN(C212)=0,"",COUNTA($C$34:C212))</f>
-        <v>166</v>
-      </c>
-      <c r="B212" s="78"/>
-      <c r="C212" s="35" t="s">
-        <v>211</v>
-      </c>
-      <c r="D212" s="35"/>
-      <c r="E212" s="134">
-        <v>183000</v>
       </c>
       <c r="F212" s="40"/>
       <c r="G212" s="12"/>
     </row>
-    <row r="213" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A213" s="37">
-        <f>IF(LEN(C213)=0,"",COUNTA($C$34:C213))</f>
-        <v>167</v>
+        <f>IF(LEN(C213)=0,"",COUNTA($C$54:C213))</f>
+        <v>150</v>
       </c>
       <c r="B213" s="78"/>
       <c r="C213" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="D213" s="35"/>
-      <c r="E213" s="135"/>
+        <v>183</v>
+      </c>
+      <c r="D213" s="35" t="s">
+        <v>184</v>
+      </c>
+      <c r="E213" s="68">
+        <v>329000</v>
+      </c>
       <c r="F213" s="40"/>
       <c r="G213" s="12"/>
     </row>
-    <row r="214" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A214" s="37">
-        <f>IF(LEN(C214)=0,"",COUNTA($C$34:C214))</f>
-        <v>168</v>
+        <f>IF(LEN(C214)=0,"",COUNTA($C$54:C214))</f>
+        <v>151</v>
       </c>
       <c r="B214" s="78"/>
-      <c r="C214" s="35" t="s">
-        <v>213</v>
-      </c>
-      <c r="D214" s="35"/>
-      <c r="E214" s="135"/>
+      <c r="C214" s="36" t="s">
+        <v>185</v>
+      </c>
+      <c r="D214" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="E214" s="68">
+        <v>605000</v>
+      </c>
       <c r="F214" s="40"/>
       <c r="G214" s="12"/>
     </row>
-    <row r="215" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A215" s="37">
-        <f>IF(LEN(C215)=0,"",COUNTA($C$34:C215))</f>
-        <v>169</v>
+        <f>IF(LEN(C215)=0,"",COUNTA($C$54:C215))</f>
+        <v>152</v>
       </c>
       <c r="B215" s="78"/>
-      <c r="C215" s="36" t="s">
-        <v>214</v>
-      </c>
-      <c r="D215" s="35"/>
-      <c r="E215" s="136"/>
+      <c r="C215" s="85" t="s">
+        <v>187</v>
+      </c>
+      <c r="D215" s="85" t="s">
+        <v>188</v>
+      </c>
+      <c r="E215" s="43">
+        <v>1100000</v>
+      </c>
       <c r="F215" s="40"/>
       <c r="G215" s="12"/>
     </row>
-    <row r="216" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A216" s="131" t="s">
-        <v>412</v>
-      </c>
-      <c r="B216" s="132"/>
-      <c r="C216" s="132"/>
-      <c r="D216" s="133"/>
-      <c r="E216" s="66"/>
-      <c r="F216" s="67"/>
+    <row r="216" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A216" s="37">
+        <f>IF(LEN(C216)=0,"",COUNTA($C$54:C216))</f>
+        <v>153</v>
+      </c>
+      <c r="B216" s="78"/>
+      <c r="C216" s="85" t="s">
+        <v>276</v>
+      </c>
+      <c r="D216" s="85" t="s">
+        <v>273</v>
+      </c>
+      <c r="E216" s="43">
+        <v>187000</v>
+      </c>
+      <c r="F216" s="40"/>
       <c r="G216" s="12"/>
     </row>
     <row r="217" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A217" s="37">
-        <f>IF(LEN(C217)=0,"",COUNTA($C$34:C217))</f>
-        <v>170</v>
+        <f>IF(LEN(C217)=0,"",COUNTA($C$54:C217))</f>
+        <v>154</v>
       </c>
       <c r="B217" s="78"/>
       <c r="C217" s="35" t="s">
-        <v>413</v>
-      </c>
-      <c r="D217" s="35"/>
-      <c r="E217" s="72">
-        <v>205000</v>
+        <v>189</v>
+      </c>
+      <c r="D217" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="E217" s="68">
+        <v>220000</v>
       </c>
       <c r="F217" s="40"/>
       <c r="G217" s="12"/>
     </row>
-    <row r="218" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A218" s="37">
-        <f>IF(LEN(C218)=0,"",COUNTA($C$34:C218))</f>
-        <v>171</v>
+        <f>IF(LEN(C218)=0,"",COUNTA($C$54:C218))</f>
+        <v>155</v>
       </c>
       <c r="B218" s="78"/>
       <c r="C218" s="35" t="s">
-        <v>414</v>
-      </c>
-      <c r="D218" s="35"/>
-      <c r="E218" s="72">
-        <v>340000</v>
+        <v>384</v>
+      </c>
+      <c r="D218" s="35" t="s">
+        <v>386</v>
+      </c>
+      <c r="E218" s="68">
+        <v>817000</v>
       </c>
       <c r="F218" s="40"/>
       <c r="G218" s="12"/>
     </row>
-    <row r="219" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A219" s="37">
-        <f>IF(LEN(C219)=0,"",COUNTA($C$34:C219))</f>
-        <v>172</v>
+        <f>IF(LEN(C219)=0,"",COUNTA($C$54:C219))</f>
+        <v>156</v>
       </c>
       <c r="B219" s="78"/>
       <c r="C219" s="35" t="s">
-        <v>415</v>
-      </c>
-      <c r="D219" s="35"/>
-      <c r="E219" s="72">
-        <v>1700000</v>
+        <v>385</v>
+      </c>
+      <c r="D219" s="35" t="s">
+        <v>387</v>
+      </c>
+      <c r="E219" s="68">
+        <v>1500000</v>
       </c>
       <c r="F219" s="40"/>
       <c r="G219" s="12"/>
     </row>
-    <row r="220" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A220" s="37">
-        <f>IF(LEN(C220)=0,"",COUNTA($C$34:C220))</f>
-        <v>173</v>
+        <f>IF(LEN(C220)=0,"",COUNTA($C$54:C220))</f>
+        <v>157</v>
       </c>
       <c r="B220" s="78"/>
-      <c r="C220" s="36" t="s">
-        <v>416</v>
-      </c>
-      <c r="D220" s="35"/>
+      <c r="C220" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="D220" s="35" t="s">
+        <v>192</v>
+      </c>
       <c r="E220" s="72">
-        <v>1360000</v>
+        <v>220000</v>
       </c>
       <c r="F220" s="40"/>
       <c r="G220" s="12"/>
     </row>
     <row r="221" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A221" s="90"/>
-      <c r="B221" s="91"/>
-      <c r="C221" s="90"/>
-      <c r="D221" s="90"/>
-      <c r="E221" s="92"/>
-      <c r="F221" s="93"/>
-    </row>
-    <row r="222" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A222" s="124" t="s">
+      <c r="A221" s="171" t="s">
+        <v>322</v>
+      </c>
+      <c r="B221" s="172"/>
+      <c r="C221" s="172"/>
+      <c r="D221" s="173"/>
+      <c r="E221" s="66"/>
+      <c r="F221" s="67"/>
+      <c r="G221" s="12"/>
+    </row>
+    <row r="222" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A222" s="37">
+        <f>IF(LEN(C222)=0,"",COUNTA($C$54:C222))</f>
+        <v>158</v>
+      </c>
+      <c r="B222" s="78"/>
+      <c r="C222" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="D222" s="35"/>
+      <c r="E222" s="106">
+        <v>165000</v>
+      </c>
+      <c r="F222" s="40"/>
+      <c r="G222" s="12"/>
+    </row>
+    <row r="223" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A223" s="37">
+        <f>IF(LEN(C223)=0,"",COUNTA($C$54:C223))</f>
+        <v>159</v>
+      </c>
+      <c r="B223" s="78"/>
+      <c r="C223" s="35" t="s">
+        <v>314</v>
+      </c>
+      <c r="D223" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="E223" s="72">
+        <v>220000</v>
+      </c>
+      <c r="F223" s="40"/>
+      <c r="G223" s="12"/>
+    </row>
+    <row r="224" spans="1:7" ht="132" x14ac:dyDescent="0.25">
+      <c r="A224" s="37">
+        <f>IF(LEN(C224)=0,"",COUNTA($C$54:C224))</f>
+        <v>160</v>
+      </c>
+      <c r="B224" s="78"/>
+      <c r="C224" s="35" t="s">
+        <v>316</v>
+      </c>
+      <c r="D224" s="35" t="s">
+        <v>317</v>
+      </c>
+      <c r="E224" s="72">
+        <v>380000</v>
+      </c>
+      <c r="F224" s="40"/>
+      <c r="G224" s="12"/>
+    </row>
+    <row r="225" spans="1:7" ht="99" x14ac:dyDescent="0.25">
+      <c r="A225" s="37">
+        <f>IF(LEN(C225)=0,"",COUNTA($C$54:C225))</f>
+        <v>161</v>
+      </c>
+      <c r="B225" s="78"/>
+      <c r="C225" s="35" t="s">
+        <v>318</v>
+      </c>
+      <c r="D225" s="35" t="s">
+        <v>319</v>
+      </c>
+      <c r="E225" s="72">
+        <v>4500000</v>
+      </c>
+      <c r="F225" s="40"/>
+      <c r="G225" s="12"/>
+    </row>
+    <row r="226" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A226" s="37">
+        <f>IF(LEN(C226)=0,"",COUNTA($C$54:C226))</f>
+        <v>162</v>
+      </c>
+      <c r="B226" s="78"/>
+      <c r="C226" s="35" t="s">
+        <v>320</v>
+      </c>
+      <c r="D226" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="E226" s="72">
+        <v>3200000</v>
+      </c>
+      <c r="F226" s="40"/>
+      <c r="G226" s="12"/>
+    </row>
+    <row r="227" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A227" s="171" t="s">
+        <v>221</v>
+      </c>
+      <c r="B227" s="172"/>
+      <c r="C227" s="172"/>
+      <c r="D227" s="173"/>
+      <c r="E227" s="66"/>
+      <c r="F227" s="67"/>
+      <c r="G227" s="12"/>
+    </row>
+    <row r="228" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A228" s="37">
+        <f>IF(LEN(C228)=0,"",COUNTA($C$54:C228))</f>
+        <v>163</v>
+      </c>
+      <c r="B228" s="78"/>
+      <c r="C228" s="86" t="s">
+        <v>215</v>
+      </c>
+      <c r="D228" s="86" t="s">
+        <v>216</v>
+      </c>
+      <c r="E228" s="87">
+        <v>233000</v>
+      </c>
+      <c r="F228" s="40"/>
+      <c r="G228" s="12"/>
+    </row>
+    <row r="229" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A229" s="37">
+        <f>IF(LEN(C229)=0,"",COUNTA($C$54:C229))</f>
+        <v>164</v>
+      </c>
+      <c r="B229" s="78"/>
+      <c r="C229" s="88" t="s">
+        <v>217</v>
+      </c>
+      <c r="D229" s="88" t="s">
+        <v>218</v>
+      </c>
+      <c r="E229" s="89">
+        <v>227000</v>
+      </c>
+      <c r="F229" s="40"/>
+      <c r="G229" s="12"/>
+    </row>
+    <row r="230" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A230" s="37">
+        <f>IF(LEN(C230)=0,"",COUNTA($C$54:C230))</f>
+        <v>165</v>
+      </c>
+      <c r="B230" s="78"/>
+      <c r="C230" s="88" t="s">
+        <v>219</v>
+      </c>
+      <c r="D230" s="88" t="s">
+        <v>220</v>
+      </c>
+      <c r="E230" s="89">
+        <v>72000</v>
+      </c>
+      <c r="F230" s="40"/>
+      <c r="G230" s="12"/>
+    </row>
+    <row r="231" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A231" s="171" t="s">
+        <v>210</v>
+      </c>
+      <c r="B231" s="172"/>
+      <c r="C231" s="172"/>
+      <c r="D231" s="173"/>
+      <c r="E231" s="66"/>
+      <c r="F231" s="67"/>
+      <c r="G231" s="12"/>
+    </row>
+    <row r="232" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A232" s="37">
+        <f>IF(LEN(C232)=0,"",COUNTA($C$54:C232))</f>
+        <v>166</v>
+      </c>
+      <c r="B232" s="78"/>
+      <c r="C232" s="35" t="s">
+        <v>211</v>
+      </c>
+      <c r="D232" s="35"/>
+      <c r="E232" s="146">
+        <v>183000</v>
+      </c>
+      <c r="F232" s="40"/>
+      <c r="G232" s="12"/>
+    </row>
+    <row r="233" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A233" s="37">
+        <f>IF(LEN(C233)=0,"",COUNTA($C$54:C233))</f>
+        <v>167</v>
+      </c>
+      <c r="B233" s="78"/>
+      <c r="C233" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="D233" s="35"/>
+      <c r="E233" s="147"/>
+      <c r="F233" s="40"/>
+      <c r="G233" s="12"/>
+    </row>
+    <row r="234" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A234" s="37">
+        <f>IF(LEN(C234)=0,"",COUNTA($C$54:C234))</f>
+        <v>168</v>
+      </c>
+      <c r="B234" s="78"/>
+      <c r="C234" s="35" t="s">
+        <v>213</v>
+      </c>
+      <c r="D234" s="35"/>
+      <c r="E234" s="147"/>
+      <c r="F234" s="40"/>
+      <c r="G234" s="12"/>
+    </row>
+    <row r="235" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A235" s="37">
+        <f>IF(LEN(C235)=0,"",COUNTA($C$54:C235))</f>
+        <v>169</v>
+      </c>
+      <c r="B235" s="78"/>
+      <c r="C235" s="36" t="s">
+        <v>214</v>
+      </c>
+      <c r="D235" s="35"/>
+      <c r="E235" s="148"/>
+      <c r="F235" s="40"/>
+      <c r="G235" s="12"/>
+    </row>
+    <row r="236" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A236" s="171" t="s">
+        <v>412</v>
+      </c>
+      <c r="B236" s="172"/>
+      <c r="C236" s="172"/>
+      <c r="D236" s="173"/>
+      <c r="E236" s="66"/>
+      <c r="F236" s="67"/>
+      <c r="G236" s="12"/>
+    </row>
+    <row r="237" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A237" s="37">
+        <f>IF(LEN(C237)=0,"",COUNTA($C$54:C237))</f>
+        <v>170</v>
+      </c>
+      <c r="B237" s="78"/>
+      <c r="C237" s="35" t="s">
+        <v>413</v>
+      </c>
+      <c r="D237" s="35"/>
+      <c r="E237" s="72">
+        <v>205000</v>
+      </c>
+      <c r="F237" s="40"/>
+      <c r="G237" s="12"/>
+    </row>
+    <row r="238" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A238" s="37">
+        <f>IF(LEN(C238)=0,"",COUNTA($C$54:C238))</f>
+        <v>171</v>
+      </c>
+      <c r="B238" s="78"/>
+      <c r="C238" s="35" t="s">
+        <v>414</v>
+      </c>
+      <c r="D238" s="35"/>
+      <c r="E238" s="72">
+        <v>340000</v>
+      </c>
+      <c r="F238" s="40"/>
+      <c r="G238" s="12"/>
+    </row>
+    <row r="239" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A239" s="37">
+        <f>IF(LEN(C239)=0,"",COUNTA($C$54:C239))</f>
+        <v>172</v>
+      </c>
+      <c r="B239" s="78"/>
+      <c r="C239" s="35" t="s">
+        <v>415</v>
+      </c>
+      <c r="D239" s="35"/>
+      <c r="E239" s="72">
+        <v>1700000</v>
+      </c>
+      <c r="F239" s="40"/>
+      <c r="G239" s="12"/>
+    </row>
+    <row r="240" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A240" s="37">
+        <f>IF(LEN(C240)=0,"",COUNTA($C$54:C240))</f>
+        <v>173</v>
+      </c>
+      <c r="B240" s="78"/>
+      <c r="C240" s="36" t="s">
+        <v>416</v>
+      </c>
+      <c r="D240" s="35"/>
+      <c r="E240" s="72">
+        <v>1360000</v>
+      </c>
+      <c r="F240" s="40"/>
+      <c r="G240" s="12"/>
+    </row>
+    <row r="241" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A241" s="90"/>
+      <c r="B241" s="91"/>
+      <c r="C241" s="90"/>
+      <c r="D241" s="90"/>
+      <c r="E241" s="92"/>
+      <c r="F241" s="93"/>
+    </row>
+    <row r="242" spans="1:6" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A242" s="182" t="s">
         <v>27</v>
       </c>
-      <c r="B222" s="124"/>
-      <c r="C222" s="124"/>
-      <c r="D222" s="124"/>
-      <c r="E222" s="26"/>
-      <c r="F222" s="94"/>
-    </row>
-    <row r="223" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A223" s="95"/>
-      <c r="B223" s="122" t="s">
+      <c r="B242" s="182"/>
+      <c r="C242" s="182"/>
+      <c r="D242" s="182"/>
+      <c r="E242" s="26"/>
+      <c r="F242" s="94"/>
+    </row>
+    <row r="243" spans="1:6" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A243" s="95"/>
+      <c r="B243" s="185" t="s">
         <v>266</v>
       </c>
-      <c r="C223" s="122"/>
-      <c r="D223" s="122"/>
-      <c r="E223" s="122"/>
-      <c r="F223" s="122"/>
-    </row>
-    <row r="224" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A224" s="95"/>
-      <c r="B224" s="122" t="s">
+      <c r="C243" s="185"/>
+      <c r="D243" s="185"/>
+      <c r="E243" s="185"/>
+      <c r="F243" s="185"/>
+    </row>
+    <row r="244" spans="1:6" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A244" s="95"/>
+      <c r="B244" s="185" t="s">
         <v>417</v>
       </c>
-      <c r="C224" s="122"/>
-      <c r="D224" s="122"/>
-      <c r="E224" s="122"/>
-      <c r="F224" s="122"/>
-    </row>
-    <row r="225" spans="1:6" s="2" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A225" s="96"/>
-      <c r="B225" s="122" t="s">
+      <c r="C244" s="185"/>
+      <c r="D244" s="185"/>
+      <c r="E244" s="185"/>
+      <c r="F244" s="185"/>
+    </row>
+    <row r="245" spans="1:6" s="2" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A245" s="96"/>
+      <c r="B245" s="185" t="s">
         <v>28</v>
       </c>
-      <c r="C225" s="122"/>
-      <c r="D225" s="122"/>
-      <c r="E225" s="122"/>
-      <c r="F225" s="122"/>
-    </row>
-    <row r="226" spans="1:6" s="17" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A226" s="97"/>
-      <c r="B226" s="123" t="s">
+      <c r="C245" s="185"/>
+      <c r="D245" s="185"/>
+      <c r="E245" s="185"/>
+      <c r="F245" s="185"/>
+    </row>
+    <row r="246" spans="1:6" s="17" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A246" s="97"/>
+      <c r="B246" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="C226" s="123"/>
-      <c r="D226" s="123"/>
-      <c r="E226" s="123"/>
-      <c r="F226" s="123"/>
-    </row>
-    <row r="227" spans="1:6" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A227" s="94"/>
-      <c r="B227" s="122" t="s">
+      <c r="C246" s="186"/>
+      <c r="D246" s="186"/>
+      <c r="E246" s="186"/>
+      <c r="F246" s="186"/>
+    </row>
+    <row r="247" spans="1:6" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A247" s="94"/>
+      <c r="B247" s="185" t="s">
         <v>30</v>
       </c>
-      <c r="C227" s="122"/>
-      <c r="D227" s="122"/>
-      <c r="E227" s="122"/>
-      <c r="F227" s="122"/>
-    </row>
-    <row r="228" spans="1:6" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A228" s="94"/>
-      <c r="B228" s="96" t="s">
+      <c r="C247" s="185"/>
+      <c r="D247" s="185"/>
+      <c r="E247" s="185"/>
+      <c r="F247" s="185"/>
+    </row>
+    <row r="248" spans="1:6" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A248" s="94"/>
+      <c r="B248" s="96" t="s">
         <v>31</v>
       </c>
-      <c r="C228" s="96"/>
-      <c r="D228" s="98"/>
-      <c r="E228" s="26"/>
-      <c r="F228" s="23"/>
-    </row>
-    <row r="229" spans="1:6" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A229" s="94"/>
-      <c r="B229" s="96" t="s">
+      <c r="C248" s="96"/>
+      <c r="D248" s="98"/>
+      <c r="E248" s="26"/>
+      <c r="F248" s="23"/>
+    </row>
+    <row r="249" spans="1:6" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A249" s="94"/>
+      <c r="B249" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="C229" s="96"/>
-      <c r="D229" s="98"/>
-      <c r="E229" s="26"/>
-      <c r="F229" s="23"/>
-    </row>
-    <row r="230" spans="1:6" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A230" s="100" t="s">
+      <c r="C249" s="96"/>
+      <c r="D249" s="98"/>
+      <c r="E249" s="26"/>
+      <c r="F249" s="23"/>
+    </row>
+    <row r="250" spans="1:6" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A250" s="100" t="s">
         <v>33</v>
       </c>
-      <c r="B230" s="101"/>
-      <c r="C230" s="101"/>
-      <c r="D230" s="101"/>
-      <c r="E230" s="119"/>
-      <c r="F230" s="99"/>
-    </row>
-    <row r="231" spans="1:6" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A231" s="94"/>
-      <c r="B231" s="23" t="s">
+      <c r="B250" s="101"/>
+      <c r="C250" s="101"/>
+      <c r="D250" s="101"/>
+      <c r="E250" s="118"/>
+      <c r="F250" s="99"/>
+    </row>
+    <row r="251" spans="1:6" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A251" s="94"/>
+      <c r="B251" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="C231" s="23"/>
-      <c r="D231" s="98"/>
-      <c r="E231" s="102"/>
-      <c r="F231" s="23"/>
-    </row>
-    <row r="232" spans="1:6" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A232" s="94"/>
-      <c r="B232" s="23" t="s">
+      <c r="C251" s="23"/>
+      <c r="D251" s="98"/>
+      <c r="E251" s="102"/>
+      <c r="F251" s="23"/>
+    </row>
+    <row r="252" spans="1:6" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A252" s="94"/>
+      <c r="B252" s="23" t="s">
         <v>419</v>
       </c>
-      <c r="C232" s="23"/>
-      <c r="D232" s="98"/>
-      <c r="E232" s="102"/>
-      <c r="F232" s="23"/>
-    </row>
-    <row r="233" spans="1:6" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A233" s="94"/>
-      <c r="B233" s="23" t="s">
+      <c r="C252" s="23"/>
+      <c r="D252" s="98"/>
+      <c r="E252" s="102"/>
+      <c r="F252" s="23"/>
+    </row>
+    <row r="253" spans="1:6" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A253" s="94"/>
+      <c r="B253" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="C233" s="23"/>
-      <c r="D233" s="98"/>
-      <c r="E233" s="102"/>
-      <c r="F233" s="23"/>
+      <c r="C253" s="23"/>
+      <c r="D253" s="98"/>
+      <c r="E253" s="102"/>
+      <c r="F253" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="66">
-    <mergeCell ref="A28:D28"/>
+  <mergeCells count="69">
+    <mergeCell ref="F29:F33"/>
+    <mergeCell ref="B243:F243"/>
+    <mergeCell ref="B244:F244"/>
+    <mergeCell ref="B245:F245"/>
+    <mergeCell ref="B246:F246"/>
+    <mergeCell ref="B247:F247"/>
+    <mergeCell ref="A242:D242"/>
+    <mergeCell ref="F197:F198"/>
+    <mergeCell ref="A199:D199"/>
+    <mergeCell ref="F200:F202"/>
+    <mergeCell ref="A208:D208"/>
+    <mergeCell ref="A210:D210"/>
+    <mergeCell ref="A221:D221"/>
+    <mergeCell ref="A227:D227"/>
+    <mergeCell ref="A231:D231"/>
+    <mergeCell ref="E232:E235"/>
+    <mergeCell ref="A236:D236"/>
+    <mergeCell ref="A196:D196"/>
+    <mergeCell ref="B117:B118"/>
+    <mergeCell ref="B120:B133"/>
+    <mergeCell ref="A134:D134"/>
+    <mergeCell ref="A137:D137"/>
+    <mergeCell ref="B138:B146"/>
+    <mergeCell ref="B147:B152"/>
+    <mergeCell ref="B153:B159"/>
+    <mergeCell ref="B160:B189"/>
+    <mergeCell ref="A190:D190"/>
+    <mergeCell ref="B194:B195"/>
+    <mergeCell ref="B115:B116"/>
+    <mergeCell ref="A79:D79"/>
+    <mergeCell ref="B80:B92"/>
+    <mergeCell ref="B93:B95"/>
+    <mergeCell ref="D93:D95"/>
+    <mergeCell ref="A100:D100"/>
+    <mergeCell ref="B101:B108"/>
+    <mergeCell ref="B109:B110"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="A114:D114"/>
+    <mergeCell ref="F93:F95"/>
+    <mergeCell ref="B96:B99"/>
+    <mergeCell ref="D96:D97"/>
+    <mergeCell ref="B69:B72"/>
+    <mergeCell ref="F70:F72"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="F74:F75"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="F77:F78"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="B60:B64"/>
+    <mergeCell ref="F60:F64"/>
+    <mergeCell ref="B66:B68"/>
+    <mergeCell ref="F66:F68"/>
+    <mergeCell ref="A48:D48"/>
     <mergeCell ref="D1:F5"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="B9:F9"/>
@@ -6664,75 +7109,28 @@
     <mergeCell ref="C14:C19"/>
     <mergeCell ref="E14:E19"/>
     <mergeCell ref="F14:F19"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="B40:B44"/>
-    <mergeCell ref="F40:F44"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="F46:F48"/>
-    <mergeCell ref="F73:F75"/>
-    <mergeCell ref="B76:B79"/>
-    <mergeCell ref="D76:D77"/>
-    <mergeCell ref="B49:B52"/>
-    <mergeCell ref="F50:F52"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="F54:F55"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="F57:F58"/>
-    <mergeCell ref="B95:B96"/>
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="B60:B72"/>
-    <mergeCell ref="B73:B75"/>
-    <mergeCell ref="D73:D75"/>
-    <mergeCell ref="A80:D80"/>
-    <mergeCell ref="B81:B88"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="B91:B93"/>
-    <mergeCell ref="A94:D94"/>
-    <mergeCell ref="A176:D176"/>
-    <mergeCell ref="B97:B98"/>
-    <mergeCell ref="B100:B113"/>
-    <mergeCell ref="A114:D114"/>
-    <mergeCell ref="A117:D117"/>
-    <mergeCell ref="B118:B126"/>
-    <mergeCell ref="B127:B132"/>
-    <mergeCell ref="B133:B139"/>
-    <mergeCell ref="B140:B169"/>
-    <mergeCell ref="A170:D170"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="A222:D222"/>
-    <mergeCell ref="F177:F178"/>
-    <mergeCell ref="A179:D179"/>
-    <mergeCell ref="F180:F182"/>
-    <mergeCell ref="A188:D188"/>
-    <mergeCell ref="A190:D190"/>
-    <mergeCell ref="A201:D201"/>
-    <mergeCell ref="A207:D207"/>
-    <mergeCell ref="A211:D211"/>
-    <mergeCell ref="E212:E215"/>
-    <mergeCell ref="A216:D216"/>
-    <mergeCell ref="B223:F223"/>
-    <mergeCell ref="B224:F224"/>
-    <mergeCell ref="B225:F225"/>
-    <mergeCell ref="B226:F226"/>
-    <mergeCell ref="B227:F227"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B29:B33"/>
   </mergeCells>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.35433070866141736" right="0.15748031496062992" top="0.23622047244094491" bottom="0.19685039370078741" header="0.15748031496062992" footer="0.15748031496062992"/>
   <pageSetup paperSize="9" scale="70" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <rowBreaks count="10" manualBreakCount="10">
-    <brk id="28" max="5" man="1"/>
-    <brk id="58" max="5" man="1"/>
-    <brk id="79" max="5" man="1"/>
-    <brk id="94" max="5" man="1"/>
-    <brk id="116" max="5" man="1"/>
-    <brk id="139" max="5" man="1"/>
-    <brk id="154" max="5" man="1"/>
-    <brk id="169" max="5" man="1"/>
-    <brk id="187" max="5" man="1"/>
-    <brk id="203" max="5" man="1"/>
+    <brk id="48" max="5" man="1"/>
+    <brk id="78" max="5" man="1"/>
+    <brk id="99" max="5" man="1"/>
+    <brk id="114" max="5" man="1"/>
+    <brk id="136" max="5" man="1"/>
+    <brk id="159" max="5" man="1"/>
+    <brk id="174" max="5" man="1"/>
+    <brk id="189" max="5" man="1"/>
+    <brk id="207" max="5" man="1"/>
+    <brk id="223" max="5" man="1"/>
   </rowBreaks>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="6" max="163" man="1"/>

--- a/Hoàng/SALE/BÁO GIÁ KSK 2025 - THAM KHẢO.xlsx
+++ b/Hoàng/SALE/BÁO GIÁ KSK 2025 - THAM KHẢO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\SALE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C8589E-D9D8-4D5E-B8C4-6A12FFFCF1E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9909668-A5ED-4F1D-B774-CB881A3A37BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,8 @@
     <sheet name="BÁO GIÁ KSK" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'BÁO GIÁ KSK'!$A$1:$F$253</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'BÁO GIÁ KSK'!$52:$52</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'BÁO GIÁ KSK'!$A$1:$F$234</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'BÁO GIÁ KSK'!$33:$33</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="422">
   <si>
     <t>Ghi chú</t>
   </si>
@@ -2325,6 +2325,12 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2388,9 +2394,24 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2399,27 +2420,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2796,7 +2796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46C4EFAC-5358-4031-B8BC-663929F6ADDF}">
-  <dimension ref="A1:K253"/>
+  <dimension ref="A1:K234"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="9" bestFit="1" customWidth="1"/>
@@ -2938,7 +2938,7 @@
       <c r="E12" s="31"/>
       <c r="F12" s="32"/>
     </row>
-    <row r="13" spans="1:11" ht="33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A13" s="33" t="s">
         <v>259</v>
       </c>
@@ -3038,10 +3038,10 @@
         <v>2</v>
       </c>
       <c r="B20" s="71"/>
-      <c r="C20" s="187" t="s">
+      <c r="C20" s="157" t="s">
         <v>420</v>
       </c>
-      <c r="D20" s="188"/>
+      <c r="D20" s="158"/>
       <c r="E20" s="121" t="s">
         <v>421</v>
       </c>
@@ -3068,4037 +3068,3686 @@
       <c r="F21" s="40"/>
       <c r="G21" s="12"/>
     </row>
-    <row r="22" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A22" s="37">
         <f>IF(LEN(C22)=0,"",COUNTA($C$14:C22))</f>
         <v>4</v>
       </c>
-      <c r="B22" s="79"/>
+      <c r="B22" s="38" t="s">
+        <v>15</v>
+      </c>
       <c r="C22" s="36" t="s">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>136</v>
-      </c>
-      <c r="E22" s="105">
-        <v>140000</v>
+        <v>17</v>
+      </c>
+      <c r="E22" s="39">
+        <v>75000</v>
       </c>
       <c r="F22" s="40"/>
       <c r="G22" s="12"/>
     </row>
-    <row r="23" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A23" s="37">
         <f>IF(LEN(C23)=0,"",COUNTA($C$14:C23))</f>
         <v>5</v>
       </c>
-      <c r="B23" s="78"/>
-      <c r="C23" s="35" t="s">
-        <v>159</v>
-      </c>
-      <c r="D23" s="35" t="s">
-        <v>160</v>
-      </c>
-      <c r="E23" s="72">
-        <v>88000</v>
+      <c r="B23" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="39">
+        <v>27000</v>
       </c>
       <c r="F23" s="40"/>
       <c r="G23" s="12"/>
     </row>
-    <row r="24" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A24" s="37">
         <f>IF(LEN(C24)=0,"",COUNTA($C$14:C24))</f>
         <v>6</v>
       </c>
-      <c r="B24" s="78"/>
+      <c r="B24" s="38" t="s">
+        <v>44</v>
+      </c>
       <c r="C24" s="36" t="s">
-        <v>324</v>
-      </c>
-      <c r="D24" s="107" t="s">
-        <v>328</v>
-      </c>
-      <c r="E24" s="105">
-        <v>230000</v>
+        <v>45</v>
+      </c>
+      <c r="D24" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" s="43">
+        <v>41000</v>
       </c>
       <c r="F24" s="40"/>
       <c r="G24" s="12"/>
     </row>
-    <row r="25" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <f>IF(LEN(C25)=0,"",COUNTA($C$14:C25))</f>
         <v>7</v>
       </c>
-      <c r="B25" s="78"/>
-      <c r="C25" s="36" t="s">
-        <v>323</v>
-      </c>
-      <c r="D25" s="36" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="105">
-        <v>230000</v>
-      </c>
-      <c r="F25" s="40"/>
+      <c r="B25" s="152" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="153">
+        <v>60000</v>
+      </c>
+      <c r="F25" s="155" t="s">
+        <v>381</v>
+      </c>
       <c r="G25" s="12"/>
     </row>
-    <row r="26" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A26" s="37">
         <f>IF(LEN(C26)=0,"",COUNTA($C$14:C26))</f>
         <v>8</v>
       </c>
-      <c r="B26" s="78"/>
-      <c r="C26" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="105">
-        <v>220000</v>
-      </c>
-      <c r="F26" s="40"/>
+      <c r="B26" s="152"/>
+      <c r="C26" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" s="154"/>
+      <c r="F26" s="156"/>
       <c r="G26" s="12"/>
     </row>
-    <row r="27" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A27" s="37">
         <f>IF(LEN(C27)=0,"",COUNTA($C$14:C27))</f>
         <v>9</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C27" s="36" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D27" s="36" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E27" s="39">
-        <v>75000</v>
+        <v>59000</v>
       </c>
       <c r="F27" s="40"/>
       <c r="G27" s="12"/>
     </row>
-    <row r="28" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A28" s="37">
         <f>IF(LEN(C28)=0,"",COUNTA($C$14:C28))</f>
         <v>10</v>
       </c>
-      <c r="B28" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="39">
-        <v>27000</v>
+      <c r="B28" s="78"/>
+      <c r="C28" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="46" t="s">
+        <v>25</v>
       </c>
       <c r="F28" s="40"/>
       <c r="G28" s="12"/>
     </row>
-    <row r="29" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="37">
-        <f>IF(LEN(C29)=0,"",COUNTA($C$14:C29))</f>
-        <v>11</v>
-      </c>
-      <c r="B29" s="157" t="s">
-        <v>60</v>
-      </c>
-      <c r="C29" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="D29" s="70" t="s">
-        <v>62</v>
-      </c>
-      <c r="E29" s="69">
-        <v>41000</v>
-      </c>
-      <c r="F29" s="158" t="s">
-        <v>377</v>
-      </c>
+    <row r="29" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="123" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="124"/>
+      <c r="C29" s="124"/>
+      <c r="D29" s="125"/>
+      <c r="E29" s="120">
+        <f>SUM(E14:E28)</f>
+        <v>564000</v>
+      </c>
+      <c r="F29" s="47"/>
       <c r="G29" s="12"/>
     </row>
-    <row r="30" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A30" s="37">
-        <f>IF(LEN(C30)=0,"",COUNTA($C$14:C30))</f>
-        <v>12</v>
-      </c>
-      <c r="B30" s="157"/>
-      <c r="C30" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="D30" s="70" t="s">
-        <v>64</v>
-      </c>
-      <c r="E30" s="69">
-        <v>59000</v>
-      </c>
-      <c r="F30" s="159"/>
+    <row r="30" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="48"/>
+      <c r="B30" s="49"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="52"/>
       <c r="G30" s="12"/>
     </row>
-    <row r="31" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A31" s="37">
-        <f>IF(LEN(C31)=0,"",COUNTA($C$14:C31))</f>
-        <v>13</v>
-      </c>
-      <c r="B31" s="157"/>
-      <c r="C31" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="D31" s="70" t="s">
-        <v>66</v>
-      </c>
-      <c r="E31" s="69">
-        <v>59000</v>
-      </c>
-      <c r="F31" s="159"/>
-      <c r="G31" s="12"/>
-    </row>
-    <row r="32" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A32" s="37">
-        <f>IF(LEN(C32)=0,"",COUNTA($C$14:C32))</f>
-        <v>14</v>
-      </c>
-      <c r="B32" s="157"/>
-      <c r="C32" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D32" s="70" t="s">
-        <v>68</v>
-      </c>
-      <c r="E32" s="69">
-        <v>47000</v>
-      </c>
-      <c r="F32" s="159"/>
+    <row r="31" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A31" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" s="54"/>
+      <c r="C31" s="54"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="115"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="13"/>
+    </row>
+    <row r="32" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="56"/>
+      <c r="B32" s="57"/>
+      <c r="C32" s="58"/>
+      <c r="D32" s="58"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="60"/>
       <c r="G32" s="12"/>
     </row>
-    <row r="33" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A33" s="37">
-        <f>IF(LEN(C33)=0,"",COUNTA($C$14:C33))</f>
-        <v>15</v>
-      </c>
-      <c r="B33" s="157"/>
-      <c r="C33" s="41" t="s">
-        <v>69</v>
-      </c>
-      <c r="D33" s="70" t="s">
-        <v>70</v>
-      </c>
-      <c r="E33" s="69">
-        <v>41000</v>
-      </c>
-      <c r="F33" s="160"/>
+    <row r="33" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A33" s="61" t="s">
+        <v>259</v>
+      </c>
+      <c r="B33" s="123" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="125"/>
+      <c r="D33" s="61" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="120" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="34" t="s">
+        <v>0</v>
+      </c>
       <c r="G33" s="12"/>
     </row>
-    <row r="34" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="37">
-        <f>IF(LEN(C34)=0,"",COUNTA($C$14:C34))</f>
-        <v>16</v>
-      </c>
-      <c r="B34" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="C34" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="D34" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="E34" s="43">
-        <v>41000</v>
-      </c>
-      <c r="F34" s="40"/>
+    <row r="34" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A34" s="62" t="s">
+        <v>209</v>
+      </c>
+      <c r="B34" s="63"/>
+      <c r="C34" s="64"/>
+      <c r="D34" s="65"/>
+      <c r="E34" s="66"/>
+      <c r="F34" s="67"/>
       <c r="G34" s="12"/>
     </row>
     <row r="35" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
-        <f>IF(LEN(C35)=0,"",COUNTA($C$14:C35))</f>
-        <v>17</v>
-      </c>
-      <c r="B35" s="152" t="s">
-        <v>40</v>
-      </c>
-      <c r="C35" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" s="41" t="s">
-        <v>42</v>
-      </c>
-      <c r="E35" s="153">
-        <v>60000</v>
-      </c>
-      <c r="F35" s="155" t="s">
-        <v>381</v>
-      </c>
+        <f>IF(LEN(C35)=0,"",COUNTA($C$35:C35))</f>
+        <v>1</v>
+      </c>
+      <c r="B35" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="68">
+        <v>169000</v>
+      </c>
+      <c r="F35" s="40"/>
       <c r="G35" s="12"/>
     </row>
     <row r="36" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A36" s="37">
-        <f>IF(LEN(C36)=0,"",COUNTA($C$14:C36))</f>
-        <v>18</v>
-      </c>
-      <c r="B36" s="152"/>
-      <c r="C36" s="41" t="s">
-        <v>43</v>
-      </c>
-      <c r="D36" s="41" t="s">
-        <v>42</v>
-      </c>
-      <c r="E36" s="154"/>
-      <c r="F36" s="156"/>
+        <f>IF(LEN(C36)=0,"",COUNTA($C$35:C36))</f>
+        <v>2</v>
+      </c>
+      <c r="B36" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D36" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="E36" s="68">
+        <v>41000</v>
+      </c>
+      <c r="F36" s="40"/>
       <c r="G36" s="12"/>
     </row>
-    <row r="37" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
-        <f>IF(LEN(C37)=0,"",COUNTA($C37:C$54))</f>
-        <v>12</v>
-      </c>
-      <c r="B37" s="38"/>
-      <c r="C37" s="35" t="s">
-        <v>98</v>
-      </c>
-      <c r="D37" s="35" t="s">
-        <v>99</v>
-      </c>
-      <c r="E37" s="72">
-        <v>123000</v>
+        <f>IF(LEN(C37)=0,"",COUNTA($C$35:C37))</f>
+        <v>3</v>
+      </c>
+      <c r="B37" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="D37" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="E37" s="69">
+        <v>41000</v>
       </c>
       <c r="F37" s="40"/>
       <c r="G37" s="12"/>
     </row>
     <row r="38" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A38" s="37">
-        <f>IF(LEN(C38)=0,"",COUNTA($C38:C$54))</f>
-        <v>11</v>
-      </c>
-      <c r="B38" s="38"/>
-      <c r="C38" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="D38" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="E38" s="72">
-        <v>174000</v>
+        <f>IF(LEN(C38)=0,"",COUNTA($C$35:C38))</f>
+        <v>4</v>
+      </c>
+      <c r="B38" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="D38" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="E38" s="69">
+        <v>47000</v>
       </c>
       <c r="F38" s="40"/>
       <c r="G38" s="12"/>
     </row>
-    <row r="39" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A39" s="37">
-        <f>IF(LEN(C39)=0,"",COUNTA($C39:C$54))</f>
-        <v>10</v>
-      </c>
-      <c r="B39" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="C39" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D39" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="E39" s="68">
+        <f>IF(LEN(C39)=0,"",COUNTA($C$35:C39))</f>
+        <v>5</v>
+      </c>
+      <c r="B39" s="140" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="D39" s="41" t="s">
+        <v>268</v>
+      </c>
+      <c r="E39" s="69">
         <v>41000</v>
       </c>
-      <c r="F39" s="40"/>
+      <c r="F39" s="108" t="s">
+        <v>376</v>
+      </c>
       <c r="G39" s="12"/>
     </row>
-    <row r="40" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A40" s="37">
-        <f>IF(LEN(C40)=0,"",COUNTA($C$14:C40))</f>
-        <v>22</v>
-      </c>
-      <c r="B40" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="D40" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="E40" s="39">
-        <v>59000</v>
-      </c>
-      <c r="F40" s="40"/>
+        <f>IF(LEN(C40)=0,"",COUNTA($C$35:C40))</f>
+        <v>6</v>
+      </c>
+      <c r="B40" s="142"/>
+      <c r="C40" s="41" t="s">
+        <v>274</v>
+      </c>
+      <c r="D40" s="41" t="s">
+        <v>275</v>
+      </c>
+      <c r="E40" s="69">
+        <v>41000</v>
+      </c>
+      <c r="F40" s="108" t="s">
+        <v>375</v>
+      </c>
       <c r="G40" s="12"/>
     </row>
-    <row r="41" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="37">
-        <f>IF(LEN(C41)=0,"",COUNTA($C41:C$54))</f>
-        <v>8</v>
-      </c>
-      <c r="B41" s="78"/>
-      <c r="C41" s="35" t="s">
-        <v>183</v>
-      </c>
-      <c r="D41" s="35" t="s">
-        <v>184</v>
-      </c>
-      <c r="E41" s="68">
-        <v>329000</v>
-      </c>
-      <c r="F41" s="40"/>
+        <f>IF(LEN(C41)=0,"",COUNTA($C$35:C41))</f>
+        <v>7</v>
+      </c>
+      <c r="B41" s="159" t="s">
+        <v>60</v>
+      </c>
+      <c r="C41" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="D41" s="70" t="s">
+        <v>62</v>
+      </c>
+      <c r="E41" s="69">
+        <v>41000</v>
+      </c>
+      <c r="F41" s="160" t="s">
+        <v>377</v>
+      </c>
       <c r="G41" s="12"/>
     </row>
     <row r="42" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A42" s="37">
-        <f>IF(LEN(C42)=0,"",COUNTA($C42:C$54))</f>
-        <v>7</v>
-      </c>
-      <c r="B42" s="78"/>
-      <c r="C42" s="36" t="s">
-        <v>181</v>
-      </c>
-      <c r="D42" s="36" t="s">
-        <v>182</v>
-      </c>
-      <c r="E42" s="68">
-        <v>72000</v>
-      </c>
-      <c r="F42" s="40"/>
+        <f>IF(LEN(C42)=0,"",COUNTA($C$35:C42))</f>
+        <v>8</v>
+      </c>
+      <c r="B42" s="159"/>
+      <c r="C42" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="D42" s="70" t="s">
+        <v>64</v>
+      </c>
+      <c r="E42" s="69">
+        <v>59000</v>
+      </c>
+      <c r="F42" s="161"/>
       <c r="G42" s="12"/>
     </row>
-    <row r="43" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A43" s="37">
-        <f>IF(LEN(C43)=0,"",COUNTA($C43:C$54))</f>
-        <v>6</v>
-      </c>
-      <c r="B43" s="78"/>
-      <c r="C43" s="73" t="s">
-        <v>73</v>
-      </c>
-      <c r="D43" s="74" t="s">
-        <v>280</v>
-      </c>
-      <c r="E43" s="39">
-        <v>290000</v>
-      </c>
-      <c r="F43" s="40" t="s">
-        <v>74</v>
-      </c>
+        <f>IF(LEN(C43)=0,"",COUNTA($C$35:C43))</f>
+        <v>9</v>
+      </c>
+      <c r="B43" s="159"/>
+      <c r="C43" s="41" t="s">
+        <v>65</v>
+      </c>
+      <c r="D43" s="70" t="s">
+        <v>66</v>
+      </c>
+      <c r="E43" s="69">
+        <v>59000</v>
+      </c>
+      <c r="F43" s="161"/>
       <c r="G43" s="12"/>
     </row>
-    <row r="44" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A44" s="37">
-        <f>IF(LEN(C44)=0,"",COUNTA($C44:C$54))</f>
-        <v>5</v>
-      </c>
-      <c r="B44" s="78"/>
-      <c r="C44" s="73" t="s">
-        <v>71</v>
-      </c>
-      <c r="D44" s="74" t="s">
-        <v>72</v>
-      </c>
-      <c r="E44" s="39">
-        <v>174000</v>
-      </c>
-      <c r="F44" s="40"/>
-      <c r="G44" s="13"/>
-    </row>
-    <row r="45" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+        <f>IF(LEN(C44)=0,"",COUNTA($C$35:C44))</f>
+        <v>10</v>
+      </c>
+      <c r="B44" s="159"/>
+      <c r="C44" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D44" s="70" t="s">
+        <v>68</v>
+      </c>
+      <c r="E44" s="69">
+        <v>47000</v>
+      </c>
+      <c r="F44" s="161"/>
+      <c r="G44" s="12"/>
+    </row>
+    <row r="45" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A45" s="37">
-        <f>IF(LEN(C45)=0,"",COUNTA($C45:C$54))</f>
-        <v>4</v>
-      </c>
-      <c r="B45" s="78"/>
-      <c r="C45" s="73" t="s">
-        <v>79</v>
-      </c>
-      <c r="D45" s="74" t="s">
-        <v>279</v>
-      </c>
-      <c r="E45" s="116">
-        <v>121000</v>
-      </c>
-      <c r="F45" s="40"/>
-      <c r="G45" s="13"/>
-    </row>
-    <row r="46" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+        <f>IF(LEN(C45)=0,"",COUNTA($C$35:C45))</f>
+        <v>11</v>
+      </c>
+      <c r="B45" s="159"/>
+      <c r="C45" s="41" t="s">
+        <v>69</v>
+      </c>
+      <c r="D45" s="70" t="s">
+        <v>70</v>
+      </c>
+      <c r="E45" s="69">
+        <v>41000</v>
+      </c>
+      <c r="F45" s="162"/>
+      <c r="G45" s="12"/>
+    </row>
+    <row r="46" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A46" s="37">
-        <f>IF(LEN(C46)=0,"",COUNTA($C46:C$54))</f>
-        <v>3</v>
-      </c>
-      <c r="B46" s="78"/>
-      <c r="C46" s="73" t="s">
-        <v>75</v>
-      </c>
-      <c r="D46" s="74" t="s">
-        <v>76</v>
-      </c>
-      <c r="E46" s="39">
-        <v>231000</v>
+        <f>IF(LEN(C46)=0,"",COUNTA($C$35:C46))</f>
+        <v>12</v>
+      </c>
+      <c r="B46" s="71" t="s">
+        <v>127</v>
+      </c>
+      <c r="C46" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="D46" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="E46" s="72">
+        <v>102000</v>
       </c>
       <c r="F46" s="40"/>
-      <c r="G46" s="13"/>
-    </row>
-    <row r="47" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="G46" s="12"/>
+    </row>
+    <row r="47" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="37">
-        <f>IF(LEN(C47)=0,"",COUNTA($C$14:C47))</f>
-        <v>29</v>
-      </c>
-      <c r="B47" s="78"/>
-      <c r="C47" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="D47" s="45" t="s">
-        <v>24</v>
-      </c>
-      <c r="E47" s="46" t="s">
-        <v>25</v>
-      </c>
-      <c r="F47" s="40"/>
+        <f>IF(LEN(C47)=0,"",COUNTA($C$35:C47))</f>
+        <v>13</v>
+      </c>
+      <c r="B47" s="140" t="s">
+        <v>277</v>
+      </c>
+      <c r="C47" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="D47" s="35" t="s">
+        <v>195</v>
+      </c>
+      <c r="E47" s="72">
+        <v>62000</v>
+      </c>
+      <c r="F47" s="160" t="s">
+        <v>378</v>
+      </c>
       <c r="G47" s="12"/>
     </row>
     <row r="48" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="123" t="s">
-        <v>26</v>
-      </c>
-      <c r="B48" s="124"/>
-      <c r="C48" s="124"/>
-      <c r="D48" s="125"/>
-      <c r="E48" s="120">
-        <f>SUM(E14:E47)</f>
-        <v>3274000</v>
-      </c>
-      <c r="F48" s="47"/>
+      <c r="A48" s="37">
+        <f>IF(LEN(C48)=0,"",COUNTA($C$35:C48))</f>
+        <v>14</v>
+      </c>
+      <c r="B48" s="141"/>
+      <c r="C48" s="35" t="s">
+        <v>196</v>
+      </c>
+      <c r="D48" s="35" t="s">
+        <v>197</v>
+      </c>
+      <c r="E48" s="72">
+        <v>165000</v>
+      </c>
+      <c r="F48" s="161"/>
       <c r="G48" s="12"/>
     </row>
     <row r="49" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="48"/>
-      <c r="B49" s="49"/>
-      <c r="C49" s="50"/>
-      <c r="D49" s="50"/>
-      <c r="E49" s="51"/>
-      <c r="F49" s="52"/>
+      <c r="A49" s="37">
+        <f>IF(LEN(C49)=0,"",COUNTA($C$35:C49))</f>
+        <v>15</v>
+      </c>
+      <c r="B49" s="142"/>
+      <c r="C49" s="35" t="s">
+        <v>201</v>
+      </c>
+      <c r="D49" s="35" t="s">
+        <v>202</v>
+      </c>
+      <c r="E49" s="72">
+        <v>116000</v>
+      </c>
+      <c r="F49" s="162"/>
       <c r="G49" s="12"/>
     </row>
-    <row r="50" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="53" t="s">
-        <v>47</v>
-      </c>
-      <c r="B50" s="54"/>
-      <c r="C50" s="54"/>
-      <c r="D50" s="54"/>
-      <c r="E50" s="115"/>
-      <c r="F50" s="55"/>
-      <c r="G50" s="13"/>
-    </row>
-    <row r="51" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="56"/>
-      <c r="B51" s="57"/>
-      <c r="C51" s="58"/>
-      <c r="D51" s="58"/>
-      <c r="E51" s="59"/>
-      <c r="F51" s="60"/>
+    <row r="50" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A50" s="37">
+        <f>IF(LEN(C50)=0,"",COUNTA($C$35:C50))</f>
+        <v>16</v>
+      </c>
+      <c r="B50" s="140" t="s">
+        <v>272</v>
+      </c>
+      <c r="C50" s="35" t="s">
+        <v>198</v>
+      </c>
+      <c r="D50" s="35" t="s">
+        <v>199</v>
+      </c>
+      <c r="E50" s="72">
+        <v>83000</v>
+      </c>
+      <c r="F50" s="40"/>
+      <c r="G50" s="12"/>
+    </row>
+    <row r="51" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A51" s="37">
+        <f>IF(LEN(C51)=0,"",COUNTA($C$35:C51))</f>
+        <v>17</v>
+      </c>
+      <c r="B51" s="141"/>
+      <c r="C51" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="D51" s="35" t="s">
+        <v>199</v>
+      </c>
+      <c r="E51" s="72">
+        <v>130000</v>
+      </c>
+      <c r="F51" s="160" t="s">
+        <v>378</v>
+      </c>
       <c r="G51" s="12"/>
     </row>
-    <row r="52" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A52" s="61" t="s">
-        <v>259</v>
-      </c>
-      <c r="B52" s="123" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="125"/>
-      <c r="D52" s="61" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="120" t="s">
-        <v>4</v>
-      </c>
-      <c r="F52" s="34" t="s">
-        <v>0</v>
-      </c>
+    <row r="52" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A52" s="37">
+        <f>IF(LEN(C52)=0,"",COUNTA($C$35:C52))</f>
+        <v>18</v>
+      </c>
+      <c r="B52" s="141"/>
+      <c r="C52" s="35" t="s">
+        <v>270</v>
+      </c>
+      <c r="D52" s="35" t="s">
+        <v>199</v>
+      </c>
+      <c r="E52" s="72">
+        <v>120000</v>
+      </c>
+      <c r="F52" s="161"/>
       <c r="G52" s="12"/>
     </row>
     <row r="53" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="62" t="s">
-        <v>209</v>
-      </c>
-      <c r="B53" s="63"/>
-      <c r="C53" s="64"/>
-      <c r="D53" s="65"/>
-      <c r="E53" s="66"/>
-      <c r="F53" s="67"/>
+      <c r="A53" s="37">
+        <f>IF(LEN(C53)=0,"",COUNTA($C$35:C53))</f>
+        <v>19</v>
+      </c>
+      <c r="B53" s="142"/>
+      <c r="C53" s="35" t="s">
+        <v>271</v>
+      </c>
+      <c r="D53" s="35" t="s">
+        <v>200</v>
+      </c>
+      <c r="E53" s="72">
+        <v>282000</v>
+      </c>
+      <c r="F53" s="162"/>
       <c r="G53" s="12"/>
     </row>
-    <row r="54" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A54" s="37">
-        <f>IF(LEN(C54)=0,"",COUNTA($C$54:C54))</f>
-        <v>1</v>
-      </c>
-      <c r="B54" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="C54" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="D54" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="E54" s="68">
-        <v>169000</v>
+        <f>IF(LEN(C54)=0,"",COUNTA($C$35:C54))</f>
+        <v>20</v>
+      </c>
+      <c r="B54" s="71" t="s">
+        <v>373</v>
+      </c>
+      <c r="C54" s="35" t="s">
+        <v>336</v>
+      </c>
+      <c r="D54" s="35" t="s">
+        <v>193</v>
+      </c>
+      <c r="E54" s="72">
+        <v>128000</v>
       </c>
       <c r="F54" s="40"/>
       <c r="G54" s="12"/>
     </row>
-    <row r="55" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="37">
-        <f>IF(LEN(C55)=0,"",COUNTA($C$54:C55))</f>
-        <v>2</v>
-      </c>
-      <c r="B55" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="C55" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D55" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="E55" s="68">
-        <v>41000</v>
-      </c>
-      <c r="F55" s="40"/>
+        <f>IF(LEN(C55)=0,"",COUNTA($C$35:C55))</f>
+        <v>21</v>
+      </c>
+      <c r="B55" s="168" t="s">
+        <v>130</v>
+      </c>
+      <c r="C55" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="D55" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="E55" s="72">
+        <v>71000</v>
+      </c>
+      <c r="F55" s="155" t="s">
+        <v>380</v>
+      </c>
       <c r="G55" s="12"/>
     </row>
-    <row r="56" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A56" s="37">
-        <f>IF(LEN(C56)=0,"",COUNTA($C$54:C56))</f>
-        <v>3</v>
-      </c>
-      <c r="B56" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="C56" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="D56" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="E56" s="69">
-        <v>41000</v>
-      </c>
-      <c r="F56" s="40"/>
+        <f>IF(LEN(C56)=0,"",COUNTA($C$35:C56))</f>
+        <v>22</v>
+      </c>
+      <c r="B56" s="169"/>
+      <c r="C56" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="D56" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="E56" s="68">
+        <v>138000</v>
+      </c>
+      <c r="F56" s="156"/>
       <c r="G56" s="12"/>
     </row>
-    <row r="57" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A57" s="37">
-        <f>IF(LEN(C57)=0,"",COUNTA($C$54:C57))</f>
-        <v>4</v>
-      </c>
-      <c r="B57" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="C57" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="D57" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="E57" s="69">
-        <v>47000</v>
-      </c>
-      <c r="F57" s="40"/>
+        <f>IF(LEN(C57)=0,"",COUNTA($C$35:C57))</f>
+        <v>23</v>
+      </c>
+      <c r="B57" s="109" t="s">
+        <v>389</v>
+      </c>
+      <c r="C57" s="35" t="s">
+        <v>390</v>
+      </c>
+      <c r="D57" s="35" t="s">
+        <v>391</v>
+      </c>
+      <c r="E57" s="68">
+        <v>282000</v>
+      </c>
+      <c r="F57" s="110"/>
       <c r="G57" s="12"/>
     </row>
-    <row r="58" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" s="14" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="37">
-        <f>IF(LEN(C58)=0,"",COUNTA($C$54:C58))</f>
-        <v>5</v>
-      </c>
-      <c r="B58" s="140" t="s">
-        <v>44</v>
-      </c>
-      <c r="C58" s="41" t="s">
-        <v>267</v>
-      </c>
-      <c r="D58" s="41" t="s">
-        <v>268</v>
-      </c>
-      <c r="E58" s="69">
-        <v>41000</v>
-      </c>
-      <c r="F58" s="108" t="s">
-        <v>376</v>
-      </c>
-      <c r="G58" s="12"/>
-    </row>
-    <row r="59" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+        <f>IF(LEN(C58)=0,"",COUNTA($C$35:C58))</f>
+        <v>24</v>
+      </c>
+      <c r="B58" s="170" t="s">
+        <v>205</v>
+      </c>
+      <c r="C58" s="35" t="s">
+        <v>161</v>
+      </c>
+      <c r="D58" s="35" t="s">
+        <v>162</v>
+      </c>
+      <c r="E58" s="72">
+        <v>30000</v>
+      </c>
+      <c r="F58" s="171" t="s">
+        <v>382</v>
+      </c>
+      <c r="G58" s="13"/>
+    </row>
+    <row r="59" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A59" s="37">
-        <f>IF(LEN(C59)=0,"",COUNTA($C$54:C59))</f>
-        <v>6</v>
-      </c>
-      <c r="B59" s="142"/>
-      <c r="C59" s="41" t="s">
-        <v>274</v>
-      </c>
-      <c r="D59" s="41" t="s">
-        <v>275</v>
-      </c>
-      <c r="E59" s="69">
-        <v>41000</v>
-      </c>
-      <c r="F59" s="108" t="s">
-        <v>375</v>
-      </c>
-      <c r="G59" s="12"/>
-    </row>
-    <row r="60" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="37">
-        <f>IF(LEN(C60)=0,"",COUNTA($C$54:C60))</f>
-        <v>7</v>
-      </c>
-      <c r="B60" s="157" t="s">
-        <v>60</v>
-      </c>
-      <c r="C60" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="D60" s="70" t="s">
-        <v>62</v>
-      </c>
-      <c r="E60" s="69">
-        <v>41000</v>
-      </c>
-      <c r="F60" s="158" t="s">
-        <v>377</v>
-      </c>
+        <f>IF(LEN(C59)=0,"",COUNTA($C$35:C59))</f>
+        <v>25</v>
+      </c>
+      <c r="B59" s="170"/>
+      <c r="C59" s="35" t="s">
+        <v>278</v>
+      </c>
+      <c r="D59" s="35" t="s">
+        <v>162</v>
+      </c>
+      <c r="E59" s="72">
+        <v>20000</v>
+      </c>
+      <c r="F59" s="172"/>
+      <c r="G59" s="13"/>
+    </row>
+    <row r="60" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A60" s="173" t="s">
+        <v>208</v>
+      </c>
+      <c r="B60" s="174"/>
+      <c r="C60" s="174"/>
+      <c r="D60" s="175"/>
+      <c r="E60" s="66"/>
+      <c r="F60" s="67"/>
       <c r="G60" s="12"/>
     </row>
-    <row r="61" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A61" s="37">
-        <f>IF(LEN(C61)=0,"",COUNTA($C$54:C61))</f>
-        <v>8</v>
-      </c>
-      <c r="B61" s="157"/>
-      <c r="C61" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="D61" s="70" t="s">
-        <v>64</v>
-      </c>
-      <c r="E61" s="69">
-        <v>59000</v>
-      </c>
-      <c r="F61" s="159"/>
-      <c r="G61" s="12"/>
-    </row>
-    <row r="62" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+        <f>IF(LEN(C61)=0,"",COUNTA($C$35:C61))</f>
+        <v>26</v>
+      </c>
+      <c r="B61" s="163" t="s">
+        <v>260</v>
+      </c>
+      <c r="C61" s="73" t="s">
+        <v>71</v>
+      </c>
+      <c r="D61" s="74" t="s">
+        <v>72</v>
+      </c>
+      <c r="E61" s="39">
+        <v>174000</v>
+      </c>
+      <c r="F61" s="40"/>
+      <c r="G61" s="13"/>
+    </row>
+    <row r="62" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A62" s="37">
-        <f>IF(LEN(C62)=0,"",COUNTA($C$54:C62))</f>
-        <v>9</v>
-      </c>
-      <c r="B62" s="157"/>
-      <c r="C62" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="D62" s="70" t="s">
-        <v>66</v>
-      </c>
-      <c r="E62" s="69">
-        <v>59000</v>
-      </c>
-      <c r="F62" s="159"/>
-      <c r="G62" s="12"/>
-    </row>
-    <row r="63" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+        <f>IF(LEN(C62)=0,"",COUNTA($C$35:C62))</f>
+        <v>27</v>
+      </c>
+      <c r="B62" s="164"/>
+      <c r="C62" s="73" t="s">
+        <v>83</v>
+      </c>
+      <c r="D62" s="74" t="s">
+        <v>84</v>
+      </c>
+      <c r="E62" s="106">
+        <v>231000</v>
+      </c>
+      <c r="F62" s="40"/>
+      <c r="G62" s="13"/>
+    </row>
+    <row r="63" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A63" s="37">
-        <f>IF(LEN(C63)=0,"",COUNTA($C$54:C63))</f>
-        <v>10</v>
-      </c>
-      <c r="B63" s="157"/>
-      <c r="C63" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D63" s="70" t="s">
-        <v>68</v>
-      </c>
-      <c r="E63" s="69">
-        <v>47000</v>
-      </c>
-      <c r="F63" s="159"/>
-      <c r="G63" s="12"/>
-    </row>
-    <row r="64" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+        <f>IF(LEN(C63)=0,"",COUNTA($C$35:C63))</f>
+        <v>28</v>
+      </c>
+      <c r="B63" s="164"/>
+      <c r="C63" s="73" t="s">
+        <v>85</v>
+      </c>
+      <c r="D63" s="74" t="s">
+        <v>86</v>
+      </c>
+      <c r="E63" s="39">
+        <v>732000</v>
+      </c>
+      <c r="F63" s="40"/>
+      <c r="G63" s="13"/>
+    </row>
+    <row r="64" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A64" s="37">
-        <f>IF(LEN(C64)=0,"",COUNTA($C$54:C64))</f>
-        <v>11</v>
-      </c>
-      <c r="B64" s="157"/>
-      <c r="C64" s="41" t="s">
-        <v>69</v>
-      </c>
-      <c r="D64" s="70" t="s">
-        <v>70</v>
-      </c>
-      <c r="E64" s="69">
-        <v>41000</v>
-      </c>
-      <c r="F64" s="160"/>
-      <c r="G64" s="12"/>
-    </row>
-    <row r="65" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+        <f>IF(LEN(C64)=0,"",COUNTA($C$35:C64))</f>
+        <v>29</v>
+      </c>
+      <c r="B64" s="164"/>
+      <c r="C64" s="73" t="s">
+        <v>79</v>
+      </c>
+      <c r="D64" s="74" t="s">
+        <v>279</v>
+      </c>
+      <c r="E64" s="116">
+        <v>121000</v>
+      </c>
+      <c r="F64" s="40"/>
+      <c r="G64" s="13"/>
+    </row>
+    <row r="65" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A65" s="37">
-        <f>IF(LEN(C65)=0,"",COUNTA($C$54:C65))</f>
-        <v>12</v>
-      </c>
-      <c r="B65" s="71" t="s">
-        <v>127</v>
-      </c>
-      <c r="C65" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="D65" s="35" t="s">
-        <v>129</v>
-      </c>
-      <c r="E65" s="72">
-        <v>102000</v>
+        <f>IF(LEN(C65)=0,"",COUNTA($C$35:C65))</f>
+        <v>30</v>
+      </c>
+      <c r="B65" s="164"/>
+      <c r="C65" s="73" t="s">
+        <v>93</v>
+      </c>
+      <c r="D65" s="74" t="s">
+        <v>94</v>
+      </c>
+      <c r="E65" s="39">
+        <v>192000</v>
       </c>
       <c r="F65" s="40"/>
-      <c r="G65" s="12"/>
-    </row>
-    <row r="66" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G65" s="13"/>
+    </row>
+    <row r="66" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A66" s="37">
-        <f>IF(LEN(C66)=0,"",COUNTA($C$54:C66))</f>
-        <v>13</v>
-      </c>
-      <c r="B66" s="140" t="s">
-        <v>277</v>
-      </c>
-      <c r="C66" s="35" t="s">
-        <v>194</v>
-      </c>
-      <c r="D66" s="35" t="s">
-        <v>195</v>
-      </c>
-      <c r="E66" s="72">
-        <v>62000</v>
-      </c>
-      <c r="F66" s="158" t="s">
-        <v>378</v>
-      </c>
-      <c r="G66" s="12"/>
-    </row>
-    <row r="67" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+        <f>IF(LEN(C66)=0,"",COUNTA($C$35:C66))</f>
+        <v>31</v>
+      </c>
+      <c r="B66" s="164"/>
+      <c r="C66" s="73" t="s">
+        <v>80</v>
+      </c>
+      <c r="D66" s="74" t="s">
+        <v>81</v>
+      </c>
+      <c r="E66" s="39">
+        <v>173000</v>
+      </c>
+      <c r="F66" s="40"/>
+      <c r="G66" s="13"/>
+    </row>
+    <row r="67" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A67" s="37">
-        <f>IF(LEN(C67)=0,"",COUNTA($C$54:C67))</f>
-        <v>14</v>
-      </c>
-      <c r="B67" s="141"/>
-      <c r="C67" s="35" t="s">
-        <v>196</v>
-      </c>
-      <c r="D67" s="35" t="s">
-        <v>197</v>
-      </c>
-      <c r="E67" s="72">
-        <v>165000</v>
-      </c>
-      <c r="F67" s="159"/>
-      <c r="G67" s="12"/>
-    </row>
-    <row r="68" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+        <f>IF(LEN(C67)=0,"",COUNTA($C$35:C67))</f>
+        <v>32</v>
+      </c>
+      <c r="B67" s="164"/>
+      <c r="C67" s="73" t="s">
+        <v>82</v>
+      </c>
+      <c r="D67" s="74" t="s">
+        <v>281</v>
+      </c>
+      <c r="E67" s="106">
+        <v>231000</v>
+      </c>
+      <c r="F67" s="108" t="s">
+        <v>395</v>
+      </c>
+      <c r="G67" s="13"/>
+    </row>
+    <row r="68" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A68" s="37">
-        <f>IF(LEN(C68)=0,"",COUNTA($C$54:C68))</f>
-        <v>15</v>
-      </c>
-      <c r="B68" s="142"/>
-      <c r="C68" s="35" t="s">
-        <v>201</v>
-      </c>
-      <c r="D68" s="35" t="s">
-        <v>202</v>
-      </c>
-      <c r="E68" s="72">
-        <v>116000</v>
-      </c>
-      <c r="F68" s="160"/>
-      <c r="G68" s="12"/>
-    </row>
-    <row r="69" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+        <f>IF(LEN(C68)=0,"",COUNTA($C$35:C68))</f>
+        <v>33</v>
+      </c>
+      <c r="B68" s="164"/>
+      <c r="C68" s="75" t="s">
+        <v>234</v>
+      </c>
+      <c r="D68" s="76" t="s">
+        <v>235</v>
+      </c>
+      <c r="E68" s="117">
+        <v>500000</v>
+      </c>
+      <c r="F68" s="40"/>
+      <c r="G68" s="13"/>
+    </row>
+    <row r="69" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A69" s="37">
-        <f>IF(LEN(C69)=0,"",COUNTA($C$54:C69))</f>
-        <v>16</v>
-      </c>
-      <c r="B69" s="140" t="s">
-        <v>272</v>
-      </c>
-      <c r="C69" s="35" t="s">
-        <v>198</v>
-      </c>
-      <c r="D69" s="35" t="s">
-        <v>199</v>
-      </c>
-      <c r="E69" s="72">
-        <v>83000</v>
-      </c>
-      <c r="F69" s="40"/>
+        <f>IF(LEN(C69)=0,"",COUNTA($C$35:C69))</f>
+        <v>34</v>
+      </c>
+      <c r="B69" s="164"/>
+      <c r="C69" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="D69" s="74" t="s">
+        <v>280</v>
+      </c>
+      <c r="E69" s="39">
+        <v>290000</v>
+      </c>
+      <c r="F69" s="40" t="s">
+        <v>74</v>
+      </c>
       <c r="G69" s="12"/>
     </row>
-    <row r="70" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A70" s="37">
-        <f>IF(LEN(C70)=0,"",COUNTA($C$54:C70))</f>
-        <v>17</v>
-      </c>
-      <c r="B70" s="141"/>
-      <c r="C70" s="35" t="s">
-        <v>269</v>
-      </c>
-      <c r="D70" s="35" t="s">
-        <v>199</v>
-      </c>
-      <c r="E70" s="72">
-        <v>130000</v>
-      </c>
-      <c r="F70" s="158" t="s">
-        <v>378</v>
-      </c>
-      <c r="G70" s="12"/>
-    </row>
-    <row r="71" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+        <f>IF(LEN(C70)=0,"",COUNTA($C$35:C70))</f>
+        <v>35</v>
+      </c>
+      <c r="B70" s="164"/>
+      <c r="C70" s="73" t="s">
+        <v>75</v>
+      </c>
+      <c r="D70" s="74" t="s">
+        <v>76</v>
+      </c>
+      <c r="E70" s="39">
+        <v>231000</v>
+      </c>
+      <c r="F70" s="40"/>
+      <c r="G70" s="13"/>
+    </row>
+    <row r="71" spans="1:7" s="14" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A71" s="37">
-        <f>IF(LEN(C71)=0,"",COUNTA($C$54:C71))</f>
-        <v>18</v>
-      </c>
-      <c r="B71" s="141"/>
-      <c r="C71" s="35" t="s">
-        <v>270</v>
-      </c>
-      <c r="D71" s="35" t="s">
-        <v>199</v>
-      </c>
-      <c r="E71" s="72">
-        <v>120000</v>
-      </c>
-      <c r="F71" s="159"/>
-      <c r="G71" s="12"/>
-    </row>
-    <row r="72" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+        <f>IF(LEN(C71)=0,"",COUNTA($C$35:C71))</f>
+        <v>36</v>
+      </c>
+      <c r="B71" s="164"/>
+      <c r="C71" s="73" t="s">
+        <v>77</v>
+      </c>
+      <c r="D71" s="74" t="s">
+        <v>78</v>
+      </c>
+      <c r="E71" s="39">
+        <v>616000</v>
+      </c>
+      <c r="F71" s="40"/>
+      <c r="G71" s="13"/>
+    </row>
+    <row r="72" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A72" s="37">
-        <f>IF(LEN(C72)=0,"",COUNTA($C$54:C72))</f>
-        <v>19</v>
-      </c>
-      <c r="B72" s="142"/>
-      <c r="C72" s="35" t="s">
-        <v>271</v>
-      </c>
-      <c r="D72" s="35" t="s">
-        <v>200</v>
-      </c>
-      <c r="E72" s="72">
-        <v>282000</v>
-      </c>
-      <c r="F72" s="160"/>
-      <c r="G72" s="12"/>
-    </row>
-    <row r="73" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+        <f>IF(LEN(C72)=0,"",COUNTA($C$35:C72))</f>
+        <v>37</v>
+      </c>
+      <c r="B72" s="164"/>
+      <c r="C72" s="73" t="s">
+        <v>87</v>
+      </c>
+      <c r="D72" s="74" t="s">
+        <v>88</v>
+      </c>
+      <c r="E72" s="106">
+        <v>231000</v>
+      </c>
+      <c r="F72" s="40"/>
+      <c r="G72" s="13"/>
+    </row>
+    <row r="73" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A73" s="37">
-        <f>IF(LEN(C73)=0,"",COUNTA($C$54:C73))</f>
-        <v>20</v>
-      </c>
-      <c r="B73" s="71" t="s">
-        <v>373</v>
-      </c>
-      <c r="C73" s="35" t="s">
-        <v>336</v>
-      </c>
-      <c r="D73" s="35" t="s">
-        <v>193</v>
-      </c>
-      <c r="E73" s="72">
-        <v>128000</v>
+        <f>IF(LEN(C73)=0,"",COUNTA($C$35:C73))</f>
+        <v>38</v>
+      </c>
+      <c r="B73" s="165"/>
+      <c r="C73" s="73" t="s">
+        <v>95</v>
+      </c>
+      <c r="D73" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="E73" s="39">
+        <v>412000</v>
       </c>
       <c r="F73" s="40"/>
-      <c r="G73" s="12"/>
-    </row>
-    <row r="74" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G73" s="13"/>
+    </row>
+    <row r="74" spans="1:7" s="14" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="37">
-        <f>IF(LEN(C74)=0,"",COUNTA($C$54:C74))</f>
-        <v>21</v>
-      </c>
-      <c r="B74" s="166" t="s">
-        <v>130</v>
-      </c>
-      <c r="C74" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="D74" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="E74" s="72">
-        <v>71000</v>
-      </c>
-      <c r="F74" s="155" t="s">
-        <v>380</v>
-      </c>
-      <c r="G74" s="12"/>
-    </row>
-    <row r="75" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+        <f>IF(LEN(C74)=0,"",COUNTA($C$35:C74))</f>
+        <v>39</v>
+      </c>
+      <c r="B74" s="163" t="s">
+        <v>90</v>
+      </c>
+      <c r="C74" s="73" t="s">
+        <v>89</v>
+      </c>
+      <c r="D74" s="176" t="s">
+        <v>396</v>
+      </c>
+      <c r="E74" s="39">
+        <v>137000</v>
+      </c>
+      <c r="F74" s="160" t="s">
+        <v>379</v>
+      </c>
+      <c r="G74" s="13"/>
+    </row>
+    <row r="75" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A75" s="37">
-        <f>IF(LEN(C75)=0,"",COUNTA($C$54:C75))</f>
-        <v>22</v>
-      </c>
-      <c r="B75" s="167"/>
-      <c r="C75" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="D75" s="35" t="s">
-        <v>134</v>
-      </c>
-      <c r="E75" s="68">
-        <v>138000</v>
-      </c>
-      <c r="F75" s="156"/>
-      <c r="G75" s="12"/>
-    </row>
-    <row r="76" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+        <f>IF(LEN(C75)=0,"",COUNTA($C$35:C75))</f>
+        <v>40</v>
+      </c>
+      <c r="B75" s="164"/>
+      <c r="C75" s="73" t="s">
+        <v>91</v>
+      </c>
+      <c r="D75" s="177"/>
+      <c r="E75" s="39">
+        <v>137000</v>
+      </c>
+      <c r="F75" s="161"/>
+      <c r="G75" s="13"/>
+    </row>
+    <row r="76" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A76" s="37">
-        <f>IF(LEN(C76)=0,"",COUNTA($C$54:C76))</f>
-        <v>23</v>
-      </c>
-      <c r="B76" s="109" t="s">
-        <v>389</v>
-      </c>
-      <c r="C76" s="35" t="s">
-        <v>390</v>
-      </c>
-      <c r="D76" s="35" t="s">
-        <v>391</v>
-      </c>
-      <c r="E76" s="68">
-        <v>282000</v>
-      </c>
-      <c r="F76" s="110"/>
-      <c r="G76" s="12"/>
-    </row>
-    <row r="77" spans="1:7" s="14" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <f>IF(LEN(C76)=0,"",COUNTA($C$35:C76))</f>
+        <v>41</v>
+      </c>
+      <c r="B76" s="165"/>
+      <c r="C76" s="73" t="s">
+        <v>92</v>
+      </c>
+      <c r="D76" s="178"/>
+      <c r="E76" s="39">
+        <v>208000</v>
+      </c>
+      <c r="F76" s="162"/>
+      <c r="G76" s="13"/>
+    </row>
+    <row r="77" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A77" s="37">
-        <f>IF(LEN(C77)=0,"",COUNTA($C$54:C77))</f>
-        <v>24</v>
-      </c>
-      <c r="B77" s="168" t="s">
-        <v>205</v>
-      </c>
-      <c r="C77" s="35" t="s">
-        <v>161</v>
-      </c>
-      <c r="D77" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="E77" s="72">
-        <v>30000</v>
-      </c>
-      <c r="F77" s="169" t="s">
-        <v>382</v>
-      </c>
+        <f>IF(LEN(C77)=0,"",COUNTA($C$35:C77))</f>
+        <v>42</v>
+      </c>
+      <c r="B77" s="163" t="s">
+        <v>397</v>
+      </c>
+      <c r="C77" s="73" t="s">
+        <v>398</v>
+      </c>
+      <c r="D77" s="166" t="s">
+        <v>400</v>
+      </c>
+      <c r="E77" s="39">
+        <v>215000</v>
+      </c>
+      <c r="F77" s="104"/>
       <c r="G77" s="13"/>
     </row>
     <row r="78" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A78" s="37">
-        <f>IF(LEN(C78)=0,"",COUNTA($C$54:C78))</f>
-        <v>25</v>
-      </c>
-      <c r="B78" s="168"/>
-      <c r="C78" s="35" t="s">
-        <v>278</v>
-      </c>
-      <c r="D78" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="E78" s="72">
-        <v>20000</v>
-      </c>
-      <c r="F78" s="170"/>
+        <f>IF(LEN(C78)=0,"",COUNTA($C$35:C78))</f>
+        <v>43</v>
+      </c>
+      <c r="B78" s="164"/>
+      <c r="C78" s="73" t="s">
+        <v>399</v>
+      </c>
+      <c r="D78" s="167"/>
+      <c r="E78" s="39">
+        <v>323000</v>
+      </c>
+      <c r="F78" s="104"/>
       <c r="G78" s="13"/>
     </row>
-    <row r="79" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A79" s="171" t="s">
-        <v>208</v>
-      </c>
-      <c r="B79" s="172"/>
-      <c r="C79" s="172"/>
-      <c r="D79" s="173"/>
-      <c r="E79" s="66"/>
-      <c r="F79" s="67"/>
-      <c r="G79" s="12"/>
-    </row>
-    <row r="80" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" s="14" customFormat="1" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="37">
+        <f>IF(LEN(C79)=0,"",COUNTA($C$35:C79))</f>
+        <v>44</v>
+      </c>
+      <c r="B79" s="164"/>
+      <c r="C79" s="73" t="s">
+        <v>402</v>
+      </c>
+      <c r="D79" s="111" t="s">
+        <v>401</v>
+      </c>
+      <c r="E79" s="39">
+        <v>269000</v>
+      </c>
+      <c r="F79" s="104"/>
+      <c r="G79" s="13"/>
+    </row>
+    <row r="80" spans="1:7" s="14" customFormat="1" ht="82.5" x14ac:dyDescent="0.25">
       <c r="A80" s="37">
-        <f>IF(LEN(C80)=0,"",COUNTA($C$54:C80))</f>
-        <v>26</v>
-      </c>
-      <c r="B80" s="161" t="s">
-        <v>260</v>
-      </c>
+        <f>IF(LEN(C80)=0,"",COUNTA($C$35:C80))</f>
+        <v>45</v>
+      </c>
+      <c r="B80" s="165"/>
       <c r="C80" s="73" t="s">
-        <v>71</v>
-      </c>
-      <c r="D80" s="74" t="s">
-        <v>72</v>
+        <v>403</v>
+      </c>
+      <c r="D80" s="111" t="s">
+        <v>404</v>
       </c>
       <c r="E80" s="39">
+        <v>588000</v>
+      </c>
+      <c r="F80" s="104"/>
+      <c r="G80" s="13"/>
+    </row>
+    <row r="81" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A81" s="173" t="s">
+        <v>207</v>
+      </c>
+      <c r="B81" s="174"/>
+      <c r="C81" s="174"/>
+      <c r="D81" s="175"/>
+      <c r="E81" s="66"/>
+      <c r="F81" s="67"/>
+      <c r="G81" s="13"/>
+    </row>
+    <row r="82" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A82" s="37">
+        <f>IF(LEN(C82)=0,"",COUNTA($C$35:C82))</f>
+        <v>46</v>
+      </c>
+      <c r="B82" s="159" t="s">
+        <v>97</v>
+      </c>
+      <c r="C82" s="35" t="s">
+        <v>98</v>
+      </c>
+      <c r="D82" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="E82" s="72">
+        <v>123000</v>
+      </c>
+      <c r="F82" s="40"/>
+      <c r="G82" s="12"/>
+    </row>
+    <row r="83" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A83" s="37">
+        <f>IF(LEN(C83)=0,"",COUNTA($C$35:C83))</f>
+        <v>47</v>
+      </c>
+      <c r="B83" s="159"/>
+      <c r="C83" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="D83" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="E83" s="72">
+        <v>66000</v>
+      </c>
+      <c r="F83" s="40"/>
+      <c r="G83" s="12"/>
+    </row>
+    <row r="84" spans="1:7" ht="115.5" x14ac:dyDescent="0.25">
+      <c r="A84" s="37">
+        <f>IF(LEN(C84)=0,"",COUNTA($C$35:C84))</f>
+        <v>48</v>
+      </c>
+      <c r="B84" s="159"/>
+      <c r="C84" s="35" t="s">
+        <v>102</v>
+      </c>
+      <c r="D84" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="E84" s="72">
+        <v>139000</v>
+      </c>
+      <c r="F84" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="G84" s="12"/>
+    </row>
+    <row r="85" spans="1:7" ht="115.5" x14ac:dyDescent="0.25">
+      <c r="A85" s="37">
+        <f>IF(LEN(C85)=0,"",COUNTA($C$35:C85))</f>
+        <v>49</v>
+      </c>
+      <c r="B85" s="159"/>
+      <c r="C85" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="D85" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="E85" s="72">
+        <v>66000</v>
+      </c>
+      <c r="F85" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="G85" s="12"/>
+    </row>
+    <row r="86" spans="1:7" ht="148.5" x14ac:dyDescent="0.25">
+      <c r="A86" s="37">
+        <f>IF(LEN(C86)=0,"",COUNTA($C$35:C86))</f>
+        <v>50</v>
+      </c>
+      <c r="B86" s="159"/>
+      <c r="C86" s="35" t="s">
+        <v>405</v>
+      </c>
+      <c r="D86" s="35" t="s">
+        <v>406</v>
+      </c>
+      <c r="E86" s="72">
+        <v>212000</v>
+      </c>
+      <c r="F86" s="40"/>
+      <c r="G86" s="12"/>
+    </row>
+    <row r="87" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A87" s="37">
+        <f>IF(LEN(C87)=0,"",COUNTA($C$35:C87))</f>
+        <v>51</v>
+      </c>
+      <c r="B87" s="159"/>
+      <c r="C87" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="D87" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="E87" s="72">
+        <v>868000</v>
+      </c>
+      <c r="F87" s="108" t="s">
+        <v>109</v>
+      </c>
+      <c r="G87" s="12"/>
+    </row>
+    <row r="88" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A88" s="37">
+        <f>IF(LEN(C88)=0,"",COUNTA($C$35:C88))</f>
+        <v>52</v>
+      </c>
+      <c r="B88" s="159"/>
+      <c r="C88" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="D88" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="E88" s="72">
+        <v>139000</v>
+      </c>
+      <c r="F88" s="108" t="s">
+        <v>112</v>
+      </c>
+      <c r="G88" s="12"/>
+    </row>
+    <row r="89" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A89" s="37">
+        <f>IF(LEN(C89)=0,"",COUNTA($C$35:C89))</f>
+        <v>53</v>
+      </c>
+      <c r="B89" s="159"/>
+      <c r="C89" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="D89" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="E89" s="72">
+        <v>72000</v>
+      </c>
+      <c r="F89" s="108" t="s">
+        <v>115</v>
+      </c>
+      <c r="G89" s="12"/>
+    </row>
+    <row r="90" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A90" s="37">
+        <f>IF(LEN(C90)=0,"",COUNTA($C$35:C90))</f>
+        <v>54</v>
+      </c>
+      <c r="B90" s="159" t="s">
+        <v>116</v>
+      </c>
+      <c r="C90" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="D90" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="E90" s="72">
         <v>174000</v>
       </c>
-      <c r="F80" s="40"/>
-      <c r="G80" s="13"/>
-    </row>
-    <row r="81" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A81" s="37">
-        <f>IF(LEN(C81)=0,"",COUNTA($C$54:C81))</f>
-        <v>27</v>
-      </c>
-      <c r="B81" s="162"/>
-      <c r="C81" s="73" t="s">
-        <v>83</v>
-      </c>
-      <c r="D81" s="74" t="s">
-        <v>84</v>
-      </c>
-      <c r="E81" s="106">
-        <v>231000</v>
-      </c>
-      <c r="F81" s="40"/>
-      <c r="G81" s="13"/>
-    </row>
-    <row r="82" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A82" s="37">
-        <f>IF(LEN(C82)=0,"",COUNTA($C$54:C82))</f>
-        <v>28</v>
-      </c>
-      <c r="B82" s="162"/>
-      <c r="C82" s="73" t="s">
-        <v>85</v>
-      </c>
-      <c r="D82" s="74" t="s">
-        <v>86</v>
-      </c>
-      <c r="E82" s="39">
-        <v>732000</v>
-      </c>
-      <c r="F82" s="40"/>
-      <c r="G82" s="13"/>
-    </row>
-    <row r="83" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A83" s="37">
-        <f>IF(LEN(C83)=0,"",COUNTA($C$54:C83))</f>
-        <v>29</v>
-      </c>
-      <c r="B83" s="162"/>
-      <c r="C83" s="73" t="s">
-        <v>79</v>
-      </c>
-      <c r="D83" s="74" t="s">
-        <v>279</v>
-      </c>
-      <c r="E83" s="116">
-        <v>121000</v>
-      </c>
-      <c r="F83" s="40"/>
-      <c r="G83" s="13"/>
-    </row>
-    <row r="84" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A84" s="37">
-        <f>IF(LEN(C84)=0,"",COUNTA($C$54:C84))</f>
-        <v>30</v>
-      </c>
-      <c r="B84" s="162"/>
-      <c r="C84" s="73" t="s">
-        <v>93</v>
-      </c>
-      <c r="D84" s="74" t="s">
-        <v>94</v>
-      </c>
-      <c r="E84" s="39">
-        <v>192000</v>
-      </c>
-      <c r="F84" s="40"/>
-      <c r="G84" s="13"/>
-    </row>
-    <row r="85" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A85" s="37">
-        <f>IF(LEN(C85)=0,"",COUNTA($C$54:C85))</f>
-        <v>31</v>
-      </c>
-      <c r="B85" s="162"/>
-      <c r="C85" s="73" t="s">
-        <v>80</v>
-      </c>
-      <c r="D85" s="74" t="s">
-        <v>81</v>
-      </c>
-      <c r="E85" s="39">
-        <v>173000</v>
-      </c>
-      <c r="F85" s="40"/>
-      <c r="G85" s="13"/>
-    </row>
-    <row r="86" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A86" s="37">
-        <f>IF(LEN(C86)=0,"",COUNTA($C$54:C86))</f>
-        <v>32</v>
-      </c>
-      <c r="B86" s="162"/>
-      <c r="C86" s="73" t="s">
-        <v>82</v>
-      </c>
-      <c r="D86" s="74" t="s">
-        <v>281</v>
-      </c>
-      <c r="E86" s="106">
-        <v>231000</v>
-      </c>
-      <c r="F86" s="108" t="s">
-        <v>395</v>
-      </c>
-      <c r="G86" s="13"/>
-    </row>
-    <row r="87" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A87" s="37">
-        <f>IF(LEN(C87)=0,"",COUNTA($C$54:C87))</f>
-        <v>33</v>
-      </c>
-      <c r="B87" s="162"/>
-      <c r="C87" s="75" t="s">
-        <v>234</v>
-      </c>
-      <c r="D87" s="76" t="s">
-        <v>235</v>
-      </c>
-      <c r="E87" s="117">
-        <v>500000</v>
-      </c>
-      <c r="F87" s="40"/>
-      <c r="G87" s="13"/>
-    </row>
-    <row r="88" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A88" s="37">
-        <f>IF(LEN(C88)=0,"",COUNTA($C$54:C88))</f>
-        <v>34</v>
-      </c>
-      <c r="B88" s="162"/>
-      <c r="C88" s="73" t="s">
-        <v>73</v>
-      </c>
-      <c r="D88" s="74" t="s">
-        <v>280</v>
-      </c>
-      <c r="E88" s="39">
-        <v>290000</v>
-      </c>
-      <c r="F88" s="40" t="s">
-        <v>74</v>
-      </c>
-      <c r="G88" s="12"/>
-    </row>
-    <row r="89" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A89" s="37">
-        <f>IF(LEN(C89)=0,"",COUNTA($C$54:C89))</f>
-        <v>35</v>
-      </c>
-      <c r="B89" s="162"/>
-      <c r="C89" s="73" t="s">
-        <v>75</v>
-      </c>
-      <c r="D89" s="74" t="s">
-        <v>76</v>
-      </c>
-      <c r="E89" s="39">
-        <v>231000</v>
-      </c>
-      <c r="F89" s="40"/>
-      <c r="G89" s="13"/>
-    </row>
-    <row r="90" spans="1:7" s="14" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A90" s="37">
-        <f>IF(LEN(C90)=0,"",COUNTA($C$54:C90))</f>
-        <v>36</v>
-      </c>
-      <c r="B90" s="162"/>
-      <c r="C90" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="D90" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="E90" s="39">
-        <v>616000</v>
-      </c>
       <c r="F90" s="40"/>
-      <c r="G90" s="13"/>
-    </row>
-    <row r="91" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="G90" s="12"/>
+    </row>
+    <row r="91" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A91" s="37">
-        <f>IF(LEN(C91)=0,"",COUNTA($C$54:C91))</f>
-        <v>37</v>
-      </c>
-      <c r="B91" s="162"/>
-      <c r="C91" s="73" t="s">
-        <v>87</v>
-      </c>
-      <c r="D91" s="74" t="s">
-        <v>88</v>
-      </c>
-      <c r="E91" s="106">
-        <v>231000</v>
+        <f>IF(LEN(C91)=0,"",COUNTA($C$35:C91))</f>
+        <v>55</v>
+      </c>
+      <c r="B91" s="159"/>
+      <c r="C91" s="35" t="s">
+        <v>119</v>
+      </c>
+      <c r="D91" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="E91" s="72">
+        <v>88000</v>
       </c>
       <c r="F91" s="40"/>
-      <c r="G91" s="13"/>
-    </row>
-    <row r="92" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="G91" s="12"/>
+    </row>
+    <row r="92" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A92" s="37">
-        <f>IF(LEN(C92)=0,"",COUNTA($C$54:C92))</f>
-        <v>38</v>
-      </c>
-      <c r="B92" s="163"/>
-      <c r="C92" s="73" t="s">
-        <v>95</v>
-      </c>
-      <c r="D92" s="74" t="s">
-        <v>96</v>
-      </c>
-      <c r="E92" s="39">
-        <v>412000</v>
+        <f>IF(LEN(C92)=0,"",COUNTA($C$35:C92))</f>
+        <v>56</v>
+      </c>
+      <c r="B92" s="168" t="s">
+        <v>121</v>
+      </c>
+      <c r="C92" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="D92" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="E92" s="68">
+        <v>168000</v>
       </c>
       <c r="F92" s="40"/>
-      <c r="G92" s="13"/>
-    </row>
-    <row r="93" spans="1:7" s="14" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G92" s="12"/>
+    </row>
+    <row r="93" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A93" s="37">
-        <f>IF(LEN(C93)=0,"",COUNTA($C$54:C93))</f>
-        <v>39</v>
-      </c>
-      <c r="B93" s="161" t="s">
-        <v>90</v>
-      </c>
-      <c r="C93" s="73" t="s">
-        <v>89</v>
-      </c>
-      <c r="D93" s="174" t="s">
-        <v>396</v>
-      </c>
-      <c r="E93" s="39">
-        <v>137000</v>
-      </c>
-      <c r="F93" s="158" t="s">
-        <v>379</v>
-      </c>
-      <c r="G93" s="13"/>
-    </row>
-    <row r="94" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+        <f>IF(LEN(C93)=0,"",COUNTA($C$35:C93))</f>
+        <v>57</v>
+      </c>
+      <c r="B93" s="179"/>
+      <c r="C93" s="35" t="s">
+        <v>388</v>
+      </c>
+      <c r="D93" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="E93" s="68">
+        <v>168000</v>
+      </c>
+      <c r="F93" s="40"/>
+      <c r="G93" s="12"/>
+    </row>
+    <row r="94" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A94" s="37">
-        <f>IF(LEN(C94)=0,"",COUNTA($C$54:C94))</f>
-        <v>40</v>
-      </c>
-      <c r="B94" s="162"/>
-      <c r="C94" s="73" t="s">
-        <v>91</v>
-      </c>
-      <c r="D94" s="175"/>
-      <c r="E94" s="39">
-        <v>137000</v>
-      </c>
-      <c r="F94" s="159"/>
-      <c r="G94" s="13"/>
-    </row>
-    <row r="95" spans="1:7" s="14" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A95" s="37">
-        <f>IF(LEN(C95)=0,"",COUNTA($C$54:C95))</f>
-        <v>41</v>
-      </c>
-      <c r="B95" s="163"/>
-      <c r="C95" s="73" t="s">
-        <v>92</v>
-      </c>
-      <c r="D95" s="176"/>
-      <c r="E95" s="39">
-        <v>208000</v>
-      </c>
-      <c r="F95" s="160"/>
-      <c r="G95" s="13"/>
-    </row>
-    <row r="96" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+        <f>IF(LEN(C94)=0,"",COUNTA($C$35:C94))</f>
+        <v>58</v>
+      </c>
+      <c r="B94" s="169"/>
+      <c r="C94" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="D94" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="E94" s="68">
+        <v>253000</v>
+      </c>
+      <c r="F94" s="40"/>
+      <c r="G94" s="12"/>
+    </row>
+    <row r="95" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A95" s="173" t="s">
+        <v>261</v>
+      </c>
+      <c r="B95" s="174"/>
+      <c r="C95" s="174"/>
+      <c r="D95" s="175"/>
+      <c r="E95" s="77"/>
+      <c r="F95" s="67"/>
+      <c r="G95" s="12"/>
+    </row>
+    <row r="96" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A96" s="37">
-        <f>IF(LEN(C96)=0,"",COUNTA($C$54:C96))</f>
-        <v>42</v>
-      </c>
-      <c r="B96" s="161" t="s">
-        <v>397</v>
-      </c>
-      <c r="C96" s="73" t="s">
-        <v>398</v>
-      </c>
-      <c r="D96" s="164" t="s">
-        <v>400</v>
-      </c>
-      <c r="E96" s="39">
-        <v>215000</v>
-      </c>
-      <c r="F96" s="104"/>
-      <c r="G96" s="13"/>
-    </row>
-    <row r="97" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+        <f>IF(LEN(C96)=0,"",COUNTA($C$35:C96))</f>
+        <v>59</v>
+      </c>
+      <c r="B96" s="140" t="s">
+        <v>240</v>
+      </c>
+      <c r="C96" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="D96" s="35" t="s">
+        <v>237</v>
+      </c>
+      <c r="E96" s="68">
+        <v>250000</v>
+      </c>
+      <c r="F96" s="40"/>
+      <c r="G96" s="12"/>
+    </row>
+    <row r="97" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A97" s="37">
-        <f>IF(LEN(C97)=0,"",COUNTA($C$54:C97))</f>
-        <v>43</v>
-      </c>
-      <c r="B97" s="162"/>
-      <c r="C97" s="73" t="s">
-        <v>399</v>
-      </c>
-      <c r="D97" s="165"/>
-      <c r="E97" s="39">
-        <v>323000</v>
-      </c>
-      <c r="F97" s="104"/>
-      <c r="G97" s="13"/>
-    </row>
-    <row r="98" spans="1:7" s="14" customFormat="1" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
+        <f>IF(LEN(C97)=0,"",COUNTA($C$35:C97))</f>
+        <v>60</v>
+      </c>
+      <c r="B97" s="142"/>
+      <c r="C97" s="35" t="s">
+        <v>239</v>
+      </c>
+      <c r="D97" s="35" t="s">
+        <v>238</v>
+      </c>
+      <c r="E97" s="68">
+        <v>399000</v>
+      </c>
+      <c r="F97" s="40"/>
+      <c r="G97" s="12"/>
+    </row>
+    <row r="98" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A98" s="37">
-        <f>IF(LEN(C98)=0,"",COUNTA($C$54:C98))</f>
-        <v>44</v>
-      </c>
-      <c r="B98" s="162"/>
-      <c r="C98" s="73" t="s">
-        <v>402</v>
-      </c>
-      <c r="D98" s="111" t="s">
-        <v>401</v>
-      </c>
-      <c r="E98" s="39">
-        <v>269000</v>
-      </c>
-      <c r="F98" s="104"/>
-      <c r="G98" s="13"/>
-    </row>
-    <row r="99" spans="1:7" s="14" customFormat="1" ht="66" x14ac:dyDescent="0.25">
+        <f>IF(LEN(C98)=0,"",COUNTA($C$35:C98))</f>
+        <v>61</v>
+      </c>
+      <c r="B98" s="168" t="s">
+        <v>243</v>
+      </c>
+      <c r="C98" s="35" t="s">
+        <v>241</v>
+      </c>
+      <c r="D98" s="35"/>
+      <c r="E98" s="68">
+        <v>2500000</v>
+      </c>
+      <c r="F98" s="40"/>
+      <c r="G98" s="12"/>
+    </row>
+    <row r="99" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A99" s="37">
-        <f>IF(LEN(C99)=0,"",COUNTA($C$54:C99))</f>
-        <v>45</v>
-      </c>
-      <c r="B99" s="163"/>
-      <c r="C99" s="73" t="s">
-        <v>403</v>
-      </c>
-      <c r="D99" s="111" t="s">
-        <v>404</v>
-      </c>
-      <c r="E99" s="39">
-        <v>588000</v>
-      </c>
-      <c r="F99" s="104"/>
-      <c r="G99" s="13"/>
-    </row>
-    <row r="100" spans="1:7" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A100" s="171" t="s">
-        <v>207</v>
-      </c>
-      <c r="B100" s="172"/>
-      <c r="C100" s="172"/>
-      <c r="D100" s="173"/>
-      <c r="E100" s="66"/>
-      <c r="F100" s="67"/>
-      <c r="G100" s="13"/>
-    </row>
-    <row r="101" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+        <f>IF(LEN(C99)=0,"",COUNTA($C$35:C99))</f>
+        <v>62</v>
+      </c>
+      <c r="B99" s="169"/>
+      <c r="C99" s="35" t="s">
+        <v>242</v>
+      </c>
+      <c r="D99" s="35"/>
+      <c r="E99" s="68">
+        <v>2200000</v>
+      </c>
+      <c r="F99" s="40"/>
+      <c r="G99" s="12"/>
+    </row>
+    <row r="100" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A100" s="37">
+        <f>IF(LEN(C100)=0,"",COUNTA($C$35:C100))</f>
+        <v>63</v>
+      </c>
+      <c r="B100" s="103" t="s">
+        <v>311</v>
+      </c>
+      <c r="C100" s="35" t="s">
+        <v>374</v>
+      </c>
+      <c r="D100" s="35"/>
+      <c r="E100" s="68">
+        <v>250000</v>
+      </c>
+      <c r="F100" s="40" t="s">
+        <v>335</v>
+      </c>
+      <c r="G100" s="12"/>
+    </row>
+    <row r="101" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A101" s="37">
-        <f>IF(LEN(C101)=0,"",COUNTA($C$54:C101))</f>
-        <v>46</v>
-      </c>
-      <c r="B101" s="157" t="s">
-        <v>97</v>
+        <f>IF(LEN(C101)=0,"",COUNTA($C$35:C101))</f>
+        <v>64</v>
+      </c>
+      <c r="B101" s="168" t="s">
+        <v>258</v>
       </c>
       <c r="C101" s="35" t="s">
-        <v>98</v>
-      </c>
-      <c r="D101" s="35" t="s">
-        <v>99</v>
-      </c>
-      <c r="E101" s="72">
-        <v>123000</v>
+        <v>244</v>
+      </c>
+      <c r="D101" s="35"/>
+      <c r="E101" s="68">
+        <v>275000</v>
       </c>
       <c r="F101" s="40"/>
       <c r="G101" s="12"/>
     </row>
-    <row r="102" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A102" s="37">
-        <f>IF(LEN(C102)=0,"",COUNTA($C$54:C102))</f>
-        <v>47</v>
-      </c>
-      <c r="B102" s="157"/>
+        <f>IF(LEN(C102)=0,"",COUNTA($C$35:C102))</f>
+        <v>65</v>
+      </c>
+      <c r="B102" s="179"/>
       <c r="C102" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="D102" s="35" t="s">
-        <v>101</v>
-      </c>
-      <c r="E102" s="72">
-        <v>66000</v>
+        <v>245</v>
+      </c>
+      <c r="D102" s="35"/>
+      <c r="E102" s="68">
+        <v>187000</v>
       </c>
       <c r="F102" s="40"/>
       <c r="G102" s="12"/>
     </row>
-    <row r="103" spans="1:7" ht="115.5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A103" s="37">
-        <f>IF(LEN(C103)=0,"",COUNTA($C$54:C103))</f>
-        <v>48</v>
-      </c>
-      <c r="B103" s="157"/>
+        <f>IF(LEN(C103)=0,"",COUNTA($C$35:C103))</f>
+        <v>66</v>
+      </c>
+      <c r="B103" s="179"/>
       <c r="C103" s="35" t="s">
-        <v>102</v>
-      </c>
-      <c r="D103" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="E103" s="72">
-        <v>139000</v>
-      </c>
-      <c r="F103" s="40" t="s">
-        <v>104</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="D103" s="35"/>
+      <c r="E103" s="68">
+        <v>187000</v>
+      </c>
+      <c r="F103" s="40"/>
       <c r="G103" s="12"/>
     </row>
-    <row r="104" spans="1:7" ht="115.5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A104" s="37">
-        <f>IF(LEN(C104)=0,"",COUNTA($C$54:C104))</f>
-        <v>49</v>
-      </c>
-      <c r="B104" s="157"/>
+        <f>IF(LEN(C104)=0,"",COUNTA($C$35:C104))</f>
+        <v>67</v>
+      </c>
+      <c r="B104" s="179"/>
       <c r="C104" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="D104" s="35" t="s">
-        <v>106</v>
-      </c>
-      <c r="E104" s="72">
-        <v>66000</v>
-      </c>
-      <c r="F104" s="40" t="s">
-        <v>104</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="D104" s="35"/>
+      <c r="E104" s="68">
+        <v>189000</v>
+      </c>
+      <c r="F104" s="40"/>
       <c r="G104" s="12"/>
     </row>
-    <row r="105" spans="1:7" ht="148.5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A105" s="37">
-        <f>IF(LEN(C105)=0,"",COUNTA($C$54:C105))</f>
-        <v>50</v>
-      </c>
-      <c r="B105" s="157"/>
+        <f>IF(LEN(C105)=0,"",COUNTA($C$35:C105))</f>
+        <v>68</v>
+      </c>
+      <c r="B105" s="179"/>
       <c r="C105" s="35" t="s">
-        <v>405</v>
-      </c>
-      <c r="D105" s="35" t="s">
-        <v>406</v>
-      </c>
-      <c r="E105" s="72">
-        <v>212000</v>
+        <v>248</v>
+      </c>
+      <c r="D105" s="35"/>
+      <c r="E105" s="68">
+        <v>150000</v>
       </c>
       <c r="F105" s="40"/>
       <c r="G105" s="12"/>
     </row>
-    <row r="106" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A106" s="37">
-        <f>IF(LEN(C106)=0,"",COUNTA($C$54:C106))</f>
-        <v>51</v>
-      </c>
-      <c r="B106" s="157"/>
+        <f>IF(LEN(C106)=0,"",COUNTA($C$35:C106))</f>
+        <v>69</v>
+      </c>
+      <c r="B106" s="179"/>
       <c r="C106" s="35" t="s">
-        <v>107</v>
-      </c>
-      <c r="D106" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="E106" s="72">
-        <v>868000</v>
-      </c>
-      <c r="F106" s="108" t="s">
-        <v>109</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="D106" s="35"/>
+      <c r="E106" s="68">
+        <v>189000</v>
+      </c>
+      <c r="F106" s="40"/>
       <c r="G106" s="12"/>
     </row>
-    <row r="107" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A107" s="37">
-        <f>IF(LEN(C107)=0,"",COUNTA($C$54:C107))</f>
-        <v>52</v>
-      </c>
-      <c r="B107" s="157"/>
+        <f>IF(LEN(C107)=0,"",COUNTA($C$35:C107))</f>
+        <v>70</v>
+      </c>
+      <c r="B107" s="179"/>
       <c r="C107" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="D107" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="E107" s="72">
-        <v>139000</v>
-      </c>
-      <c r="F107" s="108" t="s">
-        <v>112</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="D107" s="35"/>
+      <c r="E107" s="68">
+        <v>189000</v>
+      </c>
+      <c r="F107" s="40"/>
       <c r="G107" s="12"/>
     </row>
-    <row r="108" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A108" s="37">
-        <f>IF(LEN(C108)=0,"",COUNTA($C$54:C108))</f>
-        <v>53</v>
-      </c>
-      <c r="B108" s="157"/>
+        <f>IF(LEN(C108)=0,"",COUNTA($C$35:C108))</f>
+        <v>71</v>
+      </c>
+      <c r="B108" s="179"/>
       <c r="C108" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="D108" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="E108" s="72">
-        <v>72000</v>
-      </c>
-      <c r="F108" s="108" t="s">
-        <v>115</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="D108" s="35"/>
+      <c r="E108" s="68">
+        <v>187000</v>
+      </c>
+      <c r="F108" s="40"/>
       <c r="G108" s="12"/>
     </row>
-    <row r="109" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A109" s="37">
-        <f>IF(LEN(C109)=0,"",COUNTA($C$54:C109))</f>
-        <v>54</v>
-      </c>
-      <c r="B109" s="157" t="s">
-        <v>116</v>
-      </c>
+        <f>IF(LEN(C109)=0,"",COUNTA($C$35:C109))</f>
+        <v>72</v>
+      </c>
+      <c r="B109" s="179"/>
       <c r="C109" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="D109" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="E109" s="72">
-        <v>174000</v>
+        <v>252</v>
+      </c>
+      <c r="D109" s="35"/>
+      <c r="E109" s="68">
+        <v>201000</v>
       </c>
       <c r="F109" s="40"/>
       <c r="G109" s="12"/>
     </row>
-    <row r="110" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A110" s="37">
-        <f>IF(LEN(C110)=0,"",COUNTA($C$54:C110))</f>
-        <v>55</v>
-      </c>
-      <c r="B110" s="157"/>
+        <f>IF(LEN(C110)=0,"",COUNTA($C$35:C110))</f>
+        <v>73</v>
+      </c>
+      <c r="B110" s="179"/>
       <c r="C110" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="D110" s="35" t="s">
-        <v>120</v>
-      </c>
-      <c r="E110" s="72">
-        <v>88000</v>
+        <v>253</v>
+      </c>
+      <c r="D110" s="35"/>
+      <c r="E110" s="68">
+        <v>187000</v>
       </c>
       <c r="F110" s="40"/>
       <c r="G110" s="12"/>
     </row>
-    <row r="111" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A111" s="37">
-        <f>IF(LEN(C111)=0,"",COUNTA($C$54:C111))</f>
-        <v>56</v>
-      </c>
-      <c r="B111" s="166" t="s">
-        <v>121</v>
-      </c>
+        <f>IF(LEN(C111)=0,"",COUNTA($C$35:C111))</f>
+        <v>74</v>
+      </c>
+      <c r="B111" s="179"/>
       <c r="C111" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="D111" s="35" t="s">
-        <v>123</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="D111" s="35"/>
       <c r="E111" s="68">
-        <v>168000</v>
+        <v>187000</v>
       </c>
       <c r="F111" s="40"/>
       <c r="G111" s="12"/>
     </row>
-    <row r="112" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A112" s="37">
-        <f>IF(LEN(C112)=0,"",COUNTA($C$54:C112))</f>
-        <v>57</v>
-      </c>
-      <c r="B112" s="177"/>
+        <f>IF(LEN(C112)=0,"",COUNTA($C$35:C112))</f>
+        <v>75</v>
+      </c>
+      <c r="B112" s="179"/>
       <c r="C112" s="35" t="s">
-        <v>388</v>
-      </c>
-      <c r="D112" s="35" t="s">
-        <v>124</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="D112" s="35"/>
       <c r="E112" s="68">
-        <v>168000</v>
+        <v>132000</v>
       </c>
       <c r="F112" s="40"/>
       <c r="G112" s="12"/>
     </row>
     <row r="113" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A113" s="37">
-        <f>IF(LEN(C113)=0,"",COUNTA($C$54:C113))</f>
-        <v>58</v>
-      </c>
-      <c r="B113" s="167"/>
+        <f>IF(LEN(C113)=0,"",COUNTA($C$35:C113))</f>
+        <v>76</v>
+      </c>
+      <c r="B113" s="179"/>
       <c r="C113" s="35" t="s">
-        <v>125</v>
-      </c>
-      <c r="D113" s="35" t="s">
-        <v>126</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="D113" s="35"/>
       <c r="E113" s="68">
-        <v>253000</v>
+        <v>187000</v>
       </c>
       <c r="F113" s="40"/>
       <c r="G113" s="12"/>
     </row>
     <row r="114" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="171" t="s">
-        <v>261</v>
-      </c>
-      <c r="B114" s="172"/>
-      <c r="C114" s="172"/>
-      <c r="D114" s="173"/>
-      <c r="E114" s="77"/>
-      <c r="F114" s="67"/>
+      <c r="A114" s="37">
+        <f>IF(LEN(C114)=0,"",COUNTA($C$35:C114))</f>
+        <v>77</v>
+      </c>
+      <c r="B114" s="169"/>
+      <c r="C114" s="35" t="s">
+        <v>257</v>
+      </c>
+      <c r="D114" s="35"/>
+      <c r="E114" s="68">
+        <v>1073000</v>
+      </c>
+      <c r="F114" s="40"/>
       <c r="G114" s="12"/>
     </row>
     <row r="115" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A115" s="37">
-        <f>IF(LEN(C115)=0,"",COUNTA($C$54:C115))</f>
-        <v>59</v>
-      </c>
-      <c r="B115" s="140" t="s">
-        <v>240</v>
-      </c>
-      <c r="C115" s="35" t="s">
-        <v>236</v>
-      </c>
-      <c r="D115" s="35" t="s">
-        <v>237</v>
-      </c>
-      <c r="E115" s="68">
-        <v>250000</v>
-      </c>
-      <c r="F115" s="40"/>
+      <c r="A115" s="173" t="s">
+        <v>226</v>
+      </c>
+      <c r="B115" s="174"/>
+      <c r="C115" s="174"/>
+      <c r="D115" s="175"/>
+      <c r="E115" s="66"/>
+      <c r="F115" s="67"/>
       <c r="G115" s="12"/>
     </row>
     <row r="116" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A116" s="37">
-        <f>IF(LEN(C116)=0,"",COUNTA($C$54:C116))</f>
-        <v>60</v>
-      </c>
-      <c r="B116" s="142"/>
+        <f>IF(LEN(C116)=0,"",COUNTA($C$35:C116))</f>
+        <v>78</v>
+      </c>
+      <c r="B116" s="71" t="s">
+        <v>231</v>
+      </c>
       <c r="C116" s="35" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="D116" s="35" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="E116" s="68">
-        <v>399000</v>
+        <v>50000</v>
       </c>
       <c r="F116" s="40"/>
       <c r="G116" s="12"/>
     </row>
-    <row r="117" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A117" s="37">
-        <f>IF(LEN(C117)=0,"",COUNTA($C$54:C117))</f>
-        <v>61</v>
-      </c>
-      <c r="B117" s="166" t="s">
-        <v>243</v>
+        <f>IF(LEN(C117)=0,"",COUNTA($C$35:C117))</f>
+        <v>79</v>
+      </c>
+      <c r="B117" s="71" t="s">
+        <v>230</v>
       </c>
       <c r="C117" s="35" t="s">
-        <v>241</v>
-      </c>
-      <c r="D117" s="35"/>
+        <v>228</v>
+      </c>
+      <c r="D117" s="35" t="s">
+        <v>229</v>
+      </c>
       <c r="E117" s="68">
-        <v>2500000</v>
+        <v>108000</v>
       </c>
       <c r="F117" s="40"/>
       <c r="G117" s="12"/>
     </row>
     <row r="118" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A118" s="37">
-        <f>IF(LEN(C118)=0,"",COUNTA($C$54:C118))</f>
-        <v>62</v>
-      </c>
-      <c r="B118" s="167"/>
-      <c r="C118" s="35" t="s">
-        <v>242</v>
-      </c>
-      <c r="D118" s="35"/>
-      <c r="E118" s="68">
-        <v>2200000</v>
-      </c>
-      <c r="F118" s="40"/>
+      <c r="A118" s="184" t="s">
+        <v>262</v>
+      </c>
+      <c r="B118" s="184"/>
+      <c r="C118" s="184"/>
+      <c r="D118" s="184"/>
+      <c r="E118" s="77"/>
+      <c r="F118" s="67"/>
       <c r="G118" s="12"/>
     </row>
-    <row r="119" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A119" s="37">
-        <f>IF(LEN(C119)=0,"",COUNTA($C$54:C119))</f>
-        <v>63</v>
-      </c>
-      <c r="B119" s="103" t="s">
-        <v>311</v>
-      </c>
-      <c r="C119" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="D119" s="35"/>
-      <c r="E119" s="68">
-        <v>250000</v>
-      </c>
-      <c r="F119" s="40" t="s">
-        <v>335</v>
-      </c>
+        <f>IF(LEN(C119)=0,"",COUNTA($C$35:C119))</f>
+        <v>80</v>
+      </c>
+      <c r="B119" s="186" t="s">
+        <v>204</v>
+      </c>
+      <c r="C119" s="36" t="s">
+        <v>323</v>
+      </c>
+      <c r="D119" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E119" s="105">
+        <v>230000</v>
+      </c>
+      <c r="F119" s="40"/>
       <c r="G119" s="12"/>
     </row>
-    <row r="120" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A120" s="37">
-        <f>IF(LEN(C120)=0,"",COUNTA($C$54:C120))</f>
-        <v>64</v>
-      </c>
-      <c r="B120" s="166" t="s">
-        <v>258</v>
-      </c>
-      <c r="C120" s="35" t="s">
-        <v>244</v>
-      </c>
-      <c r="D120" s="35"/>
-      <c r="E120" s="68">
-        <v>275000</v>
+        <f>IF(LEN(C120)=0,"",COUNTA($C$35:C120))</f>
+        <v>81</v>
+      </c>
+      <c r="B120" s="187"/>
+      <c r="C120" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D120" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E120" s="105">
+        <v>220000</v>
       </c>
       <c r="F120" s="40"/>
       <c r="G120" s="12"/>
     </row>
-    <row r="121" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A121" s="37">
-        <f>IF(LEN(C121)=0,"",COUNTA($C$54:C121))</f>
-        <v>65</v>
-      </c>
-      <c r="B121" s="177"/>
-      <c r="C121" s="35" t="s">
-        <v>245</v>
-      </c>
-      <c r="D121" s="35"/>
-      <c r="E121" s="68">
-        <v>187000</v>
+        <f>IF(LEN(C121)=0,"",COUNTA($C$35:C121))</f>
+        <v>82</v>
+      </c>
+      <c r="B121" s="187"/>
+      <c r="C121" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="D121" s="107" t="s">
+        <v>328</v>
+      </c>
+      <c r="E121" s="105">
+        <v>230000</v>
       </c>
       <c r="F121" s="40"/>
       <c r="G121" s="12"/>
     </row>
-    <row r="122" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A122" s="37">
-        <f>IF(LEN(C122)=0,"",COUNTA($C$54:C122))</f>
-        <v>66</v>
-      </c>
-      <c r="B122" s="177"/>
+        <f>IF(LEN(C122)=0,"",COUNTA($C$35:C122))</f>
+        <v>83</v>
+      </c>
+      <c r="B122" s="187"/>
       <c r="C122" s="35" t="s">
-        <v>246</v>
+        <v>407</v>
       </c>
       <c r="D122" s="35"/>
-      <c r="E122" s="68">
-        <v>187000</v>
+      <c r="E122" s="72">
+        <v>250000</v>
       </c>
       <c r="F122" s="40"/>
       <c r="G122" s="12"/>
     </row>
     <row r="123" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A123" s="37">
-        <f>IF(LEN(C123)=0,"",COUNTA($C$54:C123))</f>
-        <v>67</v>
-      </c>
-      <c r="B123" s="177"/>
+        <f>IF(LEN(C123)=0,"",COUNTA($C$35:C123))</f>
+        <v>84</v>
+      </c>
+      <c r="B123" s="187"/>
       <c r="C123" s="35" t="s">
-        <v>247</v>
+        <v>408</v>
       </c>
       <c r="D123" s="35"/>
-      <c r="E123" s="68">
-        <v>189000</v>
+      <c r="E123" s="72">
+        <v>375000</v>
       </c>
       <c r="F123" s="40"/>
       <c r="G123" s="12"/>
     </row>
-    <row r="124" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A124" s="37">
-        <f>IF(LEN(C124)=0,"",COUNTA($C$54:C124))</f>
-        <v>68</v>
-      </c>
-      <c r="B124" s="177"/>
+        <f>IF(LEN(C124)=0,"",COUNTA($C$35:C124))</f>
+        <v>85</v>
+      </c>
+      <c r="B124" s="187"/>
       <c r="C124" s="35" t="s">
-        <v>248</v>
+        <v>409</v>
       </c>
       <c r="D124" s="35"/>
-      <c r="E124" s="68">
-        <v>150000</v>
+      <c r="E124" s="72">
+        <v>500000</v>
       </c>
       <c r="F124" s="40"/>
       <c r="G124" s="12"/>
     </row>
-    <row r="125" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A125" s="37">
-        <f>IF(LEN(C125)=0,"",COUNTA($C$54:C125))</f>
-        <v>69</v>
-      </c>
-      <c r="B125" s="177"/>
-      <c r="C125" s="35" t="s">
-        <v>249</v>
-      </c>
-      <c r="D125" s="35"/>
+        <f>IF(LEN(C125)=0,"",COUNTA($C$35:C125))</f>
+        <v>86</v>
+      </c>
+      <c r="B125" s="187"/>
+      <c r="C125" s="36" t="s">
+        <v>410</v>
+      </c>
+      <c r="D125" s="36" t="s">
+        <v>137</v>
+      </c>
       <c r="E125" s="68">
-        <v>189000</v>
+        <v>700000</v>
       </c>
       <c r="F125" s="40"/>
       <c r="G125" s="12"/>
     </row>
-    <row r="126" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A126" s="37">
-        <f>IF(LEN(C126)=0,"",COUNTA($C$54:C126))</f>
-        <v>70</v>
-      </c>
-      <c r="B126" s="177"/>
-      <c r="C126" s="35" t="s">
-        <v>250</v>
-      </c>
-      <c r="D126" s="35"/>
+        <f>IF(LEN(C126)=0,"",COUNTA($C$35:C126))</f>
+        <v>87</v>
+      </c>
+      <c r="B126" s="187"/>
+      <c r="C126" s="36" t="s">
+        <v>138</v>
+      </c>
+      <c r="D126" s="107" t="s">
+        <v>329</v>
+      </c>
       <c r="E126" s="68">
-        <v>189000</v>
+        <v>770000</v>
       </c>
       <c r="F126" s="40"/>
       <c r="G126" s="12"/>
     </row>
-    <row r="127" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A127" s="37">
-        <f>IF(LEN(C127)=0,"",COUNTA($C$54:C127))</f>
-        <v>71</v>
-      </c>
-      <c r="B127" s="177"/>
-      <c r="C127" s="35" t="s">
-        <v>251</v>
-      </c>
-      <c r="D127" s="35"/>
+        <f>IF(LEN(C127)=0,"",COUNTA($C$35:C127))</f>
+        <v>88</v>
+      </c>
+      <c r="B127" s="188"/>
+      <c r="C127" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="D127" s="36" t="s">
+        <v>140</v>
+      </c>
       <c r="E127" s="68">
-        <v>187000</v>
+        <v>249000</v>
       </c>
       <c r="F127" s="40"/>
       <c r="G127" s="12"/>
     </row>
-    <row r="128" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A128" s="37">
-        <f>IF(LEN(C128)=0,"",COUNTA($C$54:C128))</f>
-        <v>72</v>
-      </c>
-      <c r="B128" s="177"/>
+        <f>IF(LEN(C128)=0,"",COUNTA($C$35:C128))</f>
+        <v>89</v>
+      </c>
+      <c r="B128" s="140" t="s">
+        <v>282</v>
+      </c>
       <c r="C128" s="35" t="s">
-        <v>252</v>
-      </c>
-      <c r="D128" s="35"/>
-      <c r="E128" s="68">
-        <v>201000</v>
+        <v>141</v>
+      </c>
+      <c r="D128" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="E128" s="72">
+        <v>157000</v>
       </c>
       <c r="F128" s="40"/>
       <c r="G128" s="12"/>
     </row>
-    <row r="129" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A129" s="37">
-        <f>IF(LEN(C129)=0,"",COUNTA($C$54:C129))</f>
-        <v>73</v>
-      </c>
-      <c r="B129" s="177"/>
+        <f>IF(LEN(C129)=0,"",COUNTA($C$35:C129))</f>
+        <v>90</v>
+      </c>
+      <c r="B129" s="141"/>
       <c r="C129" s="35" t="s">
-        <v>253</v>
-      </c>
-      <c r="D129" s="35"/>
-      <c r="E129" s="68">
-        <v>187000</v>
+        <v>143</v>
+      </c>
+      <c r="D129" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="E129" s="72">
+        <v>157000</v>
       </c>
       <c r="F129" s="40"/>
       <c r="G129" s="12"/>
     </row>
     <row r="130" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A130" s="37">
-        <f>IF(LEN(C130)=0,"",COUNTA($C$54:C130))</f>
-        <v>74</v>
-      </c>
-      <c r="B130" s="177"/>
+        <f>IF(LEN(C130)=0,"",COUNTA($C$35:C130))</f>
+        <v>91</v>
+      </c>
+      <c r="B130" s="141"/>
       <c r="C130" s="35" t="s">
-        <v>254</v>
-      </c>
-      <c r="D130" s="35"/>
-      <c r="E130" s="68">
-        <v>187000</v>
+        <v>392</v>
+      </c>
+      <c r="D130" s="35" t="s">
+        <v>393</v>
+      </c>
+      <c r="E130" s="72">
+        <v>143000</v>
       </c>
       <c r="F130" s="40"/>
       <c r="G130" s="12"/>
     </row>
     <row r="131" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A131" s="37">
-        <f>IF(LEN(C131)=0,"",COUNTA($C$54:C131))</f>
-        <v>75</v>
-      </c>
-      <c r="B131" s="177"/>
+        <f>IF(LEN(C131)=0,"",COUNTA($C$35:C131))</f>
+        <v>92</v>
+      </c>
+      <c r="B131" s="141"/>
       <c r="C131" s="35" t="s">
-        <v>255</v>
-      </c>
-      <c r="D131" s="35"/>
-      <c r="E131" s="68">
-        <v>132000</v>
+        <v>394</v>
+      </c>
+      <c r="D131" s="35" t="s">
+        <v>393</v>
+      </c>
+      <c r="E131" s="72">
+        <v>185000</v>
       </c>
       <c r="F131" s="40"/>
       <c r="G131" s="12"/>
     </row>
-    <row r="132" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A132" s="37">
-        <f>IF(LEN(C132)=0,"",COUNTA($C$54:C132))</f>
-        <v>76</v>
-      </c>
-      <c r="B132" s="177"/>
+        <f>IF(LEN(C132)=0,"",COUNTA($C$35:C132))</f>
+        <v>93</v>
+      </c>
+      <c r="B132" s="141"/>
       <c r="C132" s="35" t="s">
-        <v>256</v>
-      </c>
-      <c r="D132" s="35"/>
-      <c r="E132" s="68">
-        <v>187000</v>
-      </c>
-      <c r="F132" s="40"/>
+        <v>369</v>
+      </c>
+      <c r="D132" s="35" t="s">
+        <v>370</v>
+      </c>
+      <c r="E132" s="72">
+        <v>1200000</v>
+      </c>
+      <c r="F132" s="108"/>
       <c r="G132" s="12"/>
     </row>
-    <row r="133" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A133" s="37">
-        <f>IF(LEN(C133)=0,"",COUNTA($C$54:C133))</f>
-        <v>77</v>
-      </c>
-      <c r="B133" s="167"/>
+        <f>IF(LEN(C133)=0,"",COUNTA($C$35:C133))</f>
+        <v>94</v>
+      </c>
+      <c r="B133" s="142"/>
       <c r="C133" s="35" t="s">
-        <v>257</v>
-      </c>
-      <c r="D133" s="35"/>
-      <c r="E133" s="68">
-        <v>1073000</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="D133" s="35" t="s">
+        <v>146</v>
+      </c>
+      <c r="E133" s="72"/>
       <c r="F133" s="40"/>
       <c r="G133" s="12"/>
     </row>
-    <row r="134" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A134" s="171" t="s">
-        <v>226</v>
-      </c>
-      <c r="B134" s="172"/>
-      <c r="C134" s="172"/>
-      <c r="D134" s="173"/>
-      <c r="E134" s="66"/>
-      <c r="F134" s="67"/>
+    <row r="134" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A134" s="37">
+        <f>IF(LEN(C134)=0,"",COUNTA($C$35:C134))</f>
+        <v>95</v>
+      </c>
+      <c r="B134" s="141" t="s">
+        <v>283</v>
+      </c>
+      <c r="C134" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="D134" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="E134" s="72"/>
+      <c r="F134" s="40"/>
       <c r="G134" s="12"/>
     </row>
-    <row r="135" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A135" s="37">
-        <f>IF(LEN(C135)=0,"",COUNTA($C$54:C135))</f>
-        <v>78</v>
-      </c>
-      <c r="B135" s="71" t="s">
-        <v>231</v>
-      </c>
+        <f>IF(LEN(C135)=0,"",COUNTA($C$35:C135))</f>
+        <v>96</v>
+      </c>
+      <c r="B135" s="141"/>
       <c r="C135" s="35" t="s">
-        <v>232</v>
-      </c>
-      <c r="D135" s="35" t="s">
-        <v>227</v>
-      </c>
-      <c r="E135" s="68">
-        <v>50000</v>
+        <v>330</v>
+      </c>
+      <c r="D135" s="107" t="s">
+        <v>331</v>
+      </c>
+      <c r="E135" s="72">
+        <v>700000</v>
       </c>
       <c r="F135" s="40"/>
       <c r="G135" s="12"/>
     </row>
-    <row r="136" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A136" s="37">
-        <f>IF(LEN(C136)=0,"",COUNTA($C$54:C136))</f>
-        <v>79</v>
-      </c>
-      <c r="B136" s="71" t="s">
-        <v>230</v>
-      </c>
+        <f>IF(LEN(C136)=0,"",COUNTA($C$35:C136))</f>
+        <v>97</v>
+      </c>
+      <c r="B136" s="141"/>
       <c r="C136" s="35" t="s">
-        <v>228</v>
+        <v>151</v>
       </c>
       <c r="D136" s="35" t="s">
-        <v>229</v>
+        <v>152</v>
       </c>
       <c r="E136" s="68">
-        <v>108000</v>
+        <v>847000</v>
       </c>
       <c r="F136" s="40"/>
       <c r="G136" s="12"/>
     </row>
-    <row r="137" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A137" s="178" t="s">
-        <v>262</v>
-      </c>
-      <c r="B137" s="178"/>
-      <c r="C137" s="178"/>
-      <c r="D137" s="178"/>
-      <c r="E137" s="77"/>
-      <c r="F137" s="67"/>
+    <row r="137" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A137" s="37">
+        <f>IF(LEN(C137)=0,"",COUNTA($C$35:C137))</f>
+        <v>98</v>
+      </c>
+      <c r="B137" s="141"/>
+      <c r="C137" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="D137" s="35" t="s">
+        <v>154</v>
+      </c>
+      <c r="E137" s="68">
+        <v>2178000</v>
+      </c>
+      <c r="F137" s="40"/>
       <c r="G137" s="12"/>
     </row>
-    <row r="138" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A138" s="37">
-        <f>IF(LEN(C138)=0,"",COUNTA($C$54:C138))</f>
-        <v>80</v>
-      </c>
-      <c r="B138" s="179" t="s">
-        <v>204</v>
-      </c>
-      <c r="C138" s="36" t="s">
-        <v>323</v>
-      </c>
-      <c r="D138" s="36" t="s">
-        <v>11</v>
-      </c>
-      <c r="E138" s="105">
-        <v>230000</v>
+        <f>IF(LEN(C138)=0,"",COUNTA($C$35:C138))</f>
+        <v>99</v>
+      </c>
+      <c r="B138" s="141"/>
+      <c r="C138" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="D138" s="35" t="s">
+        <v>156</v>
+      </c>
+      <c r="E138" s="68">
+        <v>847000</v>
       </c>
       <c r="F138" s="40"/>
       <c r="G138" s="12"/>
     </row>
-    <row r="139" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A139" s="37">
-        <f>IF(LEN(C139)=0,"",COUNTA($C$54:C139))</f>
-        <v>81</v>
-      </c>
-      <c r="B139" s="180"/>
-      <c r="C139" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="D139" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E139" s="105">
-        <v>220000</v>
+        <f>IF(LEN(C139)=0,"",COUNTA($C$35:C139))</f>
+        <v>100</v>
+      </c>
+      <c r="B139" s="141"/>
+      <c r="C139" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="D139" s="107" t="s">
+        <v>332</v>
+      </c>
+      <c r="E139" s="68">
+        <v>1700000</v>
       </c>
       <c r="F139" s="40"/>
       <c r="G139" s="12"/>
     </row>
     <row r="140" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A140" s="37">
-        <f>IF(LEN(C140)=0,"",COUNTA($C$54:C140))</f>
-        <v>82</v>
-      </c>
-      <c r="B140" s="180"/>
-      <c r="C140" s="36" t="s">
-        <v>324</v>
-      </c>
-      <c r="D140" s="107" t="s">
-        <v>328</v>
-      </c>
-      <c r="E140" s="105">
-        <v>230000</v>
-      </c>
+        <f>IF(LEN(C140)=0,"",COUNTA($C$35:C140))</f>
+        <v>101</v>
+      </c>
+      <c r="B140" s="141"/>
+      <c r="C140" s="35" t="s">
+        <v>158</v>
+      </c>
+      <c r="D140" s="35" t="s">
+        <v>146</v>
+      </c>
+      <c r="E140" s="68"/>
       <c r="F140" s="40"/>
       <c r="G140" s="12"/>
     </row>
-    <row r="141" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A141" s="37">
-        <f>IF(LEN(C141)=0,"",COUNTA($C$54:C141))</f>
-        <v>83</v>
-      </c>
-      <c r="B141" s="180"/>
+        <f>IF(LEN(C141)=0,"",COUNTA($C$35:C141))</f>
+        <v>102</v>
+      </c>
+      <c r="B141" s="152" t="s">
+        <v>304</v>
+      </c>
       <c r="C141" s="35" t="s">
-        <v>407</v>
-      </c>
-      <c r="D141" s="35"/>
-      <c r="E141" s="72">
-        <v>250000</v>
-      </c>
-      <c r="F141" s="40"/>
-      <c r="G141" s="12"/>
-    </row>
-    <row r="142" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+        <v>341</v>
+      </c>
+      <c r="D141" s="35" t="s">
+        <v>284</v>
+      </c>
+      <c r="E141" s="106">
+        <v>3420000</v>
+      </c>
+      <c r="F141" s="112" t="s">
+        <v>334</v>
+      </c>
+      <c r="G141" s="113"/>
+    </row>
+    <row r="142" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A142" s="37">
-        <f>IF(LEN(C142)=0,"",COUNTA($C$54:C142))</f>
-        <v>84</v>
-      </c>
-      <c r="B142" s="180"/>
+        <f>IF(LEN(C142)=0,"",COUNTA($C$35:C142))</f>
+        <v>103</v>
+      </c>
+      <c r="B142" s="152"/>
       <c r="C142" s="35" t="s">
-        <v>408</v>
-      </c>
-      <c r="D142" s="35"/>
-      <c r="E142" s="72">
-        <v>375000</v>
+        <v>342</v>
+      </c>
+      <c r="D142" s="35" t="s">
+        <v>285</v>
+      </c>
+      <c r="E142" s="106">
+        <v>3420000</v>
       </c>
       <c r="F142" s="40"/>
       <c r="G142" s="12"/>
     </row>
-    <row r="143" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A143" s="37">
-        <f>IF(LEN(C143)=0,"",COUNTA($C$54:C143))</f>
-        <v>85</v>
-      </c>
-      <c r="B143" s="180"/>
+        <f>IF(LEN(C143)=0,"",COUNTA($C$35:C143))</f>
+        <v>104</v>
+      </c>
+      <c r="B143" s="152"/>
       <c r="C143" s="35" t="s">
-        <v>409</v>
-      </c>
-      <c r="D143" s="35"/>
-      <c r="E143" s="72">
-        <v>500000</v>
-      </c>
-      <c r="F143" s="40"/>
-      <c r="G143" s="12"/>
-    </row>
-    <row r="144" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+        <v>343</v>
+      </c>
+      <c r="D143" s="35" t="s">
+        <v>309</v>
+      </c>
+      <c r="E143" s="106">
+        <v>3420000</v>
+      </c>
+      <c r="F143" s="112" t="s">
+        <v>334</v>
+      </c>
+      <c r="G143" s="113"/>
+    </row>
+    <row r="144" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A144" s="37">
-        <f>IF(LEN(C144)=0,"",COUNTA($C$54:C144))</f>
-        <v>86</v>
-      </c>
-      <c r="B144" s="180"/>
-      <c r="C144" s="36" t="s">
-        <v>410</v>
-      </c>
-      <c r="D144" s="36" t="s">
-        <v>137</v>
-      </c>
-      <c r="E144" s="68">
-        <v>700000</v>
+        <f>IF(LEN(C144)=0,"",COUNTA($C$35:C144))</f>
+        <v>105</v>
+      </c>
+      <c r="B144" s="152"/>
+      <c r="C144" s="35" t="s">
+        <v>344</v>
+      </c>
+      <c r="D144" s="35" t="s">
+        <v>310</v>
+      </c>
+      <c r="E144" s="106">
+        <v>3420000</v>
       </c>
       <c r="F144" s="40"/>
       <c r="G144" s="12"/>
     </row>
-    <row r="145" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A145" s="37">
-        <f>IF(LEN(C145)=0,"",COUNTA($C$54:C145))</f>
-        <v>87</v>
-      </c>
-      <c r="B145" s="180"/>
-      <c r="C145" s="36" t="s">
-        <v>138</v>
-      </c>
-      <c r="D145" s="107" t="s">
-        <v>329</v>
-      </c>
-      <c r="E145" s="68">
-        <v>770000</v>
+        <f>IF(LEN(C145)=0,"",COUNTA($C$35:C145))</f>
+        <v>106</v>
+      </c>
+      <c r="B145" s="152"/>
+      <c r="C145" s="35" t="s">
+        <v>345</v>
+      </c>
+      <c r="D145" s="35" t="s">
+        <v>286</v>
+      </c>
+      <c r="E145" s="106">
+        <v>3420000</v>
       </c>
       <c r="F145" s="40"/>
       <c r="G145" s="12"/>
     </row>
     <row r="146" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A146" s="37">
-        <f>IF(LEN(C146)=0,"",COUNTA($C$54:C146))</f>
-        <v>88</v>
-      </c>
-      <c r="B146" s="181"/>
-      <c r="C146" s="36" t="s">
-        <v>139</v>
-      </c>
-      <c r="D146" s="36" t="s">
-        <v>140</v>
-      </c>
-      <c r="E146" s="68">
-        <v>249000</v>
+        <f>IF(LEN(C146)=0,"",COUNTA($C$35:C146))</f>
+        <v>107</v>
+      </c>
+      <c r="B146" s="152"/>
+      <c r="C146" s="107" t="s">
+        <v>372</v>
+      </c>
+      <c r="D146" s="35" t="s">
+        <v>287</v>
+      </c>
+      <c r="E146" s="106">
+        <v>5730000</v>
       </c>
       <c r="F146" s="40"/>
       <c r="G146" s="12"/>
     </row>
-    <row r="147" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A147" s="37">
-        <f>IF(LEN(C147)=0,"",COUNTA($C$54:C147))</f>
-        <v>89</v>
-      </c>
-      <c r="B147" s="140" t="s">
-        <v>282</v>
-      </c>
+        <f>IF(LEN(C147)=0,"",COUNTA($C$35:C147))</f>
+        <v>108</v>
+      </c>
+      <c r="B147" s="152"/>
       <c r="C147" s="35" t="s">
-        <v>141</v>
+        <v>346</v>
       </c>
       <c r="D147" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="E147" s="72">
-        <v>157000</v>
+        <v>288</v>
+      </c>
+      <c r="E147" s="106">
+        <v>3420000</v>
       </c>
       <c r="F147" s="40"/>
       <c r="G147" s="12"/>
     </row>
-    <row r="148" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A148" s="37">
-        <f>IF(LEN(C148)=0,"",COUNTA($C$54:C148))</f>
-        <v>90</v>
-      </c>
-      <c r="B148" s="141"/>
+        <f>IF(LEN(C148)=0,"",COUNTA($C$35:C148))</f>
+        <v>109</v>
+      </c>
+      <c r="B148" s="152"/>
       <c r="C148" s="35" t="s">
-        <v>143</v>
+        <v>347</v>
       </c>
       <c r="D148" s="35" t="s">
-        <v>144</v>
-      </c>
-      <c r="E148" s="72">
-        <v>157000</v>
+        <v>288</v>
+      </c>
+      <c r="E148" s="106">
+        <v>4530000</v>
       </c>
       <c r="F148" s="40"/>
       <c r="G148" s="12"/>
     </row>
-    <row r="149" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A149" s="37">
-        <f>IF(LEN(C149)=0,"",COUNTA($C$54:C149))</f>
-        <v>91</v>
-      </c>
-      <c r="B149" s="141"/>
+        <f>IF(LEN(C149)=0,"",COUNTA($C$35:C149))</f>
+        <v>110</v>
+      </c>
+      <c r="B149" s="152"/>
       <c r="C149" s="35" t="s">
-        <v>392</v>
+        <v>348</v>
       </c>
       <c r="D149" s="35" t="s">
-        <v>393</v>
-      </c>
-      <c r="E149" s="72">
-        <v>143000</v>
+        <v>289</v>
+      </c>
+      <c r="E149" s="106">
+        <v>3420000</v>
       </c>
       <c r="F149" s="40"/>
       <c r="G149" s="12"/>
     </row>
-    <row r="150" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A150" s="37">
-        <f>IF(LEN(C150)=0,"",COUNTA($C$54:C150))</f>
-        <v>92</v>
-      </c>
-      <c r="B150" s="141"/>
-      <c r="C150" s="35" t="s">
-        <v>394</v>
+        <f>IF(LEN(C150)=0,"",COUNTA($C$35:C150))</f>
+        <v>111</v>
+      </c>
+      <c r="B150" s="152"/>
+      <c r="C150" s="107" t="s">
+        <v>371</v>
       </c>
       <c r="D150" s="35" t="s">
-        <v>393</v>
-      </c>
-      <c r="E150" s="72">
-        <v>185000</v>
+        <v>290</v>
+      </c>
+      <c r="E150" s="106">
+        <v>5515200</v>
       </c>
       <c r="F150" s="40"/>
       <c r="G150" s="12"/>
     </row>
-    <row r="151" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A151" s="37">
-        <f>IF(LEN(C151)=0,"",COUNTA($C$54:C151))</f>
-        <v>93</v>
-      </c>
-      <c r="B151" s="141"/>
+        <f>IF(LEN(C151)=0,"",COUNTA($C$35:C151))</f>
+        <v>112</v>
+      </c>
+      <c r="B151" s="152"/>
       <c r="C151" s="35" t="s">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="D151" s="35" t="s">
-        <v>370</v>
+        <v>292</v>
       </c>
       <c r="E151" s="72">
-        <v>1200000</v>
-      </c>
-      <c r="F151" s="108"/>
+        <v>2790000</v>
+      </c>
+      <c r="F151" s="114" t="s">
+        <v>291</v>
+      </c>
       <c r="G151" s="12"/>
     </row>
-    <row r="152" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A152" s="37">
-        <f>IF(LEN(C152)=0,"",COUNTA($C$54:C152))</f>
-        <v>94</v>
-      </c>
-      <c r="B152" s="142"/>
+        <f>IF(LEN(C152)=0,"",COUNTA($C$35:C152))</f>
+        <v>113</v>
+      </c>
+      <c r="B152" s="152"/>
       <c r="C152" s="35" t="s">
-        <v>145</v>
+        <v>350</v>
       </c>
       <c r="D152" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="E152" s="72"/>
+        <v>293</v>
+      </c>
+      <c r="E152" s="106">
+        <v>3078000</v>
+      </c>
       <c r="F152" s="40"/>
       <c r="G152" s="12"/>
     </row>
-    <row r="153" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A153" s="37">
-        <f>IF(LEN(C153)=0,"",COUNTA($C$54:C153))</f>
-        <v>95</v>
-      </c>
-      <c r="B153" s="141" t="s">
-        <v>283</v>
-      </c>
+        <f>IF(LEN(C153)=0,"",COUNTA($C$35:C153))</f>
+        <v>114</v>
+      </c>
+      <c r="B153" s="152"/>
       <c r="C153" s="35" t="s">
-        <v>149</v>
+        <v>351</v>
       </c>
       <c r="D153" s="35" t="s">
-        <v>150</v>
-      </c>
-      <c r="E153" s="72"/>
+        <v>293</v>
+      </c>
+      <c r="E153" s="106">
+        <v>4200000</v>
+      </c>
       <c r="F153" s="40"/>
       <c r="G153" s="12"/>
     </row>
-    <row r="154" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A154" s="37">
-        <f>IF(LEN(C154)=0,"",COUNTA($C$54:C154))</f>
-        <v>96</v>
-      </c>
-      <c r="B154" s="141"/>
+        <f>IF(LEN(C154)=0,"",COUNTA($C$35:C154))</f>
+        <v>115</v>
+      </c>
+      <c r="B154" s="152"/>
       <c r="C154" s="35" t="s">
-        <v>330</v>
-      </c>
-      <c r="D154" s="107" t="s">
-        <v>331</v>
-      </c>
-      <c r="E154" s="72">
-        <v>700000</v>
+        <v>352</v>
+      </c>
+      <c r="D154" s="35" t="s">
+        <v>294</v>
+      </c>
+      <c r="E154" s="106">
+        <v>3078000</v>
       </c>
       <c r="F154" s="40"/>
       <c r="G154" s="12"/>
     </row>
-    <row r="155" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A155" s="37">
-        <f>IF(LEN(C155)=0,"",COUNTA($C$54:C155))</f>
-        <v>97</v>
-      </c>
-      <c r="B155" s="141"/>
+        <f>IF(LEN(C155)=0,"",COUNTA($C$35:C155))</f>
+        <v>116</v>
+      </c>
+      <c r="B155" s="152"/>
       <c r="C155" s="35" t="s">
-        <v>151</v>
+        <v>353</v>
       </c>
       <c r="D155" s="35" t="s">
-        <v>152</v>
-      </c>
-      <c r="E155" s="68">
-        <v>847000</v>
+        <v>294</v>
+      </c>
+      <c r="E155" s="106">
+        <v>4200000</v>
       </c>
       <c r="F155" s="40"/>
       <c r="G155" s="12"/>
     </row>
-    <row r="156" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A156" s="37">
-        <f>IF(LEN(C156)=0,"",COUNTA($C$54:C156))</f>
-        <v>98</v>
-      </c>
-      <c r="B156" s="141"/>
+        <f>IF(LEN(C156)=0,"",COUNTA($C$35:C156))</f>
+        <v>117</v>
+      </c>
+      <c r="B156" s="152"/>
       <c r="C156" s="35" t="s">
-        <v>153</v>
+        <v>354</v>
       </c>
       <c r="D156" s="35" t="s">
-        <v>154</v>
-      </c>
-      <c r="E156" s="68">
-        <v>2178000</v>
+        <v>295</v>
+      </c>
+      <c r="E156" s="106">
+        <v>3078000</v>
       </c>
       <c r="F156" s="40"/>
       <c r="G156" s="12"/>
     </row>
     <row r="157" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A157" s="37">
-        <f>IF(LEN(C157)=0,"",COUNTA($C$54:C157))</f>
-        <v>99</v>
-      </c>
-      <c r="B157" s="141"/>
+        <f>IF(LEN(C157)=0,"",COUNTA($C$35:C157))</f>
+        <v>118</v>
+      </c>
+      <c r="B157" s="152"/>
       <c r="C157" s="35" t="s">
-        <v>155</v>
+        <v>355</v>
       </c>
       <c r="D157" s="35" t="s">
-        <v>156</v>
-      </c>
-      <c r="E157" s="68">
-        <v>847000</v>
+        <v>296</v>
+      </c>
+      <c r="E157" s="106">
+        <v>3420000</v>
       </c>
       <c r="F157" s="40"/>
       <c r="G157" s="12"/>
     </row>
     <row r="158" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A158" s="37">
-        <f>IF(LEN(C158)=0,"",COUNTA($C$54:C158))</f>
-        <v>100</v>
-      </c>
-      <c r="B158" s="141"/>
+        <f>IF(LEN(C158)=0,"",COUNTA($C$35:C158))</f>
+        <v>119</v>
+      </c>
+      <c r="B158" s="152"/>
       <c r="C158" s="35" t="s">
-        <v>157</v>
-      </c>
-      <c r="D158" s="107" t="s">
-        <v>332</v>
-      </c>
-      <c r="E158" s="68">
-        <v>1700000</v>
+        <v>356</v>
+      </c>
+      <c r="D158" s="35" t="s">
+        <v>297</v>
+      </c>
+      <c r="E158" s="106">
+        <v>3420000</v>
       </c>
       <c r="F158" s="40"/>
       <c r="G158" s="12"/>
     </row>
     <row r="159" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A159" s="37">
-        <f>IF(LEN(C159)=0,"",COUNTA($C$54:C159))</f>
-        <v>101</v>
-      </c>
-      <c r="B159" s="141"/>
+        <f>IF(LEN(C159)=0,"",COUNTA($C$35:C159))</f>
+        <v>120</v>
+      </c>
+      <c r="B159" s="152"/>
       <c r="C159" s="35" t="s">
-        <v>158</v>
+        <v>357</v>
       </c>
       <c r="D159" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="E159" s="68"/>
+        <v>298</v>
+      </c>
+      <c r="E159" s="106">
+        <v>3420000</v>
+      </c>
       <c r="F159" s="40"/>
       <c r="G159" s="12"/>
     </row>
-    <row r="160" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A160" s="37">
-        <f>IF(LEN(C160)=0,"",COUNTA($C$54:C160))</f>
-        <v>102</v>
-      </c>
-      <c r="B160" s="152" t="s">
-        <v>304</v>
-      </c>
+        <f>IF(LEN(C160)=0,"",COUNTA($C$35:C160))</f>
+        <v>121</v>
+      </c>
+      <c r="B160" s="152"/>
       <c r="C160" s="35" t="s">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="D160" s="35" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="E160" s="106">
         <v>3420000</v>
       </c>
-      <c r="F160" s="112" t="s">
-        <v>334</v>
-      </c>
-      <c r="G160" s="113"/>
-    </row>
-    <row r="161" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="F160" s="40"/>
+      <c r="G160" s="12"/>
+    </row>
+    <row r="161" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A161" s="37">
-        <f>IF(LEN(C161)=0,"",COUNTA($C$54:C161))</f>
-        <v>103</v>
+        <f>IF(LEN(C161)=0,"",COUNTA($C$35:C161))</f>
+        <v>122</v>
       </c>
       <c r="B161" s="152"/>
       <c r="C161" s="35" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="D161" s="35" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="E161" s="106">
-        <v>3420000</v>
+        <v>7740000</v>
       </c>
       <c r="F161" s="40"/>
       <c r="G161" s="12"/>
     </row>
-    <row r="162" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A162" s="37">
-        <f>IF(LEN(C162)=0,"",COUNTA($C$54:C162))</f>
-        <v>104</v>
+        <f>IF(LEN(C162)=0,"",COUNTA($C$35:C162))</f>
+        <v>123</v>
       </c>
       <c r="B162" s="152"/>
       <c r="C162" s="35" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="D162" s="35" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="E162" s="106">
         <v>3420000</v>
       </c>
-      <c r="F162" s="112" t="s">
-        <v>334</v>
-      </c>
-      <c r="G162" s="113"/>
-    </row>
-    <row r="163" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="F162" s="40"/>
+      <c r="G162" s="12"/>
+    </row>
+    <row r="163" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A163" s="37">
-        <f>IF(LEN(C163)=0,"",COUNTA($C$54:C163))</f>
-        <v>105</v>
+        <f>IF(LEN(C163)=0,"",COUNTA($C$35:C163))</f>
+        <v>124</v>
       </c>
       <c r="B163" s="152"/>
       <c r="C163" s="35" t="s">
-        <v>344</v>
+        <v>361</v>
       </c>
       <c r="D163" s="35" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E163" s="106">
-        <v>3420000</v>
+        <v>4740000</v>
       </c>
       <c r="F163" s="40"/>
       <c r="G163" s="12"/>
     </row>
-    <row r="164" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A164" s="37">
-        <f>IF(LEN(C164)=0,"",COUNTA($C$54:C164))</f>
-        <v>106</v>
+        <f>IF(LEN(C164)=0,"",COUNTA($C$35:C164))</f>
+        <v>125</v>
       </c>
       <c r="B164" s="152"/>
       <c r="C164" s="35" t="s">
-        <v>345</v>
+        <v>362</v>
       </c>
       <c r="D164" s="35" t="s">
-        <v>286</v>
-      </c>
-      <c r="E164" s="106">
-        <v>3420000</v>
+        <v>308</v>
+      </c>
+      <c r="E164" s="72">
+        <v>3720000</v>
       </c>
       <c r="F164" s="40"/>
       <c r="G164" s="12"/>
     </row>
-    <row r="165" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A165" s="37">
-        <f>IF(LEN(C165)=0,"",COUNTA($C$54:C165))</f>
-        <v>107</v>
+        <f>IF(LEN(C165)=0,"",COUNTA($C$35:C165))</f>
+        <v>126</v>
       </c>
       <c r="B165" s="152"/>
-      <c r="C165" s="107" t="s">
-        <v>372</v>
-      </c>
-      <c r="D165" s="35" t="s">
-        <v>287</v>
-      </c>
+      <c r="C165" s="35" t="s">
+        <v>363</v>
+      </c>
+      <c r="D165" s="35"/>
       <c r="E165" s="106">
-        <v>5730000</v>
+        <v>6060000</v>
       </c>
       <c r="F165" s="40"/>
       <c r="G165" s="12"/>
     </row>
-    <row r="166" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A166" s="37">
-        <f>IF(LEN(C166)=0,"",COUNTA($C$54:C166))</f>
-        <v>108</v>
+        <f>IF(LEN(C166)=0,"",COUNTA($C$35:C166))</f>
+        <v>127</v>
       </c>
       <c r="B166" s="152"/>
       <c r="C166" s="35" t="s">
-        <v>346</v>
-      </c>
-      <c r="D166" s="35" t="s">
-        <v>288</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="D166" s="35"/>
       <c r="E166" s="106">
-        <v>3420000</v>
+        <v>6060000</v>
       </c>
       <c r="F166" s="40"/>
       <c r="G166" s="12"/>
     </row>
-    <row r="167" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A167" s="37">
-        <f>IF(LEN(C167)=0,"",COUNTA($C$54:C167))</f>
-        <v>109</v>
+        <f>IF(LEN(C167)=0,"",COUNTA($C$35:C167))</f>
+        <v>128</v>
       </c>
       <c r="B167" s="152"/>
       <c r="C167" s="35" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="D167" s="35" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="E167" s="106">
-        <v>4530000</v>
+        <v>5520000</v>
       </c>
       <c r="F167" s="40"/>
       <c r="G167" s="12"/>
     </row>
-    <row r="168" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A168" s="37">
-        <f>IF(LEN(C168)=0,"",COUNTA($C$54:C168))</f>
-        <v>110</v>
+        <f>IF(LEN(C168)=0,"",COUNTA($C$35:C168))</f>
+        <v>129</v>
       </c>
       <c r="B168" s="152"/>
       <c r="C168" s="35" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="D168" s="35" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="E168" s="106">
-        <v>3420000</v>
+        <v>9930000</v>
       </c>
       <c r="F168" s="40"/>
       <c r="G168" s="12"/>
     </row>
-    <row r="169" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A169" s="37">
-        <f>IF(LEN(C169)=0,"",COUNTA($C$54:C169))</f>
-        <v>111</v>
+        <f>IF(LEN(C169)=0,"",COUNTA($C$35:C169))</f>
+        <v>130</v>
       </c>
       <c r="B169" s="152"/>
-      <c r="C169" s="107" t="s">
-        <v>371</v>
+      <c r="C169" s="35" t="s">
+        <v>367</v>
       </c>
       <c r="D169" s="35" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="E169" s="106">
-        <v>5515200</v>
+        <v>7740000</v>
       </c>
       <c r="F169" s="40"/>
       <c r="G169" s="12"/>
     </row>
-    <row r="170" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A170" s="37">
-        <f>IF(LEN(C170)=0,"",COUNTA($C$54:C170))</f>
-        <v>112</v>
+        <f>IF(LEN(C170)=0,"",COUNTA($C$35:C170))</f>
+        <v>131</v>
       </c>
       <c r="B170" s="152"/>
       <c r="C170" s="35" t="s">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="D170" s="35" t="s">
-        <v>292</v>
-      </c>
-      <c r="E170" s="72">
-        <v>2790000</v>
-      </c>
-      <c r="F170" s="114" t="s">
-        <v>291</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="E170" s="106">
+        <v>23160000</v>
+      </c>
+      <c r="F170" s="40"/>
       <c r="G170" s="12"/>
     </row>
-    <row r="171" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A171" s="37">
-        <f>IF(LEN(C171)=0,"",COUNTA($C$54:C171))</f>
-        <v>113</v>
-      </c>
-      <c r="B171" s="152"/>
-      <c r="C171" s="35" t="s">
-        <v>350</v>
-      </c>
-      <c r="D171" s="35" t="s">
-        <v>293</v>
-      </c>
-      <c r="E171" s="106">
-        <v>3078000</v>
-      </c>
-      <c r="F171" s="40"/>
+    <row r="171" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A171" s="184" t="s">
+        <v>206</v>
+      </c>
+      <c r="B171" s="184"/>
+      <c r="C171" s="184"/>
+      <c r="D171" s="184"/>
+      <c r="E171" s="77"/>
+      <c r="F171" s="67"/>
       <c r="G171" s="12"/>
     </row>
-    <row r="172" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A172" s="37">
-        <f>IF(LEN(C172)=0,"",COUNTA($C$54:C172))</f>
-        <v>114</v>
-      </c>
-      <c r="B172" s="152"/>
+        <f>IF(LEN(C172)=0,"",COUNTA($C$35:C172))</f>
+        <v>132</v>
+      </c>
+      <c r="B172" s="78"/>
       <c r="C172" s="35" t="s">
-        <v>351</v>
+        <v>159</v>
       </c>
       <c r="D172" s="35" t="s">
-        <v>293</v>
-      </c>
-      <c r="E172" s="106">
-        <v>4200000</v>
+        <v>160</v>
+      </c>
+      <c r="E172" s="72">
+        <v>88000</v>
       </c>
       <c r="F172" s="40"/>
       <c r="G172" s="12"/>
     </row>
-    <row r="173" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A173" s="37">
-        <f>IF(LEN(C173)=0,"",COUNTA($C$54:C173))</f>
-        <v>115</v>
-      </c>
-      <c r="B173" s="152"/>
-      <c r="C173" s="35" t="s">
-        <v>352</v>
-      </c>
-      <c r="D173" s="35" t="s">
-        <v>294</v>
-      </c>
-      <c r="E173" s="106">
-        <v>3078000</v>
+        <f>IF(LEN(C173)=0,"",COUNTA($C$35:C173))</f>
+        <v>133</v>
+      </c>
+      <c r="B173" s="79"/>
+      <c r="C173" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="D173" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="E173" s="105">
+        <v>140000</v>
       </c>
       <c r="F173" s="40"/>
       <c r="G173" s="12"/>
     </row>
-    <row r="174" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" ht="33" x14ac:dyDescent="0.25">
       <c r="A174" s="37">
-        <f>IF(LEN(C174)=0,"",COUNTA($C$54:C174))</f>
-        <v>116</v>
-      </c>
-      <c r="B174" s="152"/>
-      <c r="C174" s="35" t="s">
-        <v>353</v>
-      </c>
-      <c r="D174" s="35" t="s">
-        <v>294</v>
-      </c>
-      <c r="E174" s="106">
-        <v>4200000</v>
+        <f>IF(LEN(C174)=0,"",COUNTA($C$35:C174))</f>
+        <v>134</v>
+      </c>
+      <c r="B174" s="80"/>
+      <c r="C174" s="81" t="s">
+        <v>147</v>
+      </c>
+      <c r="D174" s="81" t="s">
+        <v>148</v>
+      </c>
+      <c r="E174" s="82">
+        <v>450000</v>
       </c>
       <c r="F174" s="40"/>
       <c r="G174" s="12"/>
-    </row>
-    <row r="175" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="H174" s="12"/>
+    </row>
+    <row r="175" spans="1:8" s="15" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A175" s="37">
-        <f>IF(LEN(C175)=0,"",COUNTA($C$54:C175))</f>
-        <v>117</v>
-      </c>
-      <c r="B175" s="152"/>
+        <f>IF(LEN(C175)=0,"",COUNTA($C$35:C175))</f>
+        <v>135</v>
+      </c>
+      <c r="B175" s="140" t="s">
+        <v>203</v>
+      </c>
       <c r="C175" s="35" t="s">
-        <v>354</v>
+        <v>222</v>
       </c>
       <c r="D175" s="35" t="s">
-        <v>295</v>
-      </c>
-      <c r="E175" s="106">
-        <v>3078000</v>
+        <v>223</v>
+      </c>
+      <c r="E175" s="72">
+        <v>178000</v>
       </c>
       <c r="F175" s="40"/>
-      <c r="G175" s="12"/>
-    </row>
-    <row r="176" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="176" spans="1:8" s="15" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A176" s="37">
-        <f>IF(LEN(C176)=0,"",COUNTA($C$54:C176))</f>
-        <v>118</v>
-      </c>
-      <c r="B176" s="152"/>
+        <f>IF(LEN(C176)=0,"",COUNTA($C$35:C176))</f>
+        <v>136</v>
+      </c>
+      <c r="B176" s="142"/>
       <c r="C176" s="35" t="s">
-        <v>355</v>
+        <v>224</v>
       </c>
       <c r="D176" s="35" t="s">
-        <v>296</v>
-      </c>
-      <c r="E176" s="106">
-        <v>3420000</v>
+        <v>225</v>
+      </c>
+      <c r="E176" s="72">
+        <v>127000</v>
       </c>
       <c r="F176" s="40"/>
-      <c r="G176" s="12"/>
-    </row>
-    <row r="177" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A177" s="37">
-        <f>IF(LEN(C177)=0,"",COUNTA($C$54:C177))</f>
-        <v>119</v>
-      </c>
-      <c r="B177" s="152"/>
-      <c r="C177" s="35" t="s">
-        <v>356</v>
-      </c>
-      <c r="D177" s="35" t="s">
-        <v>297</v>
-      </c>
-      <c r="E177" s="106">
-        <v>3420000</v>
-      </c>
-      <c r="F177" s="40"/>
-      <c r="G177" s="12"/>
-    </row>
-    <row r="178" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="177" spans="1:7" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A177" s="173" t="s">
+        <v>163</v>
+      </c>
+      <c r="B177" s="174"/>
+      <c r="C177" s="174"/>
+      <c r="D177" s="175"/>
+      <c r="E177" s="119"/>
+      <c r="F177" s="62"/>
+    </row>
+    <row r="178" spans="1:7" s="16" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A178" s="37">
-        <f>IF(LEN(C178)=0,"",COUNTA($C$54:C178))</f>
-        <v>120</v>
-      </c>
-      <c r="B178" s="152"/>
-      <c r="C178" s="35" t="s">
-        <v>357</v>
-      </c>
-      <c r="D178" s="35" t="s">
-        <v>298</v>
-      </c>
-      <c r="E178" s="106">
-        <v>3420000</v>
-      </c>
-      <c r="F178" s="40"/>
-      <c r="G178" s="12"/>
-    </row>
-    <row r="179" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+        <f>IF(LEN(C178)=0,"",COUNTA($C$35:C178))</f>
+        <v>137</v>
+      </c>
+      <c r="B178" s="84"/>
+      <c r="C178" s="85" t="s">
+        <v>164</v>
+      </c>
+      <c r="D178" s="85" t="s">
+        <v>165</v>
+      </c>
+      <c r="E178" s="83">
+        <v>71000</v>
+      </c>
+      <c r="F178" s="182" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" s="16" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A179" s="37">
-        <f>IF(LEN(C179)=0,"",COUNTA($C$54:C179))</f>
-        <v>121</v>
-      </c>
-      <c r="B179" s="152"/>
-      <c r="C179" s="35" t="s">
-        <v>358</v>
-      </c>
-      <c r="D179" s="35" t="s">
-        <v>305</v>
-      </c>
-      <c r="E179" s="106">
-        <v>3420000</v>
-      </c>
-      <c r="F179" s="40"/>
-      <c r="G179" s="12"/>
-    </row>
-    <row r="180" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A180" s="37">
-        <f>IF(LEN(C180)=0,"",COUNTA($C$54:C180))</f>
-        <v>122</v>
-      </c>
-      <c r="B180" s="152"/>
-      <c r="C180" s="35" t="s">
-        <v>359</v>
-      </c>
-      <c r="D180" s="35" t="s">
-        <v>299</v>
-      </c>
-      <c r="E180" s="106">
-        <v>7740000</v>
-      </c>
-      <c r="F180" s="40"/>
+        <f>IF(LEN(C179)=0,"",COUNTA($C$35:C179))</f>
+        <v>138</v>
+      </c>
+      <c r="B179" s="84"/>
+      <c r="C179" s="85" t="s">
+        <v>166</v>
+      </c>
+      <c r="D179" s="85" t="s">
+        <v>167</v>
+      </c>
+      <c r="E179" s="83">
+        <v>86000</v>
+      </c>
+      <c r="F179" s="183"/>
+    </row>
+    <row r="180" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A180" s="184" t="s">
+        <v>168</v>
+      </c>
+      <c r="B180" s="184"/>
+      <c r="C180" s="184"/>
+      <c r="D180" s="184"/>
+      <c r="E180" s="77"/>
+      <c r="F180" s="67"/>
       <c r="G180" s="12"/>
     </row>
-    <row r="181" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="37">
-        <f>IF(LEN(C181)=0,"",COUNTA($C$54:C181))</f>
-        <v>123</v>
-      </c>
-      <c r="B181" s="152"/>
+        <f>IF(LEN(C181)=0,"",COUNTA($C$35:C181))</f>
+        <v>139</v>
+      </c>
+      <c r="B181" s="38"/>
       <c r="C181" s="35" t="s">
-        <v>360</v>
+        <v>169</v>
       </c>
       <c r="D181" s="35" t="s">
-        <v>306</v>
+        <v>170</v>
       </c>
       <c r="E181" s="106">
-        <v>3420000</v>
-      </c>
-      <c r="F181" s="40"/>
+        <v>1968000</v>
+      </c>
+      <c r="F181" s="160" t="s">
+        <v>325</v>
+      </c>
       <c r="G181" s="12"/>
     </row>
-    <row r="182" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A182" s="37">
-        <f>IF(LEN(C182)=0,"",COUNTA($C$54:C182))</f>
-        <v>124</v>
-      </c>
-      <c r="B182" s="152"/>
+        <f>IF(LEN(C182)=0,"",COUNTA($C$35:C182))</f>
+        <v>140</v>
+      </c>
+      <c r="B182" s="38"/>
       <c r="C182" s="35" t="s">
-        <v>361</v>
+        <v>171</v>
       </c>
       <c r="D182" s="35" t="s">
-        <v>307</v>
+        <v>172</v>
       </c>
       <c r="E182" s="106">
-        <v>4740000</v>
-      </c>
-      <c r="F182" s="40"/>
+        <v>2952000</v>
+      </c>
+      <c r="F182" s="161"/>
       <c r="G182" s="12"/>
     </row>
-    <row r="183" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A183" s="37">
-        <f>IF(LEN(C183)=0,"",COUNTA($C$54:C183))</f>
-        <v>125</v>
-      </c>
-      <c r="B183" s="152"/>
+        <f>IF(LEN(C183)=0,"",COUNTA($C$35:C183))</f>
+        <v>141</v>
+      </c>
+      <c r="B183" s="38"/>
       <c r="C183" s="35" t="s">
-        <v>362</v>
+        <v>173</v>
       </c>
       <c r="D183" s="35" t="s">
-        <v>308</v>
-      </c>
-      <c r="E183" s="72">
-        <v>3720000</v>
-      </c>
-      <c r="F183" s="40"/>
+        <v>174</v>
+      </c>
+      <c r="E183" s="106">
+        <v>4100000</v>
+      </c>
+      <c r="F183" s="162"/>
       <c r="G183" s="12"/>
     </row>
-    <row r="184" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A184" s="37">
-        <f>IF(LEN(C184)=0,"",COUNTA($C$54:C184))</f>
-        <v>126</v>
-      </c>
-      <c r="B184" s="152"/>
+        <f>IF(LEN(C184)=0,"",COUNTA($C$35:C184))</f>
+        <v>142</v>
+      </c>
+      <c r="B184" s="38"/>
       <c r="C184" s="35" t="s">
-        <v>363</v>
-      </c>
-      <c r="D184" s="35"/>
+        <v>339</v>
+      </c>
+      <c r="D184" s="35" t="s">
+        <v>340</v>
+      </c>
       <c r="E184" s="106">
-        <v>6060000</v>
-      </c>
-      <c r="F184" s="40"/>
+        <v>550000</v>
+      </c>
+      <c r="F184" s="104"/>
       <c r="G184" s="12"/>
     </row>
-    <row r="185" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" ht="148.5" x14ac:dyDescent="0.25">
       <c r="A185" s="37">
-        <f>IF(LEN(C185)=0,"",COUNTA($C$54:C185))</f>
-        <v>127</v>
-      </c>
-      <c r="B185" s="152"/>
+        <f>IF(LEN(C185)=0,"",COUNTA($C$35:C185))</f>
+        <v>143</v>
+      </c>
+      <c r="B185" s="38"/>
       <c r="C185" s="35" t="s">
-        <v>364</v>
-      </c>
-      <c r="D185" s="35"/>
-      <c r="E185" s="106">
-        <v>6060000</v>
-      </c>
-      <c r="F185" s="40"/>
+        <v>175</v>
+      </c>
+      <c r="D185" s="35" t="s">
+        <v>176</v>
+      </c>
+      <c r="E185" s="72">
+        <v>495000</v>
+      </c>
+      <c r="F185" s="104" t="s">
+        <v>327</v>
+      </c>
       <c r="G185" s="12"/>
     </row>
-    <row r="186" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A186" s="37">
-        <f>IF(LEN(C186)=0,"",COUNTA($C$54:C186))</f>
-        <v>128</v>
-      </c>
-      <c r="B186" s="152"/>
+        <f>IF(LEN(C186)=0,"",COUNTA($C$35:C186))</f>
+        <v>144</v>
+      </c>
+      <c r="B186" s="38"/>
       <c r="C186" s="35" t="s">
-        <v>365</v>
+        <v>177</v>
       </c>
       <c r="D186" s="35" t="s">
-        <v>301</v>
-      </c>
-      <c r="E186" s="106">
-        <v>5520000</v>
+        <v>178</v>
+      </c>
+      <c r="E186" s="72">
+        <v>268000</v>
       </c>
       <c r="F186" s="40"/>
       <c r="G186" s="12"/>
     </row>
-    <row r="187" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A187" s="37">
-        <f>IF(LEN(C187)=0,"",COUNTA($C$54:C187))</f>
-        <v>129</v>
-      </c>
-      <c r="B187" s="152"/>
+        <f>IF(LEN(C187)=0,"",COUNTA($C$35:C187))</f>
+        <v>145</v>
+      </c>
+      <c r="B187" s="38"/>
       <c r="C187" s="35" t="s">
-        <v>366</v>
+        <v>179</v>
       </c>
       <c r="D187" s="35" t="s">
-        <v>302</v>
-      </c>
-      <c r="E187" s="106">
-        <v>9930000</v>
+        <v>180</v>
+      </c>
+      <c r="E187" s="72">
+        <v>151000</v>
       </c>
       <c r="F187" s="40"/>
       <c r="G187" s="12"/>
     </row>
-    <row r="188" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A188" s="37">
-        <f>IF(LEN(C188)=0,"",COUNTA($C$54:C188))</f>
-        <v>130</v>
-      </c>
-      <c r="B188" s="152"/>
+        <f>IF(LEN(C188)=0,"",COUNTA($C$35:C188))</f>
+        <v>146</v>
+      </c>
+      <c r="B188" s="38"/>
       <c r="C188" s="35" t="s">
-        <v>367</v>
+        <v>337</v>
       </c>
       <c r="D188" s="35" t="s">
-        <v>303</v>
-      </c>
-      <c r="E188" s="106">
-        <v>7740000</v>
+        <v>338</v>
+      </c>
+      <c r="E188" s="72">
+        <v>220000</v>
       </c>
       <c r="F188" s="40"/>
       <c r="G188" s="12"/>
     </row>
-    <row r="189" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A189" s="37">
-        <f>IF(LEN(C189)=0,"",COUNTA($C$54:C189))</f>
-        <v>131</v>
-      </c>
-      <c r="B189" s="152"/>
-      <c r="C189" s="35" t="s">
-        <v>368</v>
-      </c>
-      <c r="D189" s="35" t="s">
-        <v>300</v>
-      </c>
-      <c r="E189" s="106">
-        <v>23160000</v>
-      </c>
-      <c r="F189" s="40"/>
+    <row r="189" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A189" s="184" t="s">
+        <v>263</v>
+      </c>
+      <c r="B189" s="184"/>
+      <c r="C189" s="184"/>
+      <c r="D189" s="184"/>
+      <c r="E189" s="77"/>
+      <c r="F189" s="67"/>
       <c r="G189" s="12"/>
     </row>
-    <row r="190" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A190" s="178" t="s">
-        <v>206</v>
-      </c>
-      <c r="B190" s="178"/>
-      <c r="C190" s="178"/>
-      <c r="D190" s="178"/>
-      <c r="E190" s="77"/>
-      <c r="F190" s="67"/>
+    <row r="190" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+      <c r="A190" s="37">
+        <f>IF(LEN(C190)=0,"",COUNTA($C$35:C190))</f>
+        <v>147</v>
+      </c>
+      <c r="B190" s="38"/>
+      <c r="C190" s="35" t="s">
+        <v>264</v>
+      </c>
+      <c r="D190" s="35" t="s">
+        <v>265</v>
+      </c>
+      <c r="E190" s="72">
+        <v>390000</v>
+      </c>
+      <c r="F190" s="40"/>
       <c r="G190" s="12"/>
     </row>
-    <row r="191" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A191" s="37">
-        <f>IF(LEN(C191)=0,"",COUNTA($C$54:C191))</f>
-        <v>132</v>
-      </c>
-      <c r="B191" s="78"/>
-      <c r="C191" s="35" t="s">
-        <v>159</v>
-      </c>
-      <c r="D191" s="35" t="s">
-        <v>160</v>
-      </c>
-      <c r="E191" s="72">
-        <v>88000</v>
-      </c>
-      <c r="F191" s="40"/>
+    <row r="191" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A191" s="184" t="s">
+        <v>233</v>
+      </c>
+      <c r="B191" s="184"/>
+      <c r="C191" s="184"/>
+      <c r="D191" s="184"/>
+      <c r="E191" s="77"/>
+      <c r="F191" s="67"/>
       <c r="G191" s="12"/>
     </row>
-    <row r="192" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A192" s="37">
-        <f>IF(LEN(C192)=0,"",COUNTA($C$54:C192))</f>
-        <v>133</v>
-      </c>
-      <c r="B192" s="79"/>
+        <f>IF(LEN(C192)=0,"",COUNTA($C$35:C192))</f>
+        <v>148</v>
+      </c>
+      <c r="B192" s="78"/>
       <c r="C192" s="36" t="s">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="D192" s="36" t="s">
-        <v>136</v>
+        <v>22</v>
       </c>
       <c r="E192" s="105">
-        <v>140000</v>
+        <v>165000</v>
       </c>
       <c r="F192" s="40"/>
       <c r="G192" s="12"/>
     </row>
-    <row r="193" spans="1:8" ht="33" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A193" s="37">
-        <f>IF(LEN(C193)=0,"",COUNTA($C$54:C193))</f>
-        <v>134</v>
-      </c>
-      <c r="B193" s="80"/>
-      <c r="C193" s="81" t="s">
-        <v>147</v>
-      </c>
-      <c r="D193" s="81" t="s">
-        <v>148</v>
-      </c>
-      <c r="E193" s="82">
-        <v>450000</v>
+        <f>IF(LEN(C193)=0,"",COUNTA($C$35:C193))</f>
+        <v>149</v>
+      </c>
+      <c r="B193" s="78"/>
+      <c r="C193" s="36" t="s">
+        <v>181</v>
+      </c>
+      <c r="D193" s="36" t="s">
+        <v>182</v>
+      </c>
+      <c r="E193" s="68">
+        <v>72000</v>
       </c>
       <c r="F193" s="40"/>
       <c r="G193" s="12"/>
-      <c r="H193" s="12"/>
-    </row>
-    <row r="194" spans="1:8" s="15" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="194" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A194" s="37">
-        <f>IF(LEN(C194)=0,"",COUNTA($C$54:C194))</f>
-        <v>135</v>
-      </c>
-      <c r="B194" s="140" t="s">
-        <v>203</v>
-      </c>
+        <f>IF(LEN(C194)=0,"",COUNTA($C$35:C194))</f>
+        <v>150</v>
+      </c>
+      <c r="B194" s="78"/>
       <c r="C194" s="35" t="s">
-        <v>222</v>
+        <v>183</v>
       </c>
       <c r="D194" s="35" t="s">
-        <v>223</v>
-      </c>
-      <c r="E194" s="72">
-        <v>178000</v>
+        <v>184</v>
+      </c>
+      <c r="E194" s="68">
+        <v>329000</v>
       </c>
       <c r="F194" s="40"/>
-    </row>
-    <row r="195" spans="1:8" s="15" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="G194" s="12"/>
+    </row>
+    <row r="195" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A195" s="37">
-        <f>IF(LEN(C195)=0,"",COUNTA($C$54:C195))</f>
-        <v>136</v>
-      </c>
-      <c r="B195" s="142"/>
-      <c r="C195" s="35" t="s">
-        <v>224</v>
-      </c>
-      <c r="D195" s="35" t="s">
-        <v>225</v>
-      </c>
-      <c r="E195" s="72">
-        <v>127000</v>
+        <f>IF(LEN(C195)=0,"",COUNTA($C$35:C195))</f>
+        <v>151</v>
+      </c>
+      <c r="B195" s="78"/>
+      <c r="C195" s="36" t="s">
+        <v>185</v>
+      </c>
+      <c r="D195" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="E195" s="68">
+        <v>605000</v>
       </c>
       <c r="F195" s="40"/>
-    </row>
-    <row r="196" spans="1:8" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A196" s="171" t="s">
-        <v>163</v>
-      </c>
-      <c r="B196" s="172"/>
-      <c r="C196" s="172"/>
-      <c r="D196" s="173"/>
-      <c r="E196" s="119"/>
-      <c r="F196" s="62"/>
-    </row>
-    <row r="197" spans="1:8" s="16" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+      <c r="G195" s="12"/>
+    </row>
+    <row r="196" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+      <c r="A196" s="37">
+        <f>IF(LEN(C196)=0,"",COUNTA($C$35:C196))</f>
+        <v>152</v>
+      </c>
+      <c r="B196" s="78"/>
+      <c r="C196" s="85" t="s">
+        <v>187</v>
+      </c>
+      <c r="D196" s="85" t="s">
+        <v>188</v>
+      </c>
+      <c r="E196" s="43">
+        <v>1100000</v>
+      </c>
+      <c r="F196" s="40"/>
+      <c r="G196" s="12"/>
+    </row>
+    <row r="197" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A197" s="37">
-        <f>IF(LEN(C197)=0,"",COUNTA($C$54:C197))</f>
-        <v>137</v>
-      </c>
-      <c r="B197" s="84"/>
+        <f>IF(LEN(C197)=0,"",COUNTA($C$35:C197))</f>
+        <v>153</v>
+      </c>
+      <c r="B197" s="78"/>
       <c r="C197" s="85" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="D197" s="85" t="s">
-        <v>165</v>
-      </c>
-      <c r="E197" s="83">
-        <v>71000</v>
-      </c>
-      <c r="F197" s="183" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="198" spans="1:8" s="16" customFormat="1" ht="49.5" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="E197" s="43">
+        <v>187000</v>
+      </c>
+      <c r="F197" s="40"/>
+      <c r="G197" s="12"/>
+    </row>
+    <row r="198" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A198" s="37">
-        <f>IF(LEN(C198)=0,"",COUNTA($C$54:C198))</f>
-        <v>138</v>
-      </c>
-      <c r="B198" s="84"/>
-      <c r="C198" s="85" t="s">
-        <v>166</v>
-      </c>
-      <c r="D198" s="85" t="s">
-        <v>167</v>
-      </c>
-      <c r="E198" s="83">
-        <v>86000</v>
-      </c>
-      <c r="F198" s="184"/>
-    </row>
-    <row r="199" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A199" s="178" t="s">
-        <v>168</v>
-      </c>
-      <c r="B199" s="178"/>
-      <c r="C199" s="178"/>
-      <c r="D199" s="178"/>
-      <c r="E199" s="77"/>
-      <c r="F199" s="67"/>
+        <f>IF(LEN(C198)=0,"",COUNTA($C$35:C198))</f>
+        <v>154</v>
+      </c>
+      <c r="B198" s="78"/>
+      <c r="C198" s="35" t="s">
+        <v>189</v>
+      </c>
+      <c r="D198" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="E198" s="68">
+        <v>220000</v>
+      </c>
+      <c r="F198" s="40"/>
+      <c r="G198" s="12"/>
+    </row>
+    <row r="199" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A199" s="37">
+        <f>IF(LEN(C199)=0,"",COUNTA($C$35:C199))</f>
+        <v>155</v>
+      </c>
+      <c r="B199" s="78"/>
+      <c r="C199" s="35" t="s">
+        <v>384</v>
+      </c>
+      <c r="D199" s="35" t="s">
+        <v>386</v>
+      </c>
+      <c r="E199" s="68">
+        <v>817000</v>
+      </c>
+      <c r="F199" s="40"/>
       <c r="G199" s="12"/>
     </row>
-    <row r="200" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A200" s="37">
-        <f>IF(LEN(C200)=0,"",COUNTA($C$54:C200))</f>
-        <v>139</v>
-      </c>
-      <c r="B200" s="38"/>
+        <f>IF(LEN(C200)=0,"",COUNTA($C$35:C200))</f>
+        <v>156</v>
+      </c>
+      <c r="B200" s="78"/>
       <c r="C200" s="35" t="s">
-        <v>169</v>
+        <v>385</v>
       </c>
       <c r="D200" s="35" t="s">
-        <v>170</v>
-      </c>
-      <c r="E200" s="106">
-        <v>1968000</v>
-      </c>
-      <c r="F200" s="158" t="s">
-        <v>325</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="E200" s="68">
+        <v>1500000</v>
+      </c>
+      <c r="F200" s="40"/>
       <c r="G200" s="12"/>
     </row>
-    <row r="201" spans="1:8" ht="33" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A201" s="37">
-        <f>IF(LEN(C201)=0,"",COUNTA($C$54:C201))</f>
-        <v>140</v>
-      </c>
-      <c r="B201" s="38"/>
+        <f>IF(LEN(C201)=0,"",COUNTA($C$35:C201))</f>
+        <v>157</v>
+      </c>
+      <c r="B201" s="78"/>
       <c r="C201" s="35" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="D201" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="E201" s="106">
-        <v>2952000</v>
-      </c>
-      <c r="F201" s="159"/>
+        <v>192</v>
+      </c>
+      <c r="E201" s="72">
+        <v>220000</v>
+      </c>
+      <c r="F201" s="40"/>
       <c r="G201" s="12"/>
     </row>
-    <row r="202" spans="1:8" ht="66" x14ac:dyDescent="0.25">
-      <c r="A202" s="37">
-        <f>IF(LEN(C202)=0,"",COUNTA($C$54:C202))</f>
-        <v>141</v>
-      </c>
-      <c r="B202" s="38"/>
-      <c r="C202" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="D202" s="35" t="s">
-        <v>174</v>
-      </c>
-      <c r="E202" s="106">
-        <v>4100000</v>
-      </c>
-      <c r="F202" s="160"/>
+    <row r="202" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A202" s="173" t="s">
+        <v>322</v>
+      </c>
+      <c r="B202" s="174"/>
+      <c r="C202" s="174"/>
+      <c r="D202" s="175"/>
+      <c r="E202" s="66"/>
+      <c r="F202" s="67"/>
       <c r="G202" s="12"/>
     </row>
-    <row r="203" spans="1:8" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A203" s="37">
-        <f>IF(LEN(C203)=0,"",COUNTA($C$54:C203))</f>
-        <v>142</v>
-      </c>
-      <c r="B203" s="38"/>
+        <f>IF(LEN(C203)=0,"",COUNTA($C$35:C203))</f>
+        <v>158</v>
+      </c>
+      <c r="B203" s="78"/>
       <c r="C203" s="35" t="s">
-        <v>339</v>
-      </c>
-      <c r="D203" s="35" t="s">
-        <v>340</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="D203" s="35"/>
       <c r="E203" s="106">
-        <v>550000</v>
-      </c>
-      <c r="F203" s="104"/>
+        <v>165000</v>
+      </c>
+      <c r="F203" s="40"/>
       <c r="G203" s="12"/>
     </row>
-    <row r="204" spans="1:8" ht="148.5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A204" s="37">
-        <f>IF(LEN(C204)=0,"",COUNTA($C$54:C204))</f>
-        <v>143</v>
-      </c>
-      <c r="B204" s="38"/>
+        <f>IF(LEN(C204)=0,"",COUNTA($C$35:C204))</f>
+        <v>159</v>
+      </c>
+      <c r="B204" s="78"/>
       <c r="C204" s="35" t="s">
-        <v>175</v>
+        <v>314</v>
       </c>
       <c r="D204" s="35" t="s">
-        <v>176</v>
+        <v>315</v>
       </c>
       <c r="E204" s="72">
-        <v>495000</v>
-      </c>
-      <c r="F204" s="104" t="s">
-        <v>327</v>
-      </c>
+        <v>220000</v>
+      </c>
+      <c r="F204" s="40"/>
       <c r="G204" s="12"/>
     </row>
-    <row r="205" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" ht="132" x14ac:dyDescent="0.25">
       <c r="A205" s="37">
-        <f>IF(LEN(C205)=0,"",COUNTA($C$54:C205))</f>
-        <v>144</v>
-      </c>
-      <c r="B205" s="38"/>
+        <f>IF(LEN(C205)=0,"",COUNTA($C$35:C205))</f>
+        <v>160</v>
+      </c>
+      <c r="B205" s="78"/>
       <c r="C205" s="35" t="s">
-        <v>177</v>
+        <v>316</v>
       </c>
       <c r="D205" s="35" t="s">
-        <v>178</v>
+        <v>317</v>
       </c>
       <c r="E205" s="72">
-        <v>268000</v>
+        <v>380000</v>
       </c>
       <c r="F205" s="40"/>
       <c r="G205" s="12"/>
     </row>
-    <row r="206" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" ht="99" x14ac:dyDescent="0.25">
       <c r="A206" s="37">
-        <f>IF(LEN(C206)=0,"",COUNTA($C$54:C206))</f>
-        <v>145</v>
-      </c>
-      <c r="B206" s="38"/>
+        <f>IF(LEN(C206)=0,"",COUNTA($C$35:C206))</f>
+        <v>161</v>
+      </c>
+      <c r="B206" s="78"/>
       <c r="C206" s="35" t="s">
-        <v>179</v>
+        <v>318</v>
       </c>
       <c r="D206" s="35" t="s">
-        <v>180</v>
+        <v>319</v>
       </c>
       <c r="E206" s="72">
-        <v>151000</v>
+        <v>4500000</v>
       </c>
       <c r="F206" s="40"/>
       <c r="G206" s="12"/>
     </row>
-    <row r="207" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A207" s="37">
-        <f>IF(LEN(C207)=0,"",COUNTA($C$54:C207))</f>
-        <v>146</v>
-      </c>
-      <c r="B207" s="38"/>
+        <f>IF(LEN(C207)=0,"",COUNTA($C$35:C207))</f>
+        <v>162</v>
+      </c>
+      <c r="B207" s="78"/>
       <c r="C207" s="35" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="D207" s="35" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="E207" s="72">
-        <v>220000</v>
+        <v>3200000</v>
       </c>
       <c r="F207" s="40"/>
       <c r="G207" s="12"/>
     </row>
-    <row r="208" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A208" s="178" t="s">
-        <v>263</v>
-      </c>
-      <c r="B208" s="178"/>
-      <c r="C208" s="178"/>
-      <c r="D208" s="178"/>
-      <c r="E208" s="77"/>
+    <row r="208" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A208" s="173" t="s">
+        <v>221</v>
+      </c>
+      <c r="B208" s="174"/>
+      <c r="C208" s="174"/>
+      <c r="D208" s="175"/>
+      <c r="E208" s="66"/>
       <c r="F208" s="67"/>
       <c r="G208" s="12"/>
     </row>
-    <row r="209" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A209" s="37">
-        <f>IF(LEN(C209)=0,"",COUNTA($C$54:C209))</f>
-        <v>147</v>
-      </c>
-      <c r="B209" s="38"/>
-      <c r="C209" s="35" t="s">
-        <v>264</v>
-      </c>
-      <c r="D209" s="35" t="s">
-        <v>265</v>
-      </c>
-      <c r="E209" s="72">
-        <v>390000</v>
+        <f>IF(LEN(C209)=0,"",COUNTA($C$35:C209))</f>
+        <v>163</v>
+      </c>
+      <c r="B209" s="78"/>
+      <c r="C209" s="86" t="s">
+        <v>215</v>
+      </c>
+      <c r="D209" s="86" t="s">
+        <v>216</v>
+      </c>
+      <c r="E209" s="87">
+        <v>233000</v>
       </c>
       <c r="F209" s="40"/>
       <c r="G209" s="12"/>
     </row>
     <row r="210" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A210" s="178" t="s">
-        <v>233</v>
-      </c>
-      <c r="B210" s="178"/>
-      <c r="C210" s="178"/>
-      <c r="D210" s="178"/>
-      <c r="E210" s="77"/>
-      <c r="F210" s="67"/>
+      <c r="A210" s="37">
+        <f>IF(LEN(C210)=0,"",COUNTA($C$35:C210))</f>
+        <v>164</v>
+      </c>
+      <c r="B210" s="78"/>
+      <c r="C210" s="88" t="s">
+        <v>217</v>
+      </c>
+      <c r="D210" s="88" t="s">
+        <v>218</v>
+      </c>
+      <c r="E210" s="89">
+        <v>227000</v>
+      </c>
+      <c r="F210" s="40"/>
       <c r="G210" s="12"/>
     </row>
     <row r="211" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A211" s="37">
-        <f>IF(LEN(C211)=0,"",COUNTA($C$54:C211))</f>
-        <v>148</v>
+        <f>IF(LEN(C211)=0,"",COUNTA($C$35:C211))</f>
+        <v>165</v>
       </c>
       <c r="B211" s="78"/>
-      <c r="C211" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="D211" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="E211" s="105">
-        <v>165000</v>
+      <c r="C211" s="88" t="s">
+        <v>219</v>
+      </c>
+      <c r="D211" s="88" t="s">
+        <v>220</v>
+      </c>
+      <c r="E211" s="89">
+        <v>72000</v>
       </c>
       <c r="F211" s="40"/>
       <c r="G211" s="12"/>
     </row>
-    <row r="212" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A212" s="37">
-        <f>IF(LEN(C212)=0,"",COUNTA($C$54:C212))</f>
-        <v>149</v>
-      </c>
-      <c r="B212" s="78"/>
-      <c r="C212" s="36" t="s">
-        <v>181</v>
-      </c>
-      <c r="D212" s="36" t="s">
-        <v>182</v>
-      </c>
-      <c r="E212" s="68">
-        <v>72000</v>
-      </c>
-      <c r="F212" s="40"/>
+    <row r="212" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A212" s="173" t="s">
+        <v>210</v>
+      </c>
+      <c r="B212" s="174"/>
+      <c r="C212" s="174"/>
+      <c r="D212" s="175"/>
+      <c r="E212" s="66"/>
+      <c r="F212" s="67"/>
       <c r="G212" s="12"/>
     </row>
-    <row r="213" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A213" s="37">
-        <f>IF(LEN(C213)=0,"",COUNTA($C$54:C213))</f>
-        <v>150</v>
+        <f>IF(LEN(C213)=0,"",COUNTA($C$35:C213))</f>
+        <v>166</v>
       </c>
       <c r="B213" s="78"/>
       <c r="C213" s="35" t="s">
-        <v>183</v>
-      </c>
-      <c r="D213" s="35" t="s">
-        <v>184</v>
-      </c>
-      <c r="E213" s="68">
-        <v>329000</v>
+        <v>211</v>
+      </c>
+      <c r="D213" s="35"/>
+      <c r="E213" s="146">
+        <v>183000</v>
       </c>
       <c r="F213" s="40"/>
       <c r="G213" s="12"/>
     </row>
-    <row r="214" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A214" s="37">
-        <f>IF(LEN(C214)=0,"",COUNTA($C$54:C214))</f>
-        <v>151</v>
+        <f>IF(LEN(C214)=0,"",COUNTA($C$35:C214))</f>
+        <v>167</v>
       </c>
       <c r="B214" s="78"/>
-      <c r="C214" s="36" t="s">
-        <v>185</v>
-      </c>
-      <c r="D214" s="36" t="s">
-        <v>186</v>
-      </c>
-      <c r="E214" s="68">
-        <v>605000</v>
-      </c>
+      <c r="C214" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="D214" s="35"/>
+      <c r="E214" s="147"/>
       <c r="F214" s="40"/>
       <c r="G214" s="12"/>
     </row>
-    <row r="215" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A215" s="37">
-        <f>IF(LEN(C215)=0,"",COUNTA($C$54:C215))</f>
-        <v>152</v>
+        <f>IF(LEN(C215)=0,"",COUNTA($C$35:C215))</f>
+        <v>168</v>
       </c>
       <c r="B215" s="78"/>
-      <c r="C215" s="85" t="s">
-        <v>187</v>
-      </c>
-      <c r="D215" s="85" t="s">
-        <v>188</v>
-      </c>
-      <c r="E215" s="43">
-        <v>1100000</v>
-      </c>
+      <c r="C215" s="35" t="s">
+        <v>213</v>
+      </c>
+      <c r="D215" s="35"/>
+      <c r="E215" s="147"/>
       <c r="F215" s="40"/>
       <c r="G215" s="12"/>
     </row>
-    <row r="216" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A216" s="37">
-        <f>IF(LEN(C216)=0,"",COUNTA($C$54:C216))</f>
-        <v>153</v>
+        <f>IF(LEN(C216)=0,"",COUNTA($C$35:C216))</f>
+        <v>169</v>
       </c>
       <c r="B216" s="78"/>
-      <c r="C216" s="85" t="s">
-        <v>276</v>
-      </c>
-      <c r="D216" s="85" t="s">
-        <v>273</v>
-      </c>
-      <c r="E216" s="43">
-        <v>187000</v>
-      </c>
+      <c r="C216" s="36" t="s">
+        <v>214</v>
+      </c>
+      <c r="D216" s="35"/>
+      <c r="E216" s="148"/>
       <c r="F216" s="40"/>
       <c r="G216" s="12"/>
     </row>
     <row r="217" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A217" s="37">
-        <f>IF(LEN(C217)=0,"",COUNTA($C$54:C217))</f>
-        <v>154</v>
-      </c>
-      <c r="B217" s="78"/>
-      <c r="C217" s="35" t="s">
-        <v>189</v>
-      </c>
-      <c r="D217" s="35" t="s">
-        <v>190</v>
-      </c>
-      <c r="E217" s="68">
-        <v>220000</v>
-      </c>
-      <c r="F217" s="40"/>
+      <c r="A217" s="173" t="s">
+        <v>412</v>
+      </c>
+      <c r="B217" s="174"/>
+      <c r="C217" s="174"/>
+      <c r="D217" s="175"/>
+      <c r="E217" s="66"/>
+      <c r="F217" s="67"/>
       <c r="G217" s="12"/>
     </row>
-    <row r="218" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A218" s="37">
-        <f>IF(LEN(C218)=0,"",COUNTA($C$54:C218))</f>
-        <v>155</v>
+        <f>IF(LEN(C218)=0,"",COUNTA($C$35:C218))</f>
+        <v>170</v>
       </c>
       <c r="B218" s="78"/>
       <c r="C218" s="35" t="s">
-        <v>384</v>
-      </c>
-      <c r="D218" s="35" t="s">
-        <v>386</v>
-      </c>
-      <c r="E218" s="68">
-        <v>817000</v>
+        <v>413</v>
+      </c>
+      <c r="D218" s="35"/>
+      <c r="E218" s="72">
+        <v>205000</v>
       </c>
       <c r="F218" s="40"/>
       <c r="G218" s="12"/>
     </row>
-    <row r="219" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A219" s="37">
-        <f>IF(LEN(C219)=0,"",COUNTA($C$54:C219))</f>
-        <v>156</v>
+        <f>IF(LEN(C219)=0,"",COUNTA($C$35:C219))</f>
+        <v>171</v>
       </c>
       <c r="B219" s="78"/>
       <c r="C219" s="35" t="s">
-        <v>385</v>
-      </c>
-      <c r="D219" s="35" t="s">
-        <v>387</v>
-      </c>
-      <c r="E219" s="68">
-        <v>1500000</v>
+        <v>414</v>
+      </c>
+      <c r="D219" s="35"/>
+      <c r="E219" s="72">
+        <v>340000</v>
       </c>
       <c r="F219" s="40"/>
       <c r="G219" s="12"/>
     </row>
-    <row r="220" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A220" s="37">
-        <f>IF(LEN(C220)=0,"",COUNTA($C$54:C220))</f>
-        <v>157</v>
+        <f>IF(LEN(C220)=0,"",COUNTA($C$35:C220))</f>
+        <v>172</v>
       </c>
       <c r="B220" s="78"/>
       <c r="C220" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="D220" s="35" t="s">
-        <v>192</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="D220" s="35"/>
       <c r="E220" s="72">
-        <v>220000</v>
+        <v>1700000</v>
       </c>
       <c r="F220" s="40"/>
       <c r="G220" s="12"/>
     </row>
     <row r="221" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A221" s="171" t="s">
-        <v>322</v>
-      </c>
-      <c r="B221" s="172"/>
-      <c r="C221" s="172"/>
-      <c r="D221" s="173"/>
-      <c r="E221" s="66"/>
-      <c r="F221" s="67"/>
+      <c r="A221" s="37">
+        <f>IF(LEN(C221)=0,"",COUNTA($C$35:C221))</f>
+        <v>173</v>
+      </c>
+      <c r="B221" s="78"/>
+      <c r="C221" s="36" t="s">
+        <v>416</v>
+      </c>
+      <c r="D221" s="35"/>
+      <c r="E221" s="72">
+        <v>1360000</v>
+      </c>
+      <c r="F221" s="40"/>
       <c r="G221" s="12"/>
     </row>
     <row r="222" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A222" s="37">
-        <f>IF(LEN(C222)=0,"",COUNTA($C$54:C222))</f>
-        <v>158</v>
-      </c>
-      <c r="B222" s="78"/>
-      <c r="C222" s="35" t="s">
-        <v>313</v>
-      </c>
-      <c r="D222" s="35"/>
-      <c r="E222" s="106">
-        <v>165000</v>
-      </c>
-      <c r="F222" s="40"/>
-      <c r="G222" s="12"/>
-    </row>
-    <row r="223" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A223" s="37">
-        <f>IF(LEN(C223)=0,"",COUNTA($C$54:C223))</f>
-        <v>159</v>
-      </c>
-      <c r="B223" s="78"/>
-      <c r="C223" s="35" t="s">
-        <v>314</v>
-      </c>
-      <c r="D223" s="35" t="s">
-        <v>315</v>
-      </c>
-      <c r="E223" s="72">
-        <v>220000</v>
-      </c>
-      <c r="F223" s="40"/>
-      <c r="G223" s="12"/>
-    </row>
-    <row r="224" spans="1:7" ht="132" x14ac:dyDescent="0.25">
-      <c r="A224" s="37">
-        <f>IF(LEN(C224)=0,"",COUNTA($C$54:C224))</f>
-        <v>160</v>
-      </c>
-      <c r="B224" s="78"/>
-      <c r="C224" s="35" t="s">
-        <v>316</v>
-      </c>
-      <c r="D224" s="35" t="s">
-        <v>317</v>
-      </c>
-      <c r="E224" s="72">
-        <v>380000</v>
-      </c>
-      <c r="F224" s="40"/>
-      <c r="G224" s="12"/>
-    </row>
-    <row r="225" spans="1:7" ht="99" x14ac:dyDescent="0.25">
-      <c r="A225" s="37">
-        <f>IF(LEN(C225)=0,"",COUNTA($C$54:C225))</f>
-        <v>161</v>
-      </c>
-      <c r="B225" s="78"/>
-      <c r="C225" s="35" t="s">
-        <v>318</v>
-      </c>
-      <c r="D225" s="35" t="s">
-        <v>319</v>
-      </c>
-      <c r="E225" s="72">
-        <v>4500000</v>
-      </c>
-      <c r="F225" s="40"/>
-      <c r="G225" s="12"/>
-    </row>
-    <row r="226" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A226" s="37">
-        <f>IF(LEN(C226)=0,"",COUNTA($C$54:C226))</f>
-        <v>162</v>
-      </c>
-      <c r="B226" s="78"/>
-      <c r="C226" s="35" t="s">
-        <v>320</v>
-      </c>
-      <c r="D226" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="E226" s="72">
-        <v>3200000</v>
-      </c>
-      <c r="F226" s="40"/>
-      <c r="G226" s="12"/>
-    </row>
-    <row r="227" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A227" s="171" t="s">
-        <v>221</v>
-      </c>
-      <c r="B227" s="172"/>
-      <c r="C227" s="172"/>
-      <c r="D227" s="173"/>
-      <c r="E227" s="66"/>
-      <c r="F227" s="67"/>
-      <c r="G227" s="12"/>
-    </row>
-    <row r="228" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A228" s="37">
-        <f>IF(LEN(C228)=0,"",COUNTA($C$54:C228))</f>
-        <v>163</v>
-      </c>
-      <c r="B228" s="78"/>
-      <c r="C228" s="86" t="s">
-        <v>215</v>
-      </c>
-      <c r="D228" s="86" t="s">
-        <v>216</v>
-      </c>
-      <c r="E228" s="87">
-        <v>233000</v>
-      </c>
-      <c r="F228" s="40"/>
-      <c r="G228" s="12"/>
-    </row>
-    <row r="229" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A229" s="37">
-        <f>IF(LEN(C229)=0,"",COUNTA($C$54:C229))</f>
-        <v>164</v>
-      </c>
-      <c r="B229" s="78"/>
-      <c r="C229" s="88" t="s">
-        <v>217</v>
-      </c>
-      <c r="D229" s="88" t="s">
-        <v>218</v>
-      </c>
-      <c r="E229" s="89">
-        <v>227000</v>
-      </c>
-      <c r="F229" s="40"/>
-      <c r="G229" s="12"/>
-    </row>
-    <row r="230" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A230" s="37">
-        <f>IF(LEN(C230)=0,"",COUNTA($C$54:C230))</f>
-        <v>165</v>
-      </c>
-      <c r="B230" s="78"/>
-      <c r="C230" s="88" t="s">
-        <v>219</v>
-      </c>
-      <c r="D230" s="88" t="s">
-        <v>220</v>
-      </c>
-      <c r="E230" s="89">
-        <v>72000</v>
-      </c>
-      <c r="F230" s="40"/>
-      <c r="G230" s="12"/>
-    </row>
-    <row r="231" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A231" s="171" t="s">
-        <v>210</v>
-      </c>
-      <c r="B231" s="172"/>
-      <c r="C231" s="172"/>
-      <c r="D231" s="173"/>
-      <c r="E231" s="66"/>
-      <c r="F231" s="67"/>
-      <c r="G231" s="12"/>
-    </row>
-    <row r="232" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A232" s="37">
-        <f>IF(LEN(C232)=0,"",COUNTA($C$54:C232))</f>
-        <v>166</v>
-      </c>
-      <c r="B232" s="78"/>
-      <c r="C232" s="35" t="s">
-        <v>211</v>
-      </c>
-      <c r="D232" s="35"/>
-      <c r="E232" s="146">
-        <v>183000</v>
-      </c>
-      <c r="F232" s="40"/>
-      <c r="G232" s="12"/>
-    </row>
-    <row r="233" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A233" s="37">
-        <f>IF(LEN(C233)=0,"",COUNTA($C$54:C233))</f>
-        <v>167</v>
-      </c>
-      <c r="B233" s="78"/>
-      <c r="C233" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="D233" s="35"/>
-      <c r="E233" s="147"/>
-      <c r="F233" s="40"/>
-      <c r="G233" s="12"/>
-    </row>
-    <row r="234" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A234" s="37">
-        <f>IF(LEN(C234)=0,"",COUNTA($C$54:C234))</f>
-        <v>168</v>
-      </c>
-      <c r="B234" s="78"/>
-      <c r="C234" s="35" t="s">
-        <v>213</v>
-      </c>
-      <c r="D234" s="35"/>
-      <c r="E234" s="147"/>
-      <c r="F234" s="40"/>
-      <c r="G234" s="12"/>
-    </row>
-    <row r="235" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A235" s="37">
-        <f>IF(LEN(C235)=0,"",COUNTA($C$54:C235))</f>
-        <v>169</v>
-      </c>
-      <c r="B235" s="78"/>
-      <c r="C235" s="36" t="s">
-        <v>214</v>
-      </c>
-      <c r="D235" s="35"/>
-      <c r="E235" s="148"/>
-      <c r="F235" s="40"/>
-      <c r="G235" s="12"/>
-    </row>
-    <row r="236" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A236" s="171" t="s">
-        <v>412</v>
-      </c>
-      <c r="B236" s="172"/>
-      <c r="C236" s="172"/>
-      <c r="D236" s="173"/>
-      <c r="E236" s="66"/>
-      <c r="F236" s="67"/>
-      <c r="G236" s="12"/>
-    </row>
-    <row r="237" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A237" s="37">
-        <f>IF(LEN(C237)=0,"",COUNTA($C$54:C237))</f>
-        <v>170</v>
-      </c>
-      <c r="B237" s="78"/>
-      <c r="C237" s="35" t="s">
-        <v>413</v>
-      </c>
-      <c r="D237" s="35"/>
-      <c r="E237" s="72">
-        <v>205000</v>
-      </c>
-      <c r="F237" s="40"/>
-      <c r="G237" s="12"/>
-    </row>
-    <row r="238" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A238" s="37">
-        <f>IF(LEN(C238)=0,"",COUNTA($C$54:C238))</f>
-        <v>171</v>
-      </c>
-      <c r="B238" s="78"/>
-      <c r="C238" s="35" t="s">
-        <v>414</v>
-      </c>
-      <c r="D238" s="35"/>
-      <c r="E238" s="72">
-        <v>340000</v>
-      </c>
-      <c r="F238" s="40"/>
-      <c r="G238" s="12"/>
-    </row>
-    <row r="239" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A239" s="37">
-        <f>IF(LEN(C239)=0,"",COUNTA($C$54:C239))</f>
-        <v>172</v>
-      </c>
-      <c r="B239" s="78"/>
-      <c r="C239" s="35" t="s">
-        <v>415</v>
-      </c>
-      <c r="D239" s="35"/>
-      <c r="E239" s="72">
-        <v>1700000</v>
-      </c>
-      <c r="F239" s="40"/>
-      <c r="G239" s="12"/>
-    </row>
-    <row r="240" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A240" s="37">
-        <f>IF(LEN(C240)=0,"",COUNTA($C$54:C240))</f>
-        <v>173</v>
-      </c>
-      <c r="B240" s="78"/>
-      <c r="C240" s="36" t="s">
-        <v>416</v>
-      </c>
-      <c r="D240" s="35"/>
-      <c r="E240" s="72">
-        <v>1360000</v>
-      </c>
-      <c r="F240" s="40"/>
-      <c r="G240" s="12"/>
-    </row>
-    <row r="241" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A241" s="90"/>
-      <c r="B241" s="91"/>
-      <c r="C241" s="90"/>
-      <c r="D241" s="90"/>
-      <c r="E241" s="92"/>
-      <c r="F241" s="93"/>
-    </row>
-    <row r="242" spans="1:6" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A242" s="182" t="s">
+      <c r="A222" s="90"/>
+      <c r="B222" s="91"/>
+      <c r="C222" s="90"/>
+      <c r="D222" s="90"/>
+      <c r="E222" s="92"/>
+      <c r="F222" s="93"/>
+    </row>
+    <row r="223" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A223" s="181" t="s">
         <v>27</v>
       </c>
-      <c r="B242" s="182"/>
-      <c r="C242" s="182"/>
-      <c r="D242" s="182"/>
-      <c r="E242" s="26"/>
-      <c r="F242" s="94"/>
-    </row>
-    <row r="243" spans="1:6" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A243" s="95"/>
-      <c r="B243" s="185" t="s">
+      <c r="B223" s="181"/>
+      <c r="C223" s="181"/>
+      <c r="D223" s="181"/>
+      <c r="E223" s="26"/>
+      <c r="F223" s="94"/>
+    </row>
+    <row r="224" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A224" s="95"/>
+      <c r="B224" s="180" t="s">
         <v>266</v>
       </c>
-      <c r="C243" s="185"/>
-      <c r="D243" s="185"/>
-      <c r="E243" s="185"/>
-      <c r="F243" s="185"/>
-    </row>
-    <row r="244" spans="1:6" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A244" s="95"/>
-      <c r="B244" s="185" t="s">
+      <c r="C224" s="180"/>
+      <c r="D224" s="180"/>
+      <c r="E224" s="180"/>
+      <c r="F224" s="180"/>
+    </row>
+    <row r="225" spans="1:6" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A225" s="95"/>
+      <c r="B225" s="180" t="s">
         <v>417</v>
       </c>
-      <c r="C244" s="185"/>
-      <c r="D244" s="185"/>
-      <c r="E244" s="185"/>
-      <c r="F244" s="185"/>
-    </row>
-    <row r="245" spans="1:6" s="2" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A245" s="96"/>
-      <c r="B245" s="185" t="s">
+      <c r="C225" s="180"/>
+      <c r="D225" s="180"/>
+      <c r="E225" s="180"/>
+      <c r="F225" s="180"/>
+    </row>
+    <row r="226" spans="1:6" s="2" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A226" s="96"/>
+      <c r="B226" s="180" t="s">
         <v>28</v>
       </c>
-      <c r="C245" s="185"/>
-      <c r="D245" s="185"/>
-      <c r="E245" s="185"/>
-      <c r="F245" s="185"/>
-    </row>
-    <row r="246" spans="1:6" s="17" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A246" s="97"/>
-      <c r="B246" s="186" t="s">
+      <c r="C226" s="180"/>
+      <c r="D226" s="180"/>
+      <c r="E226" s="180"/>
+      <c r="F226" s="180"/>
+    </row>
+    <row r="227" spans="1:6" s="17" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A227" s="97"/>
+      <c r="B227" s="185" t="s">
         <v>29</v>
       </c>
-      <c r="C246" s="186"/>
-      <c r="D246" s="186"/>
-      <c r="E246" s="186"/>
-      <c r="F246" s="186"/>
-    </row>
-    <row r="247" spans="1:6" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A247" s="94"/>
-      <c r="B247" s="185" t="s">
+      <c r="C227" s="185"/>
+      <c r="D227" s="185"/>
+      <c r="E227" s="185"/>
+      <c r="F227" s="185"/>
+    </row>
+    <row r="228" spans="1:6" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A228" s="94"/>
+      <c r="B228" s="180" t="s">
         <v>30</v>
       </c>
-      <c r="C247" s="185"/>
-      <c r="D247" s="185"/>
-      <c r="E247" s="185"/>
-      <c r="F247" s="185"/>
-    </row>
-    <row r="248" spans="1:6" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A248" s="94"/>
-      <c r="B248" s="96" t="s">
+      <c r="C228" s="180"/>
+      <c r="D228" s="180"/>
+      <c r="E228" s="180"/>
+      <c r="F228" s="180"/>
+    </row>
+    <row r="229" spans="1:6" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A229" s="94"/>
+      <c r="B229" s="96" t="s">
         <v>31</v>
       </c>
-      <c r="C248" s="96"/>
-      <c r="D248" s="98"/>
-      <c r="E248" s="26"/>
-      <c r="F248" s="23"/>
-    </row>
-    <row r="249" spans="1:6" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A249" s="94"/>
-      <c r="B249" s="96" t="s">
+      <c r="C229" s="96"/>
+      <c r="D229" s="98"/>
+      <c r="E229" s="26"/>
+      <c r="F229" s="23"/>
+    </row>
+    <row r="230" spans="1:6" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A230" s="94"/>
+      <c r="B230" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="C249" s="96"/>
-      <c r="D249" s="98"/>
-      <c r="E249" s="26"/>
-      <c r="F249" s="23"/>
-    </row>
-    <row r="250" spans="1:6" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A250" s="100" t="s">
+      <c r="C230" s="96"/>
+      <c r="D230" s="98"/>
+      <c r="E230" s="26"/>
+      <c r="F230" s="23"/>
+    </row>
+    <row r="231" spans="1:6" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A231" s="100" t="s">
         <v>33</v>
       </c>
-      <c r="B250" s="101"/>
-      <c r="C250" s="101"/>
-      <c r="D250" s="101"/>
-      <c r="E250" s="118"/>
-      <c r="F250" s="99"/>
-    </row>
-    <row r="251" spans="1:6" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A251" s="94"/>
-      <c r="B251" s="23" t="s">
+      <c r="B231" s="101"/>
+      <c r="C231" s="101"/>
+      <c r="D231" s="101"/>
+      <c r="E231" s="118"/>
+      <c r="F231" s="99"/>
+    </row>
+    <row r="232" spans="1:6" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A232" s="94"/>
+      <c r="B232" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="C251" s="23"/>
-      <c r="D251" s="98"/>
-      <c r="E251" s="102"/>
-      <c r="F251" s="23"/>
-    </row>
-    <row r="252" spans="1:6" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A252" s="94"/>
-      <c r="B252" s="23" t="s">
+      <c r="C232" s="23"/>
+      <c r="D232" s="98"/>
+      <c r="E232" s="102"/>
+      <c r="F232" s="23"/>
+    </row>
+    <row r="233" spans="1:6" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A233" s="94"/>
+      <c r="B233" s="23" t="s">
         <v>419</v>
       </c>
-      <c r="C252" s="23"/>
-      <c r="D252" s="98"/>
-      <c r="E252" s="102"/>
-      <c r="F252" s="23"/>
-    </row>
-    <row r="253" spans="1:6" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A253" s="94"/>
-      <c r="B253" s="23" t="s">
+      <c r="C233" s="23"/>
+      <c r="D233" s="98"/>
+      <c r="E233" s="102"/>
+      <c r="F233" s="23"/>
+    </row>
+    <row r="234" spans="1:6" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A234" s="94"/>
+      <c r="B234" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="C253" s="23"/>
-      <c r="D253" s="98"/>
-      <c r="E253" s="102"/>
-      <c r="F253" s="23"/>
+      <c r="C234" s="23"/>
+      <c r="D234" s="98"/>
+      <c r="E234" s="102"/>
+      <c r="F234" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="69">
-    <mergeCell ref="F29:F33"/>
-    <mergeCell ref="B243:F243"/>
-    <mergeCell ref="B244:F244"/>
-    <mergeCell ref="B245:F245"/>
-    <mergeCell ref="B246:F246"/>
-    <mergeCell ref="B247:F247"/>
-    <mergeCell ref="A242:D242"/>
-    <mergeCell ref="F197:F198"/>
-    <mergeCell ref="A199:D199"/>
-    <mergeCell ref="F200:F202"/>
+  <mergeCells count="67">
+    <mergeCell ref="B224:F224"/>
+    <mergeCell ref="B225:F225"/>
+    <mergeCell ref="B226:F226"/>
+    <mergeCell ref="B227:F227"/>
+    <mergeCell ref="A177:D177"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="B101:B114"/>
+    <mergeCell ref="A115:D115"/>
+    <mergeCell ref="A118:D118"/>
+    <mergeCell ref="B119:B127"/>
+    <mergeCell ref="B128:B133"/>
+    <mergeCell ref="B134:B140"/>
+    <mergeCell ref="B141:B170"/>
+    <mergeCell ref="A171:D171"/>
+    <mergeCell ref="B175:B176"/>
+    <mergeCell ref="B228:F228"/>
+    <mergeCell ref="A223:D223"/>
+    <mergeCell ref="F178:F179"/>
+    <mergeCell ref="A180:D180"/>
+    <mergeCell ref="F181:F183"/>
+    <mergeCell ref="A189:D189"/>
+    <mergeCell ref="A191:D191"/>
+    <mergeCell ref="A202:D202"/>
     <mergeCell ref="A208:D208"/>
-    <mergeCell ref="A210:D210"/>
-    <mergeCell ref="A221:D221"/>
-    <mergeCell ref="A227:D227"/>
-    <mergeCell ref="A231:D231"/>
-    <mergeCell ref="E232:E235"/>
-    <mergeCell ref="A236:D236"/>
-    <mergeCell ref="A196:D196"/>
-    <mergeCell ref="B117:B118"/>
-    <mergeCell ref="B120:B133"/>
-    <mergeCell ref="A134:D134"/>
-    <mergeCell ref="A137:D137"/>
-    <mergeCell ref="B138:B146"/>
-    <mergeCell ref="B147:B152"/>
-    <mergeCell ref="B153:B159"/>
-    <mergeCell ref="B160:B189"/>
-    <mergeCell ref="A190:D190"/>
-    <mergeCell ref="B194:B195"/>
-    <mergeCell ref="B115:B116"/>
-    <mergeCell ref="A79:D79"/>
-    <mergeCell ref="B80:B92"/>
-    <mergeCell ref="B93:B95"/>
-    <mergeCell ref="D93:D95"/>
-    <mergeCell ref="A100:D100"/>
-    <mergeCell ref="B101:B108"/>
-    <mergeCell ref="B109:B110"/>
-    <mergeCell ref="B111:B113"/>
-    <mergeCell ref="A114:D114"/>
-    <mergeCell ref="F93:F95"/>
-    <mergeCell ref="B96:B99"/>
-    <mergeCell ref="D96:D97"/>
-    <mergeCell ref="B69:B72"/>
-    <mergeCell ref="F70:F72"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="F74:F75"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="F77:F78"/>
-    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="A212:D212"/>
+    <mergeCell ref="E213:E216"/>
+    <mergeCell ref="A217:D217"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="B61:B73"/>
+    <mergeCell ref="B74:B76"/>
+    <mergeCell ref="D74:D76"/>
+    <mergeCell ref="A81:D81"/>
+    <mergeCell ref="B82:B89"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="A95:D95"/>
+    <mergeCell ref="F74:F76"/>
+    <mergeCell ref="B77:B80"/>
+    <mergeCell ref="D77:D78"/>
+    <mergeCell ref="B50:B53"/>
+    <mergeCell ref="F51:F53"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="F55:F56"/>
     <mergeCell ref="B58:B59"/>
-    <mergeCell ref="B60:B64"/>
-    <mergeCell ref="F60:F64"/>
-    <mergeCell ref="B66:B68"/>
-    <mergeCell ref="F66:F68"/>
-    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B41:B45"/>
+    <mergeCell ref="F41:F45"/>
+    <mergeCell ref="B47:B49"/>
+    <mergeCell ref="F47:F49"/>
+    <mergeCell ref="A29:D29"/>
     <mergeCell ref="D1:F5"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="B9:F9"/>
@@ -7109,11 +6758,10 @@
     <mergeCell ref="C14:C19"/>
     <mergeCell ref="E14:E19"/>
     <mergeCell ref="F14:F19"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="F25:F26"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="B29:B33"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -7121,16 +6769,16 @@
   <pageMargins left="0.35433070866141736" right="0.15748031496062992" top="0.23622047244094491" bottom="0.19685039370078741" header="0.15748031496062992" footer="0.15748031496062992"/>
   <pageSetup paperSize="9" scale="70" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <rowBreaks count="10" manualBreakCount="10">
-    <brk id="48" max="5" man="1"/>
-    <brk id="78" max="5" man="1"/>
-    <brk id="99" max="5" man="1"/>
-    <brk id="114" max="5" man="1"/>
-    <brk id="136" max="5" man="1"/>
-    <brk id="159" max="5" man="1"/>
-    <brk id="174" max="5" man="1"/>
-    <brk id="189" max="5" man="1"/>
-    <brk id="207" max="5" man="1"/>
-    <brk id="223" max="5" man="1"/>
+    <brk id="29" max="5" man="1"/>
+    <brk id="59" max="5" man="1"/>
+    <brk id="80" max="5" man="1"/>
+    <brk id="95" max="5" man="1"/>
+    <brk id="117" max="5" man="1"/>
+    <brk id="140" max="5" man="1"/>
+    <brk id="155" max="5" man="1"/>
+    <brk id="170" max="5" man="1"/>
+    <brk id="188" max="5" man="1"/>
+    <brk id="204" max="5" man="1"/>
   </rowBreaks>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="6" max="163" man="1"/>
